--- a/artfynd/A 35484-2025 artfynd.xlsx
+++ b/artfynd/A 35484-2025 artfynd.xlsx
@@ -1627,7 +1627,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127621416</v>
+        <v>127621322</v>
       </c>
       <c r="B11" t="n">
         <v>79018</v>
@@ -1665,10 +1665,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>443416</v>
+        <v>443330</v>
       </c>
       <c r="R11" t="n">
-        <v>6766663</v>
+        <v>6766763</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1705,7 +1705,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>På levande Björk</t>
+          <t>2 granar</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1733,7 +1733,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127621322</v>
+        <v>127621416</v>
       </c>
       <c r="B12" t="n">
         <v>79018</v>
@@ -1771,10 +1771,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>443330</v>
+        <v>443416</v>
       </c>
       <c r="R12" t="n">
-        <v>6766763</v>
+        <v>6766663</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1811,7 +1811,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>2 granar</t>
+          <t>På levande Björk</t>
         </is>
       </c>
       <c r="AD12" t="b">

--- a/artfynd/A 35484-2025 artfynd.xlsx
+++ b/artfynd/A 35484-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY136"/>
+  <dimension ref="A1:AY138"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,7 +678,7 @@
         <v>127621301</v>
       </c>
       <c r="B2" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>127621346</v>
       </c>
       <c r="B3" t="n">
-        <v>78776</v>
+        <v>78778</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -885,7 +885,7 @@
         <v>127621344</v>
       </c>
       <c r="B4" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -991,7 +991,7 @@
         <v>127621350</v>
       </c>
       <c r="B5" t="n">
-        <v>56596</v>
+        <v>56598</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1098,7 +1098,7 @@
         <v>127621456</v>
       </c>
       <c r="B6" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1311,7 +1311,7 @@
         <v>127621380</v>
       </c>
       <c r="B8" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1412,7 +1412,7 @@
         <v>127621440</v>
       </c>
       <c r="B9" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1630,7 +1630,7 @@
         <v>127621322</v>
       </c>
       <c r="B11" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1736,7 +1736,7 @@
         <v>127621416</v>
       </c>
       <c r="B12" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1842,7 +1842,7 @@
         <v>127723164</v>
       </c>
       <c r="B13" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1936,10 +1936,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127723117</v>
+        <v>127723151</v>
       </c>
       <c r="B14" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1971,10 +1971,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>443514</v>
+        <v>443430</v>
       </c>
       <c r="R14" t="n">
-        <v>6766630</v>
+        <v>6766608</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2033,10 +2033,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127723151</v>
+        <v>127723117</v>
       </c>
       <c r="B15" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2068,10 +2068,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>443430</v>
+        <v>443514</v>
       </c>
       <c r="R15" t="n">
-        <v>6766608</v>
+        <v>6766630</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2235,7 +2235,7 @@
         <v>127723187</v>
       </c>
       <c r="B17" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2332,7 +2332,7 @@
         <v>127722870</v>
       </c>
       <c r="B18" t="n">
-        <v>57821</v>
+        <v>57823</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2431,50 +2431,45 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127722947</v>
+        <v>127723093</v>
       </c>
       <c r="B19" t="n">
-        <v>8450</v>
+        <v>79020</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>443486</v>
+        <v>443572</v>
       </c>
       <c r="R19" t="n">
-        <v>6766604</v>
+        <v>6766645</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2533,10 +2528,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127723093</v>
+        <v>127723099</v>
       </c>
       <c r="B20" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2568,10 +2563,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>443572</v>
+        <v>443567</v>
       </c>
       <c r="R20" t="n">
-        <v>6766645</v>
+        <v>6766695</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2630,7 +2625,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127722942</v>
+        <v>127722947</v>
       </c>
       <c r="B21" t="n">
         <v>8450</v>
@@ -2670,10 +2665,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>443542</v>
+        <v>443486</v>
       </c>
       <c r="R21" t="n">
-        <v>6766699</v>
+        <v>6766604</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2732,45 +2727,50 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127723099</v>
+        <v>127722942</v>
       </c>
       <c r="B22" t="n">
-        <v>79018</v>
+        <v>8450</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>443567</v>
+        <v>443542</v>
       </c>
       <c r="R22" t="n">
-        <v>6766695</v>
+        <v>6766699</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2829,50 +2829,45 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127722950</v>
+        <v>127722874</v>
       </c>
       <c r="B23" t="n">
-        <v>8450</v>
+        <v>91352</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>106545</v>
+        <v>5442</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>443438</v>
+        <v>443388</v>
       </c>
       <c r="R23" t="n">
-        <v>6766650</v>
+        <v>6766675</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2931,10 +2926,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127722874</v>
+        <v>127723112</v>
       </c>
       <c r="B24" t="n">
-        <v>91350</v>
+        <v>79020</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2942,21 +2937,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2966,10 +2961,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>443388</v>
+        <v>443476</v>
       </c>
       <c r="R24" t="n">
-        <v>6766675</v>
+        <v>6766681</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3028,10 +3023,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127723112</v>
+        <v>127723166</v>
       </c>
       <c r="B25" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3063,10 +3058,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>443476</v>
+        <v>443326</v>
       </c>
       <c r="R25" t="n">
-        <v>6766681</v>
+        <v>6766711</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3125,10 +3120,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127723166</v>
+        <v>127723181</v>
       </c>
       <c r="B26" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3160,10 +3155,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>443326</v>
+        <v>443436</v>
       </c>
       <c r="R26" t="n">
-        <v>6766711</v>
+        <v>6766667</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3222,45 +3217,50 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127723181</v>
+        <v>127722950</v>
       </c>
       <c r="B27" t="n">
-        <v>79018</v>
+        <v>8450</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>443436</v>
+        <v>443438</v>
       </c>
       <c r="R27" t="n">
-        <v>6766667</v>
+        <v>6766650</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3322,7 +3322,7 @@
         <v>127723040</v>
       </c>
       <c r="B28" t="n">
-        <v>78777</v>
+        <v>78779</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3416,10 +3416,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127723619</v>
+        <v>127723039</v>
       </c>
       <c r="B29" t="n">
-        <v>57661</v>
+        <v>78779</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3427,39 +3427,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>228912</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>nyligen använt bo</t>
-        </is>
-      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>443387</v>
+        <v>443356</v>
       </c>
       <c r="R29" t="n">
-        <v>6766675</v>
+        <v>6766650</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3492,11 +3487,6 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-08-21</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>I gammal tall med tallticka</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3523,10 +3513,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127723039</v>
+        <v>127723179</v>
       </c>
       <c r="B30" t="n">
-        <v>78777</v>
+        <v>79020</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3534,21 +3524,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3558,10 +3548,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>443356</v>
+        <v>443411</v>
       </c>
       <c r="R30" t="n">
-        <v>6766650</v>
+        <v>6766676</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3620,45 +3610,50 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127723152</v>
+        <v>127722945</v>
       </c>
       <c r="B31" t="n">
-        <v>79018</v>
+        <v>8450</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>443424</v>
+        <v>443568</v>
       </c>
       <c r="R31" t="n">
-        <v>6766627</v>
+        <v>6766605</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3720,7 +3715,7 @@
         <v>127722875</v>
       </c>
       <c r="B32" t="n">
-        <v>91350</v>
+        <v>91352</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3814,10 +3809,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127723179</v>
+        <v>127723152</v>
       </c>
       <c r="B33" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3849,10 +3844,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>443411</v>
+        <v>443424</v>
       </c>
       <c r="R33" t="n">
-        <v>6766676</v>
+        <v>6766627</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3911,50 +3906,45 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>127722945</v>
+        <v>127723107</v>
       </c>
       <c r="B34" t="n">
-        <v>8450</v>
+        <v>79020</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>443568</v>
+        <v>443493</v>
       </c>
       <c r="R34" t="n">
-        <v>6766605</v>
+        <v>6766717</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4013,32 +4003,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127722921</v>
+        <v>127723109</v>
       </c>
       <c r="B35" t="n">
-        <v>97325</v>
+        <v>79020</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4048,10 +4038,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>443330</v>
+        <v>443482</v>
       </c>
       <c r="R35" t="n">
-        <v>6766662</v>
+        <v>6766716</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4110,10 +4100,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127723107</v>
+        <v>127723169</v>
       </c>
       <c r="B36" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4145,10 +4135,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>443493</v>
+        <v>443321</v>
       </c>
       <c r="R36" t="n">
-        <v>6766717</v>
+        <v>6766706</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4207,50 +4197,45 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127722944</v>
+        <v>127723115</v>
       </c>
       <c r="B37" t="n">
-        <v>8450</v>
+        <v>79020</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>443488</v>
+        <v>443495</v>
       </c>
       <c r="R37" t="n">
-        <v>6766671</v>
+        <v>6766641</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4309,45 +4294,50 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127723109</v>
+        <v>127722944</v>
       </c>
       <c r="B38" t="n">
-        <v>79018</v>
+        <v>8450</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>443482</v>
+        <v>443488</v>
       </c>
       <c r="R38" t="n">
-        <v>6766716</v>
+        <v>6766671</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4406,45 +4396,50 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127723169</v>
+        <v>127722928</v>
       </c>
       <c r="B39" t="n">
-        <v>79018</v>
+        <v>8450</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>443321</v>
+        <v>443559</v>
       </c>
       <c r="R39" t="n">
-        <v>6766706</v>
+        <v>6766616</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4503,38 +4498,38 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127722928</v>
+        <v>127722896</v>
       </c>
       <c r="B40" t="n">
-        <v>8450</v>
+        <v>57660</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="M40" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
@@ -4543,10 +4538,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>443559</v>
+        <v>443537</v>
       </c>
       <c r="R40" t="n">
-        <v>6766616</v>
+        <v>6766699</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4605,50 +4600,45 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127722896</v>
+        <v>127722921</v>
       </c>
       <c r="B41" t="n">
-        <v>57658</v>
+        <v>97327</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100049</v>
+        <v>221945</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>443537</v>
+        <v>443330</v>
       </c>
       <c r="R41" t="n">
-        <v>6766699</v>
+        <v>6766662</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4707,32 +4697,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>127723115</v>
+        <v>127723064</v>
       </c>
       <c r="B42" t="n">
-        <v>79018</v>
+        <v>91493</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>1503</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4742,10 +4732,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>443495</v>
+        <v>443329</v>
       </c>
       <c r="R42" t="n">
-        <v>6766641</v>
+        <v>6766670</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4804,10 +4794,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127723091</v>
+        <v>127722876</v>
       </c>
       <c r="B43" t="n">
-        <v>79018</v>
+        <v>91352</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4815,21 +4805,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4839,10 +4829,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>443587</v>
+        <v>443366</v>
       </c>
       <c r="R43" t="n">
-        <v>6766651</v>
+        <v>6766661</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4901,10 +4891,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>127723159</v>
+        <v>127723091</v>
       </c>
       <c r="B44" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4936,10 +4926,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>443314</v>
+        <v>443587</v>
       </c>
       <c r="R44" t="n">
-        <v>6766811</v>
+        <v>6766651</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4998,10 +4988,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>127723189</v>
+        <v>127723159</v>
       </c>
       <c r="B45" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5033,10 +5023,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>443446</v>
+        <v>443314</v>
       </c>
       <c r="R45" t="n">
-        <v>6766727</v>
+        <v>6766811</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5069,11 +5059,6 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-08-21</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Med grov gran i bäckmiljö</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5100,10 +5085,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>127723121</v>
+        <v>127723189</v>
       </c>
       <c r="B46" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5135,10 +5120,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>443558</v>
+        <v>443446</v>
       </c>
       <c r="R46" t="n">
-        <v>6766620</v>
+        <v>6766727</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5171,6 +5156,11 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Med grov gran i bäckmiljö</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5197,10 +5187,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>127722876</v>
+        <v>127723121</v>
       </c>
       <c r="B47" t="n">
-        <v>91350</v>
+        <v>79020</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5208,21 +5198,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5232,10 +5222,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>443366</v>
+        <v>443558</v>
       </c>
       <c r="R47" t="n">
-        <v>6766661</v>
+        <v>6766620</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5294,45 +5284,50 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>127723064</v>
+        <v>127722868</v>
       </c>
       <c r="B48" t="n">
-        <v>91491</v>
+        <v>57823</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1503</v>
+        <v>103021</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>443329</v>
+        <v>443305</v>
       </c>
       <c r="R48" t="n">
-        <v>6766670</v>
+        <v>6766767</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5391,45 +5386,50 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>127723180</v>
+        <v>127722957</v>
       </c>
       <c r="B49" t="n">
-        <v>79018</v>
+        <v>8450</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>443425</v>
+        <v>443457</v>
       </c>
       <c r="R49" t="n">
-        <v>6766665</v>
+        <v>6766726</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5488,10 +5488,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>127722868</v>
+        <v>127723180</v>
       </c>
       <c r="B50" t="n">
-        <v>57821</v>
+        <v>79020</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5499,39 +5499,34 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>443305</v>
+        <v>443425</v>
       </c>
       <c r="R50" t="n">
-        <v>6766767</v>
+        <v>6766665</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5593,7 +5588,7 @@
         <v>127723102</v>
       </c>
       <c r="B51" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5687,50 +5682,45 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>127722957</v>
+        <v>127723185</v>
       </c>
       <c r="B52" t="n">
-        <v>8450</v>
+        <v>79020</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>443457</v>
+        <v>443452</v>
       </c>
       <c r="R52" t="n">
-        <v>6766726</v>
+        <v>6766711</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5789,10 +5779,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>127723185</v>
+        <v>127723110</v>
       </c>
       <c r="B53" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5824,10 +5814,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>443452</v>
+        <v>443479</v>
       </c>
       <c r="R53" t="n">
-        <v>6766711</v>
+        <v>6766703</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5886,10 +5876,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>127723110</v>
+        <v>127723184</v>
       </c>
       <c r="B54" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5921,10 +5911,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>443479</v>
+        <v>443446</v>
       </c>
       <c r="R54" t="n">
-        <v>6766703</v>
+        <v>6766702</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5983,45 +5973,50 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>127723184</v>
+        <v>127722943</v>
       </c>
       <c r="B55" t="n">
-        <v>79018</v>
+        <v>8450</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>443446</v>
+        <v>443527</v>
       </c>
       <c r="R55" t="n">
-        <v>6766702</v>
+        <v>6766711</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6080,7 +6075,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>127722943</v>
+        <v>127722956</v>
       </c>
       <c r="B56" t="n">
         <v>8450</v>
@@ -6120,10 +6115,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>443527</v>
+        <v>443454</v>
       </c>
       <c r="R56" t="n">
-        <v>6766711</v>
+        <v>6766718</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6185,7 +6180,7 @@
         <v>127723138</v>
       </c>
       <c r="B57" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6279,50 +6274,45 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>127722956</v>
+        <v>127722841</v>
       </c>
       <c r="B58" t="n">
-        <v>8450</v>
+        <v>79052</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>106545</v>
+        <v>185</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P58" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>443454</v>
+        <v>443568</v>
       </c>
       <c r="R58" t="n">
-        <v>6766718</v>
+        <v>6766695</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6381,10 +6371,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>127723167</v>
+        <v>127723134</v>
       </c>
       <c r="B59" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6416,10 +6406,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>443316</v>
+        <v>443465</v>
       </c>
       <c r="R59" t="n">
-        <v>6766701</v>
+        <v>6766607</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6478,10 +6468,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>127723153</v>
+        <v>127723106</v>
       </c>
       <c r="B60" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6513,10 +6503,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>443436</v>
+        <v>443516</v>
       </c>
       <c r="R60" t="n">
-        <v>6766648</v>
+        <v>6766720</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6575,10 +6565,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>127722841</v>
+        <v>127723167</v>
       </c>
       <c r="B61" t="n">
-        <v>79050</v>
+        <v>79020</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6586,21 +6576,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6610,10 +6600,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>443568</v>
+        <v>443316</v>
       </c>
       <c r="R61" t="n">
-        <v>6766695</v>
+        <v>6766701</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6672,10 +6662,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>127723119</v>
+        <v>127723153</v>
       </c>
       <c r="B62" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6707,10 +6697,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>443535</v>
+        <v>443436</v>
       </c>
       <c r="R62" t="n">
-        <v>6766639</v>
+        <v>6766648</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6769,10 +6759,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>127723106</v>
+        <v>127723119</v>
       </c>
       <c r="B63" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6804,10 +6794,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>443516</v>
+        <v>443535</v>
       </c>
       <c r="R63" t="n">
-        <v>6766720</v>
+        <v>6766639</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6869,7 +6859,7 @@
         <v>127723188</v>
       </c>
       <c r="B64" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6966,7 +6956,7 @@
         <v>127723175</v>
       </c>
       <c r="B65" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7060,45 +7050,50 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>127723134</v>
+        <v>127722941</v>
       </c>
       <c r="B66" t="n">
-        <v>79018</v>
+        <v>8450</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P66" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>443465</v>
+        <v>443557</v>
       </c>
       <c r="R66" t="n">
-        <v>6766607</v>
+        <v>6766635</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7157,10 +7152,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>127729137</v>
+        <v>127723177</v>
       </c>
       <c r="B67" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7188,14 +7183,14 @@
       <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Oxeråsen S. om, Dlr</t>
+          <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>443391</v>
+        <v>443397</v>
       </c>
       <c r="R67" t="n">
-        <v>6766598</v>
+        <v>6766673</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7225,50 +7220,39 @@
           <t>2025-08-21</t>
         </is>
       </c>
-      <c r="Z67" t="inlineStr">
-        <is>
-          <t>14:00</t>
-        </is>
-      </c>
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-08-21</t>
         </is>
       </c>
-      <c r="AB67" t="inlineStr">
-        <is>
-          <t>14:00</t>
-        </is>
-      </c>
       <c r="AD67" t="b">
         <v>0</v>
       </c>
       <c r="AE67" t="b">
         <v>0</v>
       </c>
-      <c r="AF67" t="inlineStr"/>
       <c r="AG67" t="b">
         <v>0</v>
       </c>
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>127723177</v>
+        <v>127729137</v>
       </c>
       <c r="B68" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7296,14 +7280,14 @@
       <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Oxeråsen, Dlr</t>
+          <t>Oxeråsen S. om, Dlr</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>443397</v>
+        <v>443391</v>
       </c>
       <c r="R68" t="n">
-        <v>6766673</v>
+        <v>6766598</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7333,61 +7317,72 @@
           <t>2025-08-21</t>
         </is>
       </c>
+      <c r="Z68" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
       <c r="AA68" t="inlineStr">
         <is>
           <t>2025-08-21</t>
         </is>
       </c>
+      <c r="AB68" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
       <c r="AD68" t="b">
         <v>0</v>
       </c>
       <c r="AE68" t="b">
         <v>0</v>
       </c>
+      <c r="AF68" t="inlineStr"/>
       <c r="AG68" t="b">
         <v>0</v>
       </c>
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>127723065</v>
+        <v>127723158</v>
       </c>
       <c r="B69" t="n">
-        <v>91491</v>
+        <v>79020</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>1503</v>
+        <v>6425</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7397,10 +7392,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>443425</v>
+        <v>443312</v>
       </c>
       <c r="R69" t="n">
-        <v>6766668</v>
+        <v>6766818</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7459,32 +7454,32 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>127723158</v>
+        <v>127723065</v>
       </c>
       <c r="B70" t="n">
-        <v>79018</v>
+        <v>91493</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6425</v>
+        <v>1503</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7494,10 +7489,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>443312</v>
+        <v>443425</v>
       </c>
       <c r="R70" t="n">
-        <v>6766818</v>
+        <v>6766668</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7556,10 +7551,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>127723150</v>
+        <v>127722847</v>
       </c>
       <c r="B71" t="n">
-        <v>79018</v>
+        <v>79052</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7567,21 +7562,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7591,10 +7586,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>443415</v>
+        <v>443320</v>
       </c>
       <c r="R71" t="n">
-        <v>6766603</v>
+        <v>6766703</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7653,10 +7648,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>127722847</v>
+        <v>127723150</v>
       </c>
       <c r="B72" t="n">
-        <v>79050</v>
+        <v>79020</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7664,21 +7659,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7688,10 +7683,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>443320</v>
+        <v>443415</v>
       </c>
       <c r="R72" t="n">
-        <v>6766703</v>
+        <v>6766603</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7750,50 +7745,45 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>127722941</v>
+        <v>127729092</v>
       </c>
       <c r="B73" t="n">
-        <v>8450</v>
+        <v>78778</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>106545</v>
+        <v>6446</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
-      <c r="M73" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Oxeråsen, Dlr</t>
+          <t>Oxeråsen S. om, Dlr</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>443557</v>
+        <v>443381</v>
       </c>
       <c r="R73" t="n">
-        <v>6766635</v>
+        <v>6766668</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7823,29 +7813,40 @@
           <t>2025-08-21</t>
         </is>
       </c>
+      <c r="Z73" t="inlineStr">
+        <is>
+          <t>13:51</t>
+        </is>
+      </c>
       <c r="AA73" t="inlineStr">
         <is>
           <t>2025-08-21</t>
         </is>
       </c>
+      <c r="AB73" t="inlineStr">
+        <is>
+          <t>13:51</t>
+        </is>
+      </c>
       <c r="AD73" t="b">
         <v>0</v>
       </c>
       <c r="AE73" t="b">
         <v>0</v>
       </c>
+      <c r="AF73" t="inlineStr"/>
       <c r="AG73" t="b">
         <v>0</v>
       </c>
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
@@ -7855,7 +7856,7 @@
         <v>127723133</v>
       </c>
       <c r="B74" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7952,7 +7953,7 @@
         <v>127723173</v>
       </c>
       <c r="B75" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8049,7 +8050,7 @@
         <v>127723108</v>
       </c>
       <c r="B76" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8143,10 +8144,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>127722839</v>
+        <v>127723090</v>
       </c>
       <c r="B77" t="n">
-        <v>79050</v>
+        <v>79020</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8154,21 +8155,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8178,10 +8179,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>443554</v>
+        <v>443593</v>
       </c>
       <c r="R77" t="n">
-        <v>6766649</v>
+        <v>6766653</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8240,10 +8241,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>127723090</v>
+        <v>127722839</v>
       </c>
       <c r="B78" t="n">
-        <v>79018</v>
+        <v>79052</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8251,21 +8252,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8275,10 +8276,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>443593</v>
+        <v>443554</v>
       </c>
       <c r="R78" t="n">
-        <v>6766653</v>
+        <v>6766649</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8337,10 +8338,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>127729092</v>
+        <v>127723571</v>
       </c>
       <c r="B79" t="n">
-        <v>78776</v>
+        <v>78687</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8348,31 +8349,31 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6446</v>
+        <v>353</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Oxeråsen S. om, Dlr</t>
+          <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>443381</v>
+        <v>443426</v>
       </c>
       <c r="R79" t="n">
         <v>6766668</v>
@@ -8405,50 +8406,39 @@
           <t>2025-08-21</t>
         </is>
       </c>
-      <c r="Z79" t="inlineStr">
-        <is>
-          <t>13:51</t>
-        </is>
-      </c>
       <c r="AA79" t="inlineStr">
         <is>
           <t>2025-08-21</t>
         </is>
       </c>
-      <c r="AB79" t="inlineStr">
-        <is>
-          <t>13:51</t>
-        </is>
-      </c>
       <c r="AD79" t="b">
         <v>0</v>
       </c>
       <c r="AE79" t="b">
         <v>0</v>
       </c>
-      <c r="AF79" t="inlineStr"/>
       <c r="AG79" t="b">
         <v>0</v>
       </c>
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>127723571</v>
+        <v>127723156</v>
       </c>
       <c r="B80" t="n">
-        <v>78685</v>
+        <v>79020</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8456,21 +8446,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8480,10 +8470,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>443426</v>
+        <v>443346</v>
       </c>
       <c r="R80" t="n">
-        <v>6766668</v>
+        <v>6766766</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8542,10 +8532,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>127723156</v>
+        <v>127723120</v>
       </c>
       <c r="B81" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8577,10 +8567,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>443346</v>
+        <v>443548</v>
       </c>
       <c r="R81" t="n">
-        <v>6766766</v>
+        <v>6766624</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8639,10 +8629,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>127723120</v>
+        <v>127723104</v>
       </c>
       <c r="B82" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8674,10 +8664,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>443548</v>
+        <v>443536</v>
       </c>
       <c r="R82" t="n">
-        <v>6766624</v>
+        <v>6766704</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8736,10 +8726,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>127723104</v>
+        <v>127723116</v>
       </c>
       <c r="B83" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8771,10 +8761,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>443536</v>
+        <v>443509</v>
       </c>
       <c r="R83" t="n">
-        <v>6766704</v>
+        <v>6766633</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -8833,10 +8823,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>127723541</v>
+        <v>127723092</v>
       </c>
       <c r="B84" t="n">
-        <v>57661</v>
+        <v>79020</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -8844,39 +8834,34 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
-      <c r="M84" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P84" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>443317</v>
+        <v>443572</v>
       </c>
       <c r="R84" t="n">
-        <v>6766816</v>
+        <v>6766650</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -8935,10 +8920,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>127723570</v>
+        <v>127723178</v>
       </c>
       <c r="B85" t="n">
-        <v>78685</v>
+        <v>79020</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -8946,21 +8931,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -8970,10 +8955,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>443319</v>
+        <v>443402</v>
       </c>
       <c r="R85" t="n">
-        <v>6766670</v>
+        <v>6766682</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9032,10 +9017,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>127723116</v>
+        <v>127723541</v>
       </c>
       <c r="B86" t="n">
-        <v>79018</v>
+        <v>57663</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9043,34 +9028,39 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P86" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>443509</v>
+        <v>443317</v>
       </c>
       <c r="R86" t="n">
-        <v>6766633</v>
+        <v>6766816</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9129,10 +9119,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>127722888</v>
+        <v>127722916</v>
       </c>
       <c r="B87" t="n">
-        <v>57658</v>
+        <v>57663</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9140,16 +9130,16 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
@@ -9160,7 +9150,7 @@
       <c r="I87" t="inlineStr"/>
       <c r="M87" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P87" t="inlineStr">
@@ -9169,10 +9159,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>443481</v>
+        <v>443342</v>
       </c>
       <c r="R87" t="n">
-        <v>6766676</v>
+        <v>6766806</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9205,6 +9195,11 @@
       <c r="AA87" t="inlineStr">
         <is>
           <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AC87" t="inlineStr">
+        <is>
+          <t>Färska ringhack (gran), 4-5 år gamla</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9231,10 +9226,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>127723092</v>
+        <v>127723570</v>
       </c>
       <c r="B88" t="n">
-        <v>79018</v>
+        <v>78687</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9242,21 +9237,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9266,10 +9261,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>443572</v>
+        <v>443319</v>
       </c>
       <c r="R88" t="n">
-        <v>6766650</v>
+        <v>6766670</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9328,10 +9323,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>127723178</v>
+        <v>127723171</v>
       </c>
       <c r="B89" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9363,10 +9358,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>443402</v>
+        <v>443342</v>
       </c>
       <c r="R89" t="n">
-        <v>6766682</v>
+        <v>6766650</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9425,10 +9420,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>127723171</v>
+        <v>127722888</v>
       </c>
       <c r="B90" t="n">
-        <v>79018</v>
+        <v>57660</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9436,34 +9431,39 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P90" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>443342</v>
+        <v>443481</v>
       </c>
       <c r="R90" t="n">
-        <v>6766650</v>
+        <v>6766676</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9522,10 +9522,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>127722916</v>
+        <v>127723569</v>
       </c>
       <c r="B91" t="n">
-        <v>57661</v>
+        <v>78687</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9533,39 +9533,34 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>100109</v>
+        <v>353</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
-      <c r="M91" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P91" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>443342</v>
+        <v>443332</v>
       </c>
       <c r="R91" t="n">
-        <v>6766806</v>
+        <v>6766677</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9598,11 +9593,6 @@
       <c r="AA91" t="inlineStr">
         <is>
           <t>2025-08-21</t>
-        </is>
-      </c>
-      <c r="AC91" t="inlineStr">
-        <is>
-          <t>Färska ringhack (gran), 4-5 år gamla</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -9632,7 +9622,7 @@
         <v>127723103</v>
       </c>
       <c r="B92" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9726,10 +9716,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>127723041</v>
+        <v>127723105</v>
       </c>
       <c r="B93" t="n">
-        <v>78777</v>
+        <v>79020</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9737,21 +9727,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -9761,10 +9751,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>443450</v>
+        <v>443525</v>
       </c>
       <c r="R93" t="n">
-        <v>6766735</v>
+        <v>6766717</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -9823,10 +9813,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>127723105</v>
+        <v>127723161</v>
       </c>
       <c r="B94" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -9858,10 +9848,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>443525</v>
+        <v>443305</v>
       </c>
       <c r="R94" t="n">
-        <v>6766717</v>
+        <v>6766767</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -9920,10 +9910,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>127723161</v>
+        <v>127723186</v>
       </c>
       <c r="B95" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -9955,10 +9945,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>443305</v>
+        <v>443454</v>
       </c>
       <c r="R95" t="n">
-        <v>6766767</v>
+        <v>6766738</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10017,10 +10007,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>127723186</v>
+        <v>127723097</v>
       </c>
       <c r="B96" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10052,10 +10042,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>443454</v>
+        <v>443561</v>
       </c>
       <c r="R96" t="n">
-        <v>6766738</v>
+        <v>6766678</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10114,10 +10104,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>127723569</v>
+        <v>127723174</v>
       </c>
       <c r="B97" t="n">
-        <v>78685</v>
+        <v>79020</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10125,21 +10115,21 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -10149,10 +10139,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>443332</v>
+        <v>443378</v>
       </c>
       <c r="R97" t="n">
-        <v>6766677</v>
+        <v>6766657</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10211,10 +10201,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>127723114</v>
+        <v>127723041</v>
       </c>
       <c r="B98" t="n">
-        <v>79018</v>
+        <v>78779</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10222,21 +10212,21 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10246,10 +10236,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>443487</v>
+        <v>443450</v>
       </c>
       <c r="R98" t="n">
-        <v>6766651</v>
+        <v>6766735</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10308,10 +10298,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>127723097</v>
+        <v>127723114</v>
       </c>
       <c r="B99" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10343,10 +10333,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>443561</v>
+        <v>443487</v>
       </c>
       <c r="R99" t="n">
-        <v>6766678</v>
+        <v>6766651</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10405,10 +10395,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>127723174</v>
+        <v>127723616</v>
       </c>
       <c r="B100" t="n">
-        <v>79018</v>
+        <v>57663</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10416,34 +10406,39 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
+      <c r="M100" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
       <c r="P100" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>443378</v>
+        <v>443475</v>
       </c>
       <c r="R100" t="n">
-        <v>6766657</v>
+        <v>6766610</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10604,10 +10599,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>127723183</v>
+        <v>127722842</v>
       </c>
       <c r="B102" t="n">
-        <v>79018</v>
+        <v>79052</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -10615,21 +10610,21 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -10639,10 +10634,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>443441</v>
+        <v>443504</v>
       </c>
       <c r="R102" t="n">
-        <v>6766686</v>
+        <v>6766708</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -10701,10 +10696,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>127723157</v>
+        <v>127723183</v>
       </c>
       <c r="B103" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -10736,10 +10731,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>443306</v>
+        <v>443441</v>
       </c>
       <c r="R103" t="n">
-        <v>6766830</v>
+        <v>6766686</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -10798,10 +10793,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>127723182</v>
+        <v>127723157</v>
       </c>
       <c r="B104" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -10833,10 +10828,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>443444</v>
+        <v>443306</v>
       </c>
       <c r="R104" t="n">
-        <v>6766677</v>
+        <v>6766830</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -10895,10 +10890,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>127723096</v>
+        <v>127723182</v>
       </c>
       <c r="B105" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -10930,10 +10925,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>443554</v>
+        <v>443444</v>
       </c>
       <c r="R105" t="n">
-        <v>6766650</v>
+        <v>6766677</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -10992,10 +10987,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>127723139</v>
+        <v>127723096</v>
       </c>
       <c r="B106" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11027,10 +11022,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>443381</v>
+        <v>443554</v>
       </c>
       <c r="R106" t="n">
-        <v>6766623</v>
+        <v>6766650</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11089,10 +11084,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>127723038</v>
+        <v>127723139</v>
       </c>
       <c r="B107" t="n">
-        <v>78777</v>
+        <v>79020</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11100,21 +11095,21 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -11124,10 +11119,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>443328</v>
+        <v>443381</v>
       </c>
       <c r="R107" t="n">
-        <v>6766721</v>
+        <v>6766623</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11186,10 +11181,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>127722842</v>
+        <v>127723170</v>
       </c>
       <c r="B108" t="n">
-        <v>79050</v>
+        <v>79020</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11197,21 +11192,21 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -11221,10 +11216,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>443504</v>
+        <v>443333</v>
       </c>
       <c r="R108" t="n">
-        <v>6766708</v>
+        <v>6766676</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11283,10 +11278,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>127723170</v>
+        <v>127723098</v>
       </c>
       <c r="B109" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11318,10 +11313,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>443333</v>
+        <v>443562</v>
       </c>
       <c r="R109" t="n">
-        <v>6766676</v>
+        <v>6766684</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11380,10 +11375,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>127723098</v>
+        <v>127723038</v>
       </c>
       <c r="B110" t="n">
-        <v>79018</v>
+        <v>78779</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -11391,21 +11386,21 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -11415,10 +11410,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>443562</v>
+        <v>443328</v>
       </c>
       <c r="R110" t="n">
-        <v>6766684</v>
+        <v>6766721</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11477,10 +11472,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>127723616</v>
+        <v>127723154</v>
       </c>
       <c r="B111" t="n">
-        <v>57661</v>
+        <v>79020</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -11488,39 +11483,34 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
-      <c r="M111" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
       <c r="P111" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>443475</v>
+        <v>443369</v>
       </c>
       <c r="R111" t="n">
-        <v>6766610</v>
+        <v>6766695</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -11579,10 +11569,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>127723137</v>
+        <v>127723172</v>
       </c>
       <c r="B112" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -11614,10 +11604,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>443418</v>
+        <v>443356</v>
       </c>
       <c r="R112" t="n">
-        <v>6766627</v>
+        <v>6766650</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -11676,10 +11666,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>127723154</v>
+        <v>127723136</v>
       </c>
       <c r="B113" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -11711,10 +11701,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>443369</v>
+        <v>443438</v>
       </c>
       <c r="R113" t="n">
-        <v>6766695</v>
+        <v>6766628</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -11773,10 +11763,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>127722904</v>
+        <v>127723160</v>
       </c>
       <c r="B114" t="n">
-        <v>57661</v>
+        <v>79020</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -11784,21 +11774,21 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -11808,10 +11798,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>443419</v>
+        <v>443309</v>
       </c>
       <c r="R114" t="n">
-        <v>6766676</v>
+        <v>6766785</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -11844,11 +11834,6 @@
       <c r="AA114" t="inlineStr">
         <is>
           <t>2025-08-21</t>
-        </is>
-      </c>
-      <c r="AC114" t="inlineStr">
-        <is>
-          <t>Äldre ringhack (tall)</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -11875,10 +11860,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>127723172</v>
+        <v>127722904</v>
       </c>
       <c r="B115" t="n">
-        <v>79018</v>
+        <v>57663</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -11886,21 +11871,21 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -11910,10 +11895,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>443356</v>
+        <v>443419</v>
       </c>
       <c r="R115" t="n">
-        <v>6766650</v>
+        <v>6766676</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -11946,6 +11931,11 @@
       <c r="AA115" t="inlineStr">
         <is>
           <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AC115" t="inlineStr">
+        <is>
+          <t>Äldre ringhack (tall)</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -11972,10 +11962,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>127723136</v>
+        <v>127723137</v>
       </c>
       <c r="B116" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -12007,10 +11997,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>443438</v>
+        <v>443418</v>
       </c>
       <c r="R116" t="n">
-        <v>6766628</v>
+        <v>6766627</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12069,10 +12059,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>127723160</v>
+        <v>127729086</v>
       </c>
       <c r="B117" t="n">
-        <v>79018</v>
+        <v>78779</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -12080,34 +12070,34 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
       <c r="P117" t="inlineStr">
         <is>
-          <t>Oxeråsen, Dlr</t>
+          <t>Oxeråsen S. om, Dlr</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>443309</v>
+        <v>443359</v>
       </c>
       <c r="R117" t="n">
-        <v>6766785</v>
+        <v>6766650</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12137,39 +12127,50 @@
           <t>2025-08-21</t>
         </is>
       </c>
+      <c r="Z117" t="inlineStr">
+        <is>
+          <t>13:53</t>
+        </is>
+      </c>
       <c r="AA117" t="inlineStr">
         <is>
           <t>2025-08-21</t>
         </is>
       </c>
+      <c r="AB117" t="inlineStr">
+        <is>
+          <t>13:53</t>
+        </is>
+      </c>
       <c r="AD117" t="b">
         <v>0</v>
       </c>
       <c r="AE117" t="b">
         <v>0</v>
       </c>
+      <c r="AF117" t="inlineStr"/>
       <c r="AG117" t="b">
         <v>0</v>
       </c>
       <c r="AT117" t="inlineStr"/>
       <c r="AW117" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX117" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>127729086</v>
+        <v>127723135</v>
       </c>
       <c r="B118" t="n">
-        <v>78777</v>
+        <v>79020</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12177,34 +12178,34 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
       <c r="P118" t="inlineStr">
         <is>
-          <t>Oxeråsen S. om, Dlr</t>
+          <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>443359</v>
+        <v>443454</v>
       </c>
       <c r="R118" t="n">
-        <v>6766650</v>
+        <v>6766614</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12234,90 +12235,74 @@
           <t>2025-08-21</t>
         </is>
       </c>
-      <c r="Z118" t="inlineStr">
-        <is>
-          <t>13:53</t>
-        </is>
-      </c>
       <c r="AA118" t="inlineStr">
         <is>
           <t>2025-08-21</t>
         </is>
       </c>
-      <c r="AB118" t="inlineStr">
-        <is>
-          <t>13:53</t>
-        </is>
-      </c>
       <c r="AD118" t="b">
         <v>0</v>
       </c>
       <c r="AE118" t="b">
         <v>0</v>
       </c>
-      <c r="AF118" t="inlineStr"/>
       <c r="AG118" t="b">
         <v>0</v>
       </c>
       <c r="AT118" t="inlineStr"/>
       <c r="AW118" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX118" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>127722955</v>
+        <v>127723113</v>
       </c>
       <c r="B119" t="n">
-        <v>8450</v>
+        <v>79020</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
-      <c r="M119" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P119" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>443397</v>
+        <v>443487</v>
       </c>
       <c r="R119" t="n">
-        <v>6766653</v>
+        <v>6766675</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -12379,7 +12364,7 @@
         <v>127723163</v>
       </c>
       <c r="B120" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -12473,50 +12458,45 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>127722948</v>
+        <v>127723176</v>
       </c>
       <c r="B121" t="n">
-        <v>8450</v>
+        <v>79020</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
-      <c r="M121" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P121" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>443457</v>
+        <v>443407</v>
       </c>
       <c r="R121" t="n">
-        <v>6766613</v>
+        <v>6766653</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -12575,10 +12555,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>127723176</v>
+        <v>127722903</v>
       </c>
       <c r="B122" t="n">
-        <v>79018</v>
+        <v>57663</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -12586,21 +12566,21 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -12610,10 +12590,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>443407</v>
+        <v>443382</v>
       </c>
       <c r="R122" t="n">
-        <v>6766653</v>
+        <v>6766657</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -12646,6 +12626,11 @@
       <c r="AA122" t="inlineStr">
         <is>
           <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AC122" t="inlineStr">
+        <is>
+          <t>Äldre ringhack (tall)</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -12672,45 +12657,50 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>127723135</v>
+        <v>127722955</v>
       </c>
       <c r="B123" t="n">
-        <v>79018</v>
+        <v>8450</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
+      <c r="M123" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P123" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>443454</v>
+        <v>443397</v>
       </c>
       <c r="R123" t="n">
-        <v>6766614</v>
+        <v>6766653</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -12769,45 +12759,50 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>127722903</v>
+        <v>127722948</v>
       </c>
       <c r="B124" t="n">
-        <v>57661</v>
+        <v>8450</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>100109</v>
+        <v>106545</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
+      <c r="M124" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P124" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>443382</v>
+        <v>443457</v>
       </c>
       <c r="R124" t="n">
-        <v>6766657</v>
+        <v>6766613</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -12840,11 +12835,6 @@
       <c r="AA124" t="inlineStr">
         <is>
           <t>2025-08-21</t>
-        </is>
-      </c>
-      <c r="AC124" t="inlineStr">
-        <is>
-          <t>Äldre ringhack (tall)</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -12871,32 +12861,32 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>127723113</v>
+        <v>127723555</v>
       </c>
       <c r="B125" t="n">
-        <v>79018</v>
+        <v>92622</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -12906,10 +12896,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>443487</v>
+        <v>443554</v>
       </c>
       <c r="R125" t="n">
-        <v>6766675</v>
+        <v>6766667</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -12968,50 +12958,45 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>127722954</v>
+        <v>127723140</v>
       </c>
       <c r="B126" t="n">
-        <v>8450</v>
+        <v>79020</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
-      <c r="M126" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P126" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>443348</v>
+        <v>443370</v>
       </c>
       <c r="R126" t="n">
-        <v>6766646</v>
+        <v>6766624</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -13070,10 +13055,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>127723037</v>
+        <v>127723165</v>
       </c>
       <c r="B127" t="n">
-        <v>78777</v>
+        <v>79020</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -13081,21 +13066,21 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -13105,10 +13090,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>443509</v>
+        <v>443327</v>
       </c>
       <c r="R127" t="n">
-        <v>6766722</v>
+        <v>6766717</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -13167,10 +13152,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>127723118</v>
+        <v>127723094</v>
       </c>
       <c r="B128" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -13202,10 +13187,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>443519</v>
+        <v>443557</v>
       </c>
       <c r="R128" t="n">
-        <v>6766624</v>
+        <v>6766635</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -13264,45 +13249,50 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>127723140</v>
+        <v>127722954</v>
       </c>
       <c r="B129" t="n">
-        <v>79018</v>
+        <v>8450</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
+      <c r="M129" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P129" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>443370</v>
+        <v>443348</v>
       </c>
       <c r="R129" t="n">
-        <v>6766624</v>
+        <v>6766646</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -13361,10 +13351,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>127723555</v>
+        <v>127722951</v>
       </c>
       <c r="B130" t="n">
-        <v>92620</v>
+        <v>8450</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -13372,34 +13362,39 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>4364</v>
+        <v>106545</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
+      <c r="M130" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P130" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>443554</v>
+        <v>443377</v>
       </c>
       <c r="R130" t="n">
-        <v>6766667</v>
+        <v>6766686</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -13458,10 +13453,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>127723165</v>
+        <v>127723118</v>
       </c>
       <c r="B131" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -13493,10 +13488,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>443327</v>
+        <v>443519</v>
       </c>
       <c r="R131" t="n">
-        <v>6766717</v>
+        <v>6766624</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -13555,10 +13550,10 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>127723094</v>
+        <v>127723037</v>
       </c>
       <c r="B132" t="n">
-        <v>79018</v>
+        <v>78779</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -13566,21 +13561,21 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
@@ -13590,10 +13585,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>443557</v>
+        <v>443509</v>
       </c>
       <c r="R132" t="n">
-        <v>6766635</v>
+        <v>6766722</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -13652,50 +13647,45 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>127722951</v>
+        <v>127723111</v>
       </c>
       <c r="B133" t="n">
-        <v>8450</v>
+        <v>79020</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
-      <c r="M133" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P133" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>443377</v>
+        <v>443474</v>
       </c>
       <c r="R133" t="n">
-        <v>6766686</v>
+        <v>6766692</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -13757,7 +13747,7 @@
         <v>127723162</v>
       </c>
       <c r="B134" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -13854,7 +13844,7 @@
         <v>127722855</v>
       </c>
       <c r="B135" t="n">
-        <v>79607</v>
+        <v>79609</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -13948,10 +13938,10 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>127723111</v>
+        <v>127723619</v>
       </c>
       <c r="B136" t="n">
-        <v>79018</v>
+        <v>57663</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -13959,34 +13949,39 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
+      <c r="M136" t="inlineStr">
+        <is>
+          <t>nyligen använt bo</t>
+        </is>
+      </c>
       <c r="P136" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>443474</v>
+        <v>443387</v>
       </c>
       <c r="R136" t="n">
-        <v>6766692</v>
+        <v>6766675</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -14021,6 +14016,11 @@
           <t>2025-08-21</t>
         </is>
       </c>
+      <c r="AC136" t="inlineStr">
+        <is>
+          <t>I gammal tall med tallticka</t>
+        </is>
+      </c>
       <c r="AD136" t="b">
         <v>0</v>
       </c>
@@ -14042,6 +14042,220 @@
         </is>
       </c>
       <c r="AY136" t="inlineStr"/>
+    </row>
+    <row r="137">
+      <c r="A137" t="n">
+        <v>127736007</v>
+      </c>
+      <c r="B137" t="n">
+        <v>91352</v>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E137" t="n">
+        <v>5442</v>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>Tallticka</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>Porodaedalea pini</t>
+        </is>
+      </c>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I137" t="inlineStr"/>
+      <c r="P137" t="inlineStr">
+        <is>
+          <t>Oxeråsen S, Dlr</t>
+        </is>
+      </c>
+      <c r="Q137" t="n">
+        <v>443384</v>
+      </c>
+      <c r="R137" t="n">
+        <v>6766669</v>
+      </c>
+      <c r="S137" t="n">
+        <v>10</v>
+      </c>
+      <c r="T137" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U137" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V137" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W137" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y137" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="Z137" t="inlineStr">
+        <is>
+          <t>13:47</t>
+        </is>
+      </c>
+      <c r="AA137" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AB137" t="inlineStr">
+        <is>
+          <t>13:47</t>
+        </is>
+      </c>
+      <c r="AD137" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE137" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG137" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT137" t="inlineStr"/>
+      <c r="AW137" t="inlineStr">
+        <is>
+          <t>Lars-Erik Nilsson</t>
+        </is>
+      </c>
+      <c r="AX137" t="inlineStr">
+        <is>
+          <t>Lars-Erik Nilsson</t>
+        </is>
+      </c>
+      <c r="AY137" t="inlineStr"/>
+    </row>
+    <row r="138">
+      <c r="A138" t="n">
+        <v>127736019</v>
+      </c>
+      <c r="B138" t="n">
+        <v>79020</v>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E138" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I138" t="inlineStr"/>
+      <c r="P138" t="inlineStr">
+        <is>
+          <t>Oxeråsen S, Dlr</t>
+        </is>
+      </c>
+      <c r="Q138" t="n">
+        <v>443437</v>
+      </c>
+      <c r="R138" t="n">
+        <v>6766684</v>
+      </c>
+      <c r="S138" t="n">
+        <v>10</v>
+      </c>
+      <c r="T138" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U138" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V138" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W138" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y138" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="Z138" t="inlineStr">
+        <is>
+          <t>13:53</t>
+        </is>
+      </c>
+      <c r="AA138" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AB138" t="inlineStr">
+        <is>
+          <t>13:53</t>
+        </is>
+      </c>
+      <c r="AD138" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE138" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG138" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT138" t="inlineStr"/>
+      <c r="AW138" t="inlineStr">
+        <is>
+          <t>Lars-Erik Nilsson</t>
+        </is>
+      </c>
+      <c r="AX138" t="inlineStr">
+        <is>
+          <t>Lars-Erik Nilsson</t>
+        </is>
+      </c>
+      <c r="AY138" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 35484-2025 artfynd.xlsx
+++ b/artfynd/A 35484-2025 artfynd.xlsx
@@ -2926,10 +2926,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127723112</v>
+        <v>127723040</v>
       </c>
       <c r="B24" t="n">
-        <v>79020</v>
+        <v>78779</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2937,21 +2937,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2961,10 +2961,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>443476</v>
+        <v>443377</v>
       </c>
       <c r="R24" t="n">
-        <v>6766681</v>
+        <v>6766659</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3023,10 +3023,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127723166</v>
+        <v>127723039</v>
       </c>
       <c r="B25" t="n">
-        <v>79020</v>
+        <v>78779</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3034,21 +3034,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3058,10 +3058,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>443326</v>
+        <v>443356</v>
       </c>
       <c r="R25" t="n">
-        <v>6766711</v>
+        <v>6766650</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3120,7 +3120,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127723181</v>
+        <v>127723166</v>
       </c>
       <c r="B26" t="n">
         <v>79020</v>
@@ -3155,10 +3155,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>443436</v>
+        <v>443326</v>
       </c>
       <c r="R26" t="n">
-        <v>6766667</v>
+        <v>6766711</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3217,50 +3217,45 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127722950</v>
+        <v>127723181</v>
       </c>
       <c r="B27" t="n">
-        <v>8450</v>
+        <v>79020</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>443438</v>
+        <v>443436</v>
       </c>
       <c r="R27" t="n">
-        <v>6766650</v>
+        <v>6766667</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3319,10 +3314,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127723040</v>
+        <v>127723112</v>
       </c>
       <c r="B28" t="n">
-        <v>78779</v>
+        <v>79020</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3330,21 +3325,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3354,10 +3349,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>443377</v>
+        <v>443476</v>
       </c>
       <c r="R28" t="n">
-        <v>6766659</v>
+        <v>6766681</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3416,42 +3411,47 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127723039</v>
+        <v>127722950</v>
       </c>
       <c r="B29" t="n">
-        <v>78779</v>
+        <v>8450</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>228912</v>
+        <v>106545</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>443356</v>
+        <v>443438</v>
       </c>
       <c r="R29" t="n">
         <v>6766650</v>
@@ -3513,7 +3513,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127723179</v>
+        <v>127723152</v>
       </c>
       <c r="B30" t="n">
         <v>79020</v>
@@ -3548,10 +3548,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>443411</v>
+        <v>443424</v>
       </c>
       <c r="R30" t="n">
-        <v>6766676</v>
+        <v>6766627</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3610,50 +3610,45 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127722945</v>
+        <v>127723179</v>
       </c>
       <c r="B31" t="n">
-        <v>8450</v>
+        <v>79020</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>443568</v>
+        <v>443411</v>
       </c>
       <c r="R31" t="n">
-        <v>6766605</v>
+        <v>6766676</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3712,45 +3707,50 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127722875</v>
+        <v>127722945</v>
       </c>
       <c r="B32" t="n">
-        <v>91352</v>
+        <v>8450</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>5442</v>
+        <v>106545</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>443312</v>
+        <v>443568</v>
       </c>
       <c r="R32" t="n">
-        <v>6766713</v>
+        <v>6766605</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3809,10 +3809,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127723152</v>
+        <v>127722875</v>
       </c>
       <c r="B33" t="n">
-        <v>79020</v>
+        <v>91352</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3820,21 +3820,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3844,10 +3844,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>443424</v>
+        <v>443312</v>
       </c>
       <c r="R33" t="n">
-        <v>6766627</v>
+        <v>6766713</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3906,7 +3906,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>127723107</v>
+        <v>127723109</v>
       </c>
       <c r="B34" t="n">
         <v>79020</v>
@@ -3941,10 +3941,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>443493</v>
+        <v>443482</v>
       </c>
       <c r="R34" t="n">
-        <v>6766717</v>
+        <v>6766716</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4003,7 +4003,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127723109</v>
+        <v>127723169</v>
       </c>
       <c r="B35" t="n">
         <v>79020</v>
@@ -4038,10 +4038,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>443482</v>
+        <v>443321</v>
       </c>
       <c r="R35" t="n">
-        <v>6766716</v>
+        <v>6766706</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4100,7 +4100,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127723169</v>
+        <v>127723107</v>
       </c>
       <c r="B36" t="n">
         <v>79020</v>
@@ -4135,10 +4135,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>443321</v>
+        <v>443493</v>
       </c>
       <c r="R36" t="n">
-        <v>6766706</v>
+        <v>6766717</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4294,38 +4294,38 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127722944</v>
+        <v>127722896</v>
       </c>
       <c r="B38" t="n">
-        <v>8450</v>
+        <v>57660</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="M38" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
@@ -4334,10 +4334,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>443488</v>
+        <v>443537</v>
       </c>
       <c r="R38" t="n">
-        <v>6766671</v>
+        <v>6766699</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4396,7 +4396,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127722928</v>
+        <v>127722944</v>
       </c>
       <c r="B39" t="n">
         <v>8450</v>
@@ -4427,7 +4427,7 @@
       <c r="I39" t="inlineStr"/>
       <c r="M39" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
@@ -4436,10 +4436,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>443559</v>
+        <v>443488</v>
       </c>
       <c r="R39" t="n">
-        <v>6766616</v>
+        <v>6766671</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4498,38 +4498,38 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127722896</v>
+        <v>127722928</v>
       </c>
       <c r="B40" t="n">
-        <v>57660</v>
+        <v>8450</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="M40" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
@@ -4538,10 +4538,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>443537</v>
+        <v>443559</v>
       </c>
       <c r="R40" t="n">
-        <v>6766699</v>
+        <v>6766616</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4794,10 +4794,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127722876</v>
+        <v>127723091</v>
       </c>
       <c r="B43" t="n">
-        <v>91352</v>
+        <v>79020</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4805,21 +4805,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4829,10 +4829,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>443366</v>
+        <v>443587</v>
       </c>
       <c r="R43" t="n">
-        <v>6766661</v>
+        <v>6766651</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4891,7 +4891,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>127723091</v>
+        <v>127723121</v>
       </c>
       <c r="B44" t="n">
         <v>79020</v>
@@ -4926,10 +4926,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>443587</v>
+        <v>443558</v>
       </c>
       <c r="R44" t="n">
-        <v>6766651</v>
+        <v>6766620</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4988,10 +4988,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>127723159</v>
+        <v>127722876</v>
       </c>
       <c r="B45" t="n">
-        <v>79020</v>
+        <v>91352</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4999,21 +4999,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5023,10 +5023,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>443314</v>
+        <v>443366</v>
       </c>
       <c r="R45" t="n">
-        <v>6766811</v>
+        <v>6766661</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5085,7 +5085,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>127723189</v>
+        <v>127723159</v>
       </c>
       <c r="B46" t="n">
         <v>79020</v>
@@ -5120,10 +5120,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>443446</v>
+        <v>443314</v>
       </c>
       <c r="R46" t="n">
-        <v>6766727</v>
+        <v>6766811</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5156,11 +5156,6 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-08-21</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Med grov gran i bäckmiljö</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5187,7 +5182,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>127723121</v>
+        <v>127723189</v>
       </c>
       <c r="B47" t="n">
         <v>79020</v>
@@ -5222,10 +5217,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>443558</v>
+        <v>443446</v>
       </c>
       <c r="R47" t="n">
-        <v>6766620</v>
+        <v>6766727</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5258,6 +5253,11 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Med grov gran i bäckmiljö</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5284,10 +5284,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>127722868</v>
+        <v>127723110</v>
       </c>
       <c r="B48" t="n">
-        <v>57823</v>
+        <v>79020</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5295,39 +5295,34 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>443305</v>
+        <v>443479</v>
       </c>
       <c r="R48" t="n">
-        <v>6766767</v>
+        <v>6766703</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5386,50 +5381,45 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>127722957</v>
+        <v>127723180</v>
       </c>
       <c r="B49" t="n">
-        <v>8450</v>
+        <v>79020</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>443457</v>
+        <v>443425</v>
       </c>
       <c r="R49" t="n">
-        <v>6766726</v>
+        <v>6766665</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5488,7 +5478,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>127723180</v>
+        <v>127723102</v>
       </c>
       <c r="B50" t="n">
         <v>79020</v>
@@ -5523,10 +5513,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>443425</v>
+        <v>443556</v>
       </c>
       <c r="R50" t="n">
-        <v>6766665</v>
+        <v>6766717</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5585,7 +5575,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>127723102</v>
+        <v>127723185</v>
       </c>
       <c r="B51" t="n">
         <v>79020</v>
@@ -5620,10 +5610,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>443556</v>
+        <v>443452</v>
       </c>
       <c r="R51" t="n">
-        <v>6766717</v>
+        <v>6766711</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5682,45 +5672,50 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>127723185</v>
+        <v>127722957</v>
       </c>
       <c r="B52" t="n">
-        <v>79020</v>
+        <v>8450</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>443452</v>
+        <v>443457</v>
       </c>
       <c r="R52" t="n">
-        <v>6766711</v>
+        <v>6766726</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5779,10 +5774,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>127723110</v>
+        <v>127722868</v>
       </c>
       <c r="B53" t="n">
-        <v>79020</v>
+        <v>57823</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5790,34 +5785,39 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>443479</v>
+        <v>443305</v>
       </c>
       <c r="R53" t="n">
-        <v>6766703</v>
+        <v>6766767</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5876,7 +5876,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>127723184</v>
+        <v>127723138</v>
       </c>
       <c r="B54" t="n">
         <v>79020</v>
@@ -5911,10 +5911,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>443446</v>
+        <v>443391</v>
       </c>
       <c r="R54" t="n">
-        <v>6766702</v>
+        <v>6766625</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5973,50 +5973,45 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>127722943</v>
+        <v>127723184</v>
       </c>
       <c r="B55" t="n">
-        <v>8450</v>
+        <v>79020</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>443527</v>
+        <v>443446</v>
       </c>
       <c r="R55" t="n">
-        <v>6766711</v>
+        <v>6766702</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6177,45 +6172,50 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>127723138</v>
+        <v>127722943</v>
       </c>
       <c r="B57" t="n">
-        <v>79020</v>
+        <v>8450</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P57" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>443391</v>
+        <v>443527</v>
       </c>
       <c r="R57" t="n">
-        <v>6766625</v>
+        <v>6766711</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6371,7 +6371,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>127723134</v>
+        <v>127723175</v>
       </c>
       <c r="B59" t="n">
         <v>79020</v>
@@ -6406,10 +6406,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>443465</v>
+        <v>443387</v>
       </c>
       <c r="R59" t="n">
-        <v>6766607</v>
+        <v>6766658</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6468,7 +6468,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>127723106</v>
+        <v>127723134</v>
       </c>
       <c r="B60" t="n">
         <v>79020</v>
@@ -6503,10 +6503,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>443516</v>
+        <v>443465</v>
       </c>
       <c r="R60" t="n">
-        <v>6766720</v>
+        <v>6766607</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6565,7 +6565,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>127723167</v>
+        <v>127723119</v>
       </c>
       <c r="B61" t="n">
         <v>79020</v>
@@ -6600,10 +6600,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>443316</v>
+        <v>443535</v>
       </c>
       <c r="R61" t="n">
-        <v>6766701</v>
+        <v>6766639</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6662,7 +6662,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>127723153</v>
+        <v>127723167</v>
       </c>
       <c r="B62" t="n">
         <v>79020</v>
@@ -6697,10 +6697,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>443436</v>
+        <v>443316</v>
       </c>
       <c r="R62" t="n">
-        <v>6766648</v>
+        <v>6766701</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6759,7 +6759,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>127723119</v>
+        <v>127723153</v>
       </c>
       <c r="B63" t="n">
         <v>79020</v>
@@ -6794,10 +6794,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>443535</v>
+        <v>443436</v>
       </c>
       <c r="R63" t="n">
-        <v>6766639</v>
+        <v>6766648</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6856,7 +6856,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>127723188</v>
+        <v>127723106</v>
       </c>
       <c r="B64" t="n">
         <v>79020</v>
@@ -6891,10 +6891,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>443454</v>
+        <v>443516</v>
       </c>
       <c r="R64" t="n">
-        <v>6766724</v>
+        <v>6766720</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -6953,7 +6953,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>127723175</v>
+        <v>127723188</v>
       </c>
       <c r="B65" t="n">
         <v>79020</v>
@@ -6988,10 +6988,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>443387</v>
+        <v>443454</v>
       </c>
       <c r="R65" t="n">
-        <v>6766658</v>
+        <v>6766724</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7050,50 +7050,45 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>127722941</v>
+        <v>127722847</v>
       </c>
       <c r="B66" t="n">
-        <v>8450</v>
+        <v>79052</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>106545</v>
+        <v>185</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
-      <c r="M66" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P66" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>443557</v>
+        <v>443320</v>
       </c>
       <c r="R66" t="n">
-        <v>6766635</v>
+        <v>6766703</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7152,32 +7147,32 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>127723177</v>
+        <v>127723065</v>
       </c>
       <c r="B67" t="n">
-        <v>79020</v>
+        <v>91493</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6425</v>
+        <v>1503</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7187,10 +7182,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>443397</v>
+        <v>443425</v>
       </c>
       <c r="R67" t="n">
-        <v>6766673</v>
+        <v>6766668</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7249,7 +7244,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>127729137</v>
+        <v>127723158</v>
       </c>
       <c r="B68" t="n">
         <v>79020</v>
@@ -7280,14 +7275,14 @@
       <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Oxeråsen S. om, Dlr</t>
+          <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>443391</v>
+        <v>443312</v>
       </c>
       <c r="R68" t="n">
-        <v>6766598</v>
+        <v>6766818</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7317,47 +7312,36 @@
           <t>2025-08-21</t>
         </is>
       </c>
-      <c r="Z68" t="inlineStr">
-        <is>
-          <t>14:00</t>
-        </is>
-      </c>
       <c r="AA68" t="inlineStr">
         <is>
           <t>2025-08-21</t>
         </is>
       </c>
-      <c r="AB68" t="inlineStr">
-        <is>
-          <t>14:00</t>
-        </is>
-      </c>
       <c r="AD68" t="b">
         <v>0</v>
       </c>
       <c r="AE68" t="b">
         <v>0</v>
       </c>
-      <c r="AF68" t="inlineStr"/>
       <c r="AG68" t="b">
         <v>0</v>
       </c>
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>127723158</v>
+        <v>127729137</v>
       </c>
       <c r="B69" t="n">
         <v>79020</v>
@@ -7388,14 +7372,14 @@
       <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Oxeråsen, Dlr</t>
+          <t>Oxeråsen S. om, Dlr</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>443312</v>
+        <v>443391</v>
       </c>
       <c r="R69" t="n">
-        <v>6766818</v>
+        <v>6766598</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7425,61 +7409,72 @@
           <t>2025-08-21</t>
         </is>
       </c>
+      <c r="Z69" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
       <c r="AA69" t="inlineStr">
         <is>
           <t>2025-08-21</t>
         </is>
       </c>
+      <c r="AB69" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
       <c r="AD69" t="b">
         <v>0</v>
       </c>
       <c r="AE69" t="b">
         <v>0</v>
       </c>
+      <c r="AF69" t="inlineStr"/>
       <c r="AG69" t="b">
         <v>0</v>
       </c>
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>127723065</v>
+        <v>127723150</v>
       </c>
       <c r="B70" t="n">
-        <v>91493</v>
+        <v>79020</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>1503</v>
+        <v>6425</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7489,10 +7484,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>443425</v>
+        <v>443415</v>
       </c>
       <c r="R70" t="n">
-        <v>6766668</v>
+        <v>6766603</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7551,10 +7546,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>127722847</v>
+        <v>127723177</v>
       </c>
       <c r="B71" t="n">
-        <v>79052</v>
+        <v>79020</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7562,21 +7557,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7586,10 +7581,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>443320</v>
+        <v>443397</v>
       </c>
       <c r="R71" t="n">
-        <v>6766703</v>
+        <v>6766673</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7648,45 +7643,50 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>127723150</v>
+        <v>127722941</v>
       </c>
       <c r="B72" t="n">
-        <v>79020</v>
+        <v>8450</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P72" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>443415</v>
+        <v>443557</v>
       </c>
       <c r="R72" t="n">
-        <v>6766603</v>
+        <v>6766635</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7745,10 +7745,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>127729092</v>
+        <v>127722839</v>
       </c>
       <c r="B73" t="n">
-        <v>78778</v>
+        <v>79052</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7756,34 +7756,34 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6446</v>
+        <v>185</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Oxeråsen S. om, Dlr</t>
+          <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>443381</v>
+        <v>443554</v>
       </c>
       <c r="R73" t="n">
-        <v>6766668</v>
+        <v>6766649</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7813,47 +7813,36 @@
           <t>2025-08-21</t>
         </is>
       </c>
-      <c r="Z73" t="inlineStr">
-        <is>
-          <t>13:51</t>
-        </is>
-      </c>
       <c r="AA73" t="inlineStr">
         <is>
           <t>2025-08-21</t>
         </is>
       </c>
-      <c r="AB73" t="inlineStr">
-        <is>
-          <t>13:51</t>
-        </is>
-      </c>
       <c r="AD73" t="b">
         <v>0</v>
       </c>
       <c r="AE73" t="b">
         <v>0</v>
       </c>
-      <c r="AF73" t="inlineStr"/>
       <c r="AG73" t="b">
         <v>0</v>
       </c>
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>127723133</v>
+        <v>127723090</v>
       </c>
       <c r="B74" t="n">
         <v>79020</v>
@@ -7888,10 +7877,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>443504</v>
+        <v>443593</v>
       </c>
       <c r="R74" t="n">
-        <v>6766593</v>
+        <v>6766653</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -7950,7 +7939,7 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>127723173</v>
+        <v>127723108</v>
       </c>
       <c r="B75" t="n">
         <v>79020</v>
@@ -7985,10 +7974,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>443365</v>
+        <v>443483</v>
       </c>
       <c r="R75" t="n">
-        <v>6766656</v>
+        <v>6766725</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8047,7 +8036,7 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>127723108</v>
+        <v>127723133</v>
       </c>
       <c r="B76" t="n">
         <v>79020</v>
@@ -8082,10 +8071,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>443483</v>
+        <v>443504</v>
       </c>
       <c r="R76" t="n">
-        <v>6766725</v>
+        <v>6766593</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8144,7 +8133,7 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>127723090</v>
+        <v>127723173</v>
       </c>
       <c r="B77" t="n">
         <v>79020</v>
@@ -8179,10 +8168,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>443593</v>
+        <v>443365</v>
       </c>
       <c r="R77" t="n">
-        <v>6766653</v>
+        <v>6766656</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8241,10 +8230,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>127722839</v>
+        <v>127729092</v>
       </c>
       <c r="B78" t="n">
-        <v>79052</v>
+        <v>78778</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8252,34 +8241,34 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>185</v>
+        <v>6446</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Oxeråsen, Dlr</t>
+          <t>Oxeråsen S. om, Dlr</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>443554</v>
+        <v>443381</v>
       </c>
       <c r="R78" t="n">
-        <v>6766649</v>
+        <v>6766668</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8309,29 +8298,40 @@
           <t>2025-08-21</t>
         </is>
       </c>
+      <c r="Z78" t="inlineStr">
+        <is>
+          <t>13:51</t>
+        </is>
+      </c>
       <c r="AA78" t="inlineStr">
         <is>
           <t>2025-08-21</t>
         </is>
       </c>
+      <c r="AB78" t="inlineStr">
+        <is>
+          <t>13:51</t>
+        </is>
+      </c>
       <c r="AD78" t="b">
         <v>0</v>
       </c>
       <c r="AE78" t="b">
         <v>0</v>
       </c>
+      <c r="AF78" t="inlineStr"/>
       <c r="AG78" t="b">
         <v>0</v>
       </c>
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
@@ -8435,7 +8435,7 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>127723156</v>
+        <v>127723104</v>
       </c>
       <c r="B80" t="n">
         <v>79020</v>
@@ -8470,10 +8470,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>443346</v>
+        <v>443536</v>
       </c>
       <c r="R80" t="n">
-        <v>6766766</v>
+        <v>6766704</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8629,7 +8629,7 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>127723104</v>
+        <v>127723156</v>
       </c>
       <c r="B82" t="n">
         <v>79020</v>
@@ -8664,10 +8664,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>443536</v>
+        <v>443346</v>
       </c>
       <c r="R82" t="n">
-        <v>6766704</v>
+        <v>6766766</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8726,7 +8726,7 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>127723116</v>
+        <v>127723178</v>
       </c>
       <c r="B83" t="n">
         <v>79020</v>
@@ -8761,10 +8761,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>443509</v>
+        <v>443402</v>
       </c>
       <c r="R83" t="n">
-        <v>6766633</v>
+        <v>6766682</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -8823,7 +8823,7 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>127723092</v>
+        <v>127723171</v>
       </c>
       <c r="B84" t="n">
         <v>79020</v>
@@ -8858,7 +8858,7 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>443572</v>
+        <v>443342</v>
       </c>
       <c r="R84" t="n">
         <v>6766650</v>
@@ -8920,7 +8920,7 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>127723178</v>
+        <v>127723092</v>
       </c>
       <c r="B85" t="n">
         <v>79020</v>
@@ -8955,10 +8955,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>443402</v>
+        <v>443572</v>
       </c>
       <c r="R85" t="n">
-        <v>6766682</v>
+        <v>6766650</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9017,10 +9017,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>127723541</v>
+        <v>127723570</v>
       </c>
       <c r="B86" t="n">
-        <v>57663</v>
+        <v>78687</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9028,39 +9028,34 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>100109</v>
+        <v>353</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
-      <c r="M86" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P86" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>443317</v>
+        <v>443319</v>
       </c>
       <c r="R86" t="n">
-        <v>6766816</v>
+        <v>6766670</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9119,10 +9114,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>127722916</v>
+        <v>127723116</v>
       </c>
       <c r="B87" t="n">
-        <v>57663</v>
+        <v>79020</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9130,39 +9125,34 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
-      <c r="M87" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P87" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>443342</v>
+        <v>443509</v>
       </c>
       <c r="R87" t="n">
-        <v>6766806</v>
+        <v>6766633</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9195,11 +9185,6 @@
       <c r="AA87" t="inlineStr">
         <is>
           <t>2025-08-21</t>
-        </is>
-      </c>
-      <c r="AC87" t="inlineStr">
-        <is>
-          <t>Färska ringhack (gran), 4-5 år gamla</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9226,10 +9211,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>127723570</v>
+        <v>127723541</v>
       </c>
       <c r="B88" t="n">
-        <v>78687</v>
+        <v>57663</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9237,34 +9222,39 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>353</v>
+        <v>100109</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P88" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>443319</v>
+        <v>443317</v>
       </c>
       <c r="R88" t="n">
-        <v>6766670</v>
+        <v>6766816</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9323,10 +9313,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>127723171</v>
+        <v>127722916</v>
       </c>
       <c r="B89" t="n">
-        <v>79020</v>
+        <v>57663</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9334,24 +9324,29 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P89" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
@@ -9361,7 +9356,7 @@
         <v>443342</v>
       </c>
       <c r="R89" t="n">
-        <v>6766650</v>
+        <v>6766806</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9394,6 +9389,11 @@
       <c r="AA89" t="inlineStr">
         <is>
           <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AC89" t="inlineStr">
+        <is>
+          <t>Färska ringhack (gran), 4-5 år gamla</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -9619,7 +9619,7 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>127723103</v>
+        <v>127723174</v>
       </c>
       <c r="B92" t="n">
         <v>79020</v>
@@ -9654,10 +9654,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>443541</v>
+        <v>443378</v>
       </c>
       <c r="R92" t="n">
-        <v>6766696</v>
+        <v>6766657</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9716,7 +9716,7 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>127723105</v>
+        <v>127723097</v>
       </c>
       <c r="B93" t="n">
         <v>79020</v>
@@ -9751,10 +9751,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>443525</v>
+        <v>443561</v>
       </c>
       <c r="R93" t="n">
-        <v>6766717</v>
+        <v>6766678</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -9813,7 +9813,7 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>127723161</v>
+        <v>127723105</v>
       </c>
       <c r="B94" t="n">
         <v>79020</v>
@@ -9848,10 +9848,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>443305</v>
+        <v>443525</v>
       </c>
       <c r="R94" t="n">
-        <v>6766767</v>
+        <v>6766717</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -9910,7 +9910,7 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>127723186</v>
+        <v>127723161</v>
       </c>
       <c r="B95" t="n">
         <v>79020</v>
@@ -9945,10 +9945,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>443454</v>
+        <v>443305</v>
       </c>
       <c r="R95" t="n">
-        <v>6766738</v>
+        <v>6766767</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10007,7 +10007,7 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>127723097</v>
+        <v>127723186</v>
       </c>
       <c r="B96" t="n">
         <v>79020</v>
@@ -10042,10 +10042,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>443561</v>
+        <v>443454</v>
       </c>
       <c r="R96" t="n">
-        <v>6766678</v>
+        <v>6766738</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10104,7 +10104,7 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>127723174</v>
+        <v>127723114</v>
       </c>
       <c r="B97" t="n">
         <v>79020</v>
@@ -10139,10 +10139,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>443378</v>
+        <v>443487</v>
       </c>
       <c r="R97" t="n">
-        <v>6766657</v>
+        <v>6766651</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10201,10 +10201,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>127723041</v>
+        <v>127723103</v>
       </c>
       <c r="B98" t="n">
-        <v>78779</v>
+        <v>79020</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10212,21 +10212,21 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10236,10 +10236,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>443450</v>
+        <v>443541</v>
       </c>
       <c r="R98" t="n">
-        <v>6766735</v>
+        <v>6766696</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10298,10 +10298,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>127723114</v>
+        <v>127723041</v>
       </c>
       <c r="B99" t="n">
-        <v>79020</v>
+        <v>78779</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10309,21 +10309,21 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -10333,10 +10333,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>443487</v>
+        <v>443450</v>
       </c>
       <c r="R99" t="n">
-        <v>6766651</v>
+        <v>6766735</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10395,10 +10395,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>127723616</v>
+        <v>127723096</v>
       </c>
       <c r="B100" t="n">
-        <v>57663</v>
+        <v>79020</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10406,39 +10406,34 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
-      <c r="M100" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
       <c r="P100" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>443475</v>
+        <v>443554</v>
       </c>
       <c r="R100" t="n">
-        <v>6766610</v>
+        <v>6766650</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10497,50 +10492,45 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>127722929</v>
+        <v>127723139</v>
       </c>
       <c r="B101" t="n">
-        <v>8450</v>
+        <v>79020</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
-      <c r="M101" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P101" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>443327</v>
+        <v>443381</v>
       </c>
       <c r="R101" t="n">
-        <v>6766698</v>
+        <v>6766623</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10696,7 +10686,7 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>127723183</v>
+        <v>127723098</v>
       </c>
       <c r="B103" t="n">
         <v>79020</v>
@@ -10731,10 +10721,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>443441</v>
+        <v>443562</v>
       </c>
       <c r="R103" t="n">
-        <v>6766686</v>
+        <v>6766684</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -10793,7 +10783,7 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>127723157</v>
+        <v>127723170</v>
       </c>
       <c r="B104" t="n">
         <v>79020</v>
@@ -10828,10 +10818,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>443306</v>
+        <v>443333</v>
       </c>
       <c r="R104" t="n">
-        <v>6766830</v>
+        <v>6766676</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -10890,7 +10880,7 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>127723182</v>
+        <v>127723183</v>
       </c>
       <c r="B105" t="n">
         <v>79020</v>
@@ -10925,10 +10915,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>443444</v>
+        <v>443441</v>
       </c>
       <c r="R105" t="n">
-        <v>6766677</v>
+        <v>6766686</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -10987,7 +10977,7 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>127723096</v>
+        <v>127723157</v>
       </c>
       <c r="B106" t="n">
         <v>79020</v>
@@ -11022,10 +11012,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>443554</v>
+        <v>443306</v>
       </c>
       <c r="R106" t="n">
-        <v>6766650</v>
+        <v>6766830</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11084,7 +11074,7 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>127723139</v>
+        <v>127723182</v>
       </c>
       <c r="B107" t="n">
         <v>79020</v>
@@ -11119,10 +11109,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>443381</v>
+        <v>443444</v>
       </c>
       <c r="R107" t="n">
-        <v>6766623</v>
+        <v>6766677</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11181,45 +11171,50 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>127723170</v>
+        <v>127722929</v>
       </c>
       <c r="B108" t="n">
-        <v>79020</v>
+        <v>8450</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
+      <c r="M108" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P108" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>443333</v>
+        <v>443327</v>
       </c>
       <c r="R108" t="n">
-        <v>6766676</v>
+        <v>6766698</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11278,10 +11273,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>127723098</v>
+        <v>127723616</v>
       </c>
       <c r="B109" t="n">
-        <v>79020</v>
+        <v>57663</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11289,34 +11284,39 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
+      <c r="M109" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
       <c r="P109" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>443562</v>
+        <v>443475</v>
       </c>
       <c r="R109" t="n">
-        <v>6766684</v>
+        <v>6766610</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11472,10 +11472,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>127723154</v>
+        <v>127722904</v>
       </c>
       <c r="B111" t="n">
-        <v>79020</v>
+        <v>57663</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -11483,21 +11483,21 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -11507,10 +11507,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>443369</v>
+        <v>443419</v>
       </c>
       <c r="R111" t="n">
-        <v>6766695</v>
+        <v>6766676</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -11543,6 +11543,11 @@
       <c r="AA111" t="inlineStr">
         <is>
           <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AC111" t="inlineStr">
+        <is>
+          <t>Äldre ringhack (tall)</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -11569,7 +11574,7 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>127723172</v>
+        <v>127723136</v>
       </c>
       <c r="B112" t="n">
         <v>79020</v>
@@ -11604,10 +11609,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>443356</v>
+        <v>443438</v>
       </c>
       <c r="R112" t="n">
-        <v>6766650</v>
+        <v>6766628</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -11666,7 +11671,7 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>127723136</v>
+        <v>127723160</v>
       </c>
       <c r="B113" t="n">
         <v>79020</v>
@@ -11701,10 +11706,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>443438</v>
+        <v>443309</v>
       </c>
       <c r="R113" t="n">
-        <v>6766628</v>
+        <v>6766785</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -11763,7 +11768,7 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>127723160</v>
+        <v>127723137</v>
       </c>
       <c r="B114" t="n">
         <v>79020</v>
@@ -11798,10 +11803,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>443309</v>
+        <v>443418</v>
       </c>
       <c r="R114" t="n">
-        <v>6766785</v>
+        <v>6766627</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -11860,10 +11865,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>127722904</v>
+        <v>127723172</v>
       </c>
       <c r="B115" t="n">
-        <v>57663</v>
+        <v>79020</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -11871,21 +11876,21 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -11895,10 +11900,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>443419</v>
+        <v>443356</v>
       </c>
       <c r="R115" t="n">
-        <v>6766676</v>
+        <v>6766650</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -11931,11 +11936,6 @@
       <c r="AA115" t="inlineStr">
         <is>
           <t>2025-08-21</t>
-        </is>
-      </c>
-      <c r="AC115" t="inlineStr">
-        <is>
-          <t>Äldre ringhack (tall)</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -11962,7 +11962,7 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>127723137</v>
+        <v>127723154</v>
       </c>
       <c r="B116" t="n">
         <v>79020</v>
@@ -11997,10 +11997,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>443418</v>
+        <v>443369</v>
       </c>
       <c r="R116" t="n">
-        <v>6766627</v>
+        <v>6766695</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12167,7 +12167,7 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>127723135</v>
+        <v>127723113</v>
       </c>
       <c r="B118" t="n">
         <v>79020</v>
@@ -12202,10 +12202,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>443454</v>
+        <v>443487</v>
       </c>
       <c r="R118" t="n">
-        <v>6766614</v>
+        <v>6766675</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12264,7 +12264,7 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>127723113</v>
+        <v>127723176</v>
       </c>
       <c r="B119" t="n">
         <v>79020</v>
@@ -12299,10 +12299,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>443487</v>
+        <v>443407</v>
       </c>
       <c r="R119" t="n">
-        <v>6766675</v>
+        <v>6766653</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -12361,7 +12361,7 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>127723163</v>
+        <v>127723135</v>
       </c>
       <c r="B120" t="n">
         <v>79020</v>
@@ -12396,10 +12396,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>443332</v>
+        <v>443454</v>
       </c>
       <c r="R120" t="n">
-        <v>6766744</v>
+        <v>6766614</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -12458,7 +12458,7 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>127723176</v>
+        <v>127723163</v>
       </c>
       <c r="B121" t="n">
         <v>79020</v>
@@ -12493,10 +12493,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>443407</v>
+        <v>443332</v>
       </c>
       <c r="R121" t="n">
-        <v>6766653</v>
+        <v>6766744</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -12958,7 +12958,7 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>127723140</v>
+        <v>127723165</v>
       </c>
       <c r="B126" t="n">
         <v>79020</v>
@@ -12993,10 +12993,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>443370</v>
+        <v>443327</v>
       </c>
       <c r="R126" t="n">
-        <v>6766624</v>
+        <v>6766717</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -13055,7 +13055,7 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>127723165</v>
+        <v>127723094</v>
       </c>
       <c r="B127" t="n">
         <v>79020</v>
@@ -13090,10 +13090,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>443327</v>
+        <v>443557</v>
       </c>
       <c r="R127" t="n">
-        <v>6766717</v>
+        <v>6766635</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -13152,7 +13152,7 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>127723094</v>
+        <v>127723140</v>
       </c>
       <c r="B128" t="n">
         <v>79020</v>
@@ -13187,10 +13187,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>443557</v>
+        <v>443370</v>
       </c>
       <c r="R128" t="n">
-        <v>6766635</v>
+        <v>6766624</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -13249,50 +13249,45 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>127722954</v>
+        <v>127723118</v>
       </c>
       <c r="B129" t="n">
-        <v>8450</v>
+        <v>79020</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
-      <c r="M129" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P129" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>443348</v>
+        <v>443519</v>
       </c>
       <c r="R129" t="n">
-        <v>6766646</v>
+        <v>6766624</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -13351,7 +13346,7 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>127722951</v>
+        <v>127722954</v>
       </c>
       <c r="B130" t="n">
         <v>8450</v>
@@ -13391,10 +13386,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>443377</v>
+        <v>443348</v>
       </c>
       <c r="R130" t="n">
-        <v>6766686</v>
+        <v>6766646</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -13453,45 +13448,50 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>127723118</v>
+        <v>127722951</v>
       </c>
       <c r="B131" t="n">
-        <v>79020</v>
+        <v>8450</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
+      <c r="M131" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P131" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>443519</v>
+        <v>443377</v>
       </c>
       <c r="R131" t="n">
-        <v>6766624</v>
+        <v>6766686</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>

--- a/artfynd/A 35484-2025 artfynd.xlsx
+++ b/artfynd/A 35484-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY138"/>
+  <dimension ref="A1:AY144"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2829,10 +2829,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127722874</v>
+        <v>127723166</v>
       </c>
       <c r="B23" t="n">
-        <v>91352</v>
+        <v>79020</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2840,21 +2840,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2864,10 +2864,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>443388</v>
+        <v>443326</v>
       </c>
       <c r="R23" t="n">
-        <v>6766675</v>
+        <v>6766711</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2926,10 +2926,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127723040</v>
+        <v>127722874</v>
       </c>
       <c r="B24" t="n">
-        <v>78779</v>
+        <v>91352</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2937,21 +2937,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>228912</v>
+        <v>5442</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2961,10 +2961,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>443377</v>
+        <v>443388</v>
       </c>
       <c r="R24" t="n">
-        <v>6766659</v>
+        <v>6766675</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3023,10 +3023,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127723039</v>
+        <v>127723112</v>
       </c>
       <c r="B25" t="n">
-        <v>78779</v>
+        <v>79020</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3034,21 +3034,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3058,10 +3058,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>443356</v>
+        <v>443476</v>
       </c>
       <c r="R25" t="n">
-        <v>6766650</v>
+        <v>6766681</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3120,45 +3120,50 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127723166</v>
+        <v>127722950</v>
       </c>
       <c r="B26" t="n">
-        <v>79020</v>
+        <v>8450</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>443326</v>
+        <v>443438</v>
       </c>
       <c r="R26" t="n">
-        <v>6766711</v>
+        <v>6766650</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3217,10 +3222,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127723181</v>
+        <v>127723040</v>
       </c>
       <c r="B27" t="n">
-        <v>79020</v>
+        <v>78779</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3228,21 +3233,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3252,10 +3257,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>443436</v>
+        <v>443377</v>
       </c>
       <c r="R27" t="n">
-        <v>6766667</v>
+        <v>6766659</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3314,10 +3319,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127723112</v>
+        <v>127723039</v>
       </c>
       <c r="B28" t="n">
-        <v>79020</v>
+        <v>78779</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3325,21 +3330,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3349,10 +3354,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>443476</v>
+        <v>443356</v>
       </c>
       <c r="R28" t="n">
-        <v>6766681</v>
+        <v>6766650</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3411,50 +3416,45 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127722950</v>
+        <v>127723181</v>
       </c>
       <c r="B29" t="n">
-        <v>8450</v>
+        <v>79020</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>443438</v>
+        <v>443436</v>
       </c>
       <c r="R29" t="n">
-        <v>6766650</v>
+        <v>6766667</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4100,7 +4100,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127723107</v>
+        <v>127723115</v>
       </c>
       <c r="B36" t="n">
         <v>79020</v>
@@ -4135,10 +4135,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>443493</v>
+        <v>443495</v>
       </c>
       <c r="R36" t="n">
-        <v>6766717</v>
+        <v>6766641</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4197,10 +4197,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127723115</v>
+        <v>127722896</v>
       </c>
       <c r="B37" t="n">
-        <v>79020</v>
+        <v>57660</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4208,34 +4208,39 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>443495</v>
+        <v>443537</v>
       </c>
       <c r="R37" t="n">
-        <v>6766641</v>
+        <v>6766699</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4294,50 +4299,45 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127722896</v>
+        <v>127722921</v>
       </c>
       <c r="B38" t="n">
-        <v>57660</v>
+        <v>97327</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100049</v>
+        <v>221945</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>443537</v>
+        <v>443330</v>
       </c>
       <c r="R38" t="n">
-        <v>6766699</v>
+        <v>6766662</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4396,50 +4396,45 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127722944</v>
+        <v>127723107</v>
       </c>
       <c r="B39" t="n">
-        <v>8450</v>
+        <v>79020</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>443488</v>
+        <v>443493</v>
       </c>
       <c r="R39" t="n">
-        <v>6766671</v>
+        <v>6766717</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4498,7 +4493,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127722928</v>
+        <v>127722944</v>
       </c>
       <c r="B40" t="n">
         <v>8450</v>
@@ -4529,7 +4524,7 @@
       <c r="I40" t="inlineStr"/>
       <c r="M40" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
@@ -4538,10 +4533,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>443559</v>
+        <v>443488</v>
       </c>
       <c r="R40" t="n">
-        <v>6766616</v>
+        <v>6766671</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4600,10 +4595,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127722921</v>
+        <v>127722928</v>
       </c>
       <c r="B41" t="n">
-        <v>97327</v>
+        <v>8450</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4611,34 +4606,39 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>221945</v>
+        <v>106545</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>443330</v>
+        <v>443559</v>
       </c>
       <c r="R41" t="n">
-        <v>6766662</v>
+        <v>6766616</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4794,7 +4794,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127723091</v>
+        <v>127723159</v>
       </c>
       <c r="B43" t="n">
         <v>79020</v>
@@ -4829,10 +4829,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>443587</v>
+        <v>443314</v>
       </c>
       <c r="R43" t="n">
-        <v>6766651</v>
+        <v>6766811</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4891,7 +4891,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>127723121</v>
+        <v>127723189</v>
       </c>
       <c r="B44" t="n">
         <v>79020</v>
@@ -4926,10 +4926,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>443558</v>
+        <v>443446</v>
       </c>
       <c r="R44" t="n">
-        <v>6766620</v>
+        <v>6766727</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4962,6 +4962,11 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Med grov gran i bäckmiljö</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -4988,10 +4993,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>127722876</v>
+        <v>127723091</v>
       </c>
       <c r="B45" t="n">
-        <v>91352</v>
+        <v>79020</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4999,21 +5004,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5023,10 +5028,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>443366</v>
+        <v>443587</v>
       </c>
       <c r="R45" t="n">
-        <v>6766661</v>
+        <v>6766651</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5085,7 +5090,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>127723159</v>
+        <v>127723121</v>
       </c>
       <c r="B46" t="n">
         <v>79020</v>
@@ -5120,10 +5125,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>443314</v>
+        <v>443558</v>
       </c>
       <c r="R46" t="n">
-        <v>6766811</v>
+        <v>6766620</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5182,10 +5187,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>127723189</v>
+        <v>127722876</v>
       </c>
       <c r="B47" t="n">
-        <v>79020</v>
+        <v>91352</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5193,21 +5198,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5217,10 +5222,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>443446</v>
+        <v>443366</v>
       </c>
       <c r="R47" t="n">
-        <v>6766727</v>
+        <v>6766661</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5253,11 +5258,6 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-08-21</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Med grov gran i bäckmiljö</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6565,7 +6565,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>127723119</v>
+        <v>127723106</v>
       </c>
       <c r="B61" t="n">
         <v>79020</v>
@@ -6600,10 +6600,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>443535</v>
+        <v>443516</v>
       </c>
       <c r="R61" t="n">
-        <v>6766639</v>
+        <v>6766720</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6662,7 +6662,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>127723167</v>
+        <v>127723188</v>
       </c>
       <c r="B62" t="n">
         <v>79020</v>
@@ -6697,10 +6697,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>443316</v>
+        <v>443454</v>
       </c>
       <c r="R62" t="n">
-        <v>6766701</v>
+        <v>6766724</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6759,7 +6759,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>127723153</v>
+        <v>127723119</v>
       </c>
       <c r="B63" t="n">
         <v>79020</v>
@@ -6794,10 +6794,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>443436</v>
+        <v>443535</v>
       </c>
       <c r="R63" t="n">
-        <v>6766648</v>
+        <v>6766639</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6856,7 +6856,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>127723106</v>
+        <v>127723167</v>
       </c>
       <c r="B64" t="n">
         <v>79020</v>
@@ -6891,10 +6891,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>443516</v>
+        <v>443316</v>
       </c>
       <c r="R64" t="n">
-        <v>6766720</v>
+        <v>6766701</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -6953,7 +6953,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>127723188</v>
+        <v>127723153</v>
       </c>
       <c r="B65" t="n">
         <v>79020</v>
@@ -6988,10 +6988,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>443454</v>
+        <v>443436</v>
       </c>
       <c r="R65" t="n">
-        <v>6766724</v>
+        <v>6766648</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7050,32 +7050,32 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>127722847</v>
+        <v>127723065</v>
       </c>
       <c r="B66" t="n">
-        <v>79052</v>
+        <v>91493</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>185</v>
+        <v>1503</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7085,10 +7085,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>443320</v>
+        <v>443425</v>
       </c>
       <c r="R66" t="n">
-        <v>6766703</v>
+        <v>6766668</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7147,32 +7147,32 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>127723065</v>
+        <v>127723150</v>
       </c>
       <c r="B67" t="n">
-        <v>91493</v>
+        <v>79020</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>1503</v>
+        <v>6425</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7182,10 +7182,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>443425</v>
+        <v>443415</v>
       </c>
       <c r="R67" t="n">
-        <v>6766668</v>
+        <v>6766603</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7244,7 +7244,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>127723158</v>
+        <v>127723177</v>
       </c>
       <c r="B68" t="n">
         <v>79020</v>
@@ -7279,10 +7279,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>443312</v>
+        <v>443397</v>
       </c>
       <c r="R68" t="n">
-        <v>6766818</v>
+        <v>6766673</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7341,10 +7341,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>127729137</v>
+        <v>127722847</v>
       </c>
       <c r="B69" t="n">
-        <v>79020</v>
+        <v>79052</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7352,34 +7352,34 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Oxeråsen S. om, Dlr</t>
+          <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>443391</v>
+        <v>443320</v>
       </c>
       <c r="R69" t="n">
-        <v>6766598</v>
+        <v>6766703</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7409,47 +7409,36 @@
           <t>2025-08-21</t>
         </is>
       </c>
-      <c r="Z69" t="inlineStr">
-        <is>
-          <t>14:00</t>
-        </is>
-      </c>
       <c r="AA69" t="inlineStr">
         <is>
           <t>2025-08-21</t>
         </is>
       </c>
-      <c r="AB69" t="inlineStr">
-        <is>
-          <t>14:00</t>
-        </is>
-      </c>
       <c r="AD69" t="b">
         <v>0</v>
       </c>
       <c r="AE69" t="b">
         <v>0</v>
       </c>
-      <c r="AF69" t="inlineStr"/>
       <c r="AG69" t="b">
         <v>0</v>
       </c>
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>127723150</v>
+        <v>127723158</v>
       </c>
       <c r="B70" t="n">
         <v>79020</v>
@@ -7484,10 +7473,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>443415</v>
+        <v>443312</v>
       </c>
       <c r="R70" t="n">
-        <v>6766603</v>
+        <v>6766818</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7546,7 +7535,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>127723177</v>
+        <v>127729137</v>
       </c>
       <c r="B71" t="n">
         <v>79020</v>
@@ -7577,14 +7566,14 @@
       <c r="I71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Oxeråsen, Dlr</t>
+          <t>Oxeråsen S. om, Dlr</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>443397</v>
+        <v>443391</v>
       </c>
       <c r="R71" t="n">
-        <v>6766673</v>
+        <v>6766598</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7614,29 +7603,40 @@
           <t>2025-08-21</t>
         </is>
       </c>
+      <c r="Z71" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
       <c r="AA71" t="inlineStr">
         <is>
           <t>2025-08-21</t>
         </is>
       </c>
+      <c r="AB71" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
       <c r="AD71" t="b">
         <v>0</v>
       </c>
       <c r="AE71" t="b">
         <v>0</v>
       </c>
+      <c r="AF71" t="inlineStr"/>
       <c r="AG71" t="b">
         <v>0</v>
       </c>
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
@@ -8726,10 +8726,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>127723178</v>
+        <v>127723570</v>
       </c>
       <c r="B83" t="n">
-        <v>79020</v>
+        <v>78687</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8737,21 +8737,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -8761,10 +8761,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>443402</v>
+        <v>443319</v>
       </c>
       <c r="R83" t="n">
-        <v>6766682</v>
+        <v>6766670</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -8823,7 +8823,7 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>127723171</v>
+        <v>127723178</v>
       </c>
       <c r="B84" t="n">
         <v>79020</v>
@@ -8858,10 +8858,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>443342</v>
+        <v>443402</v>
       </c>
       <c r="R84" t="n">
-        <v>6766650</v>
+        <v>6766682</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -8920,7 +8920,7 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>127723092</v>
+        <v>127723171</v>
       </c>
       <c r="B85" t="n">
         <v>79020</v>
@@ -8955,7 +8955,7 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>443572</v>
+        <v>443342</v>
       </c>
       <c r="R85" t="n">
         <v>6766650</v>
@@ -9017,10 +9017,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>127723570</v>
+        <v>127723541</v>
       </c>
       <c r="B86" t="n">
-        <v>78687</v>
+        <v>57663</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9028,34 +9028,39 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>353</v>
+        <v>100109</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P86" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>443319</v>
+        <v>443317</v>
       </c>
       <c r="R86" t="n">
-        <v>6766670</v>
+        <v>6766816</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9114,10 +9119,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>127723116</v>
+        <v>127722916</v>
       </c>
       <c r="B87" t="n">
-        <v>79020</v>
+        <v>57663</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9125,34 +9130,39 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P87" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>443509</v>
+        <v>443342</v>
       </c>
       <c r="R87" t="n">
-        <v>6766633</v>
+        <v>6766806</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9185,6 +9195,11 @@
       <c r="AA87" t="inlineStr">
         <is>
           <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AC87" t="inlineStr">
+        <is>
+          <t>Färska ringhack (gran), 4-5 år gamla</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9211,10 +9226,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>127723541</v>
+        <v>127722888</v>
       </c>
       <c r="B88" t="n">
-        <v>57663</v>
+        <v>57660</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9222,16 +9237,16 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
@@ -9242,7 +9257,7 @@
       <c r="I88" t="inlineStr"/>
       <c r="M88" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P88" t="inlineStr">
@@ -9251,10 +9266,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>443317</v>
+        <v>443481</v>
       </c>
       <c r="R88" t="n">
-        <v>6766816</v>
+        <v>6766676</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9313,10 +9328,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>127722916</v>
+        <v>127723092</v>
       </c>
       <c r="B89" t="n">
-        <v>57663</v>
+        <v>79020</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9324,39 +9339,34 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
-      <c r="M89" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P89" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>443342</v>
+        <v>443572</v>
       </c>
       <c r="R89" t="n">
-        <v>6766806</v>
+        <v>6766650</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9389,11 +9399,6 @@
       <c r="AA89" t="inlineStr">
         <is>
           <t>2025-08-21</t>
-        </is>
-      </c>
-      <c r="AC89" t="inlineStr">
-        <is>
-          <t>Färska ringhack (gran), 4-5 år gamla</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -9420,10 +9425,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>127722888</v>
+        <v>127723116</v>
       </c>
       <c r="B90" t="n">
-        <v>57660</v>
+        <v>79020</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9431,39 +9436,34 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
-      <c r="M90" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P90" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>443481</v>
+        <v>443509</v>
       </c>
       <c r="R90" t="n">
-        <v>6766676</v>
+        <v>6766633</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9522,10 +9522,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>127723569</v>
+        <v>127723041</v>
       </c>
       <c r="B91" t="n">
-        <v>78687</v>
+        <v>78779</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9533,21 +9533,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -9557,10 +9557,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>443332</v>
+        <v>443450</v>
       </c>
       <c r="R91" t="n">
-        <v>6766677</v>
+        <v>6766735</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10298,10 +10298,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>127723041</v>
+        <v>127723569</v>
       </c>
       <c r="B99" t="n">
-        <v>78779</v>
+        <v>78687</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10309,21 +10309,21 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -10333,10 +10333,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>443450</v>
+        <v>443332</v>
       </c>
       <c r="R99" t="n">
-        <v>6766735</v>
+        <v>6766677</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -11472,10 +11472,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>127722904</v>
+        <v>127729086</v>
       </c>
       <c r="B111" t="n">
-        <v>57663</v>
+        <v>78779</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -11483,34 +11483,34 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>100109</v>
+        <v>228912</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
       <c r="P111" t="inlineStr">
         <is>
-          <t>Oxeråsen, Dlr</t>
+          <t>Oxeråsen S. om, Dlr</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>443419</v>
+        <v>443359</v>
       </c>
       <c r="R111" t="n">
-        <v>6766676</v>
+        <v>6766650</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -11540,14 +11540,19 @@
           <t>2025-08-21</t>
         </is>
       </c>
+      <c r="Z111" t="inlineStr">
+        <is>
+          <t>13:53</t>
+        </is>
+      </c>
       <c r="AA111" t="inlineStr">
         <is>
           <t>2025-08-21</t>
         </is>
       </c>
-      <c r="AC111" t="inlineStr">
-        <is>
-          <t>Äldre ringhack (tall)</t>
+      <c r="AB111" t="inlineStr">
+        <is>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -11556,28 +11561,29 @@
       <c r="AE111" t="b">
         <v>0</v>
       </c>
+      <c r="AF111" t="inlineStr"/>
       <c r="AG111" t="b">
         <v>0</v>
       </c>
       <c r="AT111" t="inlineStr"/>
       <c r="AW111" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX111" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>127723136</v>
+        <v>127722904</v>
       </c>
       <c r="B112" t="n">
-        <v>79020</v>
+        <v>57663</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -11585,21 +11591,21 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -11609,10 +11615,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>443438</v>
+        <v>443419</v>
       </c>
       <c r="R112" t="n">
-        <v>6766628</v>
+        <v>6766676</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -11645,6 +11651,11 @@
       <c r="AA112" t="inlineStr">
         <is>
           <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AC112" t="inlineStr">
+        <is>
+          <t>Äldre ringhack (tall)</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -11671,7 +11682,7 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>127723160</v>
+        <v>127723136</v>
       </c>
       <c r="B113" t="n">
         <v>79020</v>
@@ -11706,10 +11717,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>443309</v>
+        <v>443438</v>
       </c>
       <c r="R113" t="n">
-        <v>6766785</v>
+        <v>6766628</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -11768,7 +11779,7 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>127723137</v>
+        <v>127723160</v>
       </c>
       <c r="B114" t="n">
         <v>79020</v>
@@ -11803,10 +11814,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>443418</v>
+        <v>443309</v>
       </c>
       <c r="R114" t="n">
-        <v>6766627</v>
+        <v>6766785</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -11865,7 +11876,7 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>127723172</v>
+        <v>127723137</v>
       </c>
       <c r="B115" t="n">
         <v>79020</v>
@@ -11900,10 +11911,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>443356</v>
+        <v>443418</v>
       </c>
       <c r="R115" t="n">
-        <v>6766650</v>
+        <v>6766627</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -11962,7 +11973,7 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>127723154</v>
+        <v>127723172</v>
       </c>
       <c r="B116" t="n">
         <v>79020</v>
@@ -11997,10 +12008,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>443369</v>
+        <v>443356</v>
       </c>
       <c r="R116" t="n">
-        <v>6766695</v>
+        <v>6766650</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12059,10 +12070,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>127729086</v>
+        <v>127723154</v>
       </c>
       <c r="B117" t="n">
-        <v>78779</v>
+        <v>79020</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -12070,34 +12081,34 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
       <c r="P117" t="inlineStr">
         <is>
-          <t>Oxeråsen S. om, Dlr</t>
+          <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>443359</v>
+        <v>443369</v>
       </c>
       <c r="R117" t="n">
-        <v>6766650</v>
+        <v>6766695</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12127,50 +12138,39 @@
           <t>2025-08-21</t>
         </is>
       </c>
-      <c r="Z117" t="inlineStr">
-        <is>
-          <t>13:53</t>
-        </is>
-      </c>
       <c r="AA117" t="inlineStr">
         <is>
           <t>2025-08-21</t>
         </is>
       </c>
-      <c r="AB117" t="inlineStr">
-        <is>
-          <t>13:53</t>
-        </is>
-      </c>
       <c r="AD117" t="b">
         <v>0</v>
       </c>
       <c r="AE117" t="b">
         <v>0</v>
       </c>
-      <c r="AF117" t="inlineStr"/>
       <c r="AG117" t="b">
         <v>0</v>
       </c>
       <c r="AT117" t="inlineStr"/>
       <c r="AW117" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX117" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>127723113</v>
+        <v>127722903</v>
       </c>
       <c r="B118" t="n">
-        <v>79020</v>
+        <v>57663</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12178,21 +12178,21 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -12202,10 +12202,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>443487</v>
+        <v>443382</v>
       </c>
       <c r="R118" t="n">
-        <v>6766675</v>
+        <v>6766657</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12238,6 +12238,11 @@
       <c r="AA118" t="inlineStr">
         <is>
           <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AC118" t="inlineStr">
+        <is>
+          <t>Äldre ringhack (tall)</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -12264,42 +12269,47 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>127723176</v>
+        <v>127722955</v>
       </c>
       <c r="B119" t="n">
-        <v>79020</v>
+        <v>8450</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
+      <c r="M119" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P119" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>443407</v>
+        <v>443397</v>
       </c>
       <c r="R119" t="n">
         <v>6766653</v>
@@ -12361,45 +12371,50 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>127723135</v>
+        <v>127722948</v>
       </c>
       <c r="B120" t="n">
-        <v>79020</v>
+        <v>8450</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
+      <c r="M120" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P120" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>443454</v>
+        <v>443457</v>
       </c>
       <c r="R120" t="n">
-        <v>6766614</v>
+        <v>6766613</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -12458,7 +12473,7 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>127723163</v>
+        <v>127723113</v>
       </c>
       <c r="B121" t="n">
         <v>79020</v>
@@ -12493,10 +12508,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>443332</v>
+        <v>443487</v>
       </c>
       <c r="R121" t="n">
-        <v>6766744</v>
+        <v>6766675</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -12555,10 +12570,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>127722903</v>
+        <v>127723176</v>
       </c>
       <c r="B122" t="n">
-        <v>57663</v>
+        <v>79020</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -12566,21 +12581,21 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -12590,10 +12605,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>443382</v>
+        <v>443407</v>
       </c>
       <c r="R122" t="n">
-        <v>6766657</v>
+        <v>6766653</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -12626,11 +12641,6 @@
       <c r="AA122" t="inlineStr">
         <is>
           <t>2025-08-21</t>
-        </is>
-      </c>
-      <c r="AC122" t="inlineStr">
-        <is>
-          <t>Äldre ringhack (tall)</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -12657,50 +12667,45 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>127722955</v>
+        <v>127723135</v>
       </c>
       <c r="B123" t="n">
-        <v>8450</v>
+        <v>79020</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
-      <c r="M123" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P123" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>443397</v>
+        <v>443454</v>
       </c>
       <c r="R123" t="n">
-        <v>6766653</v>
+        <v>6766614</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -12759,50 +12764,45 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>127722948</v>
+        <v>127723163</v>
       </c>
       <c r="B124" t="n">
-        <v>8450</v>
+        <v>79020</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
-      <c r="M124" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P124" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>443457</v>
+        <v>443332</v>
       </c>
       <c r="R124" t="n">
-        <v>6766613</v>
+        <v>6766744</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -14257,6 +14257,654 @@
       </c>
       <c r="AY138" t="inlineStr"/>
     </row>
+    <row r="139">
+      <c r="A139" t="n">
+        <v>127785482</v>
+      </c>
+      <c r="B139" t="n">
+        <v>79020</v>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E139" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I139" t="inlineStr"/>
+      <c r="P139" t="inlineStr">
+        <is>
+          <t>Oxeråsen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q139" t="n">
+        <v>443482</v>
+      </c>
+      <c r="R139" t="n">
+        <v>6766622</v>
+      </c>
+      <c r="S139" t="n">
+        <v>10</v>
+      </c>
+      <c r="T139" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U139" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V139" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W139" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y139" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="Z139" t="inlineStr">
+        <is>
+          <t>13:47</t>
+        </is>
+      </c>
+      <c r="AA139" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AB139" t="inlineStr">
+        <is>
+          <t>13:47</t>
+        </is>
+      </c>
+      <c r="AD139" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE139" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG139" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT139" t="inlineStr"/>
+      <c r="AW139" t="inlineStr">
+        <is>
+          <t>Jakob Bowers</t>
+        </is>
+      </c>
+      <c r="AX139" t="inlineStr">
+        <is>
+          <t>Jakob Bowers</t>
+        </is>
+      </c>
+      <c r="AY139" t="inlineStr"/>
+    </row>
+    <row r="140">
+      <c r="A140" t="n">
+        <v>127785478</v>
+      </c>
+      <c r="B140" t="n">
+        <v>79020</v>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E140" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I140" t="inlineStr"/>
+      <c r="P140" t="inlineStr">
+        <is>
+          <t>Oxeråsen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q140" t="n">
+        <v>443548</v>
+      </c>
+      <c r="R140" t="n">
+        <v>6766599</v>
+      </c>
+      <c r="S140" t="n">
+        <v>10</v>
+      </c>
+      <c r="T140" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U140" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V140" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W140" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y140" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="Z140" t="inlineStr">
+        <is>
+          <t>14:08</t>
+        </is>
+      </c>
+      <c r="AA140" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AB140" t="inlineStr">
+        <is>
+          <t>14:08</t>
+        </is>
+      </c>
+      <c r="AC140" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
+        </is>
+      </c>
+      <c r="AD140" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE140" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF140" t="inlineStr"/>
+      <c r="AG140" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT140" t="inlineStr"/>
+      <c r="AW140" t="inlineStr">
+        <is>
+          <t>Jakob Bowers</t>
+        </is>
+      </c>
+      <c r="AX140" t="inlineStr">
+        <is>
+          <t>Jakob Bowers</t>
+        </is>
+      </c>
+      <c r="AY140" t="inlineStr"/>
+    </row>
+    <row r="141">
+      <c r="A141" t="n">
+        <v>127785484</v>
+      </c>
+      <c r="B141" t="n">
+        <v>79020</v>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E141" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I141" t="inlineStr"/>
+      <c r="P141" t="inlineStr">
+        <is>
+          <t>Oxeråsen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q141" t="n">
+        <v>443359</v>
+      </c>
+      <c r="R141" t="n">
+        <v>6766692</v>
+      </c>
+      <c r="S141" t="n">
+        <v>10</v>
+      </c>
+      <c r="T141" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U141" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V141" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W141" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y141" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="Z141" t="inlineStr">
+        <is>
+          <t>13:19</t>
+        </is>
+      </c>
+      <c r="AA141" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AB141" t="inlineStr">
+        <is>
+          <t>13:19</t>
+        </is>
+      </c>
+      <c r="AD141" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE141" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG141" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT141" t="inlineStr"/>
+      <c r="AW141" t="inlineStr">
+        <is>
+          <t>Jakob Bowers</t>
+        </is>
+      </c>
+      <c r="AX141" t="inlineStr">
+        <is>
+          <t>Jakob Bowers</t>
+        </is>
+      </c>
+      <c r="AY141" t="inlineStr"/>
+    </row>
+    <row r="142">
+      <c r="A142" t="n">
+        <v>127785481</v>
+      </c>
+      <c r="B142" t="n">
+        <v>79020</v>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E142" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I142" t="inlineStr"/>
+      <c r="P142" t="inlineStr">
+        <is>
+          <t>Oxeråsen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q142" t="n">
+        <v>443474</v>
+      </c>
+      <c r="R142" t="n">
+        <v>6766608</v>
+      </c>
+      <c r="S142" t="n">
+        <v>10</v>
+      </c>
+      <c r="T142" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U142" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V142" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W142" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y142" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="Z142" t="inlineStr">
+        <is>
+          <t>13:49</t>
+        </is>
+      </c>
+      <c r="AA142" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AB142" t="inlineStr">
+        <is>
+          <t>13:49</t>
+        </is>
+      </c>
+      <c r="AD142" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE142" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG142" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT142" t="inlineStr"/>
+      <c r="AW142" t="inlineStr">
+        <is>
+          <t>Jakob Bowers</t>
+        </is>
+      </c>
+      <c r="AX142" t="inlineStr">
+        <is>
+          <t>Jakob Bowers</t>
+        </is>
+      </c>
+      <c r="AY142" t="inlineStr"/>
+    </row>
+    <row r="143">
+      <c r="A143" t="n">
+        <v>127785483</v>
+      </c>
+      <c r="B143" t="n">
+        <v>79020</v>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E143" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I143" t="inlineStr"/>
+      <c r="P143" t="inlineStr">
+        <is>
+          <t>Oxeråsen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q143" t="n">
+        <v>443409</v>
+      </c>
+      <c r="R143" t="n">
+        <v>6766675</v>
+      </c>
+      <c r="S143" t="n">
+        <v>10</v>
+      </c>
+      <c r="T143" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U143" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V143" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W143" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y143" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="Z143" t="inlineStr">
+        <is>
+          <t>13:33</t>
+        </is>
+      </c>
+      <c r="AA143" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AB143" t="inlineStr">
+        <is>
+          <t>13:33</t>
+        </is>
+      </c>
+      <c r="AD143" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE143" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG143" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT143" t="inlineStr"/>
+      <c r="AW143" t="inlineStr">
+        <is>
+          <t>Jakob Bowers</t>
+        </is>
+      </c>
+      <c r="AX143" t="inlineStr">
+        <is>
+          <t>Jakob Bowers</t>
+        </is>
+      </c>
+      <c r="AY143" t="inlineStr"/>
+    </row>
+    <row r="144">
+      <c r="A144" t="n">
+        <v>127785472</v>
+      </c>
+      <c r="B144" t="n">
+        <v>91352</v>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E144" t="n">
+        <v>5442</v>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>Tallticka</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>Porodaedalea pini</t>
+        </is>
+      </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I144" t="inlineStr"/>
+      <c r="P144" t="inlineStr">
+        <is>
+          <t>Oxeråsen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q144" t="n">
+        <v>443343</v>
+      </c>
+      <c r="R144" t="n">
+        <v>6766751</v>
+      </c>
+      <c r="S144" t="n">
+        <v>10</v>
+      </c>
+      <c r="T144" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U144" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V144" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W144" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y144" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="Z144" t="inlineStr">
+        <is>
+          <t>13:08</t>
+        </is>
+      </c>
+      <c r="AA144" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AB144" t="inlineStr">
+        <is>
+          <t>13:08</t>
+        </is>
+      </c>
+      <c r="AD144" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE144" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG144" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT144" t="inlineStr"/>
+      <c r="AW144" t="inlineStr">
+        <is>
+          <t>Jakob Bowers</t>
+        </is>
+      </c>
+      <c r="AX144" t="inlineStr">
+        <is>
+          <t>Jakob Bowers</t>
+        </is>
+      </c>
+      <c r="AY144" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 35484-2025 artfynd.xlsx
+++ b/artfynd/A 35484-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY144"/>
+  <dimension ref="A1:AY148"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127621301</v>
+        <v>127621346</v>
       </c>
       <c r="B2" t="n">
-        <v>79020</v>
+        <v>78778</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -713,10 +713,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>443316</v>
+        <v>443330</v>
       </c>
       <c r="R2" t="n">
-        <v>6766797</v>
+        <v>6766724</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -749,11 +749,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-08-14</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>På 4 tallstammar</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -781,10 +776,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127621346</v>
+        <v>127621301</v>
       </c>
       <c r="B3" t="n">
-        <v>78778</v>
+        <v>79020</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -792,21 +787,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -819,10 +814,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>443330</v>
+        <v>443316</v>
       </c>
       <c r="R3" t="n">
-        <v>6766724</v>
+        <v>6766797</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -855,6 +850,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>På 4 tallstammar</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -1839,7 +1839,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127723164</v>
+        <v>127723151</v>
       </c>
       <c r="B13" t="n">
         <v>79020</v>
@@ -1874,10 +1874,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>443329</v>
+        <v>443430</v>
       </c>
       <c r="R13" t="n">
-        <v>6766739</v>
+        <v>6766608</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1936,7 +1936,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127723151</v>
+        <v>127723117</v>
       </c>
       <c r="B14" t="n">
         <v>79020</v>
@@ -1971,10 +1971,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>443430</v>
+        <v>443514</v>
       </c>
       <c r="R14" t="n">
-        <v>6766608</v>
+        <v>6766630</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2033,7 +2033,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127723117</v>
+        <v>127723164</v>
       </c>
       <c r="B15" t="n">
         <v>79020</v>
@@ -2068,10 +2068,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>443514</v>
+        <v>443329</v>
       </c>
       <c r="R15" t="n">
-        <v>6766630</v>
+        <v>6766739</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2431,45 +2431,50 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127723093</v>
+        <v>127722942</v>
       </c>
       <c r="B19" t="n">
-        <v>79020</v>
+        <v>8450</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>443572</v>
+        <v>443542</v>
       </c>
       <c r="R19" t="n">
-        <v>6766645</v>
+        <v>6766699</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2528,7 +2533,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127723099</v>
+        <v>127723093</v>
       </c>
       <c r="B20" t="n">
         <v>79020</v>
@@ -2563,10 +2568,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>443567</v>
+        <v>443572</v>
       </c>
       <c r="R20" t="n">
-        <v>6766695</v>
+        <v>6766645</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2625,50 +2630,45 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127722947</v>
+        <v>127723099</v>
       </c>
       <c r="B21" t="n">
-        <v>8450</v>
+        <v>79020</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>443486</v>
+        <v>443567</v>
       </c>
       <c r="R21" t="n">
-        <v>6766604</v>
+        <v>6766695</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2727,7 +2727,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127722942</v>
+        <v>127722947</v>
       </c>
       <c r="B22" t="n">
         <v>8450</v>
@@ -2767,10 +2767,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>443542</v>
+        <v>443486</v>
       </c>
       <c r="R22" t="n">
-        <v>6766699</v>
+        <v>6766604</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2829,7 +2829,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127723166</v>
+        <v>127723112</v>
       </c>
       <c r="B23" t="n">
         <v>79020</v>
@@ -2864,10 +2864,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>443326</v>
+        <v>443476</v>
       </c>
       <c r="R23" t="n">
-        <v>6766711</v>
+        <v>6766681</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2926,10 +2926,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127722874</v>
+        <v>127723166</v>
       </c>
       <c r="B24" t="n">
-        <v>91352</v>
+        <v>79020</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2937,21 +2937,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2961,10 +2961,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>443388</v>
+        <v>443326</v>
       </c>
       <c r="R24" t="n">
-        <v>6766675</v>
+        <v>6766711</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3023,45 +3023,50 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127723112</v>
+        <v>127722950</v>
       </c>
       <c r="B25" t="n">
-        <v>79020</v>
+        <v>8450</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>443476</v>
+        <v>443438</v>
       </c>
       <c r="R25" t="n">
-        <v>6766681</v>
+        <v>6766650</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3120,47 +3125,42 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127722950</v>
+        <v>127723039</v>
       </c>
       <c r="B26" t="n">
-        <v>8450</v>
+        <v>78779</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>106545</v>
+        <v>228912</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>443438</v>
+        <v>443356</v>
       </c>
       <c r="R26" t="n">
         <v>6766650</v>
@@ -3222,10 +3222,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127723040</v>
+        <v>127722874</v>
       </c>
       <c r="B27" t="n">
-        <v>78779</v>
+        <v>91352</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3233,21 +3233,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>228912</v>
+        <v>5442</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3257,10 +3257,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>443377</v>
+        <v>443388</v>
       </c>
       <c r="R27" t="n">
-        <v>6766659</v>
+        <v>6766675</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3319,10 +3319,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127723039</v>
+        <v>127723181</v>
       </c>
       <c r="B28" t="n">
-        <v>78779</v>
+        <v>79020</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3330,21 +3330,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3354,10 +3354,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>443356</v>
+        <v>443436</v>
       </c>
       <c r="R28" t="n">
-        <v>6766650</v>
+        <v>6766667</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3416,10 +3416,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127723181</v>
+        <v>127723040</v>
       </c>
       <c r="B29" t="n">
-        <v>79020</v>
+        <v>78779</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3427,21 +3427,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3451,10 +3451,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>443436</v>
+        <v>443377</v>
       </c>
       <c r="R29" t="n">
-        <v>6766667</v>
+        <v>6766659</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3513,10 +3513,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127723152</v>
+        <v>127722875</v>
       </c>
       <c r="B30" t="n">
-        <v>79020</v>
+        <v>91352</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3524,21 +3524,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3548,10 +3548,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>443424</v>
+        <v>443312</v>
       </c>
       <c r="R30" t="n">
-        <v>6766627</v>
+        <v>6766713</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3707,50 +3707,45 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127722945</v>
+        <v>127723152</v>
       </c>
       <c r="B32" t="n">
-        <v>8450</v>
+        <v>79020</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>443568</v>
+        <v>443424</v>
       </c>
       <c r="R32" t="n">
-        <v>6766605</v>
+        <v>6766627</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3809,45 +3804,50 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127722875</v>
+        <v>127722945</v>
       </c>
       <c r="B33" t="n">
-        <v>91352</v>
+        <v>8450</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>5442</v>
+        <v>106545</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>443312</v>
+        <v>443568</v>
       </c>
       <c r="R33" t="n">
-        <v>6766713</v>
+        <v>6766605</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3906,7 +3906,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>127723109</v>
+        <v>127723169</v>
       </c>
       <c r="B34" t="n">
         <v>79020</v>
@@ -3941,10 +3941,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>443482</v>
+        <v>443321</v>
       </c>
       <c r="R34" t="n">
-        <v>6766716</v>
+        <v>6766706</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4003,10 +4003,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127723169</v>
+        <v>127722896</v>
       </c>
       <c r="B35" t="n">
-        <v>79020</v>
+        <v>57660</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4014,34 +4014,39 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>443321</v>
+        <v>443537</v>
       </c>
       <c r="R35" t="n">
-        <v>6766706</v>
+        <v>6766699</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4100,45 +4105,50 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127723115</v>
+        <v>127722944</v>
       </c>
       <c r="B36" t="n">
-        <v>79020</v>
+        <v>8450</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>443495</v>
+        <v>443488</v>
       </c>
       <c r="R36" t="n">
-        <v>6766641</v>
+        <v>6766671</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4197,38 +4207,38 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127722896</v>
+        <v>127722928</v>
       </c>
       <c r="B37" t="n">
-        <v>57660</v>
+        <v>8450</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="M37" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
@@ -4237,10 +4247,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>443537</v>
+        <v>443559</v>
       </c>
       <c r="R37" t="n">
-        <v>6766699</v>
+        <v>6766616</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4299,32 +4309,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127722921</v>
+        <v>127723115</v>
       </c>
       <c r="B38" t="n">
-        <v>97327</v>
+        <v>79020</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4334,10 +4344,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>443330</v>
+        <v>443495</v>
       </c>
       <c r="R38" t="n">
-        <v>6766662</v>
+        <v>6766641</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4493,50 +4503,45 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127722944</v>
+        <v>127723109</v>
       </c>
       <c r="B40" t="n">
-        <v>8450</v>
+        <v>79020</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>443488</v>
+        <v>443482</v>
       </c>
       <c r="R40" t="n">
-        <v>6766671</v>
+        <v>6766716</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4595,10 +4600,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127722928</v>
+        <v>127722921</v>
       </c>
       <c r="B41" t="n">
-        <v>8450</v>
+        <v>97327</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4606,39 +4611,34 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>106545</v>
+        <v>221945</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>443559</v>
+        <v>443330</v>
       </c>
       <c r="R41" t="n">
-        <v>6766616</v>
+        <v>6766662</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4697,32 +4697,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>127723064</v>
+        <v>127722876</v>
       </c>
       <c r="B42" t="n">
-        <v>91493</v>
+        <v>91352</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1503</v>
+        <v>5442</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4732,10 +4732,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>443329</v>
+        <v>443366</v>
       </c>
       <c r="R42" t="n">
-        <v>6766670</v>
+        <v>6766661</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4794,32 +4794,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127723159</v>
+        <v>127723064</v>
       </c>
       <c r="B43" t="n">
-        <v>79020</v>
+        <v>91493</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>1503</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4829,10 +4829,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>443314</v>
+        <v>443329</v>
       </c>
       <c r="R43" t="n">
-        <v>6766811</v>
+        <v>6766670</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4891,7 +4891,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>127723189</v>
+        <v>127723091</v>
       </c>
       <c r="B44" t="n">
         <v>79020</v>
@@ -4926,10 +4926,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>443446</v>
+        <v>443587</v>
       </c>
       <c r="R44" t="n">
-        <v>6766727</v>
+        <v>6766651</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4962,11 +4962,6 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-08-21</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Med grov gran i bäckmiljö</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -4993,7 +4988,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>127723091</v>
+        <v>127723121</v>
       </c>
       <c r="B45" t="n">
         <v>79020</v>
@@ -5028,10 +5023,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>443587</v>
+        <v>443558</v>
       </c>
       <c r="R45" t="n">
-        <v>6766651</v>
+        <v>6766620</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5090,7 +5085,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>127723121</v>
+        <v>127723159</v>
       </c>
       <c r="B46" t="n">
         <v>79020</v>
@@ -5125,10 +5120,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>443558</v>
+        <v>443314</v>
       </c>
       <c r="R46" t="n">
-        <v>6766620</v>
+        <v>6766811</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5187,10 +5182,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>127722876</v>
+        <v>127723189</v>
       </c>
       <c r="B47" t="n">
-        <v>91352</v>
+        <v>79020</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5198,21 +5193,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5222,10 +5217,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>443366</v>
+        <v>443446</v>
       </c>
       <c r="R47" t="n">
-        <v>6766661</v>
+        <v>6766727</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5258,6 +5253,11 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Med grov gran i bäckmiljö</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5284,7 +5284,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>127723110</v>
+        <v>127723185</v>
       </c>
       <c r="B48" t="n">
         <v>79020</v>
@@ -5319,10 +5319,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>443479</v>
+        <v>443452</v>
       </c>
       <c r="R48" t="n">
-        <v>6766703</v>
+        <v>6766711</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5381,7 +5381,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>127723180</v>
+        <v>127723110</v>
       </c>
       <c r="B49" t="n">
         <v>79020</v>
@@ -5416,10 +5416,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>443425</v>
+        <v>443479</v>
       </c>
       <c r="R49" t="n">
-        <v>6766665</v>
+        <v>6766703</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5478,7 +5478,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>127723102</v>
+        <v>127723180</v>
       </c>
       <c r="B50" t="n">
         <v>79020</v>
@@ -5513,10 +5513,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>443556</v>
+        <v>443425</v>
       </c>
       <c r="R50" t="n">
-        <v>6766717</v>
+        <v>6766665</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5575,7 +5575,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>127723185</v>
+        <v>127723102</v>
       </c>
       <c r="B51" t="n">
         <v>79020</v>
@@ -5610,10 +5610,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>443452</v>
+        <v>443556</v>
       </c>
       <c r="R51" t="n">
-        <v>6766711</v>
+        <v>6766717</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5672,38 +5672,38 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>127722957</v>
+        <v>127722868</v>
       </c>
       <c r="B52" t="n">
-        <v>8450</v>
+        <v>57823</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>106545</v>
+        <v>103021</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="M52" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="P52" t="inlineStr">
@@ -5712,10 +5712,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>443457</v>
+        <v>443305</v>
       </c>
       <c r="R52" t="n">
-        <v>6766726</v>
+        <v>6766767</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5774,38 +5774,38 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>127722868</v>
+        <v>127722957</v>
       </c>
       <c r="B53" t="n">
-        <v>57823</v>
+        <v>8450</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>103021</v>
+        <v>106545</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="M53" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
@@ -5814,10 +5814,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>443305</v>
+        <v>443457</v>
       </c>
       <c r="R53" t="n">
-        <v>6766767</v>
+        <v>6766726</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5876,7 +5876,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>127723138</v>
+        <v>127723184</v>
       </c>
       <c r="B54" t="n">
         <v>79020</v>
@@ -5911,10 +5911,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>443391</v>
+        <v>443446</v>
       </c>
       <c r="R54" t="n">
-        <v>6766625</v>
+        <v>6766702</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5973,7 +5973,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>127723184</v>
+        <v>127723138</v>
       </c>
       <c r="B55" t="n">
         <v>79020</v>
@@ -6008,10 +6008,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>443446</v>
+        <v>443391</v>
       </c>
       <c r="R55" t="n">
-        <v>6766702</v>
+        <v>6766625</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6070,7 +6070,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>127722956</v>
+        <v>127722943</v>
       </c>
       <c r="B56" t="n">
         <v>8450</v>
@@ -6110,10 +6110,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>443454</v>
+        <v>443527</v>
       </c>
       <c r="R56" t="n">
-        <v>6766718</v>
+        <v>6766711</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6172,7 +6172,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>127722943</v>
+        <v>127722956</v>
       </c>
       <c r="B57" t="n">
         <v>8450</v>
@@ -6212,10 +6212,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>443527</v>
+        <v>443454</v>
       </c>
       <c r="R57" t="n">
-        <v>6766711</v>
+        <v>6766718</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6371,7 +6371,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>127723175</v>
+        <v>127723119</v>
       </c>
       <c r="B59" t="n">
         <v>79020</v>
@@ -6406,10 +6406,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>443387</v>
+        <v>443535</v>
       </c>
       <c r="R59" t="n">
-        <v>6766658</v>
+        <v>6766639</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6468,7 +6468,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>127723134</v>
+        <v>127723167</v>
       </c>
       <c r="B60" t="n">
         <v>79020</v>
@@ -6503,10 +6503,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>443465</v>
+        <v>443316</v>
       </c>
       <c r="R60" t="n">
-        <v>6766607</v>
+        <v>6766701</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6565,7 +6565,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>127723106</v>
+        <v>127723153</v>
       </c>
       <c r="B61" t="n">
         <v>79020</v>
@@ -6600,10 +6600,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>443516</v>
+        <v>443436</v>
       </c>
       <c r="R61" t="n">
-        <v>6766720</v>
+        <v>6766648</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6662,7 +6662,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>127723188</v>
+        <v>127723175</v>
       </c>
       <c r="B62" t="n">
         <v>79020</v>
@@ -6697,10 +6697,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>443454</v>
+        <v>443387</v>
       </c>
       <c r="R62" t="n">
-        <v>6766724</v>
+        <v>6766658</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6759,7 +6759,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>127723119</v>
+        <v>127723134</v>
       </c>
       <c r="B63" t="n">
         <v>79020</v>
@@ -6794,10 +6794,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>443535</v>
+        <v>443465</v>
       </c>
       <c r="R63" t="n">
-        <v>6766639</v>
+        <v>6766607</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6856,7 +6856,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>127723167</v>
+        <v>127723106</v>
       </c>
       <c r="B64" t="n">
         <v>79020</v>
@@ -6891,10 +6891,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>443316</v>
+        <v>443516</v>
       </c>
       <c r="R64" t="n">
-        <v>6766701</v>
+        <v>6766720</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -6953,7 +6953,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>127723153</v>
+        <v>127723188</v>
       </c>
       <c r="B65" t="n">
         <v>79020</v>
@@ -6988,10 +6988,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>443436</v>
+        <v>443454</v>
       </c>
       <c r="R65" t="n">
-        <v>6766648</v>
+        <v>6766724</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7050,45 +7050,50 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>127723065</v>
+        <v>127722941</v>
       </c>
       <c r="B66" t="n">
-        <v>91493</v>
+        <v>8450</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>1503</v>
+        <v>106545</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P66" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>443425</v>
+        <v>443557</v>
       </c>
       <c r="R66" t="n">
-        <v>6766668</v>
+        <v>6766635</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7147,10 +7152,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>127723150</v>
+        <v>127722847</v>
       </c>
       <c r="B67" t="n">
-        <v>79020</v>
+        <v>79052</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7158,21 +7163,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7182,10 +7187,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>443415</v>
+        <v>443320</v>
       </c>
       <c r="R67" t="n">
-        <v>6766603</v>
+        <v>6766703</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7244,32 +7249,32 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>127723177</v>
+        <v>127723065</v>
       </c>
       <c r="B68" t="n">
-        <v>79020</v>
+        <v>91493</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6425</v>
+        <v>1503</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7279,10 +7284,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>443397</v>
+        <v>443425</v>
       </c>
       <c r="R68" t="n">
-        <v>6766673</v>
+        <v>6766668</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7341,10 +7346,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>127722847</v>
+        <v>127723150</v>
       </c>
       <c r="B69" t="n">
-        <v>79052</v>
+        <v>79020</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7352,21 +7357,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7376,10 +7381,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>443320</v>
+        <v>443415</v>
       </c>
       <c r="R69" t="n">
-        <v>6766703</v>
+        <v>6766603</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7643,50 +7648,45 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>127722941</v>
+        <v>127723177</v>
       </c>
       <c r="B72" t="n">
-        <v>8450</v>
+        <v>79020</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
-      <c r="M72" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P72" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>443557</v>
+        <v>443397</v>
       </c>
       <c r="R72" t="n">
-        <v>6766635</v>
+        <v>6766673</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7745,10 +7745,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>127722839</v>
+        <v>127729092</v>
       </c>
       <c r="B73" t="n">
-        <v>79052</v>
+        <v>78778</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7756,34 +7756,34 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>185</v>
+        <v>6446</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Oxeråsen, Dlr</t>
+          <t>Oxeråsen S. om, Dlr</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>443554</v>
+        <v>443381</v>
       </c>
       <c r="R73" t="n">
-        <v>6766649</v>
+        <v>6766668</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7813,39 +7813,50 @@
           <t>2025-08-21</t>
         </is>
       </c>
+      <c r="Z73" t="inlineStr">
+        <is>
+          <t>13:51</t>
+        </is>
+      </c>
       <c r="AA73" t="inlineStr">
         <is>
           <t>2025-08-21</t>
         </is>
       </c>
+      <c r="AB73" t="inlineStr">
+        <is>
+          <t>13:51</t>
+        </is>
+      </c>
       <c r="AD73" t="b">
         <v>0</v>
       </c>
       <c r="AE73" t="b">
         <v>0</v>
       </c>
+      <c r="AF73" t="inlineStr"/>
       <c r="AG73" t="b">
         <v>0</v>
       </c>
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>127723090</v>
+        <v>127722839</v>
       </c>
       <c r="B74" t="n">
-        <v>79020</v>
+        <v>79052</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7853,21 +7864,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -7877,10 +7888,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>443593</v>
+        <v>443554</v>
       </c>
       <c r="R74" t="n">
-        <v>6766653</v>
+        <v>6766649</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8036,7 +8047,7 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>127723133</v>
+        <v>127723173</v>
       </c>
       <c r="B76" t="n">
         <v>79020</v>
@@ -8071,10 +8082,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>443504</v>
+        <v>443365</v>
       </c>
       <c r="R76" t="n">
-        <v>6766593</v>
+        <v>6766656</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8133,7 +8144,7 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>127723173</v>
+        <v>127723133</v>
       </c>
       <c r="B77" t="n">
         <v>79020</v>
@@ -8168,10 +8179,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>443365</v>
+        <v>443504</v>
       </c>
       <c r="R77" t="n">
-        <v>6766656</v>
+        <v>6766593</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8230,10 +8241,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>127729092</v>
+        <v>127723090</v>
       </c>
       <c r="B78" t="n">
-        <v>78778</v>
+        <v>79020</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8241,34 +8252,34 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Oxeråsen S. om, Dlr</t>
+          <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>443381</v>
+        <v>443593</v>
       </c>
       <c r="R78" t="n">
-        <v>6766668</v>
+        <v>6766653</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8298,40 +8309,29 @@
           <t>2025-08-21</t>
         </is>
       </c>
-      <c r="Z78" t="inlineStr">
-        <is>
-          <t>13:51</t>
-        </is>
-      </c>
       <c r="AA78" t="inlineStr">
         <is>
           <t>2025-08-21</t>
         </is>
       </c>
-      <c r="AB78" t="inlineStr">
-        <is>
-          <t>13:51</t>
-        </is>
-      </c>
       <c r="AD78" t="b">
         <v>0</v>
       </c>
       <c r="AE78" t="b">
         <v>0</v>
       </c>
-      <c r="AF78" t="inlineStr"/>
       <c r="AG78" t="b">
         <v>0</v>
       </c>
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
@@ -8435,7 +8435,7 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>127723104</v>
+        <v>127723120</v>
       </c>
       <c r="B80" t="n">
         <v>79020</v>
@@ -8470,10 +8470,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>443536</v>
+        <v>443548</v>
       </c>
       <c r="R80" t="n">
-        <v>6766704</v>
+        <v>6766624</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8532,7 +8532,7 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>127723120</v>
+        <v>127723104</v>
       </c>
       <c r="B81" t="n">
         <v>79020</v>
@@ -8567,10 +8567,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>443548</v>
+        <v>443536</v>
       </c>
       <c r="R81" t="n">
-        <v>6766624</v>
+        <v>6766704</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8726,10 +8726,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>127723570</v>
+        <v>127723178</v>
       </c>
       <c r="B83" t="n">
-        <v>78687</v>
+        <v>79020</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8737,21 +8737,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -8761,10 +8761,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>443319</v>
+        <v>443402</v>
       </c>
       <c r="R83" t="n">
-        <v>6766670</v>
+        <v>6766682</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -8823,7 +8823,7 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>127723178</v>
+        <v>127723171</v>
       </c>
       <c r="B84" t="n">
         <v>79020</v>
@@ -8858,10 +8858,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>443402</v>
+        <v>443342</v>
       </c>
       <c r="R84" t="n">
-        <v>6766682</v>
+        <v>6766650</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -8920,10 +8920,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>127723171</v>
+        <v>127722888</v>
       </c>
       <c r="B85" t="n">
-        <v>79020</v>
+        <v>57660</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -8931,34 +8931,39 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P85" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>443342</v>
+        <v>443481</v>
       </c>
       <c r="R85" t="n">
-        <v>6766650</v>
+        <v>6766676</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9017,7 +9022,7 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>127723541</v>
+        <v>127722916</v>
       </c>
       <c r="B86" t="n">
         <v>57663</v>
@@ -9057,10 +9062,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>443317</v>
+        <v>443342</v>
       </c>
       <c r="R86" t="n">
-        <v>6766816</v>
+        <v>6766806</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9093,6 +9098,11 @@
       <c r="AA86" t="inlineStr">
         <is>
           <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AC86" t="inlineStr">
+        <is>
+          <t>Färska ringhack (gran), 4-5 år gamla</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9119,7 +9129,7 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>127722916</v>
+        <v>127723541</v>
       </c>
       <c r="B87" t="n">
         <v>57663</v>
@@ -9159,10 +9169,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>443342</v>
+        <v>443317</v>
       </c>
       <c r="R87" t="n">
-        <v>6766806</v>
+        <v>6766816</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9195,11 +9205,6 @@
       <c r="AA87" t="inlineStr">
         <is>
           <t>2025-08-21</t>
-        </is>
-      </c>
-      <c r="AC87" t="inlineStr">
-        <is>
-          <t>Färska ringhack (gran), 4-5 år gamla</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9226,10 +9231,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>127722888</v>
+        <v>127723570</v>
       </c>
       <c r="B88" t="n">
-        <v>57660</v>
+        <v>78687</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9237,39 +9242,34 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>100049</v>
+        <v>353</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
-      <c r="M88" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P88" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>443481</v>
+        <v>443319</v>
       </c>
       <c r="R88" t="n">
-        <v>6766676</v>
+        <v>6766670</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9328,7 +9328,7 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>127723092</v>
+        <v>127723116</v>
       </c>
       <c r="B89" t="n">
         <v>79020</v>
@@ -9363,10 +9363,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>443572</v>
+        <v>443509</v>
       </c>
       <c r="R89" t="n">
-        <v>6766650</v>
+        <v>6766633</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9425,7 +9425,7 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>127723116</v>
+        <v>127723092</v>
       </c>
       <c r="B90" t="n">
         <v>79020</v>
@@ -9460,10 +9460,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>443509</v>
+        <v>443572</v>
       </c>
       <c r="R90" t="n">
-        <v>6766633</v>
+        <v>6766650</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9522,10 +9522,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>127723041</v>
+        <v>127723161</v>
       </c>
       <c r="B91" t="n">
-        <v>78779</v>
+        <v>79020</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9533,21 +9533,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -9557,10 +9557,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>443450</v>
+        <v>443305</v>
       </c>
       <c r="R91" t="n">
-        <v>6766735</v>
+        <v>6766767</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9619,7 +9619,7 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>127723174</v>
+        <v>127723186</v>
       </c>
       <c r="B92" t="n">
         <v>79020</v>
@@ -9654,10 +9654,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>443378</v>
+        <v>443454</v>
       </c>
       <c r="R92" t="n">
-        <v>6766657</v>
+        <v>6766738</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9716,7 +9716,7 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>127723097</v>
+        <v>127723114</v>
       </c>
       <c r="B93" t="n">
         <v>79020</v>
@@ -9751,10 +9751,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>443561</v>
+        <v>443487</v>
       </c>
       <c r="R93" t="n">
-        <v>6766678</v>
+        <v>6766651</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -9813,7 +9813,7 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>127723105</v>
+        <v>127723097</v>
       </c>
       <c r="B94" t="n">
         <v>79020</v>
@@ -9848,10 +9848,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>443525</v>
+        <v>443561</v>
       </c>
       <c r="R94" t="n">
-        <v>6766717</v>
+        <v>6766678</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -9910,10 +9910,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>127723161</v>
+        <v>127723569</v>
       </c>
       <c r="B95" t="n">
-        <v>79020</v>
+        <v>78687</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -9921,21 +9921,21 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -9945,10 +9945,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>443305</v>
+        <v>443332</v>
       </c>
       <c r="R95" t="n">
-        <v>6766767</v>
+        <v>6766677</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10007,7 +10007,7 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>127723186</v>
+        <v>127723174</v>
       </c>
       <c r="B96" t="n">
         <v>79020</v>
@@ -10042,10 +10042,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>443454</v>
+        <v>443378</v>
       </c>
       <c r="R96" t="n">
-        <v>6766738</v>
+        <v>6766657</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10104,7 +10104,7 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>127723114</v>
+        <v>127723105</v>
       </c>
       <c r="B97" t="n">
         <v>79020</v>
@@ -10139,10 +10139,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>443487</v>
+        <v>443525</v>
       </c>
       <c r="R97" t="n">
-        <v>6766651</v>
+        <v>6766717</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10298,10 +10298,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>127723569</v>
+        <v>127723041</v>
       </c>
       <c r="B99" t="n">
-        <v>78687</v>
+        <v>78779</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10309,21 +10309,21 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -10333,10 +10333,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>443332</v>
+        <v>443450</v>
       </c>
       <c r="R99" t="n">
-        <v>6766677</v>
+        <v>6766735</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10395,10 +10395,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>127723096</v>
+        <v>127722842</v>
       </c>
       <c r="B100" t="n">
-        <v>79020</v>
+        <v>79052</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10406,21 +10406,21 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -10430,10 +10430,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>443554</v>
+        <v>443504</v>
       </c>
       <c r="R100" t="n">
-        <v>6766650</v>
+        <v>6766708</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10492,7 +10492,7 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>127723139</v>
+        <v>127723182</v>
       </c>
       <c r="B101" t="n">
         <v>79020</v>
@@ -10527,10 +10527,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>443381</v>
+        <v>443444</v>
       </c>
       <c r="R101" t="n">
-        <v>6766623</v>
+        <v>6766677</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10589,10 +10589,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>127722842</v>
+        <v>127723170</v>
       </c>
       <c r="B102" t="n">
-        <v>79052</v>
+        <v>79020</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -10600,21 +10600,21 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -10624,10 +10624,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>443504</v>
+        <v>443333</v>
       </c>
       <c r="R102" t="n">
-        <v>6766708</v>
+        <v>6766676</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -10686,7 +10686,7 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>127723098</v>
+        <v>127723183</v>
       </c>
       <c r="B103" t="n">
         <v>79020</v>
@@ -10721,10 +10721,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>443562</v>
+        <v>443441</v>
       </c>
       <c r="R103" t="n">
-        <v>6766684</v>
+        <v>6766686</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -10783,7 +10783,7 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>127723170</v>
+        <v>127723157</v>
       </c>
       <c r="B104" t="n">
         <v>79020</v>
@@ -10818,10 +10818,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>443333</v>
+        <v>443306</v>
       </c>
       <c r="R104" t="n">
-        <v>6766676</v>
+        <v>6766830</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -10880,7 +10880,7 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>127723183</v>
+        <v>127723139</v>
       </c>
       <c r="B105" t="n">
         <v>79020</v>
@@ -10915,10 +10915,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>443441</v>
+        <v>443381</v>
       </c>
       <c r="R105" t="n">
-        <v>6766686</v>
+        <v>6766623</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -10977,7 +10977,7 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>127723157</v>
+        <v>127723096</v>
       </c>
       <c r="B106" t="n">
         <v>79020</v>
@@ -11012,10 +11012,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>443306</v>
+        <v>443554</v>
       </c>
       <c r="R106" t="n">
-        <v>6766830</v>
+        <v>6766650</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11074,7 +11074,7 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>127723182</v>
+        <v>127723098</v>
       </c>
       <c r="B107" t="n">
         <v>79020</v>
@@ -11109,10 +11109,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>443444</v>
+        <v>443562</v>
       </c>
       <c r="R107" t="n">
-        <v>6766677</v>
+        <v>6766684</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11171,38 +11171,38 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>127722929</v>
+        <v>127723616</v>
       </c>
       <c r="B108" t="n">
-        <v>8450</v>
+        <v>57663</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>106545</v>
+        <v>100109</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
       <c r="M108" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>gammalt bo</t>
         </is>
       </c>
       <c r="P108" t="inlineStr">
@@ -11211,10 +11211,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>443327</v>
+        <v>443475</v>
       </c>
       <c r="R108" t="n">
-        <v>6766698</v>
+        <v>6766610</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11273,38 +11273,38 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>127723616</v>
+        <v>127722929</v>
       </c>
       <c r="B109" t="n">
-        <v>57663</v>
+        <v>8450</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>100109</v>
+        <v>106545</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
       <c r="M109" t="inlineStr">
         <is>
-          <t>gammalt bo</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P109" t="inlineStr">
@@ -11313,10 +11313,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>443475</v>
+        <v>443327</v>
       </c>
       <c r="R109" t="n">
-        <v>6766610</v>
+        <v>6766698</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11472,10 +11472,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>127729086</v>
+        <v>127723136</v>
       </c>
       <c r="B111" t="n">
-        <v>78779</v>
+        <v>79020</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -11483,34 +11483,34 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
       <c r="P111" t="inlineStr">
         <is>
-          <t>Oxeråsen S. om, Dlr</t>
+          <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>443359</v>
+        <v>443438</v>
       </c>
       <c r="R111" t="n">
-        <v>6766650</v>
+        <v>6766628</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -11540,50 +11540,39 @@
           <t>2025-08-21</t>
         </is>
       </c>
-      <c r="Z111" t="inlineStr">
-        <is>
-          <t>13:53</t>
-        </is>
-      </c>
       <c r="AA111" t="inlineStr">
         <is>
           <t>2025-08-21</t>
         </is>
       </c>
-      <c r="AB111" t="inlineStr">
-        <is>
-          <t>13:53</t>
-        </is>
-      </c>
       <c r="AD111" t="b">
         <v>0</v>
       </c>
       <c r="AE111" t="b">
         <v>0</v>
       </c>
-      <c r="AF111" t="inlineStr"/>
       <c r="AG111" t="b">
         <v>0</v>
       </c>
       <c r="AT111" t="inlineStr"/>
       <c r="AW111" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX111" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>127722904</v>
+        <v>127723154</v>
       </c>
       <c r="B112" t="n">
-        <v>57663</v>
+        <v>79020</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -11591,21 +11580,21 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -11615,10 +11604,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>443419</v>
+        <v>443369</v>
       </c>
       <c r="R112" t="n">
-        <v>6766676</v>
+        <v>6766695</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -11651,11 +11640,6 @@
       <c r="AA112" t="inlineStr">
         <is>
           <t>2025-08-21</t>
-        </is>
-      </c>
-      <c r="AC112" t="inlineStr">
-        <is>
-          <t>Äldre ringhack (tall)</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -11682,7 +11666,7 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>127723136</v>
+        <v>127723137</v>
       </c>
       <c r="B113" t="n">
         <v>79020</v>
@@ -11717,10 +11701,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>443438</v>
+        <v>443418</v>
       </c>
       <c r="R113" t="n">
-        <v>6766628</v>
+        <v>6766627</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -11779,7 +11763,7 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>127723160</v>
+        <v>127723172</v>
       </c>
       <c r="B114" t="n">
         <v>79020</v>
@@ -11814,10 +11798,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>443309</v>
+        <v>443356</v>
       </c>
       <c r="R114" t="n">
-        <v>6766785</v>
+        <v>6766650</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -11876,7 +11860,7 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>127723137</v>
+        <v>127723160</v>
       </c>
       <c r="B115" t="n">
         <v>79020</v>
@@ -11911,10 +11895,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>443418</v>
+        <v>443309</v>
       </c>
       <c r="R115" t="n">
-        <v>6766627</v>
+        <v>6766785</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -11973,10 +11957,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>127723172</v>
+        <v>127722904</v>
       </c>
       <c r="B116" t="n">
-        <v>79020</v>
+        <v>57663</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -11984,21 +11968,21 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -12008,10 +11992,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>443356</v>
+        <v>443419</v>
       </c>
       <c r="R116" t="n">
-        <v>6766650</v>
+        <v>6766676</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12044,6 +12028,11 @@
       <c r="AA116" t="inlineStr">
         <is>
           <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AC116" t="inlineStr">
+        <is>
+          <t>Äldre ringhack (tall)</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -12070,10 +12059,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>127723154</v>
+        <v>127729086</v>
       </c>
       <c r="B117" t="n">
-        <v>79020</v>
+        <v>78779</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -12081,34 +12070,34 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
       <c r="P117" t="inlineStr">
         <is>
-          <t>Oxeråsen, Dlr</t>
+          <t>Oxeråsen S. om, Dlr</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>443369</v>
+        <v>443359</v>
       </c>
       <c r="R117" t="n">
-        <v>6766695</v>
+        <v>6766650</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12138,29 +12127,40 @@
           <t>2025-08-21</t>
         </is>
       </c>
+      <c r="Z117" t="inlineStr">
+        <is>
+          <t>13:53</t>
+        </is>
+      </c>
       <c r="AA117" t="inlineStr">
         <is>
           <t>2025-08-21</t>
         </is>
       </c>
+      <c r="AB117" t="inlineStr">
+        <is>
+          <t>13:53</t>
+        </is>
+      </c>
       <c r="AD117" t="b">
         <v>0</v>
       </c>
       <c r="AE117" t="b">
         <v>0</v>
       </c>
+      <c r="AF117" t="inlineStr"/>
       <c r="AG117" t="b">
         <v>0</v>
       </c>
       <c r="AT117" t="inlineStr"/>
       <c r="AW117" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX117" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
@@ -12269,47 +12269,42 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>127722955</v>
+        <v>127723176</v>
       </c>
       <c r="B119" t="n">
-        <v>8450</v>
+        <v>79020</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
-      <c r="M119" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P119" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>443397</v>
+        <v>443407</v>
       </c>
       <c r="R119" t="n">
         <v>6766653</v>
@@ -12371,50 +12366,45 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>127722948</v>
+        <v>127723113</v>
       </c>
       <c r="B120" t="n">
-        <v>8450</v>
+        <v>79020</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
-      <c r="M120" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P120" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>443457</v>
+        <v>443487</v>
       </c>
       <c r="R120" t="n">
-        <v>6766613</v>
+        <v>6766675</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -12473,7 +12463,7 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>127723113</v>
+        <v>127723163</v>
       </c>
       <c r="B121" t="n">
         <v>79020</v>
@@ -12508,10 +12498,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>443487</v>
+        <v>443332</v>
       </c>
       <c r="R121" t="n">
-        <v>6766675</v>
+        <v>6766744</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -12570,7 +12560,7 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>127723176</v>
+        <v>127723135</v>
       </c>
       <c r="B122" t="n">
         <v>79020</v>
@@ -12605,10 +12595,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>443407</v>
+        <v>443454</v>
       </c>
       <c r="R122" t="n">
-        <v>6766653</v>
+        <v>6766614</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -12667,45 +12657,50 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>127723135</v>
+        <v>127722955</v>
       </c>
       <c r="B123" t="n">
-        <v>79020</v>
+        <v>8450</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
+      <c r="M123" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P123" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>443454</v>
+        <v>443397</v>
       </c>
       <c r="R123" t="n">
-        <v>6766614</v>
+        <v>6766653</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -12764,45 +12759,50 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>127723163</v>
+        <v>127722948</v>
       </c>
       <c r="B124" t="n">
-        <v>79020</v>
+        <v>8450</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
+      <c r="M124" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P124" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>443332</v>
+        <v>443457</v>
       </c>
       <c r="R124" t="n">
-        <v>6766744</v>
+        <v>6766613</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -12958,7 +12958,7 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>127723165</v>
+        <v>127723094</v>
       </c>
       <c r="B126" t="n">
         <v>79020</v>
@@ -12993,10 +12993,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>443327</v>
+        <v>443557</v>
       </c>
       <c r="R126" t="n">
-        <v>6766717</v>
+        <v>6766635</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -13055,7 +13055,7 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>127723094</v>
+        <v>127723118</v>
       </c>
       <c r="B127" t="n">
         <v>79020</v>
@@ -13090,10 +13090,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>443557</v>
+        <v>443519</v>
       </c>
       <c r="R127" t="n">
-        <v>6766635</v>
+        <v>6766624</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -13249,7 +13249,7 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>127723118</v>
+        <v>127723165</v>
       </c>
       <c r="B129" t="n">
         <v>79020</v>
@@ -13284,10 +13284,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>443519</v>
+        <v>443327</v>
       </c>
       <c r="R129" t="n">
-        <v>6766624</v>
+        <v>6766717</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -14905,6 +14905,422 @@
       </c>
       <c r="AY144" t="inlineStr"/>
     </row>
+    <row r="145">
+      <c r="A145" t="n">
+        <v>127795289</v>
+      </c>
+      <c r="B145" t="n">
+        <v>8450</v>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E145" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I145" t="inlineStr"/>
+      <c r="J145" t="inlineStr"/>
+      <c r="K145" t="inlineStr"/>
+      <c r="L145" t="inlineStr"/>
+      <c r="M145" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N145" t="inlineStr"/>
+      <c r="P145" t="inlineStr">
+        <is>
+          <t>Oxeråsen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q145" t="n">
+        <v>443331</v>
+      </c>
+      <c r="R145" t="n">
+        <v>6766805</v>
+      </c>
+      <c r="S145" t="n">
+        <v>50</v>
+      </c>
+      <c r="T145" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U145" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V145" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W145" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y145" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AA145" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AD145" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE145" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF145" t="inlineStr"/>
+      <c r="AG145" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT145" t="inlineStr"/>
+      <c r="AW145" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AX145" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AY145" t="inlineStr"/>
+    </row>
+    <row r="146">
+      <c r="A146" t="n">
+        <v>127795299</v>
+      </c>
+      <c r="B146" t="n">
+        <v>78778</v>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E146" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I146" t="inlineStr"/>
+      <c r="J146" t="inlineStr"/>
+      <c r="K146" t="inlineStr"/>
+      <c r="N146" t="inlineStr"/>
+      <c r="P146" t="inlineStr">
+        <is>
+          <t>Oxeråsen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q146" t="n">
+        <v>443322</v>
+      </c>
+      <c r="R146" t="n">
+        <v>6766753</v>
+      </c>
+      <c r="S146" t="n">
+        <v>50</v>
+      </c>
+      <c r="T146" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U146" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V146" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W146" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y146" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AA146" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AD146" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE146" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF146" t="inlineStr"/>
+      <c r="AG146" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT146" t="inlineStr"/>
+      <c r="AW146" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AX146" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AY146" t="inlineStr"/>
+    </row>
+    <row r="147">
+      <c r="A147" t="n">
+        <v>127795339</v>
+      </c>
+      <c r="B147" t="n">
+        <v>79020</v>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E147" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I147" t="inlineStr"/>
+      <c r="J147" t="inlineStr"/>
+      <c r="K147" t="inlineStr"/>
+      <c r="N147" t="inlineStr"/>
+      <c r="P147" t="inlineStr">
+        <is>
+          <t>Oxeråsen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q147" t="n">
+        <v>443592</v>
+      </c>
+      <c r="R147" t="n">
+        <v>6766673</v>
+      </c>
+      <c r="S147" t="n">
+        <v>50</v>
+      </c>
+      <c r="T147" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U147" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V147" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W147" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y147" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AA147" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AD147" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE147" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF147" t="inlineStr"/>
+      <c r="AG147" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT147" t="inlineStr"/>
+      <c r="AW147" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AX147" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AY147" t="inlineStr"/>
+    </row>
+    <row r="148">
+      <c r="A148" t="n">
+        <v>127795321</v>
+      </c>
+      <c r="B148" t="n">
+        <v>8450</v>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E148" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I148" t="inlineStr"/>
+      <c r="J148" t="inlineStr"/>
+      <c r="K148" t="inlineStr"/>
+      <c r="L148" t="inlineStr"/>
+      <c r="M148" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N148" t="inlineStr"/>
+      <c r="P148" t="inlineStr">
+        <is>
+          <t>Oxeråsen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q148" t="n">
+        <v>443411</v>
+      </c>
+      <c r="R148" t="n">
+        <v>6766588</v>
+      </c>
+      <c r="S148" t="n">
+        <v>50</v>
+      </c>
+      <c r="T148" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U148" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V148" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W148" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y148" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AA148" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AD148" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE148" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF148" t="inlineStr"/>
+      <c r="AG148" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT148" t="inlineStr"/>
+      <c r="AW148" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AX148" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AY148" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 35484-2025 artfynd.xlsx
+++ b/artfynd/A 35484-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127621346</v>
+        <v>127621301</v>
       </c>
       <c r="B2" t="n">
-        <v>78778</v>
+        <v>79020</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -713,10 +713,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>443330</v>
+        <v>443316</v>
       </c>
       <c r="R2" t="n">
-        <v>6766724</v>
+        <v>6766797</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -749,6 +749,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>På 4 tallstammar</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -776,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127621301</v>
+        <v>127621346</v>
       </c>
       <c r="B3" t="n">
-        <v>79020</v>
+        <v>78778</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -787,21 +792,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -814,10 +819,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>443316</v>
+        <v>443330</v>
       </c>
       <c r="R3" t="n">
-        <v>6766797</v>
+        <v>6766724</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -850,11 +855,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-08-14</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>På 4 tallstammar</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -1839,7 +1839,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127723151</v>
+        <v>127723164</v>
       </c>
       <c r="B13" t="n">
         <v>79020</v>
@@ -1874,10 +1874,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>443430</v>
+        <v>443329</v>
       </c>
       <c r="R13" t="n">
-        <v>6766608</v>
+        <v>6766739</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2033,7 +2033,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127723164</v>
+        <v>127723151</v>
       </c>
       <c r="B15" t="n">
         <v>79020</v>
@@ -2068,10 +2068,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>443329</v>
+        <v>443430</v>
       </c>
       <c r="R15" t="n">
-        <v>6766739</v>
+        <v>6766608</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2431,50 +2431,45 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127722942</v>
+        <v>127723093</v>
       </c>
       <c r="B19" t="n">
-        <v>8450</v>
+        <v>79020</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>443542</v>
+        <v>443572</v>
       </c>
       <c r="R19" t="n">
-        <v>6766699</v>
+        <v>6766645</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2533,7 +2528,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127723093</v>
+        <v>127723099</v>
       </c>
       <c r="B20" t="n">
         <v>79020</v>
@@ -2568,10 +2563,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>443572</v>
+        <v>443567</v>
       </c>
       <c r="R20" t="n">
-        <v>6766645</v>
+        <v>6766695</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2630,45 +2625,50 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127723099</v>
+        <v>127722947</v>
       </c>
       <c r="B21" t="n">
-        <v>79020</v>
+        <v>8450</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>443567</v>
+        <v>443486</v>
       </c>
       <c r="R21" t="n">
-        <v>6766695</v>
+        <v>6766604</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2727,7 +2727,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127722947</v>
+        <v>127722942</v>
       </c>
       <c r="B22" t="n">
         <v>8450</v>
@@ -2767,10 +2767,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>443486</v>
+        <v>443542</v>
       </c>
       <c r="R22" t="n">
-        <v>6766604</v>
+        <v>6766699</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2829,10 +2829,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127723112</v>
+        <v>127723040</v>
       </c>
       <c r="B23" t="n">
-        <v>79020</v>
+        <v>78779</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2840,21 +2840,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2864,10 +2864,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>443476</v>
+        <v>443377</v>
       </c>
       <c r="R23" t="n">
-        <v>6766681</v>
+        <v>6766659</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2926,10 +2926,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127723166</v>
+        <v>127723039</v>
       </c>
       <c r="B24" t="n">
-        <v>79020</v>
+        <v>78779</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2937,21 +2937,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2961,10 +2961,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>443326</v>
+        <v>443356</v>
       </c>
       <c r="R24" t="n">
-        <v>6766711</v>
+        <v>6766650</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3125,10 +3125,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127723039</v>
+        <v>127723112</v>
       </c>
       <c r="B26" t="n">
-        <v>78779</v>
+        <v>79020</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3136,21 +3136,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3160,10 +3160,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>443356</v>
+        <v>443476</v>
       </c>
       <c r="R26" t="n">
-        <v>6766650</v>
+        <v>6766681</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3222,10 +3222,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127722874</v>
+        <v>127723166</v>
       </c>
       <c r="B27" t="n">
-        <v>91352</v>
+        <v>79020</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3233,21 +3233,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3257,10 +3257,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>443388</v>
+        <v>443326</v>
       </c>
       <c r="R27" t="n">
-        <v>6766675</v>
+        <v>6766711</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3416,10 +3416,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127723040</v>
+        <v>127722874</v>
       </c>
       <c r="B29" t="n">
-        <v>78779</v>
+        <v>91358</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3427,21 +3427,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>228912</v>
+        <v>5442</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3451,10 +3451,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>443377</v>
+        <v>443388</v>
       </c>
       <c r="R29" t="n">
-        <v>6766659</v>
+        <v>6766675</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3513,10 +3513,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127722875</v>
+        <v>127723152</v>
       </c>
       <c r="B30" t="n">
-        <v>91352</v>
+        <v>79020</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3524,21 +3524,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3548,10 +3548,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>443312</v>
+        <v>443424</v>
       </c>
       <c r="R30" t="n">
-        <v>6766713</v>
+        <v>6766627</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3707,10 +3707,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127723152</v>
+        <v>127722875</v>
       </c>
       <c r="B32" t="n">
-        <v>79020</v>
+        <v>91358</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3718,21 +3718,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3742,10 +3742,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>443424</v>
+        <v>443312</v>
       </c>
       <c r="R32" t="n">
-        <v>6766627</v>
+        <v>6766713</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3906,7 +3906,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>127723169</v>
+        <v>127723107</v>
       </c>
       <c r="B34" t="n">
         <v>79020</v>
@@ -3941,10 +3941,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>443321</v>
+        <v>443493</v>
       </c>
       <c r="R34" t="n">
-        <v>6766706</v>
+        <v>6766717</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4003,10 +4003,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127722896</v>
+        <v>127723109</v>
       </c>
       <c r="B35" t="n">
-        <v>57660</v>
+        <v>79020</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4014,39 +4014,34 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>443537</v>
+        <v>443482</v>
       </c>
       <c r="R35" t="n">
-        <v>6766699</v>
+        <v>6766716</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4105,50 +4100,45 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127722944</v>
+        <v>127723169</v>
       </c>
       <c r="B36" t="n">
-        <v>8450</v>
+        <v>79020</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>443488</v>
+        <v>443321</v>
       </c>
       <c r="R36" t="n">
-        <v>6766671</v>
+        <v>6766706</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4207,50 +4197,45 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127722928</v>
+        <v>127723115</v>
       </c>
       <c r="B37" t="n">
-        <v>8450</v>
+        <v>79020</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>443559</v>
+        <v>443495</v>
       </c>
       <c r="R37" t="n">
-        <v>6766616</v>
+        <v>6766641</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4309,10 +4294,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127723115</v>
+        <v>127722896</v>
       </c>
       <c r="B38" t="n">
-        <v>79020</v>
+        <v>57660</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4320,34 +4305,39 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>443495</v>
+        <v>443537</v>
       </c>
       <c r="R38" t="n">
-        <v>6766641</v>
+        <v>6766699</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4406,45 +4396,50 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127723107</v>
+        <v>127722944</v>
       </c>
       <c r="B39" t="n">
-        <v>79020</v>
+        <v>8450</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>443493</v>
+        <v>443488</v>
       </c>
       <c r="R39" t="n">
-        <v>6766717</v>
+        <v>6766671</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4503,45 +4498,50 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127723109</v>
+        <v>127722928</v>
       </c>
       <c r="B40" t="n">
-        <v>79020</v>
+        <v>8450</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>443482</v>
+        <v>443559</v>
       </c>
       <c r="R40" t="n">
-        <v>6766716</v>
+        <v>6766616</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4603,7 +4603,7 @@
         <v>127722921</v>
       </c>
       <c r="B41" t="n">
-        <v>97327</v>
+        <v>97333</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4700,7 +4700,7 @@
         <v>127722876</v>
       </c>
       <c r="B42" t="n">
-        <v>91352</v>
+        <v>91358</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4797,7 +4797,7 @@
         <v>127723064</v>
       </c>
       <c r="B43" t="n">
-        <v>91493</v>
+        <v>91499</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4988,7 +4988,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>127723121</v>
+        <v>127723159</v>
       </c>
       <c r="B45" t="n">
         <v>79020</v>
@@ -5023,10 +5023,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>443558</v>
+        <v>443314</v>
       </c>
       <c r="R45" t="n">
-        <v>6766620</v>
+        <v>6766811</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5085,7 +5085,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>127723159</v>
+        <v>127723189</v>
       </c>
       <c r="B46" t="n">
         <v>79020</v>
@@ -5120,10 +5120,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>443314</v>
+        <v>443446</v>
       </c>
       <c r="R46" t="n">
-        <v>6766811</v>
+        <v>6766727</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5156,6 +5156,11 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Med grov gran i bäckmiljö</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5182,7 +5187,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>127723189</v>
+        <v>127723121</v>
       </c>
       <c r="B47" t="n">
         <v>79020</v>
@@ -5217,10 +5222,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>443446</v>
+        <v>443558</v>
       </c>
       <c r="R47" t="n">
-        <v>6766727</v>
+        <v>6766620</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5253,11 +5258,6 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-08-21</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Med grov gran i bäckmiljö</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5284,7 +5284,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>127723185</v>
+        <v>127723180</v>
       </c>
       <c r="B48" t="n">
         <v>79020</v>
@@ -5319,10 +5319,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>443452</v>
+        <v>443425</v>
       </c>
       <c r="R48" t="n">
-        <v>6766711</v>
+        <v>6766665</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5381,7 +5381,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>127723110</v>
+        <v>127723102</v>
       </c>
       <c r="B49" t="n">
         <v>79020</v>
@@ -5416,10 +5416,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>443479</v>
+        <v>443556</v>
       </c>
       <c r="R49" t="n">
-        <v>6766703</v>
+        <v>6766717</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5478,7 +5478,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>127723180</v>
+        <v>127723185</v>
       </c>
       <c r="B50" t="n">
         <v>79020</v>
@@ -5513,10 +5513,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>443425</v>
+        <v>443452</v>
       </c>
       <c r="R50" t="n">
-        <v>6766665</v>
+        <v>6766711</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5575,7 +5575,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>127723102</v>
+        <v>127723110</v>
       </c>
       <c r="B51" t="n">
         <v>79020</v>
@@ -5610,10 +5610,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>443556</v>
+        <v>443479</v>
       </c>
       <c r="R51" t="n">
-        <v>6766717</v>
+        <v>6766703</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5973,45 +5973,50 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>127723138</v>
+        <v>127722943</v>
       </c>
       <c r="B55" t="n">
-        <v>79020</v>
+        <v>8450</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>443391</v>
+        <v>443527</v>
       </c>
       <c r="R55" t="n">
-        <v>6766625</v>
+        <v>6766711</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6070,7 +6075,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>127722943</v>
+        <v>127722956</v>
       </c>
       <c r="B56" t="n">
         <v>8450</v>
@@ -6110,10 +6115,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>443527</v>
+        <v>443454</v>
       </c>
       <c r="R56" t="n">
-        <v>6766711</v>
+        <v>6766718</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6172,50 +6177,45 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>127722956</v>
+        <v>127723138</v>
       </c>
       <c r="B57" t="n">
-        <v>8450</v>
+        <v>79020</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P57" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>443454</v>
+        <v>443391</v>
       </c>
       <c r="R57" t="n">
-        <v>6766718</v>
+        <v>6766625</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6274,10 +6274,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>127722841</v>
+        <v>127723167</v>
       </c>
       <c r="B58" t="n">
-        <v>79052</v>
+        <v>79020</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6285,21 +6285,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6309,10 +6309,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>443568</v>
+        <v>443316</v>
       </c>
       <c r="R58" t="n">
-        <v>6766695</v>
+        <v>6766701</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6371,7 +6371,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>127723119</v>
+        <v>127723153</v>
       </c>
       <c r="B59" t="n">
         <v>79020</v>
@@ -6406,10 +6406,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>443535</v>
+        <v>443436</v>
       </c>
       <c r="R59" t="n">
-        <v>6766639</v>
+        <v>6766648</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6468,7 +6468,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>127723167</v>
+        <v>127723119</v>
       </c>
       <c r="B60" t="n">
         <v>79020</v>
@@ -6503,10 +6503,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>443316</v>
+        <v>443535</v>
       </c>
       <c r="R60" t="n">
-        <v>6766701</v>
+        <v>6766639</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6565,7 +6565,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>127723153</v>
+        <v>127723106</v>
       </c>
       <c r="B61" t="n">
         <v>79020</v>
@@ -6600,10 +6600,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>443436</v>
+        <v>443516</v>
       </c>
       <c r="R61" t="n">
-        <v>6766648</v>
+        <v>6766720</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6662,7 +6662,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>127723175</v>
+        <v>127723188</v>
       </c>
       <c r="B62" t="n">
         <v>79020</v>
@@ -6697,10 +6697,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>443387</v>
+        <v>443454</v>
       </c>
       <c r="R62" t="n">
-        <v>6766658</v>
+        <v>6766724</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6759,7 +6759,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>127723134</v>
+        <v>127723175</v>
       </c>
       <c r="B63" t="n">
         <v>79020</v>
@@ -6794,10 +6794,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>443465</v>
+        <v>443387</v>
       </c>
       <c r="R63" t="n">
-        <v>6766607</v>
+        <v>6766658</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6856,7 +6856,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>127723106</v>
+        <v>127723134</v>
       </c>
       <c r="B64" t="n">
         <v>79020</v>
@@ -6891,10 +6891,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>443516</v>
+        <v>443465</v>
       </c>
       <c r="R64" t="n">
-        <v>6766720</v>
+        <v>6766607</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -6953,10 +6953,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>127723188</v>
+        <v>127722841</v>
       </c>
       <c r="B65" t="n">
-        <v>79020</v>
+        <v>79052</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6964,21 +6964,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -6988,10 +6988,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>443454</v>
+        <v>443568</v>
       </c>
       <c r="R65" t="n">
-        <v>6766724</v>
+        <v>6766695</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7050,50 +7050,45 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>127722941</v>
+        <v>127723065</v>
       </c>
       <c r="B66" t="n">
-        <v>8450</v>
+        <v>91499</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>106545</v>
+        <v>1503</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
-      <c r="M66" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P66" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>443557</v>
+        <v>443425</v>
       </c>
       <c r="R66" t="n">
-        <v>6766635</v>
+        <v>6766668</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7249,32 +7244,32 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>127723065</v>
+        <v>127723177</v>
       </c>
       <c r="B68" t="n">
-        <v>91493</v>
+        <v>79020</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>1503</v>
+        <v>6425</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7284,10 +7279,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>443425</v>
+        <v>443397</v>
       </c>
       <c r="R68" t="n">
-        <v>6766668</v>
+        <v>6766673</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7346,7 +7341,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>127723150</v>
+        <v>127729137</v>
       </c>
       <c r="B69" t="n">
         <v>79020</v>
@@ -7377,14 +7372,14 @@
       <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Oxeråsen, Dlr</t>
+          <t>Oxeråsen S. om, Dlr</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>443415</v>
+        <v>443391</v>
       </c>
       <c r="R69" t="n">
-        <v>6766603</v>
+        <v>6766598</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7414,29 +7409,40 @@
           <t>2025-08-21</t>
         </is>
       </c>
+      <c r="Z69" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
       <c r="AA69" t="inlineStr">
         <is>
           <t>2025-08-21</t>
         </is>
       </c>
+      <c r="AB69" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
       <c r="AD69" t="b">
         <v>0</v>
       </c>
       <c r="AE69" t="b">
         <v>0</v>
       </c>
+      <c r="AF69" t="inlineStr"/>
       <c r="AG69" t="b">
         <v>0</v>
       </c>
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
@@ -7540,7 +7546,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>127729137</v>
+        <v>127723150</v>
       </c>
       <c r="B71" t="n">
         <v>79020</v>
@@ -7571,14 +7577,14 @@
       <c r="I71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Oxeråsen S. om, Dlr</t>
+          <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>443391</v>
+        <v>443415</v>
       </c>
       <c r="R71" t="n">
-        <v>6766598</v>
+        <v>6766603</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7608,85 +7614,79 @@
           <t>2025-08-21</t>
         </is>
       </c>
-      <c r="Z71" t="inlineStr">
-        <is>
-          <t>14:00</t>
-        </is>
-      </c>
       <c r="AA71" t="inlineStr">
         <is>
           <t>2025-08-21</t>
         </is>
       </c>
-      <c r="AB71" t="inlineStr">
-        <is>
-          <t>14:00</t>
-        </is>
-      </c>
       <c r="AD71" t="b">
         <v>0</v>
       </c>
       <c r="AE71" t="b">
         <v>0</v>
       </c>
-      <c r="AF71" t="inlineStr"/>
       <c r="AG71" t="b">
         <v>0</v>
       </c>
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>127723177</v>
+        <v>127722941</v>
       </c>
       <c r="B72" t="n">
-        <v>79020</v>
+        <v>8450</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P72" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>443397</v>
+        <v>443557</v>
       </c>
       <c r="R72" t="n">
-        <v>6766673</v>
+        <v>6766635</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7950,7 +7950,7 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>127723108</v>
+        <v>127723133</v>
       </c>
       <c r="B75" t="n">
         <v>79020</v>
@@ -7985,10 +7985,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>443483</v>
+        <v>443504</v>
       </c>
       <c r="R75" t="n">
-        <v>6766725</v>
+        <v>6766593</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8144,7 +8144,7 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>127723133</v>
+        <v>127723108</v>
       </c>
       <c r="B77" t="n">
         <v>79020</v>
@@ -8179,10 +8179,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>443504</v>
+        <v>443483</v>
       </c>
       <c r="R77" t="n">
-        <v>6766593</v>
+        <v>6766725</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8435,7 +8435,7 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>127723120</v>
+        <v>127723156</v>
       </c>
       <c r="B80" t="n">
         <v>79020</v>
@@ -8470,10 +8470,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>443548</v>
+        <v>443346</v>
       </c>
       <c r="R80" t="n">
-        <v>6766624</v>
+        <v>6766766</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8532,7 +8532,7 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>127723104</v>
+        <v>127723120</v>
       </c>
       <c r="B81" t="n">
         <v>79020</v>
@@ -8567,10 +8567,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>443536</v>
+        <v>443548</v>
       </c>
       <c r="R81" t="n">
-        <v>6766704</v>
+        <v>6766624</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8629,7 +8629,7 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>127723156</v>
+        <v>127723104</v>
       </c>
       <c r="B82" t="n">
         <v>79020</v>
@@ -8664,10 +8664,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>443346</v>
+        <v>443536</v>
       </c>
       <c r="R82" t="n">
-        <v>6766766</v>
+        <v>6766704</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8726,10 +8726,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>127723178</v>
+        <v>127723570</v>
       </c>
       <c r="B83" t="n">
-        <v>79020</v>
+        <v>78687</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8737,21 +8737,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -8761,10 +8761,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>443402</v>
+        <v>443319</v>
       </c>
       <c r="R83" t="n">
-        <v>6766682</v>
+        <v>6766670</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -8823,7 +8823,7 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>127723171</v>
+        <v>127723116</v>
       </c>
       <c r="B84" t="n">
         <v>79020</v>
@@ -8858,10 +8858,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>443342</v>
+        <v>443509</v>
       </c>
       <c r="R84" t="n">
-        <v>6766650</v>
+        <v>6766633</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -8920,10 +8920,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>127722888</v>
+        <v>127723092</v>
       </c>
       <c r="B85" t="n">
-        <v>57660</v>
+        <v>79020</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -8931,39 +8931,34 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
-      <c r="M85" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P85" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>443481</v>
+        <v>443572</v>
       </c>
       <c r="R85" t="n">
-        <v>6766676</v>
+        <v>6766650</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9022,10 +9017,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>127722916</v>
+        <v>127723171</v>
       </c>
       <c r="B86" t="n">
-        <v>57663</v>
+        <v>79020</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9033,29 +9028,24 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
-      <c r="M86" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P86" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
@@ -9065,7 +9055,7 @@
         <v>443342</v>
       </c>
       <c r="R86" t="n">
-        <v>6766806</v>
+        <v>6766650</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9098,11 +9088,6 @@
       <c r="AA86" t="inlineStr">
         <is>
           <t>2025-08-21</t>
-        </is>
-      </c>
-      <c r="AC86" t="inlineStr">
-        <is>
-          <t>Färska ringhack (gran), 4-5 år gamla</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9129,10 +9114,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>127723541</v>
+        <v>127723178</v>
       </c>
       <c r="B87" t="n">
-        <v>57663</v>
+        <v>79020</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9140,39 +9125,34 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
-      <c r="M87" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P87" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>443317</v>
+        <v>443402</v>
       </c>
       <c r="R87" t="n">
-        <v>6766816</v>
+        <v>6766682</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9231,10 +9211,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>127723570</v>
+        <v>127723541</v>
       </c>
       <c r="B88" t="n">
-        <v>78687</v>
+        <v>57663</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9242,34 +9222,39 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>353</v>
+        <v>100109</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P88" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>443319</v>
+        <v>443317</v>
       </c>
       <c r="R88" t="n">
-        <v>6766670</v>
+        <v>6766816</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9328,10 +9313,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>127723116</v>
+        <v>127722916</v>
       </c>
       <c r="B89" t="n">
-        <v>79020</v>
+        <v>57663</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9339,34 +9324,39 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P89" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>443509</v>
+        <v>443342</v>
       </c>
       <c r="R89" t="n">
-        <v>6766633</v>
+        <v>6766806</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9399,6 +9389,11 @@
       <c r="AA89" t="inlineStr">
         <is>
           <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AC89" t="inlineStr">
+        <is>
+          <t>Färska ringhack (gran), 4-5 år gamla</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -9425,10 +9420,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>127723092</v>
+        <v>127722888</v>
       </c>
       <c r="B90" t="n">
-        <v>79020</v>
+        <v>57660</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9436,34 +9431,39 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P90" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>443572</v>
+        <v>443481</v>
       </c>
       <c r="R90" t="n">
-        <v>6766650</v>
+        <v>6766676</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9522,10 +9522,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>127723161</v>
+        <v>127723569</v>
       </c>
       <c r="B91" t="n">
-        <v>79020</v>
+        <v>78687</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9533,21 +9533,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -9557,10 +9557,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>443305</v>
+        <v>443332</v>
       </c>
       <c r="R91" t="n">
-        <v>6766767</v>
+        <v>6766677</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9619,7 +9619,7 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>127723186</v>
+        <v>127723103</v>
       </c>
       <c r="B92" t="n">
         <v>79020</v>
@@ -9654,10 +9654,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>443454</v>
+        <v>443541</v>
       </c>
       <c r="R92" t="n">
-        <v>6766738</v>
+        <v>6766696</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9716,7 +9716,7 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>127723114</v>
+        <v>127723105</v>
       </c>
       <c r="B93" t="n">
         <v>79020</v>
@@ -9751,10 +9751,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>443487</v>
+        <v>443525</v>
       </c>
       <c r="R93" t="n">
-        <v>6766651</v>
+        <v>6766717</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -9813,7 +9813,7 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>127723097</v>
+        <v>127723161</v>
       </c>
       <c r="B94" t="n">
         <v>79020</v>
@@ -9848,10 +9848,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>443561</v>
+        <v>443305</v>
       </c>
       <c r="R94" t="n">
-        <v>6766678</v>
+        <v>6766767</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -9910,10 +9910,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>127723569</v>
+        <v>127723114</v>
       </c>
       <c r="B95" t="n">
-        <v>78687</v>
+        <v>79020</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -9921,21 +9921,21 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -9945,10 +9945,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>443332</v>
+        <v>443487</v>
       </c>
       <c r="R95" t="n">
-        <v>6766677</v>
+        <v>6766651</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10007,7 +10007,7 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>127723174</v>
+        <v>127723097</v>
       </c>
       <c r="B96" t="n">
         <v>79020</v>
@@ -10042,10 +10042,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>443378</v>
+        <v>443561</v>
       </c>
       <c r="R96" t="n">
-        <v>6766657</v>
+        <v>6766678</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10104,7 +10104,7 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>127723105</v>
+        <v>127723174</v>
       </c>
       <c r="B97" t="n">
         <v>79020</v>
@@ -10139,10 +10139,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>443525</v>
+        <v>443378</v>
       </c>
       <c r="R97" t="n">
-        <v>6766717</v>
+        <v>6766657</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10201,10 +10201,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>127723103</v>
+        <v>127723041</v>
       </c>
       <c r="B98" t="n">
-        <v>79020</v>
+        <v>78779</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10212,21 +10212,21 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10236,10 +10236,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>443541</v>
+        <v>443450</v>
       </c>
       <c r="R98" t="n">
-        <v>6766696</v>
+        <v>6766735</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10298,10 +10298,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>127723041</v>
+        <v>127723186</v>
       </c>
       <c r="B99" t="n">
-        <v>78779</v>
+        <v>79020</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10309,21 +10309,21 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -10333,10 +10333,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>443450</v>
+        <v>443454</v>
       </c>
       <c r="R99" t="n">
-        <v>6766735</v>
+        <v>6766738</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10395,10 +10395,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>127722842</v>
+        <v>127723616</v>
       </c>
       <c r="B100" t="n">
-        <v>79052</v>
+        <v>57663</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10406,34 +10406,39 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>185</v>
+        <v>100109</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
+      <c r="M100" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
       <c r="P100" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>443504</v>
+        <v>443475</v>
       </c>
       <c r="R100" t="n">
-        <v>6766708</v>
+        <v>6766610</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10492,10 +10497,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>127723182</v>
+        <v>127722842</v>
       </c>
       <c r="B101" t="n">
-        <v>79020</v>
+        <v>79052</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -10503,21 +10508,21 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -10527,10 +10532,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>443444</v>
+        <v>443504</v>
       </c>
       <c r="R101" t="n">
-        <v>6766677</v>
+        <v>6766708</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10589,7 +10594,7 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>127723170</v>
+        <v>127723183</v>
       </c>
       <c r="B102" t="n">
         <v>79020</v>
@@ -10624,10 +10629,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>443333</v>
+        <v>443441</v>
       </c>
       <c r="R102" t="n">
-        <v>6766676</v>
+        <v>6766686</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -10686,7 +10691,7 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>127723183</v>
+        <v>127723157</v>
       </c>
       <c r="B103" t="n">
         <v>79020</v>
@@ -10721,10 +10726,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>443441</v>
+        <v>443306</v>
       </c>
       <c r="R103" t="n">
-        <v>6766686</v>
+        <v>6766830</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -10783,7 +10788,7 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>127723157</v>
+        <v>127723182</v>
       </c>
       <c r="B104" t="n">
         <v>79020</v>
@@ -10818,10 +10823,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>443306</v>
+        <v>443444</v>
       </c>
       <c r="R104" t="n">
-        <v>6766830</v>
+        <v>6766677</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -10880,7 +10885,7 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>127723139</v>
+        <v>127723096</v>
       </c>
       <c r="B105" t="n">
         <v>79020</v>
@@ -10915,10 +10920,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>443381</v>
+        <v>443554</v>
       </c>
       <c r="R105" t="n">
-        <v>6766623</v>
+        <v>6766650</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -10977,7 +10982,7 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>127723096</v>
+        <v>127723139</v>
       </c>
       <c r="B106" t="n">
         <v>79020</v>
@@ -11012,10 +11017,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>443554</v>
+        <v>443381</v>
       </c>
       <c r="R106" t="n">
-        <v>6766650</v>
+        <v>6766623</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11074,7 +11079,7 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>127723098</v>
+        <v>127723170</v>
       </c>
       <c r="B107" t="n">
         <v>79020</v>
@@ -11109,10 +11114,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>443562</v>
+        <v>443333</v>
       </c>
       <c r="R107" t="n">
-        <v>6766684</v>
+        <v>6766676</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11171,10 +11176,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>127723616</v>
+        <v>127723098</v>
       </c>
       <c r="B108" t="n">
-        <v>57663</v>
+        <v>79020</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11182,39 +11187,34 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
-      <c r="M108" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
       <c r="P108" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>443475</v>
+        <v>443562</v>
       </c>
       <c r="R108" t="n">
-        <v>6766610</v>
+        <v>6766684</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11472,10 +11472,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>127723136</v>
+        <v>127722904</v>
       </c>
       <c r="B111" t="n">
-        <v>79020</v>
+        <v>57663</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -11483,21 +11483,21 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -11507,10 +11507,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>443438</v>
+        <v>443419</v>
       </c>
       <c r="R111" t="n">
-        <v>6766628</v>
+        <v>6766676</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -11543,6 +11543,11 @@
       <c r="AA111" t="inlineStr">
         <is>
           <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AC111" t="inlineStr">
+        <is>
+          <t>Äldre ringhack (tall)</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -11569,10 +11574,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>127723154</v>
+        <v>127729086</v>
       </c>
       <c r="B112" t="n">
-        <v>79020</v>
+        <v>78779</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -11580,34 +11585,34 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
       <c r="P112" t="inlineStr">
         <is>
-          <t>Oxeråsen, Dlr</t>
+          <t>Oxeråsen S. om, Dlr</t>
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>443369</v>
+        <v>443359</v>
       </c>
       <c r="R112" t="n">
-        <v>6766695</v>
+        <v>6766650</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -11637,29 +11642,40 @@
           <t>2025-08-21</t>
         </is>
       </c>
+      <c r="Z112" t="inlineStr">
+        <is>
+          <t>13:53</t>
+        </is>
+      </c>
       <c r="AA112" t="inlineStr">
         <is>
           <t>2025-08-21</t>
         </is>
       </c>
+      <c r="AB112" t="inlineStr">
+        <is>
+          <t>13:53</t>
+        </is>
+      </c>
       <c r="AD112" t="b">
         <v>0</v>
       </c>
       <c r="AE112" t="b">
         <v>0</v>
       </c>
+      <c r="AF112" t="inlineStr"/>
       <c r="AG112" t="b">
         <v>0</v>
       </c>
       <c r="AT112" t="inlineStr"/>
       <c r="AW112" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX112" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
@@ -11763,7 +11779,7 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>127723172</v>
+        <v>127723154</v>
       </c>
       <c r="B114" t="n">
         <v>79020</v>
@@ -11798,10 +11814,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>443356</v>
+        <v>443369</v>
       </c>
       <c r="R114" t="n">
-        <v>6766650</v>
+        <v>6766695</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -11860,7 +11876,7 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>127723160</v>
+        <v>127723172</v>
       </c>
       <c r="B115" t="n">
         <v>79020</v>
@@ -11895,10 +11911,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>443309</v>
+        <v>443356</v>
       </c>
       <c r="R115" t="n">
-        <v>6766785</v>
+        <v>6766650</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -11957,10 +11973,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>127722904</v>
+        <v>127723136</v>
       </c>
       <c r="B116" t="n">
-        <v>57663</v>
+        <v>79020</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -11968,21 +11984,21 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -11992,10 +12008,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>443419</v>
+        <v>443438</v>
       </c>
       <c r="R116" t="n">
-        <v>6766676</v>
+        <v>6766628</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12028,11 +12044,6 @@
       <c r="AA116" t="inlineStr">
         <is>
           <t>2025-08-21</t>
-        </is>
-      </c>
-      <c r="AC116" t="inlineStr">
-        <is>
-          <t>Äldre ringhack (tall)</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -12059,10 +12070,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>127729086</v>
+        <v>127723160</v>
       </c>
       <c r="B117" t="n">
-        <v>78779</v>
+        <v>79020</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -12070,34 +12081,34 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
       <c r="P117" t="inlineStr">
         <is>
-          <t>Oxeråsen S. om, Dlr</t>
+          <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>443359</v>
+        <v>443309</v>
       </c>
       <c r="R117" t="n">
-        <v>6766650</v>
+        <v>6766785</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12127,50 +12138,39 @@
           <t>2025-08-21</t>
         </is>
       </c>
-      <c r="Z117" t="inlineStr">
-        <is>
-          <t>13:53</t>
-        </is>
-      </c>
       <c r="AA117" t="inlineStr">
         <is>
           <t>2025-08-21</t>
         </is>
       </c>
-      <c r="AB117" t="inlineStr">
-        <is>
-          <t>13:53</t>
-        </is>
-      </c>
       <c r="AD117" t="b">
         <v>0</v>
       </c>
       <c r="AE117" t="b">
         <v>0</v>
       </c>
-      <c r="AF117" t="inlineStr"/>
       <c r="AG117" t="b">
         <v>0</v>
       </c>
       <c r="AT117" t="inlineStr"/>
       <c r="AW117" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX117" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>127722903</v>
+        <v>127723163</v>
       </c>
       <c r="B118" t="n">
-        <v>57663</v>
+        <v>79020</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12178,21 +12178,21 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -12202,10 +12202,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>443382</v>
+        <v>443332</v>
       </c>
       <c r="R118" t="n">
-        <v>6766657</v>
+        <v>6766744</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12238,11 +12238,6 @@
       <c r="AA118" t="inlineStr">
         <is>
           <t>2025-08-21</t>
-        </is>
-      </c>
-      <c r="AC118" t="inlineStr">
-        <is>
-          <t>Äldre ringhack (tall)</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -12366,7 +12361,7 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>127723113</v>
+        <v>127723135</v>
       </c>
       <c r="B120" t="n">
         <v>79020</v>
@@ -12401,10 +12396,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>443487</v>
+        <v>443454</v>
       </c>
       <c r="R120" t="n">
-        <v>6766675</v>
+        <v>6766614</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -12463,7 +12458,7 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>127723163</v>
+        <v>127723113</v>
       </c>
       <c r="B121" t="n">
         <v>79020</v>
@@ -12498,10 +12493,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>443332</v>
+        <v>443487</v>
       </c>
       <c r="R121" t="n">
-        <v>6766744</v>
+        <v>6766675</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -12560,10 +12555,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>127723135</v>
+        <v>127722903</v>
       </c>
       <c r="B122" t="n">
-        <v>79020</v>
+        <v>57663</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -12571,21 +12566,21 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -12595,10 +12590,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>443454</v>
+        <v>443382</v>
       </c>
       <c r="R122" t="n">
-        <v>6766614</v>
+        <v>6766657</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -12631,6 +12626,11 @@
       <c r="AA122" t="inlineStr">
         <is>
           <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AC122" t="inlineStr">
+        <is>
+          <t>Äldre ringhack (tall)</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -12861,32 +12861,32 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>127723555</v>
+        <v>127723037</v>
       </c>
       <c r="B125" t="n">
-        <v>92622</v>
+        <v>78779</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>4364</v>
+        <v>228912</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -12896,10 +12896,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>443554</v>
+        <v>443509</v>
       </c>
       <c r="R125" t="n">
-        <v>6766667</v>
+        <v>6766722</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13346,10 +13346,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>127722954</v>
+        <v>127723555</v>
       </c>
       <c r="B130" t="n">
-        <v>8450</v>
+        <v>92628</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -13357,39 +13357,34 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>106545</v>
+        <v>4364</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
-      <c r="M130" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P130" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>443348</v>
+        <v>443554</v>
       </c>
       <c r="R130" t="n">
-        <v>6766646</v>
+        <v>6766667</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -13448,7 +13443,7 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>127722951</v>
+        <v>127722954</v>
       </c>
       <c r="B131" t="n">
         <v>8450</v>
@@ -13488,10 +13483,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>443377</v>
+        <v>443348</v>
       </c>
       <c r="R131" t="n">
-        <v>6766686</v>
+        <v>6766646</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -13550,45 +13545,50 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>127723037</v>
+        <v>127722951</v>
       </c>
       <c r="B132" t="n">
-        <v>78779</v>
+        <v>8450</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>228912</v>
+        <v>106545</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
+      <c r="M132" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P132" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>443509</v>
+        <v>443377</v>
       </c>
       <c r="R132" t="n">
-        <v>6766722</v>
+        <v>6766686</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -13647,7 +13647,7 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>127723111</v>
+        <v>127723162</v>
       </c>
       <c r="B133" t="n">
         <v>79020</v>
@@ -13682,10 +13682,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>443474</v>
+        <v>443312</v>
       </c>
       <c r="R133" t="n">
-        <v>6766692</v>
+        <v>6766762</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -13744,7 +13744,7 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>127723162</v>
+        <v>127723111</v>
       </c>
       <c r="B134" t="n">
         <v>79020</v>
@@ -13779,10 +13779,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>443312</v>
+        <v>443474</v>
       </c>
       <c r="R134" t="n">
-        <v>6766762</v>
+        <v>6766692</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -14048,7 +14048,7 @@
         <v>127736007</v>
       </c>
       <c r="B137" t="n">
-        <v>91352</v>
+        <v>91358</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -14803,7 +14803,7 @@
         <v>127785472</v>
       </c>
       <c r="B144" t="n">
-        <v>91352</v>
+        <v>91358</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>

--- a/artfynd/A 35484-2025 artfynd.xlsx
+++ b/artfynd/A 35484-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127621301</v>
+        <v>127621346</v>
       </c>
       <c r="B2" t="n">
-        <v>79020</v>
+        <v>78781</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -713,10 +713,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>443316</v>
+        <v>443330</v>
       </c>
       <c r="R2" t="n">
-        <v>6766797</v>
+        <v>6766724</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -749,11 +749,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-08-14</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>På 4 tallstammar</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -781,10 +776,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127621346</v>
+        <v>127621301</v>
       </c>
       <c r="B3" t="n">
-        <v>78778</v>
+        <v>79023</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -792,21 +787,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -819,10 +814,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>443330</v>
+        <v>443316</v>
       </c>
       <c r="R3" t="n">
-        <v>6766724</v>
+        <v>6766797</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -855,6 +850,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>På 4 tallstammar</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -885,7 +885,7 @@
         <v>127621344</v>
       </c>
       <c r="B4" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -991,7 +991,7 @@
         <v>127621350</v>
       </c>
       <c r="B5" t="n">
-        <v>56598</v>
+        <v>56601</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1098,7 +1098,7 @@
         <v>127621456</v>
       </c>
       <c r="B6" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1311,7 +1311,7 @@
         <v>127621380</v>
       </c>
       <c r="B8" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1412,7 +1412,7 @@
         <v>127621440</v>
       </c>
       <c r="B9" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1630,7 +1630,7 @@
         <v>127621322</v>
       </c>
       <c r="B11" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1736,7 +1736,7 @@
         <v>127621416</v>
       </c>
       <c r="B12" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1842,7 +1842,7 @@
         <v>127723164</v>
       </c>
       <c r="B13" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1936,10 +1936,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127723117</v>
+        <v>127723151</v>
       </c>
       <c r="B14" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1971,10 +1971,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>443514</v>
+        <v>443430</v>
       </c>
       <c r="R14" t="n">
-        <v>6766630</v>
+        <v>6766608</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2033,10 +2033,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127723151</v>
+        <v>127723117</v>
       </c>
       <c r="B15" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2068,10 +2068,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>443430</v>
+        <v>443514</v>
       </c>
       <c r="R15" t="n">
-        <v>6766608</v>
+        <v>6766630</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2235,7 +2235,7 @@
         <v>127723187</v>
       </c>
       <c r="B17" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2332,7 +2332,7 @@
         <v>127722870</v>
       </c>
       <c r="B18" t="n">
-        <v>57823</v>
+        <v>57826</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2434,7 +2434,7 @@
         <v>127723093</v>
       </c>
       <c r="B19" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2531,7 +2531,7 @@
         <v>127723099</v>
       </c>
       <c r="B20" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2829,10 +2829,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127723040</v>
+        <v>127723181</v>
       </c>
       <c r="B23" t="n">
-        <v>78779</v>
+        <v>79023</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2840,21 +2840,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2864,10 +2864,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>443377</v>
+        <v>443436</v>
       </c>
       <c r="R23" t="n">
-        <v>6766659</v>
+        <v>6766667</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2926,42 +2926,47 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127723039</v>
+        <v>127722950</v>
       </c>
       <c r="B24" t="n">
-        <v>78779</v>
+        <v>8450</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>228912</v>
+        <v>106545</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>443356</v>
+        <v>443438</v>
       </c>
       <c r="R24" t="n">
         <v>6766650</v>
@@ -3023,47 +3028,42 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127722950</v>
+        <v>127723039</v>
       </c>
       <c r="B25" t="n">
-        <v>8450</v>
+        <v>78782</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>106545</v>
+        <v>228912</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>443438</v>
+        <v>443356</v>
       </c>
       <c r="R25" t="n">
         <v>6766650</v>
@@ -3125,10 +3125,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127723112</v>
+        <v>127722874</v>
       </c>
       <c r="B26" t="n">
-        <v>79020</v>
+        <v>91361</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3136,21 +3136,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3160,10 +3160,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>443476</v>
+        <v>443388</v>
       </c>
       <c r="R26" t="n">
-        <v>6766681</v>
+        <v>6766675</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3225,7 +3225,7 @@
         <v>127723166</v>
       </c>
       <c r="B27" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3319,10 +3319,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127723181</v>
+        <v>127723112</v>
       </c>
       <c r="B28" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3354,10 +3354,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>443436</v>
+        <v>443476</v>
       </c>
       <c r="R28" t="n">
-        <v>6766667</v>
+        <v>6766681</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3416,10 +3416,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127722874</v>
+        <v>127723040</v>
       </c>
       <c r="B29" t="n">
-        <v>91358</v>
+        <v>78782</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3427,21 +3427,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5442</v>
+        <v>228912</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3451,10 +3451,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>443388</v>
+        <v>443377</v>
       </c>
       <c r="R29" t="n">
-        <v>6766675</v>
+        <v>6766659</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3516,7 +3516,7 @@
         <v>127723152</v>
       </c>
       <c r="B30" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3610,10 +3610,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127723179</v>
+        <v>127722875</v>
       </c>
       <c r="B31" t="n">
-        <v>79020</v>
+        <v>91361</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3621,21 +3621,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3645,10 +3645,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>443411</v>
+        <v>443312</v>
       </c>
       <c r="R31" t="n">
-        <v>6766676</v>
+        <v>6766713</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3707,10 +3707,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127722875</v>
+        <v>127723179</v>
       </c>
       <c r="B32" t="n">
-        <v>91358</v>
+        <v>79023</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3718,21 +3718,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3742,10 +3742,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>443312</v>
+        <v>443411</v>
       </c>
       <c r="R32" t="n">
-        <v>6766713</v>
+        <v>6766676</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3906,32 +3906,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>127723107</v>
+        <v>127722921</v>
       </c>
       <c r="B34" t="n">
-        <v>79020</v>
+        <v>97336</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3941,10 +3941,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>443493</v>
+        <v>443330</v>
       </c>
       <c r="R34" t="n">
-        <v>6766717</v>
+        <v>6766662</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4003,10 +4003,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127723109</v>
+        <v>127723107</v>
       </c>
       <c r="B35" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4038,10 +4038,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>443482</v>
+        <v>443493</v>
       </c>
       <c r="R35" t="n">
-        <v>6766716</v>
+        <v>6766717</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4100,10 +4100,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127723169</v>
+        <v>127723115</v>
       </c>
       <c r="B36" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4135,10 +4135,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>443321</v>
+        <v>443495</v>
       </c>
       <c r="R36" t="n">
-        <v>6766706</v>
+        <v>6766641</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4197,45 +4197,50 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127723115</v>
+        <v>127722944</v>
       </c>
       <c r="B37" t="n">
-        <v>79020</v>
+        <v>8450</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>443495</v>
+        <v>443488</v>
       </c>
       <c r="R37" t="n">
-        <v>6766641</v>
+        <v>6766671</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4294,38 +4299,38 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127722896</v>
+        <v>127722928</v>
       </c>
       <c r="B38" t="n">
-        <v>57660</v>
+        <v>8450</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="M38" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
@@ -4334,10 +4339,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>443537</v>
+        <v>443559</v>
       </c>
       <c r="R38" t="n">
-        <v>6766699</v>
+        <v>6766616</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4396,50 +4401,45 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127722944</v>
+        <v>127723109</v>
       </c>
       <c r="B39" t="n">
-        <v>8450</v>
+        <v>79023</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>443488</v>
+        <v>443482</v>
       </c>
       <c r="R39" t="n">
-        <v>6766671</v>
+        <v>6766716</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4498,50 +4498,45 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127722928</v>
+        <v>127723169</v>
       </c>
       <c r="B40" t="n">
-        <v>8450</v>
+        <v>79023</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>443559</v>
+        <v>443321</v>
       </c>
       <c r="R40" t="n">
-        <v>6766616</v>
+        <v>6766706</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4600,45 +4595,50 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127722921</v>
+        <v>127722896</v>
       </c>
       <c r="B41" t="n">
-        <v>97333</v>
+        <v>57663</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>221945</v>
+        <v>100049</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>443330</v>
+        <v>443537</v>
       </c>
       <c r="R41" t="n">
-        <v>6766662</v>
+        <v>6766699</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4697,10 +4697,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>127722876</v>
+        <v>127723189</v>
       </c>
       <c r="B42" t="n">
-        <v>91358</v>
+        <v>79023</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4708,21 +4708,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4732,10 +4732,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>443366</v>
+        <v>443446</v>
       </c>
       <c r="R42" t="n">
-        <v>6766661</v>
+        <v>6766727</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4768,6 +4768,11 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Med grov gran i bäckmiljö</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4794,32 +4799,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127723064</v>
+        <v>127723121</v>
       </c>
       <c r="B43" t="n">
-        <v>91499</v>
+        <v>79023</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1503</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4829,10 +4834,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>443329</v>
+        <v>443558</v>
       </c>
       <c r="R43" t="n">
-        <v>6766670</v>
+        <v>6766620</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4891,32 +4896,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>127723091</v>
+        <v>127723064</v>
       </c>
       <c r="B44" t="n">
-        <v>79020</v>
+        <v>91502</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>1503</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4926,10 +4931,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>443587</v>
+        <v>443329</v>
       </c>
       <c r="R44" t="n">
-        <v>6766651</v>
+        <v>6766670</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4991,7 +4996,7 @@
         <v>127723159</v>
       </c>
       <c r="B45" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5085,10 +5090,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>127723189</v>
+        <v>127722876</v>
       </c>
       <c r="B46" t="n">
-        <v>79020</v>
+        <v>91361</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5096,21 +5101,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5120,10 +5125,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>443446</v>
+        <v>443366</v>
       </c>
       <c r="R46" t="n">
-        <v>6766727</v>
+        <v>6766661</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5156,11 +5161,6 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-08-21</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Med grov gran i bäckmiljö</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5187,10 +5187,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>127723121</v>
+        <v>127723091</v>
       </c>
       <c r="B47" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5222,10 +5222,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>443558</v>
+        <v>443587</v>
       </c>
       <c r="R47" t="n">
-        <v>6766620</v>
+        <v>6766651</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5284,10 +5284,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>127723180</v>
+        <v>127723110</v>
       </c>
       <c r="B48" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5319,10 +5319,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>443425</v>
+        <v>443479</v>
       </c>
       <c r="R48" t="n">
-        <v>6766665</v>
+        <v>6766703</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5381,10 +5381,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>127723102</v>
+        <v>127723180</v>
       </c>
       <c r="B49" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5416,10 +5416,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>443556</v>
+        <v>443425</v>
       </c>
       <c r="R49" t="n">
-        <v>6766717</v>
+        <v>6766665</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5478,10 +5478,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>127723185</v>
+        <v>127723102</v>
       </c>
       <c r="B50" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5513,10 +5513,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>443452</v>
+        <v>443556</v>
       </c>
       <c r="R50" t="n">
-        <v>6766711</v>
+        <v>6766717</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5575,10 +5575,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>127723110</v>
+        <v>127723185</v>
       </c>
       <c r="B51" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5610,10 +5610,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>443479</v>
+        <v>443452</v>
       </c>
       <c r="R51" t="n">
-        <v>6766703</v>
+        <v>6766711</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5675,7 +5675,7 @@
         <v>127722868</v>
       </c>
       <c r="B52" t="n">
-        <v>57823</v>
+        <v>57826</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5879,7 +5879,7 @@
         <v>127723184</v>
       </c>
       <c r="B54" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5973,50 +5973,45 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>127722943</v>
+        <v>127723138</v>
       </c>
       <c r="B55" t="n">
-        <v>8450</v>
+        <v>79023</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>443527</v>
+        <v>443391</v>
       </c>
       <c r="R55" t="n">
-        <v>6766711</v>
+        <v>6766625</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6075,7 +6070,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>127722956</v>
+        <v>127722943</v>
       </c>
       <c r="B56" t="n">
         <v>8450</v>
@@ -6115,10 +6110,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>443454</v>
+        <v>443527</v>
       </c>
       <c r="R56" t="n">
-        <v>6766718</v>
+        <v>6766711</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6177,45 +6172,50 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>127723138</v>
+        <v>127722956</v>
       </c>
       <c r="B57" t="n">
-        <v>79020</v>
+        <v>8450</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P57" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>443391</v>
+        <v>443454</v>
       </c>
       <c r="R57" t="n">
-        <v>6766625</v>
+        <v>6766718</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6274,10 +6274,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>127723167</v>
+        <v>127722841</v>
       </c>
       <c r="B58" t="n">
-        <v>79020</v>
+        <v>79055</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6285,21 +6285,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6309,10 +6309,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>443316</v>
+        <v>443568</v>
       </c>
       <c r="R58" t="n">
-        <v>6766701</v>
+        <v>6766695</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6371,10 +6371,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>127723153</v>
+        <v>127723167</v>
       </c>
       <c r="B59" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6406,10 +6406,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>443436</v>
+        <v>443316</v>
       </c>
       <c r="R59" t="n">
-        <v>6766648</v>
+        <v>6766701</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6468,10 +6468,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>127723119</v>
+        <v>127723153</v>
       </c>
       <c r="B60" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6503,10 +6503,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>443535</v>
+        <v>443436</v>
       </c>
       <c r="R60" t="n">
-        <v>6766639</v>
+        <v>6766648</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6565,10 +6565,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>127723106</v>
+        <v>127723119</v>
       </c>
       <c r="B61" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6600,10 +6600,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>443516</v>
+        <v>443535</v>
       </c>
       <c r="R61" t="n">
-        <v>6766720</v>
+        <v>6766639</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6662,10 +6662,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>127723188</v>
+        <v>127723106</v>
       </c>
       <c r="B62" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6697,10 +6697,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>443454</v>
+        <v>443516</v>
       </c>
       <c r="R62" t="n">
-        <v>6766724</v>
+        <v>6766720</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6759,10 +6759,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>127723175</v>
+        <v>127723188</v>
       </c>
       <c r="B63" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6794,10 +6794,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>443387</v>
+        <v>443454</v>
       </c>
       <c r="R63" t="n">
-        <v>6766658</v>
+        <v>6766724</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6856,10 +6856,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>127723134</v>
+        <v>127723175</v>
       </c>
       <c r="B64" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6891,10 +6891,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>443465</v>
+        <v>443387</v>
       </c>
       <c r="R64" t="n">
-        <v>6766607</v>
+        <v>6766658</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -6953,10 +6953,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>127722841</v>
+        <v>127723134</v>
       </c>
       <c r="B65" t="n">
-        <v>79052</v>
+        <v>79023</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6964,21 +6964,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -6988,10 +6988,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>443568</v>
+        <v>443465</v>
       </c>
       <c r="R65" t="n">
-        <v>6766695</v>
+        <v>6766607</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7053,7 +7053,7 @@
         <v>127723065</v>
       </c>
       <c r="B66" t="n">
-        <v>91499</v>
+        <v>91502</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7147,10 +7147,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>127722847</v>
+        <v>127723177</v>
       </c>
       <c r="B67" t="n">
-        <v>79052</v>
+        <v>79023</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7158,21 +7158,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7182,10 +7182,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>443320</v>
+        <v>443397</v>
       </c>
       <c r="R67" t="n">
-        <v>6766703</v>
+        <v>6766673</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7244,10 +7244,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>127723177</v>
+        <v>127729137</v>
       </c>
       <c r="B68" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7275,14 +7275,14 @@
       <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Oxeråsen, Dlr</t>
+          <t>Oxeråsen S. om, Dlr</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>443397</v>
+        <v>443391</v>
       </c>
       <c r="R68" t="n">
-        <v>6766673</v>
+        <v>6766598</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7312,39 +7312,50 @@
           <t>2025-08-21</t>
         </is>
       </c>
+      <c r="Z68" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
       <c r="AA68" t="inlineStr">
         <is>
           <t>2025-08-21</t>
         </is>
       </c>
+      <c r="AB68" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
       <c r="AD68" t="b">
         <v>0</v>
       </c>
       <c r="AE68" t="b">
         <v>0</v>
       </c>
+      <c r="AF68" t="inlineStr"/>
       <c r="AG68" t="b">
         <v>0</v>
       </c>
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>127729137</v>
+        <v>127723158</v>
       </c>
       <c r="B69" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7372,14 +7383,14 @@
       <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Oxeråsen S. om, Dlr</t>
+          <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>443391</v>
+        <v>443312</v>
       </c>
       <c r="R69" t="n">
-        <v>6766598</v>
+        <v>6766818</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7409,50 +7420,39 @@
           <t>2025-08-21</t>
         </is>
       </c>
-      <c r="Z69" t="inlineStr">
-        <is>
-          <t>14:00</t>
-        </is>
-      </c>
       <c r="AA69" t="inlineStr">
         <is>
           <t>2025-08-21</t>
         </is>
       </c>
-      <c r="AB69" t="inlineStr">
-        <is>
-          <t>14:00</t>
-        </is>
-      </c>
       <c r="AD69" t="b">
         <v>0</v>
       </c>
       <c r="AE69" t="b">
         <v>0</v>
       </c>
-      <c r="AF69" t="inlineStr"/>
       <c r="AG69" t="b">
         <v>0</v>
       </c>
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>127723158</v>
+        <v>127723150</v>
       </c>
       <c r="B70" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7484,10 +7484,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>443312</v>
+        <v>443415</v>
       </c>
       <c r="R70" t="n">
-        <v>6766818</v>
+        <v>6766603</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7546,10 +7546,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>127723150</v>
+        <v>127722847</v>
       </c>
       <c r="B71" t="n">
-        <v>79020</v>
+        <v>79055</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7557,21 +7557,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7581,10 +7581,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>443415</v>
+        <v>443320</v>
       </c>
       <c r="R71" t="n">
-        <v>6766603</v>
+        <v>6766703</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7745,10 +7745,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>127729092</v>
+        <v>127723173</v>
       </c>
       <c r="B73" t="n">
-        <v>78778</v>
+        <v>79023</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7756,34 +7756,34 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Oxeråsen S. om, Dlr</t>
+          <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>443381</v>
+        <v>443365</v>
       </c>
       <c r="R73" t="n">
-        <v>6766668</v>
+        <v>6766656</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7813,50 +7813,39 @@
           <t>2025-08-21</t>
         </is>
       </c>
-      <c r="Z73" t="inlineStr">
-        <is>
-          <t>13:51</t>
-        </is>
-      </c>
       <c r="AA73" t="inlineStr">
         <is>
           <t>2025-08-21</t>
         </is>
       </c>
-      <c r="AB73" t="inlineStr">
-        <is>
-          <t>13:51</t>
-        </is>
-      </c>
       <c r="AD73" t="b">
         <v>0</v>
       </c>
       <c r="AE73" t="b">
         <v>0</v>
       </c>
-      <c r="AF73" t="inlineStr"/>
       <c r="AG73" t="b">
         <v>0</v>
       </c>
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>127722839</v>
+        <v>127723108</v>
       </c>
       <c r="B74" t="n">
-        <v>79052</v>
+        <v>79023</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7864,21 +7853,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -7888,10 +7877,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>443554</v>
+        <v>443483</v>
       </c>
       <c r="R74" t="n">
-        <v>6766649</v>
+        <v>6766725</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -7950,10 +7939,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>127723133</v>
+        <v>127722839</v>
       </c>
       <c r="B75" t="n">
-        <v>79020</v>
+        <v>79055</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7961,21 +7950,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -7985,10 +7974,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>443504</v>
+        <v>443554</v>
       </c>
       <c r="R75" t="n">
-        <v>6766593</v>
+        <v>6766649</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8047,10 +8036,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>127723173</v>
+        <v>127723133</v>
       </c>
       <c r="B76" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8082,10 +8071,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>443365</v>
+        <v>443504</v>
       </c>
       <c r="R76" t="n">
-        <v>6766656</v>
+        <v>6766593</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8144,10 +8133,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>127723108</v>
+        <v>127729092</v>
       </c>
       <c r="B77" t="n">
-        <v>79020</v>
+        <v>78781</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8155,34 +8144,34 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Oxeråsen, Dlr</t>
+          <t>Oxeråsen S. om, Dlr</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>443483</v>
+        <v>443381</v>
       </c>
       <c r="R77" t="n">
-        <v>6766725</v>
+        <v>6766668</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8212,29 +8201,40 @@
           <t>2025-08-21</t>
         </is>
       </c>
+      <c r="Z77" t="inlineStr">
+        <is>
+          <t>13:51</t>
+        </is>
+      </c>
       <c r="AA77" t="inlineStr">
         <is>
           <t>2025-08-21</t>
         </is>
       </c>
+      <c r="AB77" t="inlineStr">
+        <is>
+          <t>13:51</t>
+        </is>
+      </c>
       <c r="AD77" t="b">
         <v>0</v>
       </c>
       <c r="AE77" t="b">
         <v>0</v>
       </c>
+      <c r="AF77" t="inlineStr"/>
       <c r="AG77" t="b">
         <v>0</v>
       </c>
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
@@ -8244,7 +8244,7 @@
         <v>127723090</v>
       </c>
       <c r="B78" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8338,10 +8338,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>127723571</v>
+        <v>127723104</v>
       </c>
       <c r="B79" t="n">
-        <v>78687</v>
+        <v>79023</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8349,21 +8349,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8373,10 +8373,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>443426</v>
+        <v>443536</v>
       </c>
       <c r="R79" t="n">
-        <v>6766668</v>
+        <v>6766704</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8435,10 +8435,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>127723156</v>
+        <v>127723571</v>
       </c>
       <c r="B80" t="n">
-        <v>79020</v>
+        <v>78690</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8446,21 +8446,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8470,10 +8470,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>443346</v>
+        <v>443426</v>
       </c>
       <c r="R80" t="n">
-        <v>6766766</v>
+        <v>6766668</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8532,10 +8532,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>127723120</v>
+        <v>127723156</v>
       </c>
       <c r="B81" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8567,10 +8567,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>443548</v>
+        <v>443346</v>
       </c>
       <c r="R81" t="n">
-        <v>6766624</v>
+        <v>6766766</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8629,10 +8629,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>127723104</v>
+        <v>127723120</v>
       </c>
       <c r="B82" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8664,10 +8664,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>443536</v>
+        <v>443548</v>
       </c>
       <c r="R82" t="n">
-        <v>6766704</v>
+        <v>6766624</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8726,10 +8726,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>127723570</v>
+        <v>127723116</v>
       </c>
       <c r="B83" t="n">
-        <v>78687</v>
+        <v>79023</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8737,21 +8737,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -8761,10 +8761,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>443319</v>
+        <v>443509</v>
       </c>
       <c r="R83" t="n">
-        <v>6766670</v>
+        <v>6766633</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -8823,10 +8823,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>127723116</v>
+        <v>127723092</v>
       </c>
       <c r="B84" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -8858,10 +8858,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>443509</v>
+        <v>443572</v>
       </c>
       <c r="R84" t="n">
-        <v>6766633</v>
+        <v>6766650</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -8920,10 +8920,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>127723092</v>
+        <v>127723178</v>
       </c>
       <c r="B85" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -8955,10 +8955,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>443572</v>
+        <v>443402</v>
       </c>
       <c r="R85" t="n">
-        <v>6766650</v>
+        <v>6766682</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9020,7 +9020,7 @@
         <v>127723171</v>
       </c>
       <c r="B86" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9114,10 +9114,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>127723178</v>
+        <v>127723570</v>
       </c>
       <c r="B87" t="n">
-        <v>79020</v>
+        <v>78690</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9125,21 +9125,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9149,10 +9149,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>443402</v>
+        <v>443319</v>
       </c>
       <c r="R87" t="n">
-        <v>6766682</v>
+        <v>6766670</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9214,7 +9214,7 @@
         <v>127723541</v>
       </c>
       <c r="B88" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9316,7 +9316,7 @@
         <v>127722916</v>
       </c>
       <c r="B89" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9423,7 +9423,7 @@
         <v>127722888</v>
       </c>
       <c r="B90" t="n">
-        <v>57660</v>
+        <v>57663</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9522,10 +9522,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>127723569</v>
+        <v>127723161</v>
       </c>
       <c r="B91" t="n">
-        <v>78687</v>
+        <v>79023</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9533,21 +9533,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -9557,10 +9557,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>443332</v>
+        <v>443305</v>
       </c>
       <c r="R91" t="n">
-        <v>6766677</v>
+        <v>6766767</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9619,10 +9619,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>127723103</v>
+        <v>127723097</v>
       </c>
       <c r="B92" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9654,10 +9654,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>443541</v>
+        <v>443561</v>
       </c>
       <c r="R92" t="n">
-        <v>6766696</v>
+        <v>6766678</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9716,10 +9716,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>127723105</v>
+        <v>127723174</v>
       </c>
       <c r="B93" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9751,10 +9751,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>443525</v>
+        <v>443378</v>
       </c>
       <c r="R93" t="n">
-        <v>6766717</v>
+        <v>6766657</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -9813,10 +9813,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>127723161</v>
+        <v>127723569</v>
       </c>
       <c r="B94" t="n">
-        <v>79020</v>
+        <v>78690</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -9824,21 +9824,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -9848,10 +9848,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>443305</v>
+        <v>443332</v>
       </c>
       <c r="R94" t="n">
-        <v>6766767</v>
+        <v>6766677</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -9910,10 +9910,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>127723114</v>
+        <v>127723041</v>
       </c>
       <c r="B95" t="n">
-        <v>79020</v>
+        <v>78782</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -9921,21 +9921,21 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -9945,10 +9945,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>443487</v>
+        <v>443450</v>
       </c>
       <c r="R95" t="n">
-        <v>6766651</v>
+        <v>6766735</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10007,10 +10007,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>127723097</v>
+        <v>127723103</v>
       </c>
       <c r="B96" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10042,10 +10042,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>443561</v>
+        <v>443541</v>
       </c>
       <c r="R96" t="n">
-        <v>6766678</v>
+        <v>6766696</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10104,10 +10104,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>127723174</v>
+        <v>127723105</v>
       </c>
       <c r="B97" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10139,10 +10139,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>443378</v>
+        <v>443525</v>
       </c>
       <c r="R97" t="n">
-        <v>6766657</v>
+        <v>6766717</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10201,10 +10201,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>127723041</v>
+        <v>127723186</v>
       </c>
       <c r="B98" t="n">
-        <v>78779</v>
+        <v>79023</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10212,21 +10212,21 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10236,10 +10236,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>443450</v>
+        <v>443454</v>
       </c>
       <c r="R98" t="n">
-        <v>6766735</v>
+        <v>6766738</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10298,10 +10298,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>127723186</v>
+        <v>127723114</v>
       </c>
       <c r="B99" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10333,10 +10333,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>443454</v>
+        <v>443487</v>
       </c>
       <c r="R99" t="n">
-        <v>6766738</v>
+        <v>6766651</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10398,7 +10398,7 @@
         <v>127723616</v>
       </c>
       <c r="B100" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10497,10 +10497,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>127722842</v>
+        <v>127723038</v>
       </c>
       <c r="B101" t="n">
-        <v>79052</v>
+        <v>78782</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -10508,21 +10508,21 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>185</v>
+        <v>228912</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -10532,10 +10532,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>443504</v>
+        <v>443328</v>
       </c>
       <c r="R101" t="n">
-        <v>6766708</v>
+        <v>6766721</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10594,10 +10594,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>127723183</v>
+        <v>127723157</v>
       </c>
       <c r="B102" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -10629,10 +10629,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>443441</v>
+        <v>443306</v>
       </c>
       <c r="R102" t="n">
-        <v>6766686</v>
+        <v>6766830</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -10691,10 +10691,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>127723157</v>
+        <v>127723182</v>
       </c>
       <c r="B103" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -10726,10 +10726,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>443306</v>
+        <v>443444</v>
       </c>
       <c r="R103" t="n">
-        <v>6766830</v>
+        <v>6766677</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -10788,10 +10788,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>127723182</v>
+        <v>127723096</v>
       </c>
       <c r="B104" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -10823,10 +10823,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>443444</v>
+        <v>443554</v>
       </c>
       <c r="R104" t="n">
-        <v>6766677</v>
+        <v>6766650</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -10885,10 +10885,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>127723096</v>
+        <v>127722842</v>
       </c>
       <c r="B105" t="n">
-        <v>79020</v>
+        <v>79055</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -10896,21 +10896,21 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -10920,10 +10920,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>443554</v>
+        <v>443504</v>
       </c>
       <c r="R105" t="n">
-        <v>6766650</v>
+        <v>6766708</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -10982,10 +10982,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>127723139</v>
+        <v>127723183</v>
       </c>
       <c r="B106" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11017,10 +11017,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>443381</v>
+        <v>443441</v>
       </c>
       <c r="R106" t="n">
-        <v>6766623</v>
+        <v>6766686</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11079,10 +11079,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>127723170</v>
+        <v>127723139</v>
       </c>
       <c r="B107" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11114,10 +11114,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>443333</v>
+        <v>443381</v>
       </c>
       <c r="R107" t="n">
-        <v>6766676</v>
+        <v>6766623</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11176,10 +11176,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>127723098</v>
+        <v>127723170</v>
       </c>
       <c r="B108" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11211,10 +11211,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>443562</v>
+        <v>443333</v>
       </c>
       <c r="R108" t="n">
-        <v>6766684</v>
+        <v>6766676</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11273,50 +11273,45 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>127722929</v>
+        <v>127723098</v>
       </c>
       <c r="B109" t="n">
-        <v>8450</v>
+        <v>79023</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
-      <c r="M109" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P109" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>443327</v>
+        <v>443562</v>
       </c>
       <c r="R109" t="n">
-        <v>6766698</v>
+        <v>6766684</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11375,45 +11370,50 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>127723038</v>
+        <v>127722929</v>
       </c>
       <c r="B110" t="n">
-        <v>78779</v>
+        <v>8450</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>228912</v>
+        <v>106545</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
+      <c r="M110" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P110" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>443328</v>
+        <v>443327</v>
       </c>
       <c r="R110" t="n">
-        <v>6766721</v>
+        <v>6766698</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11475,7 +11475,7 @@
         <v>127722904</v>
       </c>
       <c r="B111" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -11577,7 +11577,7 @@
         <v>127729086</v>
       </c>
       <c r="B112" t="n">
-        <v>78779</v>
+        <v>78782</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -11685,7 +11685,7 @@
         <v>127723137</v>
       </c>
       <c r="B113" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -11779,10 +11779,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>127723154</v>
+        <v>127723136</v>
       </c>
       <c r="B114" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -11814,10 +11814,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>443369</v>
+        <v>443438</v>
       </c>
       <c r="R114" t="n">
-        <v>6766695</v>
+        <v>6766628</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -11876,10 +11876,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>127723172</v>
+        <v>127723154</v>
       </c>
       <c r="B115" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -11911,10 +11911,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>443356</v>
+        <v>443369</v>
       </c>
       <c r="R115" t="n">
-        <v>6766650</v>
+        <v>6766695</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -11973,10 +11973,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>127723136</v>
+        <v>127723172</v>
       </c>
       <c r="B116" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -12008,10 +12008,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>443438</v>
+        <v>443356</v>
       </c>
       <c r="R116" t="n">
-        <v>6766628</v>
+        <v>6766650</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12073,7 +12073,7 @@
         <v>127723160</v>
       </c>
       <c r="B117" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -12167,45 +12167,50 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>127723163</v>
+        <v>127722948</v>
       </c>
       <c r="B118" t="n">
-        <v>79020</v>
+        <v>8450</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
+      <c r="M118" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P118" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>443332</v>
+        <v>443457</v>
       </c>
       <c r="R118" t="n">
-        <v>6766744</v>
+        <v>6766613</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12264,10 +12269,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>127723176</v>
+        <v>127723113</v>
       </c>
       <c r="B119" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -12299,10 +12304,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>443407</v>
+        <v>443487</v>
       </c>
       <c r="R119" t="n">
-        <v>6766653</v>
+        <v>6766675</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -12364,7 +12369,7 @@
         <v>127723135</v>
       </c>
       <c r="B120" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -12458,10 +12463,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>127723113</v>
+        <v>127723163</v>
       </c>
       <c r="B121" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -12493,10 +12498,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>443487</v>
+        <v>443332</v>
       </c>
       <c r="R121" t="n">
-        <v>6766675</v>
+        <v>6766744</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -12555,10 +12560,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>127722903</v>
+        <v>127723176</v>
       </c>
       <c r="B122" t="n">
-        <v>57663</v>
+        <v>79023</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -12566,21 +12571,21 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -12590,10 +12595,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>443382</v>
+        <v>443407</v>
       </c>
       <c r="R122" t="n">
-        <v>6766657</v>
+        <v>6766653</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -12626,11 +12631,6 @@
       <c r="AA122" t="inlineStr">
         <is>
           <t>2025-08-21</t>
-        </is>
-      </c>
-      <c r="AC122" t="inlineStr">
-        <is>
-          <t>Äldre ringhack (tall)</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -12657,50 +12657,45 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>127722955</v>
+        <v>127722903</v>
       </c>
       <c r="B123" t="n">
-        <v>8450</v>
+        <v>57666</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>106545</v>
+        <v>100109</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
-      <c r="M123" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P123" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>443397</v>
+        <v>443382</v>
       </c>
       <c r="R123" t="n">
-        <v>6766653</v>
+        <v>6766657</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -12733,6 +12728,11 @@
       <c r="AA123" t="inlineStr">
         <is>
           <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AC123" t="inlineStr">
+        <is>
+          <t>Äldre ringhack (tall)</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -12759,7 +12759,7 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>127722948</v>
+        <v>127722955</v>
       </c>
       <c r="B124" t="n">
         <v>8450</v>
@@ -12799,10 +12799,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>443457</v>
+        <v>443397</v>
       </c>
       <c r="R124" t="n">
-        <v>6766613</v>
+        <v>6766653</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -12861,32 +12861,32 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>127723037</v>
+        <v>127723555</v>
       </c>
       <c r="B125" t="n">
-        <v>78779</v>
+        <v>92631</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -12896,10 +12896,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>443509</v>
+        <v>443554</v>
       </c>
       <c r="R125" t="n">
-        <v>6766722</v>
+        <v>6766667</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -12958,45 +12958,50 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>127723094</v>
+        <v>127722954</v>
       </c>
       <c r="B126" t="n">
-        <v>79020</v>
+        <v>8450</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
+      <c r="M126" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P126" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>443557</v>
+        <v>443348</v>
       </c>
       <c r="R126" t="n">
-        <v>6766635</v>
+        <v>6766646</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -13055,45 +13060,50 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>127723118</v>
+        <v>127722951</v>
       </c>
       <c r="B127" t="n">
-        <v>79020</v>
+        <v>8450</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
+      <c r="M127" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P127" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>443519</v>
+        <v>443377</v>
       </c>
       <c r="R127" t="n">
-        <v>6766624</v>
+        <v>6766686</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -13152,10 +13162,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>127723140</v>
+        <v>127723037</v>
       </c>
       <c r="B128" t="n">
-        <v>79020</v>
+        <v>78782</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -13163,21 +13173,21 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
@@ -13187,10 +13197,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>443370</v>
+        <v>443509</v>
       </c>
       <c r="R128" t="n">
-        <v>6766624</v>
+        <v>6766722</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -13249,10 +13259,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>127723165</v>
+        <v>127723118</v>
       </c>
       <c r="B129" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -13284,10 +13294,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>443327</v>
+        <v>443519</v>
       </c>
       <c r="R129" t="n">
-        <v>6766717</v>
+        <v>6766624</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -13346,32 +13356,32 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>127723555</v>
+        <v>127723140</v>
       </c>
       <c r="B130" t="n">
-        <v>92628</v>
+        <v>79023</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
@@ -13381,10 +13391,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>443554</v>
+        <v>443370</v>
       </c>
       <c r="R130" t="n">
-        <v>6766667</v>
+        <v>6766624</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -13443,50 +13453,45 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>127722954</v>
+        <v>127723165</v>
       </c>
       <c r="B131" t="n">
-        <v>8450</v>
+        <v>79023</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
-      <c r="M131" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P131" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>443348</v>
+        <v>443327</v>
       </c>
       <c r="R131" t="n">
-        <v>6766646</v>
+        <v>6766717</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -13545,50 +13550,45 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>127722951</v>
+        <v>127723094</v>
       </c>
       <c r="B132" t="n">
-        <v>8450</v>
+        <v>79023</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
-      <c r="M132" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P132" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>443377</v>
+        <v>443557</v>
       </c>
       <c r="R132" t="n">
-        <v>6766686</v>
+        <v>6766635</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -13650,7 +13650,7 @@
         <v>127723162</v>
       </c>
       <c r="B133" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -13747,7 +13747,7 @@
         <v>127723111</v>
       </c>
       <c r="B134" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -13844,7 +13844,7 @@
         <v>127722855</v>
       </c>
       <c r="B135" t="n">
-        <v>79609</v>
+        <v>79612</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -13941,7 +13941,7 @@
         <v>127723619</v>
       </c>
       <c r="B136" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -14048,7 +14048,7 @@
         <v>127736007</v>
       </c>
       <c r="B137" t="n">
-        <v>91358</v>
+        <v>91361</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -14155,7 +14155,7 @@
         <v>127736019</v>
       </c>
       <c r="B138" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -14262,7 +14262,7 @@
         <v>127785482</v>
       </c>
       <c r="B139" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -14369,7 +14369,7 @@
         <v>127785478</v>
       </c>
       <c r="B140" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -14482,7 +14482,7 @@
         <v>127785484</v>
       </c>
       <c r="B141" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -14589,7 +14589,7 @@
         <v>127785481</v>
       </c>
       <c r="B142" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -14696,7 +14696,7 @@
         <v>127785483</v>
       </c>
       <c r="B143" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -14803,7 +14803,7 @@
         <v>127785472</v>
       </c>
       <c r="B144" t="n">
-        <v>91358</v>
+        <v>91361</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -15017,7 +15017,7 @@
         <v>127795299</v>
       </c>
       <c r="B146" t="n">
-        <v>78778</v>
+        <v>78781</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -15118,7 +15118,7 @@
         <v>127795339</v>
       </c>
       <c r="B147" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>

--- a/artfynd/A 35484-2025 artfynd.xlsx
+++ b/artfynd/A 35484-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127621346</v>
+        <v>127621301</v>
       </c>
       <c r="B2" t="n">
-        <v>78781</v>
+        <v>79029</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -713,10 +713,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>443330</v>
+        <v>443316</v>
       </c>
       <c r="R2" t="n">
-        <v>6766724</v>
+        <v>6766797</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -749,6 +749,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>På 4 tallstammar</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -776,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127621301</v>
+        <v>127621346</v>
       </c>
       <c r="B3" t="n">
-        <v>79023</v>
+        <v>78787</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -787,21 +792,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -814,10 +819,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>443316</v>
+        <v>443330</v>
       </c>
       <c r="R3" t="n">
-        <v>6766797</v>
+        <v>6766724</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -850,11 +855,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-08-14</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>På 4 tallstammar</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -885,7 +885,7 @@
         <v>127621344</v>
       </c>
       <c r="B4" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -991,7 +991,7 @@
         <v>127621350</v>
       </c>
       <c r="B5" t="n">
-        <v>56601</v>
+        <v>56607</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1098,7 +1098,7 @@
         <v>127621456</v>
       </c>
       <c r="B6" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1311,7 +1311,7 @@
         <v>127621380</v>
       </c>
       <c r="B8" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1412,7 +1412,7 @@
         <v>127621440</v>
       </c>
       <c r="B9" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1630,7 +1630,7 @@
         <v>127621322</v>
       </c>
       <c r="B11" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1736,7 +1736,7 @@
         <v>127621416</v>
       </c>
       <c r="B12" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1839,10 +1839,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127723164</v>
+        <v>127723151</v>
       </c>
       <c r="B13" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1874,10 +1874,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>443329</v>
+        <v>443430</v>
       </c>
       <c r="R13" t="n">
-        <v>6766739</v>
+        <v>6766608</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1936,10 +1936,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127723151</v>
+        <v>127723164</v>
       </c>
       <c r="B14" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1971,10 +1971,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>443430</v>
+        <v>443329</v>
       </c>
       <c r="R14" t="n">
-        <v>6766608</v>
+        <v>6766739</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2036,7 +2036,7 @@
         <v>127723117</v>
       </c>
       <c r="B15" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2235,7 +2235,7 @@
         <v>127723187</v>
       </c>
       <c r="B17" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2332,7 +2332,7 @@
         <v>127722870</v>
       </c>
       <c r="B18" t="n">
-        <v>57826</v>
+        <v>57832</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2434,7 +2434,7 @@
         <v>127723093</v>
       </c>
       <c r="B19" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2531,7 +2531,7 @@
         <v>127723099</v>
       </c>
       <c r="B20" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2829,10 +2829,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127723181</v>
+        <v>127723040</v>
       </c>
       <c r="B23" t="n">
-        <v>79023</v>
+        <v>78788</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2840,21 +2840,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2864,10 +2864,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>443436</v>
+        <v>443377</v>
       </c>
       <c r="R23" t="n">
-        <v>6766667</v>
+        <v>6766659</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2926,47 +2926,42 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127722950</v>
+        <v>127723039</v>
       </c>
       <c r="B24" t="n">
-        <v>8450</v>
+        <v>78788</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>106545</v>
+        <v>228912</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>443438</v>
+        <v>443356</v>
       </c>
       <c r="R24" t="n">
         <v>6766650</v>
@@ -3028,42 +3023,47 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127723039</v>
+        <v>127722950</v>
       </c>
       <c r="B25" t="n">
-        <v>78782</v>
+        <v>8450</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>228912</v>
+        <v>106545</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>443356</v>
+        <v>443438</v>
       </c>
       <c r="R25" t="n">
         <v>6766650</v>
@@ -3128,7 +3128,7 @@
         <v>127722874</v>
       </c>
       <c r="B26" t="n">
-        <v>91361</v>
+        <v>91369</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3225,7 +3225,7 @@
         <v>127723166</v>
       </c>
       <c r="B27" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3319,10 +3319,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127723112</v>
+        <v>127723181</v>
       </c>
       <c r="B28" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3354,10 +3354,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>443476</v>
+        <v>443436</v>
       </c>
       <c r="R28" t="n">
-        <v>6766681</v>
+        <v>6766667</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3416,10 +3416,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127723040</v>
+        <v>127723112</v>
       </c>
       <c r="B29" t="n">
-        <v>78782</v>
+        <v>79029</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3427,21 +3427,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3451,10 +3451,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>443377</v>
+        <v>443476</v>
       </c>
       <c r="R29" t="n">
-        <v>6766659</v>
+        <v>6766681</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3513,10 +3513,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127723152</v>
+        <v>127722875</v>
       </c>
       <c r="B30" t="n">
-        <v>79023</v>
+        <v>91369</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3524,21 +3524,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3548,10 +3548,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>443424</v>
+        <v>443312</v>
       </c>
       <c r="R30" t="n">
-        <v>6766627</v>
+        <v>6766713</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3610,10 +3610,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127722875</v>
+        <v>127723152</v>
       </c>
       <c r="B31" t="n">
-        <v>91361</v>
+        <v>79029</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3621,21 +3621,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3645,10 +3645,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>443312</v>
+        <v>443424</v>
       </c>
       <c r="R31" t="n">
-        <v>6766713</v>
+        <v>6766627</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3710,7 +3710,7 @@
         <v>127723179</v>
       </c>
       <c r="B32" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3906,32 +3906,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>127722921</v>
+        <v>127723115</v>
       </c>
       <c r="B34" t="n">
-        <v>97336</v>
+        <v>79029</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3941,10 +3941,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>443330</v>
+        <v>443495</v>
       </c>
       <c r="R34" t="n">
-        <v>6766662</v>
+        <v>6766641</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4003,10 +4003,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127723107</v>
+        <v>127723109</v>
       </c>
       <c r="B35" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4038,10 +4038,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>443493</v>
+        <v>443482</v>
       </c>
       <c r="R35" t="n">
-        <v>6766717</v>
+        <v>6766716</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4100,10 +4100,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127723115</v>
+        <v>127723169</v>
       </c>
       <c r="B36" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4135,10 +4135,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>443495</v>
+        <v>443321</v>
       </c>
       <c r="R36" t="n">
-        <v>6766641</v>
+        <v>6766706</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4197,50 +4197,45 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127722944</v>
+        <v>127723107</v>
       </c>
       <c r="B37" t="n">
-        <v>8450</v>
+        <v>79029</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>443488</v>
+        <v>443493</v>
       </c>
       <c r="R37" t="n">
-        <v>6766671</v>
+        <v>6766717</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4299,38 +4294,38 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127722928</v>
+        <v>127722896</v>
       </c>
       <c r="B38" t="n">
-        <v>8450</v>
+        <v>57669</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="M38" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
@@ -4339,10 +4334,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>443559</v>
+        <v>443537</v>
       </c>
       <c r="R38" t="n">
-        <v>6766616</v>
+        <v>6766699</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4401,32 +4396,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127723109</v>
+        <v>127722921</v>
       </c>
       <c r="B39" t="n">
-        <v>79023</v>
+        <v>97344</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4436,10 +4431,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>443482</v>
+        <v>443330</v>
       </c>
       <c r="R39" t="n">
-        <v>6766716</v>
+        <v>6766662</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4498,45 +4493,50 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127723169</v>
+        <v>127722944</v>
       </c>
       <c r="B40" t="n">
-        <v>79023</v>
+        <v>8450</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>443321</v>
+        <v>443488</v>
       </c>
       <c r="R40" t="n">
-        <v>6766706</v>
+        <v>6766671</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4595,38 +4595,38 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127722896</v>
+        <v>127722928</v>
       </c>
       <c r="B41" t="n">
-        <v>57663</v>
+        <v>8450</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="M41" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
@@ -4635,10 +4635,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>443537</v>
+        <v>443559</v>
       </c>
       <c r="R41" t="n">
-        <v>6766699</v>
+        <v>6766616</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4697,32 +4697,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>127723189</v>
+        <v>127723064</v>
       </c>
       <c r="B42" t="n">
-        <v>79023</v>
+        <v>91510</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>1503</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4732,10 +4732,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>443446</v>
+        <v>443329</v>
       </c>
       <c r="R42" t="n">
-        <v>6766727</v>
+        <v>6766670</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4768,11 +4768,6 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-08-21</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Med grov gran i bäckmiljö</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4799,10 +4794,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127723121</v>
+        <v>127722876</v>
       </c>
       <c r="B43" t="n">
-        <v>79023</v>
+        <v>91369</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4810,21 +4805,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4834,10 +4829,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>443558</v>
+        <v>443366</v>
       </c>
       <c r="R43" t="n">
-        <v>6766620</v>
+        <v>6766661</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4896,32 +4891,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>127723064</v>
+        <v>127723189</v>
       </c>
       <c r="B44" t="n">
-        <v>91502</v>
+        <v>79029</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1503</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4931,10 +4926,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>443329</v>
+        <v>443446</v>
       </c>
       <c r="R44" t="n">
-        <v>6766670</v>
+        <v>6766727</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4967,6 +4962,11 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Med grov gran i bäckmiljö</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -4993,10 +4993,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>127723159</v>
+        <v>127723091</v>
       </c>
       <c r="B45" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5028,10 +5028,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>443314</v>
+        <v>443587</v>
       </c>
       <c r="R45" t="n">
-        <v>6766811</v>
+        <v>6766651</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5090,10 +5090,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>127722876</v>
+        <v>127723159</v>
       </c>
       <c r="B46" t="n">
-        <v>91361</v>
+        <v>79029</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5101,21 +5101,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5125,10 +5125,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>443366</v>
+        <v>443314</v>
       </c>
       <c r="R46" t="n">
-        <v>6766661</v>
+        <v>6766811</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5187,10 +5187,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>127723091</v>
+        <v>127723121</v>
       </c>
       <c r="B47" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5222,10 +5222,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>443587</v>
+        <v>443558</v>
       </c>
       <c r="R47" t="n">
-        <v>6766651</v>
+        <v>6766620</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5284,10 +5284,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>127723110</v>
+        <v>127723102</v>
       </c>
       <c r="B48" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5319,10 +5319,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>443479</v>
+        <v>443556</v>
       </c>
       <c r="R48" t="n">
-        <v>6766703</v>
+        <v>6766717</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5381,10 +5381,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>127723180</v>
+        <v>127723185</v>
       </c>
       <c r="B49" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5416,10 +5416,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>443425</v>
+        <v>443452</v>
       </c>
       <c r="R49" t="n">
-        <v>6766665</v>
+        <v>6766711</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5478,10 +5478,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>127723102</v>
+        <v>127723180</v>
       </c>
       <c r="B50" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5513,10 +5513,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>443556</v>
+        <v>443425</v>
       </c>
       <c r="R50" t="n">
-        <v>6766717</v>
+        <v>6766665</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5575,10 +5575,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>127723185</v>
+        <v>127723110</v>
       </c>
       <c r="B51" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5610,10 +5610,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>443452</v>
+        <v>443479</v>
       </c>
       <c r="R51" t="n">
-        <v>6766711</v>
+        <v>6766703</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5672,38 +5672,38 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>127722868</v>
+        <v>127722957</v>
       </c>
       <c r="B52" t="n">
-        <v>57826</v>
+        <v>8450</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>103021</v>
+        <v>106545</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="M52" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P52" t="inlineStr">
@@ -5712,10 +5712,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>443305</v>
+        <v>443457</v>
       </c>
       <c r="R52" t="n">
-        <v>6766767</v>
+        <v>6766726</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5774,38 +5774,38 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>127722957</v>
+        <v>127722868</v>
       </c>
       <c r="B53" t="n">
-        <v>8450</v>
+        <v>57832</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>106545</v>
+        <v>103021</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="M53" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
@@ -5814,10 +5814,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>443457</v>
+        <v>443305</v>
       </c>
       <c r="R53" t="n">
-        <v>6766726</v>
+        <v>6766767</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5876,10 +5876,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>127723184</v>
+        <v>127723138</v>
       </c>
       <c r="B54" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5911,10 +5911,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>443446</v>
+        <v>443391</v>
       </c>
       <c r="R54" t="n">
-        <v>6766702</v>
+        <v>6766625</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5973,45 +5973,50 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>127723138</v>
+        <v>127722943</v>
       </c>
       <c r="B55" t="n">
-        <v>79023</v>
+        <v>8450</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>443391</v>
+        <v>443527</v>
       </c>
       <c r="R55" t="n">
-        <v>6766625</v>
+        <v>6766711</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6070,7 +6075,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>127722943</v>
+        <v>127722956</v>
       </c>
       <c r="B56" t="n">
         <v>8450</v>
@@ -6110,10 +6115,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>443527</v>
+        <v>443454</v>
       </c>
       <c r="R56" t="n">
-        <v>6766711</v>
+        <v>6766718</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6172,50 +6177,45 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>127722956</v>
+        <v>127723184</v>
       </c>
       <c r="B57" t="n">
-        <v>8450</v>
+        <v>79029</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P57" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>443454</v>
+        <v>443446</v>
       </c>
       <c r="R57" t="n">
-        <v>6766718</v>
+        <v>6766702</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6277,7 +6277,7 @@
         <v>127722841</v>
       </c>
       <c r="B58" t="n">
-        <v>79055</v>
+        <v>79061</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6371,10 +6371,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>127723167</v>
+        <v>127723175</v>
       </c>
       <c r="B59" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6406,10 +6406,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>443316</v>
+        <v>443387</v>
       </c>
       <c r="R59" t="n">
-        <v>6766701</v>
+        <v>6766658</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6468,10 +6468,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>127723153</v>
+        <v>127723106</v>
       </c>
       <c r="B60" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6503,10 +6503,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>443436</v>
+        <v>443516</v>
       </c>
       <c r="R60" t="n">
-        <v>6766648</v>
+        <v>6766720</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6568,7 +6568,7 @@
         <v>127723119</v>
       </c>
       <c r="B61" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6662,10 +6662,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>127723106</v>
+        <v>127723153</v>
       </c>
       <c r="B62" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6697,10 +6697,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>443516</v>
+        <v>443436</v>
       </c>
       <c r="R62" t="n">
-        <v>6766720</v>
+        <v>6766648</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6759,10 +6759,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>127723188</v>
+        <v>127723167</v>
       </c>
       <c r="B63" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6794,10 +6794,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>443454</v>
+        <v>443316</v>
       </c>
       <c r="R63" t="n">
-        <v>6766724</v>
+        <v>6766701</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6856,10 +6856,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>127723175</v>
+        <v>127723188</v>
       </c>
       <c r="B64" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6891,10 +6891,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>443387</v>
+        <v>443454</v>
       </c>
       <c r="R64" t="n">
-        <v>6766658</v>
+        <v>6766724</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -6956,7 +6956,7 @@
         <v>127723134</v>
       </c>
       <c r="B65" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7050,32 +7050,32 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>127723065</v>
+        <v>127723177</v>
       </c>
       <c r="B66" t="n">
-        <v>91502</v>
+        <v>79029</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>1503</v>
+        <v>6425</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7085,10 +7085,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>443425</v>
+        <v>443397</v>
       </c>
       <c r="R66" t="n">
-        <v>6766668</v>
+        <v>6766673</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7147,10 +7147,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>127723177</v>
+        <v>127723158</v>
       </c>
       <c r="B67" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7182,10 +7182,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>443397</v>
+        <v>443312</v>
       </c>
       <c r="R67" t="n">
-        <v>6766673</v>
+        <v>6766818</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7244,45 +7244,45 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>127729137</v>
+        <v>127723065</v>
       </c>
       <c r="B68" t="n">
-        <v>79023</v>
+        <v>91510</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6425</v>
+        <v>1503</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Oxeråsen S. om, Dlr</t>
+          <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>443391</v>
+        <v>443425</v>
       </c>
       <c r="R68" t="n">
-        <v>6766598</v>
+        <v>6766668</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7312,50 +7312,39 @@
           <t>2025-08-21</t>
         </is>
       </c>
-      <c r="Z68" t="inlineStr">
-        <is>
-          <t>14:00</t>
-        </is>
-      </c>
       <c r="AA68" t="inlineStr">
         <is>
           <t>2025-08-21</t>
         </is>
       </c>
-      <c r="AB68" t="inlineStr">
-        <is>
-          <t>14:00</t>
-        </is>
-      </c>
       <c r="AD68" t="b">
         <v>0</v>
       </c>
       <c r="AE68" t="b">
         <v>0</v>
       </c>
-      <c r="AF68" t="inlineStr"/>
       <c r="AG68" t="b">
         <v>0</v>
       </c>
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>127723158</v>
+        <v>127722847</v>
       </c>
       <c r="B69" t="n">
-        <v>79023</v>
+        <v>79061</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7363,21 +7352,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7387,10 +7376,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>443312</v>
+        <v>443320</v>
       </c>
       <c r="R69" t="n">
-        <v>6766818</v>
+        <v>6766703</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7452,7 +7441,7 @@
         <v>127723150</v>
       </c>
       <c r="B70" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7546,10 +7535,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>127722847</v>
+        <v>127729137</v>
       </c>
       <c r="B71" t="n">
-        <v>79055</v>
+        <v>79029</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7557,34 +7546,34 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Oxeråsen, Dlr</t>
+          <t>Oxeråsen S. om, Dlr</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>443320</v>
+        <v>443391</v>
       </c>
       <c r="R71" t="n">
-        <v>6766703</v>
+        <v>6766598</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7614,29 +7603,40 @@
           <t>2025-08-21</t>
         </is>
       </c>
+      <c r="Z71" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
       <c r="AA71" t="inlineStr">
         <is>
           <t>2025-08-21</t>
         </is>
       </c>
+      <c r="AB71" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
       <c r="AD71" t="b">
         <v>0</v>
       </c>
       <c r="AE71" t="b">
         <v>0</v>
       </c>
+      <c r="AF71" t="inlineStr"/>
       <c r="AG71" t="b">
         <v>0</v>
       </c>
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
@@ -7745,10 +7745,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>127723173</v>
+        <v>127722839</v>
       </c>
       <c r="B73" t="n">
-        <v>79023</v>
+        <v>79061</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7756,21 +7756,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -7780,10 +7780,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>443365</v>
+        <v>443554</v>
       </c>
       <c r="R73" t="n">
-        <v>6766656</v>
+        <v>6766649</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7842,10 +7842,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>127723108</v>
+        <v>127723133</v>
       </c>
       <c r="B74" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7877,10 +7877,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>443483</v>
+        <v>443504</v>
       </c>
       <c r="R74" t="n">
-        <v>6766725</v>
+        <v>6766593</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -7939,10 +7939,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>127722839</v>
+        <v>127723090</v>
       </c>
       <c r="B75" t="n">
-        <v>79055</v>
+        <v>79029</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7950,21 +7950,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -7974,10 +7974,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>443554</v>
+        <v>443593</v>
       </c>
       <c r="R75" t="n">
-        <v>6766649</v>
+        <v>6766653</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8036,10 +8036,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>127723133</v>
+        <v>127723173</v>
       </c>
       <c r="B76" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8071,10 +8071,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>443504</v>
+        <v>443365</v>
       </c>
       <c r="R76" t="n">
-        <v>6766593</v>
+        <v>6766656</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8133,10 +8133,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>127729092</v>
+        <v>127723108</v>
       </c>
       <c r="B77" t="n">
-        <v>78781</v>
+        <v>79029</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8144,34 +8144,34 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Oxeråsen S. om, Dlr</t>
+          <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>443381</v>
+        <v>443483</v>
       </c>
       <c r="R77" t="n">
-        <v>6766668</v>
+        <v>6766725</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8201,50 +8201,39 @@
           <t>2025-08-21</t>
         </is>
       </c>
-      <c r="Z77" t="inlineStr">
-        <is>
-          <t>13:51</t>
-        </is>
-      </c>
       <c r="AA77" t="inlineStr">
         <is>
           <t>2025-08-21</t>
         </is>
       </c>
-      <c r="AB77" t="inlineStr">
-        <is>
-          <t>13:51</t>
-        </is>
-      </c>
       <c r="AD77" t="b">
         <v>0</v>
       </c>
       <c r="AE77" t="b">
         <v>0</v>
       </c>
-      <c r="AF77" t="inlineStr"/>
       <c r="AG77" t="b">
         <v>0</v>
       </c>
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>127723090</v>
+        <v>127729092</v>
       </c>
       <c r="B78" t="n">
-        <v>79023</v>
+        <v>78787</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8252,34 +8241,34 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Oxeråsen, Dlr</t>
+          <t>Oxeråsen S. om, Dlr</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>443593</v>
+        <v>443381</v>
       </c>
       <c r="R78" t="n">
-        <v>6766653</v>
+        <v>6766668</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8309,39 +8298,50 @@
           <t>2025-08-21</t>
         </is>
       </c>
+      <c r="Z78" t="inlineStr">
+        <is>
+          <t>13:51</t>
+        </is>
+      </c>
       <c r="AA78" t="inlineStr">
         <is>
           <t>2025-08-21</t>
         </is>
       </c>
+      <c r="AB78" t="inlineStr">
+        <is>
+          <t>13:51</t>
+        </is>
+      </c>
       <c r="AD78" t="b">
         <v>0</v>
       </c>
       <c r="AE78" t="b">
         <v>0</v>
       </c>
+      <c r="AF78" t="inlineStr"/>
       <c r="AG78" t="b">
         <v>0</v>
       </c>
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>127723104</v>
+        <v>127723571</v>
       </c>
       <c r="B79" t="n">
-        <v>79023</v>
+        <v>78696</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8349,21 +8349,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8373,10 +8373,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>443536</v>
+        <v>443426</v>
       </c>
       <c r="R79" t="n">
-        <v>6766704</v>
+        <v>6766668</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8435,10 +8435,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>127723571</v>
+        <v>127723156</v>
       </c>
       <c r="B80" t="n">
-        <v>78690</v>
+        <v>79029</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8446,21 +8446,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8470,10 +8470,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>443426</v>
+        <v>443346</v>
       </c>
       <c r="R80" t="n">
-        <v>6766668</v>
+        <v>6766766</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8532,10 +8532,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>127723156</v>
+        <v>127723120</v>
       </c>
       <c r="B81" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8567,10 +8567,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>443346</v>
+        <v>443548</v>
       </c>
       <c r="R81" t="n">
-        <v>6766766</v>
+        <v>6766624</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8629,10 +8629,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>127723120</v>
+        <v>127723104</v>
       </c>
       <c r="B82" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8664,10 +8664,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>443548</v>
+        <v>443536</v>
       </c>
       <c r="R82" t="n">
-        <v>6766624</v>
+        <v>6766704</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8726,10 +8726,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>127723116</v>
+        <v>127723570</v>
       </c>
       <c r="B83" t="n">
-        <v>79023</v>
+        <v>78696</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8737,21 +8737,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -8761,10 +8761,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>443509</v>
+        <v>443319</v>
       </c>
       <c r="R83" t="n">
-        <v>6766633</v>
+        <v>6766670</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -8826,7 +8826,7 @@
         <v>127723092</v>
       </c>
       <c r="B84" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -8923,7 +8923,7 @@
         <v>127723178</v>
       </c>
       <c r="B85" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9017,10 +9017,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>127723171</v>
+        <v>127722888</v>
       </c>
       <c r="B86" t="n">
-        <v>79023</v>
+        <v>57669</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9028,34 +9028,39 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P86" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>443342</v>
+        <v>443481</v>
       </c>
       <c r="R86" t="n">
-        <v>6766650</v>
+        <v>6766676</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9114,10 +9119,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>127723570</v>
+        <v>127722916</v>
       </c>
       <c r="B87" t="n">
-        <v>78690</v>
+        <v>57672</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9125,34 +9130,39 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>353</v>
+        <v>100109</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P87" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>443319</v>
+        <v>443342</v>
       </c>
       <c r="R87" t="n">
-        <v>6766670</v>
+        <v>6766806</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9185,6 +9195,11 @@
       <c r="AA87" t="inlineStr">
         <is>
           <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AC87" t="inlineStr">
+        <is>
+          <t>Färska ringhack (gran), 4-5 år gamla</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9214,7 +9229,7 @@
         <v>127723541</v>
       </c>
       <c r="B88" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9313,10 +9328,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>127722916</v>
+        <v>127723171</v>
       </c>
       <c r="B89" t="n">
-        <v>57666</v>
+        <v>79029</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9324,29 +9339,24 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
-      <c r="M89" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P89" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
@@ -9356,7 +9366,7 @@
         <v>443342</v>
       </c>
       <c r="R89" t="n">
-        <v>6766806</v>
+        <v>6766650</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9389,11 +9399,6 @@
       <c r="AA89" t="inlineStr">
         <is>
           <t>2025-08-21</t>
-        </is>
-      </c>
-      <c r="AC89" t="inlineStr">
-        <is>
-          <t>Färska ringhack (gran), 4-5 år gamla</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -9420,10 +9425,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>127722888</v>
+        <v>127723116</v>
       </c>
       <c r="B90" t="n">
-        <v>57663</v>
+        <v>79029</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9431,39 +9436,34 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
-      <c r="M90" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P90" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>443481</v>
+        <v>443509</v>
       </c>
       <c r="R90" t="n">
-        <v>6766676</v>
+        <v>6766633</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9522,10 +9522,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>127723161</v>
+        <v>127723103</v>
       </c>
       <c r="B91" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9557,10 +9557,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>443305</v>
+        <v>443541</v>
       </c>
       <c r="R91" t="n">
-        <v>6766767</v>
+        <v>6766696</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9619,10 +9619,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>127723097</v>
+        <v>127723174</v>
       </c>
       <c r="B92" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9654,10 +9654,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>443561</v>
+        <v>443378</v>
       </c>
       <c r="R92" t="n">
-        <v>6766678</v>
+        <v>6766657</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9716,10 +9716,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>127723174</v>
+        <v>127723569</v>
       </c>
       <c r="B93" t="n">
-        <v>79023</v>
+        <v>78696</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9727,21 +9727,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -9751,10 +9751,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>443378</v>
+        <v>443332</v>
       </c>
       <c r="R93" t="n">
-        <v>6766657</v>
+        <v>6766677</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -9813,10 +9813,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>127723569</v>
+        <v>127723114</v>
       </c>
       <c r="B94" t="n">
-        <v>78690</v>
+        <v>79029</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -9824,21 +9824,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -9848,10 +9848,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>443332</v>
+        <v>443487</v>
       </c>
       <c r="R94" t="n">
-        <v>6766677</v>
+        <v>6766651</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -9910,10 +9910,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>127723041</v>
+        <v>127723097</v>
       </c>
       <c r="B95" t="n">
-        <v>78782</v>
+        <v>79029</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -9921,21 +9921,21 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -9945,10 +9945,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>443450</v>
+        <v>443561</v>
       </c>
       <c r="R95" t="n">
-        <v>6766735</v>
+        <v>6766678</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10007,10 +10007,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>127723103</v>
+        <v>127723161</v>
       </c>
       <c r="B96" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10042,10 +10042,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>443541</v>
+        <v>443305</v>
       </c>
       <c r="R96" t="n">
-        <v>6766696</v>
+        <v>6766767</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10107,7 +10107,7 @@
         <v>127723105</v>
       </c>
       <c r="B97" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10204,7 +10204,7 @@
         <v>127723186</v>
       </c>
       <c r="B98" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10298,10 +10298,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>127723114</v>
+        <v>127723041</v>
       </c>
       <c r="B99" t="n">
-        <v>79023</v>
+        <v>78788</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10309,21 +10309,21 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -10333,10 +10333,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>443487</v>
+        <v>443450</v>
       </c>
       <c r="R99" t="n">
-        <v>6766651</v>
+        <v>6766735</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10395,10 +10395,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>127723616</v>
+        <v>127723170</v>
       </c>
       <c r="B100" t="n">
-        <v>57666</v>
+        <v>79029</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10406,39 +10406,34 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
-      <c r="M100" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
       <c r="P100" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>443475</v>
+        <v>443333</v>
       </c>
       <c r="R100" t="n">
-        <v>6766610</v>
+        <v>6766676</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10497,10 +10492,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>127723038</v>
+        <v>127723096</v>
       </c>
       <c r="B101" t="n">
-        <v>78782</v>
+        <v>79029</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -10508,21 +10503,21 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -10532,10 +10527,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>443328</v>
+        <v>443554</v>
       </c>
       <c r="R101" t="n">
-        <v>6766721</v>
+        <v>6766650</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10597,7 +10592,7 @@
         <v>127723157</v>
       </c>
       <c r="B102" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -10691,10 +10686,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>127723182</v>
+        <v>127723139</v>
       </c>
       <c r="B103" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -10726,10 +10721,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>443444</v>
+        <v>443381</v>
       </c>
       <c r="R103" t="n">
-        <v>6766677</v>
+        <v>6766623</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -10788,10 +10783,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>127723096</v>
+        <v>127723098</v>
       </c>
       <c r="B104" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -10823,10 +10818,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>443554</v>
+        <v>443562</v>
       </c>
       <c r="R104" t="n">
-        <v>6766650</v>
+        <v>6766684</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -10885,10 +10880,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>127722842</v>
+        <v>127723616</v>
       </c>
       <c r="B105" t="n">
-        <v>79055</v>
+        <v>57672</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -10896,34 +10891,39 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>185</v>
+        <v>100109</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
+      <c r="M105" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
       <c r="P105" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>443504</v>
+        <v>443475</v>
       </c>
       <c r="R105" t="n">
-        <v>6766708</v>
+        <v>6766610</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -10982,10 +10982,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>127723183</v>
+        <v>127722842</v>
       </c>
       <c r="B106" t="n">
-        <v>79023</v>
+        <v>79061</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -10993,21 +10993,21 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -11017,10 +11017,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>443441</v>
+        <v>443504</v>
       </c>
       <c r="R106" t="n">
-        <v>6766686</v>
+        <v>6766708</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11079,10 +11079,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>127723139</v>
+        <v>127723183</v>
       </c>
       <c r="B107" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11114,10 +11114,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>443381</v>
+        <v>443441</v>
       </c>
       <c r="R107" t="n">
-        <v>6766623</v>
+        <v>6766686</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11176,10 +11176,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>127723170</v>
+        <v>127723182</v>
       </c>
       <c r="B108" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11211,10 +11211,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>443333</v>
+        <v>443444</v>
       </c>
       <c r="R108" t="n">
-        <v>6766676</v>
+        <v>6766677</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11273,45 +11273,50 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>127723098</v>
+        <v>127722929</v>
       </c>
       <c r="B109" t="n">
-        <v>79023</v>
+        <v>8450</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
+      <c r="M109" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P109" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>443562</v>
+        <v>443327</v>
       </c>
       <c r="R109" t="n">
-        <v>6766684</v>
+        <v>6766698</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11370,50 +11375,45 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>127722929</v>
+        <v>127723038</v>
       </c>
       <c r="B110" t="n">
-        <v>8450</v>
+        <v>78788</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>106545</v>
+        <v>228912</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
-      <c r="M110" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P110" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>443327</v>
+        <v>443328</v>
       </c>
       <c r="R110" t="n">
-        <v>6766698</v>
+        <v>6766721</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11472,10 +11472,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>127722904</v>
+        <v>127723137</v>
       </c>
       <c r="B111" t="n">
-        <v>57666</v>
+        <v>79029</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -11483,21 +11483,21 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -11507,10 +11507,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>443419</v>
+        <v>443418</v>
       </c>
       <c r="R111" t="n">
-        <v>6766676</v>
+        <v>6766627</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -11543,11 +11543,6 @@
       <c r="AA111" t="inlineStr">
         <is>
           <t>2025-08-21</t>
-        </is>
-      </c>
-      <c r="AC111" t="inlineStr">
-        <is>
-          <t>Äldre ringhack (tall)</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -11574,10 +11569,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>127729086</v>
+        <v>127723154</v>
       </c>
       <c r="B112" t="n">
-        <v>78782</v>
+        <v>79029</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -11585,34 +11580,34 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
       <c r="P112" t="inlineStr">
         <is>
-          <t>Oxeråsen S. om, Dlr</t>
+          <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>443359</v>
+        <v>443369</v>
       </c>
       <c r="R112" t="n">
-        <v>6766650</v>
+        <v>6766695</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -11642,50 +11637,39 @@
           <t>2025-08-21</t>
         </is>
       </c>
-      <c r="Z112" t="inlineStr">
-        <is>
-          <t>13:53</t>
-        </is>
-      </c>
       <c r="AA112" t="inlineStr">
         <is>
           <t>2025-08-21</t>
         </is>
       </c>
-      <c r="AB112" t="inlineStr">
-        <is>
-          <t>13:53</t>
-        </is>
-      </c>
       <c r="AD112" t="b">
         <v>0</v>
       </c>
       <c r="AE112" t="b">
         <v>0</v>
       </c>
-      <c r="AF112" t="inlineStr"/>
       <c r="AG112" t="b">
         <v>0</v>
       </c>
       <c r="AT112" t="inlineStr"/>
       <c r="AW112" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX112" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>127723137</v>
+        <v>127722904</v>
       </c>
       <c r="B113" t="n">
-        <v>79023</v>
+        <v>57672</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -11693,21 +11677,21 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -11717,10 +11701,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>443418</v>
+        <v>443419</v>
       </c>
       <c r="R113" t="n">
-        <v>6766627</v>
+        <v>6766676</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -11753,6 +11737,11 @@
       <c r="AA113" t="inlineStr">
         <is>
           <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AC113" t="inlineStr">
+        <is>
+          <t>Äldre ringhack (tall)</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -11782,7 +11771,7 @@
         <v>127723136</v>
       </c>
       <c r="B114" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -11876,10 +11865,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>127723154</v>
+        <v>127723172</v>
       </c>
       <c r="B115" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -11911,10 +11900,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>443369</v>
+        <v>443356</v>
       </c>
       <c r="R115" t="n">
-        <v>6766695</v>
+        <v>6766650</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -11973,10 +11962,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>127723172</v>
+        <v>127723160</v>
       </c>
       <c r="B116" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -12008,10 +11997,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>443356</v>
+        <v>443309</v>
       </c>
       <c r="R116" t="n">
-        <v>6766650</v>
+        <v>6766785</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12070,10 +12059,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>127723160</v>
+        <v>127729086</v>
       </c>
       <c r="B117" t="n">
-        <v>79023</v>
+        <v>78788</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -12081,34 +12070,34 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
       <c r="P117" t="inlineStr">
         <is>
-          <t>Oxeråsen, Dlr</t>
+          <t>Oxeråsen S. om, Dlr</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>443309</v>
+        <v>443359</v>
       </c>
       <c r="R117" t="n">
-        <v>6766785</v>
+        <v>6766650</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12138,79 +12127,85 @@
           <t>2025-08-21</t>
         </is>
       </c>
+      <c r="Z117" t="inlineStr">
+        <is>
+          <t>13:53</t>
+        </is>
+      </c>
       <c r="AA117" t="inlineStr">
         <is>
           <t>2025-08-21</t>
         </is>
       </c>
+      <c r="AB117" t="inlineStr">
+        <is>
+          <t>13:53</t>
+        </is>
+      </c>
       <c r="AD117" t="b">
         <v>0</v>
       </c>
       <c r="AE117" t="b">
         <v>0</v>
       </c>
+      <c r="AF117" t="inlineStr"/>
       <c r="AG117" t="b">
         <v>0</v>
       </c>
       <c r="AT117" t="inlineStr"/>
       <c r="AW117" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX117" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>127722948</v>
+        <v>127723113</v>
       </c>
       <c r="B118" t="n">
-        <v>8450</v>
+        <v>79029</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
-      <c r="M118" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P118" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>443457</v>
+        <v>443487</v>
       </c>
       <c r="R118" t="n">
-        <v>6766613</v>
+        <v>6766675</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12269,10 +12264,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>127723113</v>
+        <v>127723135</v>
       </c>
       <c r="B119" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -12304,10 +12299,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>443487</v>
+        <v>443454</v>
       </c>
       <c r="R119" t="n">
-        <v>6766675</v>
+        <v>6766614</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -12366,10 +12361,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>127723135</v>
+        <v>127723176</v>
       </c>
       <c r="B120" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -12401,10 +12396,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>443454</v>
+        <v>443407</v>
       </c>
       <c r="R120" t="n">
-        <v>6766614</v>
+        <v>6766653</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -12466,7 +12461,7 @@
         <v>127723163</v>
       </c>
       <c r="B121" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -12560,10 +12555,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>127723176</v>
+        <v>127722903</v>
       </c>
       <c r="B122" t="n">
-        <v>79023</v>
+        <v>57672</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -12571,21 +12566,21 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -12595,10 +12590,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>443407</v>
+        <v>443382</v>
       </c>
       <c r="R122" t="n">
-        <v>6766653</v>
+        <v>6766657</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -12631,6 +12626,11 @@
       <c r="AA122" t="inlineStr">
         <is>
           <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AC122" t="inlineStr">
+        <is>
+          <t>Äldre ringhack (tall)</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -12657,45 +12657,50 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>127722903</v>
+        <v>127722955</v>
       </c>
       <c r="B123" t="n">
-        <v>57666</v>
+        <v>8450</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>100109</v>
+        <v>106545</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
+      <c r="M123" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P123" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>443382</v>
+        <v>443397</v>
       </c>
       <c r="R123" t="n">
-        <v>6766657</v>
+        <v>6766653</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -12728,11 +12733,6 @@
       <c r="AA123" t="inlineStr">
         <is>
           <t>2025-08-21</t>
-        </is>
-      </c>
-      <c r="AC123" t="inlineStr">
-        <is>
-          <t>Äldre ringhack (tall)</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -12759,7 +12759,7 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>127722955</v>
+        <v>127722948</v>
       </c>
       <c r="B124" t="n">
         <v>8450</v>
@@ -12799,10 +12799,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>443397</v>
+        <v>443457</v>
       </c>
       <c r="R124" t="n">
-        <v>6766653</v>
+        <v>6766613</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -12864,7 +12864,7 @@
         <v>127723555</v>
       </c>
       <c r="B125" t="n">
-        <v>92631</v>
+        <v>92639</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -12958,50 +12958,45 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>127722954</v>
+        <v>127723140</v>
       </c>
       <c r="B126" t="n">
-        <v>8450</v>
+        <v>79029</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
-      <c r="M126" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P126" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>443348</v>
+        <v>443370</v>
       </c>
       <c r="R126" t="n">
-        <v>6766646</v>
+        <v>6766624</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -13060,50 +13055,45 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>127722951</v>
+        <v>127723094</v>
       </c>
       <c r="B127" t="n">
-        <v>8450</v>
+        <v>79029</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
-      <c r="M127" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P127" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>443377</v>
+        <v>443557</v>
       </c>
       <c r="R127" t="n">
-        <v>6766686</v>
+        <v>6766635</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -13162,45 +13152,50 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>127723037</v>
+        <v>127722954</v>
       </c>
       <c r="B128" t="n">
-        <v>78782</v>
+        <v>8450</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>228912</v>
+        <v>106545</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
+      <c r="M128" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P128" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>443509</v>
+        <v>443348</v>
       </c>
       <c r="R128" t="n">
-        <v>6766722</v>
+        <v>6766646</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -13259,45 +13254,50 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>127723118</v>
+        <v>127722951</v>
       </c>
       <c r="B129" t="n">
-        <v>79023</v>
+        <v>8450</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
+      <c r="M129" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P129" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>443519</v>
+        <v>443377</v>
       </c>
       <c r="R129" t="n">
-        <v>6766624</v>
+        <v>6766686</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -13356,10 +13356,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>127723140</v>
+        <v>127723165</v>
       </c>
       <c r="B130" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -13391,10 +13391,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>443370</v>
+        <v>443327</v>
       </c>
       <c r="R130" t="n">
-        <v>6766624</v>
+        <v>6766717</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -13453,10 +13453,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>127723165</v>
+        <v>127723118</v>
       </c>
       <c r="B131" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -13488,10 +13488,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>443327</v>
+        <v>443519</v>
       </c>
       <c r="R131" t="n">
-        <v>6766717</v>
+        <v>6766624</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -13550,10 +13550,10 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>127723094</v>
+        <v>127723037</v>
       </c>
       <c r="B132" t="n">
-        <v>79023</v>
+        <v>78788</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -13561,21 +13561,21 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
@@ -13585,10 +13585,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>443557</v>
+        <v>443509</v>
       </c>
       <c r="R132" t="n">
-        <v>6766635</v>
+        <v>6766722</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -13650,7 +13650,7 @@
         <v>127723162</v>
       </c>
       <c r="B133" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -13747,7 +13747,7 @@
         <v>127723111</v>
       </c>
       <c r="B134" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -13844,7 +13844,7 @@
         <v>127722855</v>
       </c>
       <c r="B135" t="n">
-        <v>79612</v>
+        <v>79618</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -13941,7 +13941,7 @@
         <v>127723619</v>
       </c>
       <c r="B136" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -14048,7 +14048,7 @@
         <v>127736007</v>
       </c>
       <c r="B137" t="n">
-        <v>91361</v>
+        <v>91369</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -14155,7 +14155,7 @@
         <v>127736019</v>
       </c>
       <c r="B138" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -14262,7 +14262,7 @@
         <v>127785482</v>
       </c>
       <c r="B139" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -14369,7 +14369,7 @@
         <v>127785478</v>
       </c>
       <c r="B140" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -14482,7 +14482,7 @@
         <v>127785484</v>
       </c>
       <c r="B141" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -14589,7 +14589,7 @@
         <v>127785481</v>
       </c>
       <c r="B142" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -14696,7 +14696,7 @@
         <v>127785483</v>
       </c>
       <c r="B143" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -14803,7 +14803,7 @@
         <v>127785472</v>
       </c>
       <c r="B144" t="n">
-        <v>91361</v>
+        <v>91369</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -15017,7 +15017,7 @@
         <v>127795299</v>
       </c>
       <c r="B146" t="n">
-        <v>78781</v>
+        <v>78787</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -15118,7 +15118,7 @@
         <v>127795339</v>
       </c>
       <c r="B147" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>

--- a/artfynd/A 35484-2025 artfynd.xlsx
+++ b/artfynd/A 35484-2025 artfynd.xlsx
@@ -1839,45 +1839,50 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127723151</v>
+        <v>127722932</v>
       </c>
       <c r="B13" t="n">
-        <v>79029</v>
+        <v>8450</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>443430</v>
+        <v>443590</v>
       </c>
       <c r="R13" t="n">
-        <v>6766608</v>
+        <v>6766651</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2130,50 +2135,45 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127722932</v>
+        <v>127723151</v>
       </c>
       <c r="B16" t="n">
-        <v>8450</v>
+        <v>79029</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>443590</v>
+        <v>443430</v>
       </c>
       <c r="R16" t="n">
-        <v>6766651</v>
+        <v>6766608</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2431,7 +2431,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127723093</v>
+        <v>127723099</v>
       </c>
       <c r="B19" t="n">
         <v>79029</v>
@@ -2466,10 +2466,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>443572</v>
+        <v>443567</v>
       </c>
       <c r="R19" t="n">
-        <v>6766645</v>
+        <v>6766695</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2528,45 +2528,50 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127723099</v>
+        <v>127722947</v>
       </c>
       <c r="B20" t="n">
-        <v>79029</v>
+        <v>8450</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>443567</v>
+        <v>443486</v>
       </c>
       <c r="R20" t="n">
-        <v>6766695</v>
+        <v>6766604</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2625,7 +2630,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127722947</v>
+        <v>127722942</v>
       </c>
       <c r="B21" t="n">
         <v>8450</v>
@@ -2665,10 +2670,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>443486</v>
+        <v>443542</v>
       </c>
       <c r="R21" t="n">
-        <v>6766604</v>
+        <v>6766699</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2727,50 +2732,45 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127722942</v>
+        <v>127723093</v>
       </c>
       <c r="B22" t="n">
-        <v>8450</v>
+        <v>79029</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>443542</v>
+        <v>443572</v>
       </c>
       <c r="R22" t="n">
-        <v>6766699</v>
+        <v>6766645</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3023,50 +3023,45 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127722950</v>
+        <v>127722874</v>
       </c>
       <c r="B25" t="n">
-        <v>8450</v>
+        <v>91370</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>106545</v>
+        <v>5442</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>443438</v>
+        <v>443388</v>
       </c>
       <c r="R25" t="n">
-        <v>6766650</v>
+        <v>6766675</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3125,10 +3120,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127722874</v>
+        <v>127723112</v>
       </c>
       <c r="B26" t="n">
-        <v>91369</v>
+        <v>79029</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3136,21 +3131,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3160,10 +3155,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>443388</v>
+        <v>443476</v>
       </c>
       <c r="R26" t="n">
-        <v>6766675</v>
+        <v>6766681</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3416,45 +3411,50 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127723112</v>
+        <v>127722950</v>
       </c>
       <c r="B29" t="n">
-        <v>79029</v>
+        <v>8450</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>443476</v>
+        <v>443438</v>
       </c>
       <c r="R29" t="n">
-        <v>6766681</v>
+        <v>6766650</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3513,45 +3513,50 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127722875</v>
+        <v>127722945</v>
       </c>
       <c r="B30" t="n">
-        <v>91369</v>
+        <v>8450</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>5442</v>
+        <v>106545</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>443312</v>
+        <v>443568</v>
       </c>
       <c r="R30" t="n">
-        <v>6766713</v>
+        <v>6766605</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3804,50 +3809,45 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127722945</v>
+        <v>127722875</v>
       </c>
       <c r="B33" t="n">
-        <v>8450</v>
+        <v>91370</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>106545</v>
+        <v>5442</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>443568</v>
+        <v>443312</v>
       </c>
       <c r="R33" t="n">
-        <v>6766605</v>
+        <v>6766713</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3906,10 +3906,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>127723115</v>
+        <v>127722896</v>
       </c>
       <c r="B34" t="n">
-        <v>79029</v>
+        <v>57669</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3917,34 +3917,39 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>443495</v>
+        <v>443537</v>
       </c>
       <c r="R34" t="n">
-        <v>6766641</v>
+        <v>6766699</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4003,32 +4008,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127723109</v>
+        <v>127722921</v>
       </c>
       <c r="B35" t="n">
-        <v>79029</v>
+        <v>97345</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4038,10 +4043,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>443482</v>
+        <v>443330</v>
       </c>
       <c r="R35" t="n">
-        <v>6766716</v>
+        <v>6766662</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4100,45 +4105,50 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127723169</v>
+        <v>127722944</v>
       </c>
       <c r="B36" t="n">
-        <v>79029</v>
+        <v>8450</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>443321</v>
+        <v>443488</v>
       </c>
       <c r="R36" t="n">
-        <v>6766706</v>
+        <v>6766671</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4197,45 +4207,50 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127723107</v>
+        <v>127722928</v>
       </c>
       <c r="B37" t="n">
-        <v>79029</v>
+        <v>8450</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>443493</v>
+        <v>443559</v>
       </c>
       <c r="R37" t="n">
-        <v>6766717</v>
+        <v>6766616</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4294,10 +4309,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127722896</v>
+        <v>127723107</v>
       </c>
       <c r="B38" t="n">
-        <v>57669</v>
+        <v>79029</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4305,39 +4320,34 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>443537</v>
+        <v>443493</v>
       </c>
       <c r="R38" t="n">
-        <v>6766699</v>
+        <v>6766717</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4396,32 +4406,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127722921</v>
+        <v>127723109</v>
       </c>
       <c r="B39" t="n">
-        <v>97344</v>
+        <v>79029</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4431,10 +4441,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>443330</v>
+        <v>443482</v>
       </c>
       <c r="R39" t="n">
-        <v>6766662</v>
+        <v>6766716</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4493,50 +4503,45 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127722944</v>
+        <v>127723169</v>
       </c>
       <c r="B40" t="n">
-        <v>8450</v>
+        <v>79029</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>443488</v>
+        <v>443321</v>
       </c>
       <c r="R40" t="n">
-        <v>6766671</v>
+        <v>6766706</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4595,50 +4600,45 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127722928</v>
+        <v>127723115</v>
       </c>
       <c r="B41" t="n">
-        <v>8450</v>
+        <v>79029</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>443559</v>
+        <v>443495</v>
       </c>
       <c r="R41" t="n">
-        <v>6766616</v>
+        <v>6766641</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4697,32 +4697,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>127723064</v>
+        <v>127723121</v>
       </c>
       <c r="B42" t="n">
-        <v>91510</v>
+        <v>79029</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1503</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4732,10 +4732,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>443329</v>
+        <v>443558</v>
       </c>
       <c r="R42" t="n">
-        <v>6766670</v>
+        <v>6766620</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4794,10 +4794,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127722876</v>
+        <v>127723189</v>
       </c>
       <c r="B43" t="n">
-        <v>91369</v>
+        <v>79029</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4805,21 +4805,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4829,10 +4829,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>443366</v>
+        <v>443446</v>
       </c>
       <c r="R43" t="n">
-        <v>6766661</v>
+        <v>6766727</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4865,6 +4865,11 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Med grov gran i bäckmiljö</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -4891,10 +4896,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>127723189</v>
+        <v>127722876</v>
       </c>
       <c r="B44" t="n">
-        <v>79029</v>
+        <v>91370</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4902,21 +4907,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4926,10 +4931,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>443446</v>
+        <v>443366</v>
       </c>
       <c r="R44" t="n">
-        <v>6766727</v>
+        <v>6766661</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4962,11 +4967,6 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-08-21</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Med grov gran i bäckmiljö</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -4993,32 +4993,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>127723091</v>
+        <v>127723064</v>
       </c>
       <c r="B45" t="n">
-        <v>79029</v>
+        <v>91511</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>1503</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5028,10 +5028,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>443587</v>
+        <v>443329</v>
       </c>
       <c r="R45" t="n">
-        <v>6766651</v>
+        <v>6766670</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5090,7 +5090,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>127723159</v>
+        <v>127723091</v>
       </c>
       <c r="B46" t="n">
         <v>79029</v>
@@ -5125,10 +5125,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>443314</v>
+        <v>443587</v>
       </c>
       <c r="R46" t="n">
-        <v>6766811</v>
+        <v>6766651</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5187,7 +5187,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>127723121</v>
+        <v>127723159</v>
       </c>
       <c r="B47" t="n">
         <v>79029</v>
@@ -5222,10 +5222,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>443558</v>
+        <v>443314</v>
       </c>
       <c r="R47" t="n">
-        <v>6766620</v>
+        <v>6766811</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5284,45 +5284,50 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>127723102</v>
+        <v>127722957</v>
       </c>
       <c r="B48" t="n">
-        <v>79029</v>
+        <v>8450</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>443556</v>
+        <v>443457</v>
       </c>
       <c r="R48" t="n">
-        <v>6766717</v>
+        <v>6766726</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5381,10 +5386,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>127723185</v>
+        <v>127722868</v>
       </c>
       <c r="B49" t="n">
-        <v>79029</v>
+        <v>57832</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5392,34 +5397,39 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>443452</v>
+        <v>443305</v>
       </c>
       <c r="R49" t="n">
-        <v>6766711</v>
+        <v>6766767</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5478,7 +5488,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>127723180</v>
+        <v>127723185</v>
       </c>
       <c r="B50" t="n">
         <v>79029</v>
@@ -5513,10 +5523,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>443425</v>
+        <v>443452</v>
       </c>
       <c r="R50" t="n">
-        <v>6766665</v>
+        <v>6766711</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5575,7 +5585,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>127723110</v>
+        <v>127723180</v>
       </c>
       <c r="B51" t="n">
         <v>79029</v>
@@ -5610,10 +5620,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>443479</v>
+        <v>443425</v>
       </c>
       <c r="R51" t="n">
-        <v>6766703</v>
+        <v>6766665</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5672,50 +5682,45 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>127722957</v>
+        <v>127723102</v>
       </c>
       <c r="B52" t="n">
-        <v>8450</v>
+        <v>79029</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>443457</v>
+        <v>443556</v>
       </c>
       <c r="R52" t="n">
-        <v>6766726</v>
+        <v>6766717</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5774,10 +5779,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>127722868</v>
+        <v>127723110</v>
       </c>
       <c r="B53" t="n">
-        <v>57832</v>
+        <v>79029</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5785,39 +5790,34 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>443305</v>
+        <v>443479</v>
       </c>
       <c r="R53" t="n">
-        <v>6766767</v>
+        <v>6766703</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5876,45 +5876,50 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>127723138</v>
+        <v>127722943</v>
       </c>
       <c r="B54" t="n">
-        <v>79029</v>
+        <v>8450</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P54" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>443391</v>
+        <v>443527</v>
       </c>
       <c r="R54" t="n">
-        <v>6766625</v>
+        <v>6766711</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5973,7 +5978,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>127722943</v>
+        <v>127722956</v>
       </c>
       <c r="B55" t="n">
         <v>8450</v>
@@ -6013,10 +6018,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>443527</v>
+        <v>443454</v>
       </c>
       <c r="R55" t="n">
-        <v>6766711</v>
+        <v>6766718</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6075,50 +6080,45 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>127722956</v>
+        <v>127723138</v>
       </c>
       <c r="B56" t="n">
-        <v>8450</v>
+        <v>79029</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
-      <c r="M56" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P56" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>443454</v>
+        <v>443391</v>
       </c>
       <c r="R56" t="n">
-        <v>6766718</v>
+        <v>6766625</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6371,7 +6371,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>127723175</v>
+        <v>127723167</v>
       </c>
       <c r="B59" t="n">
         <v>79029</v>
@@ -6406,10 +6406,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>443387</v>
+        <v>443316</v>
       </c>
       <c r="R59" t="n">
-        <v>6766658</v>
+        <v>6766701</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6468,7 +6468,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>127723106</v>
+        <v>127723119</v>
       </c>
       <c r="B60" t="n">
         <v>79029</v>
@@ -6503,10 +6503,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>443516</v>
+        <v>443535</v>
       </c>
       <c r="R60" t="n">
-        <v>6766720</v>
+        <v>6766639</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6565,7 +6565,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>127723119</v>
+        <v>127723134</v>
       </c>
       <c r="B61" t="n">
         <v>79029</v>
@@ -6600,10 +6600,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>443535</v>
+        <v>443465</v>
       </c>
       <c r="R61" t="n">
-        <v>6766639</v>
+        <v>6766607</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6759,7 +6759,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>127723167</v>
+        <v>127723106</v>
       </c>
       <c r="B63" t="n">
         <v>79029</v>
@@ -6794,10 +6794,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>443316</v>
+        <v>443516</v>
       </c>
       <c r="R63" t="n">
-        <v>6766701</v>
+        <v>6766720</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6953,7 +6953,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>127723134</v>
+        <v>127723175</v>
       </c>
       <c r="B65" t="n">
         <v>79029</v>
@@ -6988,10 +6988,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>443465</v>
+        <v>443387</v>
       </c>
       <c r="R65" t="n">
-        <v>6766607</v>
+        <v>6766658</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7050,7 +7050,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>127723177</v>
+        <v>127723150</v>
       </c>
       <c r="B66" t="n">
         <v>79029</v>
@@ -7085,10 +7085,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>443397</v>
+        <v>443415</v>
       </c>
       <c r="R66" t="n">
-        <v>6766673</v>
+        <v>6766603</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7147,10 +7147,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>127723158</v>
+        <v>127722847</v>
       </c>
       <c r="B67" t="n">
-        <v>79029</v>
+        <v>79061</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7158,21 +7158,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7182,10 +7182,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>443312</v>
+        <v>443320</v>
       </c>
       <c r="R67" t="n">
-        <v>6766818</v>
+        <v>6766703</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7244,45 +7244,45 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>127723065</v>
+        <v>127729137</v>
       </c>
       <c r="B68" t="n">
-        <v>91510</v>
+        <v>79029</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>1503</v>
+        <v>6425</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Oxeråsen, Dlr</t>
+          <t>Oxeråsen S. om, Dlr</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>443425</v>
+        <v>443391</v>
       </c>
       <c r="R68" t="n">
-        <v>6766668</v>
+        <v>6766598</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7312,39 +7312,50 @@
           <t>2025-08-21</t>
         </is>
       </c>
+      <c r="Z68" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
       <c r="AA68" t="inlineStr">
         <is>
           <t>2025-08-21</t>
         </is>
       </c>
+      <c r="AB68" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
       <c r="AD68" t="b">
         <v>0</v>
       </c>
       <c r="AE68" t="b">
         <v>0</v>
       </c>
+      <c r="AF68" t="inlineStr"/>
       <c r="AG68" t="b">
         <v>0</v>
       </c>
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>127722847</v>
+        <v>127723158</v>
       </c>
       <c r="B69" t="n">
-        <v>79061</v>
+        <v>79029</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7352,21 +7363,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7376,10 +7387,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>443320</v>
+        <v>443312</v>
       </c>
       <c r="R69" t="n">
-        <v>6766703</v>
+        <v>6766818</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7438,7 +7449,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>127723150</v>
+        <v>127723177</v>
       </c>
       <c r="B70" t="n">
         <v>79029</v>
@@ -7473,10 +7484,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>443415</v>
+        <v>443397</v>
       </c>
       <c r="R70" t="n">
-        <v>6766603</v>
+        <v>6766673</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7535,45 +7546,50 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>127729137</v>
+        <v>127722941</v>
       </c>
       <c r="B71" t="n">
-        <v>79029</v>
+        <v>8450</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Oxeråsen S. om, Dlr</t>
+          <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>443391</v>
+        <v>443557</v>
       </c>
       <c r="R71" t="n">
-        <v>6766598</v>
+        <v>6766635</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7603,90 +7619,74 @@
           <t>2025-08-21</t>
         </is>
       </c>
-      <c r="Z71" t="inlineStr">
-        <is>
-          <t>14:00</t>
-        </is>
-      </c>
       <c r="AA71" t="inlineStr">
         <is>
           <t>2025-08-21</t>
         </is>
       </c>
-      <c r="AB71" t="inlineStr">
-        <is>
-          <t>14:00</t>
-        </is>
-      </c>
       <c r="AD71" t="b">
         <v>0</v>
       </c>
       <c r="AE71" t="b">
         <v>0</v>
       </c>
-      <c r="AF71" t="inlineStr"/>
       <c r="AG71" t="b">
         <v>0</v>
       </c>
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>127722941</v>
+        <v>127723065</v>
       </c>
       <c r="B72" t="n">
-        <v>8450</v>
+        <v>91511</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>106545</v>
+        <v>1503</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
-      <c r="M72" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P72" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>443557</v>
+        <v>443425</v>
       </c>
       <c r="R72" t="n">
-        <v>6766635</v>
+        <v>6766668</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7745,10 +7745,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>127722839</v>
+        <v>127723133</v>
       </c>
       <c r="B73" t="n">
-        <v>79061</v>
+        <v>79029</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7756,21 +7756,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -7780,10 +7780,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>443554</v>
+        <v>443504</v>
       </c>
       <c r="R73" t="n">
-        <v>6766649</v>
+        <v>6766593</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7842,7 +7842,7 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>127723133</v>
+        <v>127723173</v>
       </c>
       <c r="B74" t="n">
         <v>79029</v>
@@ -7877,10 +7877,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>443504</v>
+        <v>443365</v>
       </c>
       <c r="R74" t="n">
-        <v>6766593</v>
+        <v>6766656</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -7939,10 +7939,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>127723090</v>
+        <v>127729092</v>
       </c>
       <c r="B75" t="n">
-        <v>79029</v>
+        <v>78787</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7950,34 +7950,34 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Oxeråsen, Dlr</t>
+          <t>Oxeråsen S. om, Dlr</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>443593</v>
+        <v>443381</v>
       </c>
       <c r="R75" t="n">
-        <v>6766653</v>
+        <v>6766668</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8007,36 +8007,47 @@
           <t>2025-08-21</t>
         </is>
       </c>
+      <c r="Z75" t="inlineStr">
+        <is>
+          <t>13:51</t>
+        </is>
+      </c>
       <c r="AA75" t="inlineStr">
         <is>
           <t>2025-08-21</t>
         </is>
       </c>
+      <c r="AB75" t="inlineStr">
+        <is>
+          <t>13:51</t>
+        </is>
+      </c>
       <c r="AD75" t="b">
         <v>0</v>
       </c>
       <c r="AE75" t="b">
         <v>0</v>
       </c>
+      <c r="AF75" t="inlineStr"/>
       <c r="AG75" t="b">
         <v>0</v>
       </c>
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>127723173</v>
+        <v>127723108</v>
       </c>
       <c r="B76" t="n">
         <v>79029</v>
@@ -8071,10 +8082,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>443365</v>
+        <v>443483</v>
       </c>
       <c r="R76" t="n">
-        <v>6766656</v>
+        <v>6766725</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8133,10 +8144,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>127723108</v>
+        <v>127722839</v>
       </c>
       <c r="B77" t="n">
-        <v>79029</v>
+        <v>79061</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8144,21 +8155,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8168,10 +8179,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>443483</v>
+        <v>443554</v>
       </c>
       <c r="R77" t="n">
-        <v>6766725</v>
+        <v>6766649</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8230,10 +8241,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>127729092</v>
+        <v>127723090</v>
       </c>
       <c r="B78" t="n">
-        <v>78787</v>
+        <v>79029</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8241,34 +8252,34 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Oxeråsen S. om, Dlr</t>
+          <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>443381</v>
+        <v>443593</v>
       </c>
       <c r="R78" t="n">
-        <v>6766668</v>
+        <v>6766653</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8298,40 +8309,29 @@
           <t>2025-08-21</t>
         </is>
       </c>
-      <c r="Z78" t="inlineStr">
-        <is>
-          <t>13:51</t>
-        </is>
-      </c>
       <c r="AA78" t="inlineStr">
         <is>
           <t>2025-08-21</t>
         </is>
       </c>
-      <c r="AB78" t="inlineStr">
-        <is>
-          <t>13:51</t>
-        </is>
-      </c>
       <c r="AD78" t="b">
         <v>0</v>
       </c>
       <c r="AE78" t="b">
         <v>0</v>
       </c>
-      <c r="AF78" t="inlineStr"/>
       <c r="AG78" t="b">
         <v>0</v>
       </c>
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
@@ -8726,10 +8726,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>127723570</v>
+        <v>127723116</v>
       </c>
       <c r="B83" t="n">
-        <v>78696</v>
+        <v>79029</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8737,21 +8737,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -8761,10 +8761,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>443319</v>
+        <v>443509</v>
       </c>
       <c r="R83" t="n">
-        <v>6766670</v>
+        <v>6766633</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -8823,7 +8823,7 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>127723092</v>
+        <v>127723178</v>
       </c>
       <c r="B84" t="n">
         <v>79029</v>
@@ -8858,10 +8858,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>443572</v>
+        <v>443402</v>
       </c>
       <c r="R84" t="n">
-        <v>6766650</v>
+        <v>6766682</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -8920,7 +8920,7 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>127723178</v>
+        <v>127723092</v>
       </c>
       <c r="B85" t="n">
         <v>79029</v>
@@ -8955,10 +8955,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>443402</v>
+        <v>443572</v>
       </c>
       <c r="R85" t="n">
-        <v>6766682</v>
+        <v>6766650</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9017,10 +9017,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>127722888</v>
+        <v>127723171</v>
       </c>
       <c r="B86" t="n">
-        <v>57669</v>
+        <v>79029</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9028,39 +9028,34 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
-      <c r="M86" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P86" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>443481</v>
+        <v>443342</v>
       </c>
       <c r="R86" t="n">
-        <v>6766676</v>
+        <v>6766650</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9119,10 +9114,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>127722916</v>
+        <v>127722888</v>
       </c>
       <c r="B87" t="n">
-        <v>57672</v>
+        <v>57669</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9130,16 +9125,16 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
@@ -9150,7 +9145,7 @@
       <c r="I87" t="inlineStr"/>
       <c r="M87" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P87" t="inlineStr">
@@ -9159,10 +9154,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>443342</v>
+        <v>443481</v>
       </c>
       <c r="R87" t="n">
-        <v>6766806</v>
+        <v>6766676</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9195,11 +9190,6 @@
       <c r="AA87" t="inlineStr">
         <is>
           <t>2025-08-21</t>
-        </is>
-      </c>
-      <c r="AC87" t="inlineStr">
-        <is>
-          <t>Färska ringhack (gran), 4-5 år gamla</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9328,10 +9318,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>127723171</v>
+        <v>127722916</v>
       </c>
       <c r="B89" t="n">
-        <v>79029</v>
+        <v>57672</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9339,24 +9329,29 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P89" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
@@ -9366,7 +9361,7 @@
         <v>443342</v>
       </c>
       <c r="R89" t="n">
-        <v>6766650</v>
+        <v>6766806</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9399,6 +9394,11 @@
       <c r="AA89" t="inlineStr">
         <is>
           <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AC89" t="inlineStr">
+        <is>
+          <t>Färska ringhack (gran), 4-5 år gamla</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -9425,10 +9425,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>127723116</v>
+        <v>127723570</v>
       </c>
       <c r="B90" t="n">
-        <v>79029</v>
+        <v>78696</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9436,21 +9436,21 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9460,10 +9460,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>443509</v>
+        <v>443319</v>
       </c>
       <c r="R90" t="n">
-        <v>6766633</v>
+        <v>6766670</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9522,7 +9522,7 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>127723103</v>
+        <v>127723105</v>
       </c>
       <c r="B91" t="n">
         <v>79029</v>
@@ -9557,10 +9557,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>443541</v>
+        <v>443525</v>
       </c>
       <c r="R91" t="n">
-        <v>6766696</v>
+        <v>6766717</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9619,7 +9619,7 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>127723174</v>
+        <v>127723103</v>
       </c>
       <c r="B92" t="n">
         <v>79029</v>
@@ -9654,10 +9654,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>443378</v>
+        <v>443541</v>
       </c>
       <c r="R92" t="n">
-        <v>6766657</v>
+        <v>6766696</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9716,10 +9716,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>127723569</v>
+        <v>127723161</v>
       </c>
       <c r="B93" t="n">
-        <v>78696</v>
+        <v>79029</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9727,21 +9727,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -9751,10 +9751,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>443332</v>
+        <v>443305</v>
       </c>
       <c r="R93" t="n">
-        <v>6766677</v>
+        <v>6766767</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -9813,7 +9813,7 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>127723114</v>
+        <v>127723186</v>
       </c>
       <c r="B94" t="n">
         <v>79029</v>
@@ -9848,10 +9848,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>443487</v>
+        <v>443454</v>
       </c>
       <c r="R94" t="n">
-        <v>6766651</v>
+        <v>6766738</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -9910,7 +9910,7 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>127723097</v>
+        <v>127723174</v>
       </c>
       <c r="B95" t="n">
         <v>79029</v>
@@ -9945,10 +9945,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>443561</v>
+        <v>443378</v>
       </c>
       <c r="R95" t="n">
-        <v>6766678</v>
+        <v>6766657</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10007,10 +10007,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>127723161</v>
+        <v>127723041</v>
       </c>
       <c r="B96" t="n">
-        <v>79029</v>
+        <v>78788</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10018,21 +10018,21 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10042,10 +10042,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>443305</v>
+        <v>443450</v>
       </c>
       <c r="R96" t="n">
-        <v>6766767</v>
+        <v>6766735</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10104,10 +10104,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>127723105</v>
+        <v>127723569</v>
       </c>
       <c r="B97" t="n">
-        <v>79029</v>
+        <v>78696</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10115,21 +10115,21 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -10139,10 +10139,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>443525</v>
+        <v>443332</v>
       </c>
       <c r="R97" t="n">
-        <v>6766717</v>
+        <v>6766677</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10201,7 +10201,7 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>127723186</v>
+        <v>127723114</v>
       </c>
       <c r="B98" t="n">
         <v>79029</v>
@@ -10236,10 +10236,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>443454</v>
+        <v>443487</v>
       </c>
       <c r="R98" t="n">
-        <v>6766738</v>
+        <v>6766651</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10298,10 +10298,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>127723041</v>
+        <v>127723097</v>
       </c>
       <c r="B99" t="n">
-        <v>78788</v>
+        <v>79029</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10309,21 +10309,21 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -10333,10 +10333,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>443450</v>
+        <v>443561</v>
       </c>
       <c r="R99" t="n">
-        <v>6766735</v>
+        <v>6766678</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10395,7 +10395,7 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>127723170</v>
+        <v>127723183</v>
       </c>
       <c r="B100" t="n">
         <v>79029</v>
@@ -10430,10 +10430,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>443333</v>
+        <v>443441</v>
       </c>
       <c r="R100" t="n">
-        <v>6766676</v>
+        <v>6766686</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10492,7 +10492,7 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>127723096</v>
+        <v>127723139</v>
       </c>
       <c r="B101" t="n">
         <v>79029</v>
@@ -10527,10 +10527,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>443554</v>
+        <v>443381</v>
       </c>
       <c r="R101" t="n">
-        <v>6766650</v>
+        <v>6766623</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10686,7 +10686,7 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>127723139</v>
+        <v>127723182</v>
       </c>
       <c r="B103" t="n">
         <v>79029</v>
@@ -10721,10 +10721,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>443381</v>
+        <v>443444</v>
       </c>
       <c r="R103" t="n">
-        <v>6766623</v>
+        <v>6766677</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -10783,7 +10783,7 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>127723098</v>
+        <v>127723170</v>
       </c>
       <c r="B104" t="n">
         <v>79029</v>
@@ -10818,10 +10818,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>443562</v>
+        <v>443333</v>
       </c>
       <c r="R104" t="n">
-        <v>6766684</v>
+        <v>6766676</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -10880,10 +10880,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>127723616</v>
+        <v>127723098</v>
       </c>
       <c r="B105" t="n">
-        <v>57672</v>
+        <v>79029</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -10891,39 +10891,34 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
-      <c r="M105" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
       <c r="P105" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>443475</v>
+        <v>443562</v>
       </c>
       <c r="R105" t="n">
-        <v>6766610</v>
+        <v>6766684</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -10982,10 +10977,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>127722842</v>
+        <v>127723038</v>
       </c>
       <c r="B106" t="n">
-        <v>79061</v>
+        <v>78788</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -10993,21 +10988,21 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>185</v>
+        <v>228912</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -11017,10 +11012,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>443504</v>
+        <v>443328</v>
       </c>
       <c r="R106" t="n">
-        <v>6766708</v>
+        <v>6766721</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11079,7 +11074,7 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>127723183</v>
+        <v>127723096</v>
       </c>
       <c r="B107" t="n">
         <v>79029</v>
@@ -11114,10 +11109,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>443441</v>
+        <v>443554</v>
       </c>
       <c r="R107" t="n">
-        <v>6766686</v>
+        <v>6766650</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11176,10 +11171,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>127723182</v>
+        <v>127723616</v>
       </c>
       <c r="B108" t="n">
-        <v>79029</v>
+        <v>57672</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11187,34 +11182,39 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
+      <c r="M108" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
       <c r="P108" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>443444</v>
+        <v>443475</v>
       </c>
       <c r="R108" t="n">
-        <v>6766677</v>
+        <v>6766610</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11375,10 +11375,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>127723038</v>
+        <v>127722842</v>
       </c>
       <c r="B110" t="n">
-        <v>78788</v>
+        <v>79061</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -11386,21 +11386,21 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>228912</v>
+        <v>185</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -11410,10 +11410,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>443328</v>
+        <v>443504</v>
       </c>
       <c r="R110" t="n">
-        <v>6766721</v>
+        <v>6766708</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11472,10 +11472,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>127723137</v>
+        <v>127729086</v>
       </c>
       <c r="B111" t="n">
-        <v>79029</v>
+        <v>78788</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -11483,34 +11483,34 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
       <c r="P111" t="inlineStr">
         <is>
-          <t>Oxeråsen, Dlr</t>
+          <t>Oxeråsen S. om, Dlr</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>443418</v>
+        <v>443359</v>
       </c>
       <c r="R111" t="n">
-        <v>6766627</v>
+        <v>6766650</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -11540,36 +11540,47 @@
           <t>2025-08-21</t>
         </is>
       </c>
+      <c r="Z111" t="inlineStr">
+        <is>
+          <t>13:53</t>
+        </is>
+      </c>
       <c r="AA111" t="inlineStr">
         <is>
           <t>2025-08-21</t>
         </is>
       </c>
+      <c r="AB111" t="inlineStr">
+        <is>
+          <t>13:53</t>
+        </is>
+      </c>
       <c r="AD111" t="b">
         <v>0</v>
       </c>
       <c r="AE111" t="b">
         <v>0</v>
       </c>
+      <c r="AF111" t="inlineStr"/>
       <c r="AG111" t="b">
         <v>0</v>
       </c>
       <c r="AT111" t="inlineStr"/>
       <c r="AW111" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX111" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>127723154</v>
+        <v>127723137</v>
       </c>
       <c r="B112" t="n">
         <v>79029</v>
@@ -11604,10 +11615,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>443369</v>
+        <v>443418</v>
       </c>
       <c r="R112" t="n">
-        <v>6766695</v>
+        <v>6766627</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -11666,10 +11677,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>127722904</v>
+        <v>127723154</v>
       </c>
       <c r="B113" t="n">
-        <v>57672</v>
+        <v>79029</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -11677,21 +11688,21 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -11701,10 +11712,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>443419</v>
+        <v>443369</v>
       </c>
       <c r="R113" t="n">
-        <v>6766676</v>
+        <v>6766695</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -11737,11 +11748,6 @@
       <c r="AA113" t="inlineStr">
         <is>
           <t>2025-08-21</t>
-        </is>
-      </c>
-      <c r="AC113" t="inlineStr">
-        <is>
-          <t>Äldre ringhack (tall)</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -11768,7 +11774,7 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>127723136</v>
+        <v>127723172</v>
       </c>
       <c r="B114" t="n">
         <v>79029</v>
@@ -11803,10 +11809,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>443438</v>
+        <v>443356</v>
       </c>
       <c r="R114" t="n">
-        <v>6766628</v>
+        <v>6766650</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -11865,7 +11871,7 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>127723172</v>
+        <v>127723136</v>
       </c>
       <c r="B115" t="n">
         <v>79029</v>
@@ -11900,10 +11906,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>443356</v>
+        <v>443438</v>
       </c>
       <c r="R115" t="n">
-        <v>6766650</v>
+        <v>6766628</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12059,10 +12065,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>127729086</v>
+        <v>127722904</v>
       </c>
       <c r="B117" t="n">
-        <v>78788</v>
+        <v>57672</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -12070,34 +12076,34 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
       <c r="P117" t="inlineStr">
         <is>
-          <t>Oxeråsen S. om, Dlr</t>
+          <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>443359</v>
+        <v>443419</v>
       </c>
       <c r="R117" t="n">
-        <v>6766650</v>
+        <v>6766676</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12127,19 +12133,14 @@
           <t>2025-08-21</t>
         </is>
       </c>
-      <c r="Z117" t="inlineStr">
-        <is>
-          <t>13:53</t>
-        </is>
-      </c>
       <c r="AA117" t="inlineStr">
         <is>
           <t>2025-08-21</t>
         </is>
       </c>
-      <c r="AB117" t="inlineStr">
-        <is>
-          <t>13:53</t>
+      <c r="AC117" t="inlineStr">
+        <is>
+          <t>Äldre ringhack (tall)</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -12148,26 +12149,25 @@
       <c r="AE117" t="b">
         <v>0</v>
       </c>
-      <c r="AF117" t="inlineStr"/>
       <c r="AG117" t="b">
         <v>0</v>
       </c>
       <c r="AT117" t="inlineStr"/>
       <c r="AW117" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX117" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>127723113</v>
+        <v>127723135</v>
       </c>
       <c r="B118" t="n">
         <v>79029</v>
@@ -12202,10 +12202,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>443487</v>
+        <v>443454</v>
       </c>
       <c r="R118" t="n">
-        <v>6766675</v>
+        <v>6766614</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12264,7 +12264,7 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>127723135</v>
+        <v>127723163</v>
       </c>
       <c r="B119" t="n">
         <v>79029</v>
@@ -12299,10 +12299,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>443454</v>
+        <v>443332</v>
       </c>
       <c r="R119" t="n">
-        <v>6766614</v>
+        <v>6766744</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -12458,10 +12458,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>127723163</v>
+        <v>127722903</v>
       </c>
       <c r="B121" t="n">
-        <v>79029</v>
+        <v>57672</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -12469,21 +12469,21 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -12493,10 +12493,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>443332</v>
+        <v>443382</v>
       </c>
       <c r="R121" t="n">
-        <v>6766744</v>
+        <v>6766657</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -12529,6 +12529,11 @@
       <c r="AA121" t="inlineStr">
         <is>
           <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AC121" t="inlineStr">
+        <is>
+          <t>Äldre ringhack (tall)</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -12555,45 +12560,50 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>127722903</v>
+        <v>127722955</v>
       </c>
       <c r="B122" t="n">
-        <v>57672</v>
+        <v>8450</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>100109</v>
+        <v>106545</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
+      <c r="M122" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P122" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>443382</v>
+        <v>443397</v>
       </c>
       <c r="R122" t="n">
-        <v>6766657</v>
+        <v>6766653</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -12626,11 +12636,6 @@
       <c r="AA122" t="inlineStr">
         <is>
           <t>2025-08-21</t>
-        </is>
-      </c>
-      <c r="AC122" t="inlineStr">
-        <is>
-          <t>Äldre ringhack (tall)</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -12657,7 +12662,7 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>127722955</v>
+        <v>127722948</v>
       </c>
       <c r="B123" t="n">
         <v>8450</v>
@@ -12697,10 +12702,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>443397</v>
+        <v>443457</v>
       </c>
       <c r="R123" t="n">
-        <v>6766653</v>
+        <v>6766613</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -12759,50 +12764,45 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>127722948</v>
+        <v>127723113</v>
       </c>
       <c r="B124" t="n">
-        <v>8450</v>
+        <v>79029</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
-      <c r="M124" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P124" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>443457</v>
+        <v>443487</v>
       </c>
       <c r="R124" t="n">
-        <v>6766613</v>
+        <v>6766675</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -12864,7 +12864,7 @@
         <v>127723555</v>
       </c>
       <c r="B125" t="n">
-        <v>92639</v>
+        <v>92640</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -12958,45 +12958,50 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>127723140</v>
+        <v>127722954</v>
       </c>
       <c r="B126" t="n">
-        <v>79029</v>
+        <v>8450</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
+      <c r="M126" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P126" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>443370</v>
+        <v>443348</v>
       </c>
       <c r="R126" t="n">
-        <v>6766624</v>
+        <v>6766646</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -13055,10 +13060,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>127723094</v>
+        <v>127723037</v>
       </c>
       <c r="B127" t="n">
-        <v>79029</v>
+        <v>78788</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -13066,21 +13071,21 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -13090,10 +13095,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>443557</v>
+        <v>443509</v>
       </c>
       <c r="R127" t="n">
-        <v>6766635</v>
+        <v>6766722</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -13152,50 +13157,45 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>127722954</v>
+        <v>127723094</v>
       </c>
       <c r="B128" t="n">
-        <v>8450</v>
+        <v>79029</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
-      <c r="M128" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P128" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>443348</v>
+        <v>443557</v>
       </c>
       <c r="R128" t="n">
-        <v>6766646</v>
+        <v>6766635</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -13254,50 +13254,45 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>127722951</v>
+        <v>127723165</v>
       </c>
       <c r="B129" t="n">
-        <v>8450</v>
+        <v>79029</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
-      <c r="M129" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P129" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>443377</v>
+        <v>443327</v>
       </c>
       <c r="R129" t="n">
-        <v>6766686</v>
+        <v>6766717</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -13356,7 +13351,7 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>127723165</v>
+        <v>127723118</v>
       </c>
       <c r="B130" t="n">
         <v>79029</v>
@@ -13391,10 +13386,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>443327</v>
+        <v>443519</v>
       </c>
       <c r="R130" t="n">
-        <v>6766717</v>
+        <v>6766624</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -13453,7 +13448,7 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>127723118</v>
+        <v>127723140</v>
       </c>
       <c r="B131" t="n">
         <v>79029</v>
@@ -13488,7 +13483,7 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>443519</v>
+        <v>443370</v>
       </c>
       <c r="R131" t="n">
         <v>6766624</v>
@@ -13550,45 +13545,50 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>127723037</v>
+        <v>127722951</v>
       </c>
       <c r="B132" t="n">
-        <v>78788</v>
+        <v>8450</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>228912</v>
+        <v>106545</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
+      <c r="M132" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P132" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>443509</v>
+        <v>443377</v>
       </c>
       <c r="R132" t="n">
-        <v>6766722</v>
+        <v>6766686</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -14048,7 +14048,7 @@
         <v>127736007</v>
       </c>
       <c r="B137" t="n">
-        <v>91369</v>
+        <v>91370</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -14803,7 +14803,7 @@
         <v>127785472</v>
       </c>
       <c r="B144" t="n">
-        <v>91369</v>
+        <v>91370</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>

--- a/artfynd/A 35484-2025 artfynd.xlsx
+++ b/artfynd/A 35484-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127621301</v>
+        <v>127621346</v>
       </c>
       <c r="B2" t="n">
-        <v>79029</v>
+        <v>78787</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -713,10 +713,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>443316</v>
+        <v>443330</v>
       </c>
       <c r="R2" t="n">
-        <v>6766797</v>
+        <v>6766724</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -749,11 +749,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-08-14</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>På 4 tallstammar</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -781,10 +776,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127621346</v>
+        <v>127621301</v>
       </c>
       <c r="B3" t="n">
-        <v>78787</v>
+        <v>79029</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -792,21 +787,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -819,10 +814,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>443330</v>
+        <v>443316</v>
       </c>
       <c r="R3" t="n">
-        <v>6766724</v>
+        <v>6766797</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -855,6 +850,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>På 4 tallstammar</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -1627,7 +1627,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127621322</v>
+        <v>127621416</v>
       </c>
       <c r="B11" t="n">
         <v>79029</v>
@@ -1665,10 +1665,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>443330</v>
+        <v>443416</v>
       </c>
       <c r="R11" t="n">
-        <v>6766763</v>
+        <v>6766663</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1705,7 +1705,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>2 granar</t>
+          <t>På levande Björk</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1733,7 +1733,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127621416</v>
+        <v>127621322</v>
       </c>
       <c r="B12" t="n">
         <v>79029</v>
@@ -1771,10 +1771,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>443416</v>
+        <v>443330</v>
       </c>
       <c r="R12" t="n">
-        <v>6766663</v>
+        <v>6766763</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1811,7 +1811,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>På levande Björk</t>
+          <t>2 granar</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1839,50 +1839,45 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127722932</v>
+        <v>127723164</v>
       </c>
       <c r="B13" t="n">
-        <v>8450</v>
+        <v>79029</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>443590</v>
+        <v>443329</v>
       </c>
       <c r="R13" t="n">
-        <v>6766651</v>
+        <v>6766739</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1941,7 +1936,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127723164</v>
+        <v>127723117</v>
       </c>
       <c r="B14" t="n">
         <v>79029</v>
@@ -1976,10 +1971,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>443329</v>
+        <v>443514</v>
       </c>
       <c r="R14" t="n">
-        <v>6766739</v>
+        <v>6766630</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2038,7 +2033,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127723117</v>
+        <v>127723151</v>
       </c>
       <c r="B15" t="n">
         <v>79029</v>
@@ -2073,10 +2068,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>443514</v>
+        <v>443430</v>
       </c>
       <c r="R15" t="n">
-        <v>6766630</v>
+        <v>6766608</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2135,45 +2130,50 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127723151</v>
+        <v>127722932</v>
       </c>
       <c r="B16" t="n">
-        <v>79029</v>
+        <v>8450</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>443430</v>
+        <v>443590</v>
       </c>
       <c r="R16" t="n">
-        <v>6766608</v>
+        <v>6766651</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2431,7 +2431,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127723099</v>
+        <v>127723093</v>
       </c>
       <c r="B19" t="n">
         <v>79029</v>
@@ -2466,10 +2466,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>443567</v>
+        <v>443572</v>
       </c>
       <c r="R19" t="n">
-        <v>6766695</v>
+        <v>6766645</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2528,50 +2528,45 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127722947</v>
+        <v>127723099</v>
       </c>
       <c r="B20" t="n">
-        <v>8450</v>
+        <v>79029</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>443486</v>
+        <v>443567</v>
       </c>
       <c r="R20" t="n">
-        <v>6766604</v>
+        <v>6766695</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2630,7 +2625,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127722942</v>
+        <v>127722947</v>
       </c>
       <c r="B21" t="n">
         <v>8450</v>
@@ -2670,10 +2665,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>443542</v>
+        <v>443486</v>
       </c>
       <c r="R21" t="n">
-        <v>6766699</v>
+        <v>6766604</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2732,45 +2727,50 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127723093</v>
+        <v>127722942</v>
       </c>
       <c r="B22" t="n">
-        <v>79029</v>
+        <v>8450</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>443572</v>
+        <v>443542</v>
       </c>
       <c r="R22" t="n">
-        <v>6766645</v>
+        <v>6766699</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2829,10 +2829,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127723040</v>
+        <v>127723112</v>
       </c>
       <c r="B23" t="n">
-        <v>78788</v>
+        <v>79029</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2840,21 +2840,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2864,10 +2864,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>443377</v>
+        <v>443476</v>
       </c>
       <c r="R23" t="n">
-        <v>6766659</v>
+        <v>6766681</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2926,10 +2926,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127723039</v>
+        <v>127723166</v>
       </c>
       <c r="B24" t="n">
-        <v>78788</v>
+        <v>79029</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2937,21 +2937,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2961,10 +2961,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>443356</v>
+        <v>443326</v>
       </c>
       <c r="R24" t="n">
-        <v>6766650</v>
+        <v>6766711</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3023,10 +3023,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127722874</v>
+        <v>127723181</v>
       </c>
       <c r="B25" t="n">
-        <v>91370</v>
+        <v>79029</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3034,21 +3034,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3058,10 +3058,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>443388</v>
+        <v>443436</v>
       </c>
       <c r="R25" t="n">
-        <v>6766675</v>
+        <v>6766667</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3120,10 +3120,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127723112</v>
+        <v>127722874</v>
       </c>
       <c r="B26" t="n">
-        <v>79029</v>
+        <v>91370</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3131,21 +3131,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3155,10 +3155,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>443476</v>
+        <v>443388</v>
       </c>
       <c r="R26" t="n">
-        <v>6766681</v>
+        <v>6766675</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3217,45 +3217,50 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127723166</v>
+        <v>127722950</v>
       </c>
       <c r="B27" t="n">
-        <v>79029</v>
+        <v>8450</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>443326</v>
+        <v>443438</v>
       </c>
       <c r="R27" t="n">
-        <v>6766711</v>
+        <v>6766650</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3314,10 +3319,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127723181</v>
+        <v>127723039</v>
       </c>
       <c r="B28" t="n">
-        <v>79029</v>
+        <v>78788</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3325,21 +3330,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3349,10 +3354,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>443436</v>
+        <v>443356</v>
       </c>
       <c r="R28" t="n">
-        <v>6766667</v>
+        <v>6766650</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3411,50 +3416,45 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127722950</v>
+        <v>127723040</v>
       </c>
       <c r="B29" t="n">
-        <v>8450</v>
+        <v>78788</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>106545</v>
+        <v>228912</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>443438</v>
+        <v>443377</v>
       </c>
       <c r="R29" t="n">
-        <v>6766650</v>
+        <v>6766659</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3513,50 +3513,45 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127722945</v>
+        <v>127723152</v>
       </c>
       <c r="B30" t="n">
-        <v>8450</v>
+        <v>79029</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>443568</v>
+        <v>443424</v>
       </c>
       <c r="R30" t="n">
-        <v>6766605</v>
+        <v>6766627</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3615,45 +3610,50 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127723152</v>
+        <v>127722945</v>
       </c>
       <c r="B31" t="n">
-        <v>79029</v>
+        <v>8450</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>443424</v>
+        <v>443568</v>
       </c>
       <c r="R31" t="n">
-        <v>6766627</v>
+        <v>6766605</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3712,10 +3712,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127723179</v>
+        <v>127722875</v>
       </c>
       <c r="B32" t="n">
-        <v>79029</v>
+        <v>91370</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3723,21 +3723,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3747,10 +3747,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>443411</v>
+        <v>443312</v>
       </c>
       <c r="R32" t="n">
-        <v>6766676</v>
+        <v>6766713</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3809,10 +3809,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127722875</v>
+        <v>127723179</v>
       </c>
       <c r="B33" t="n">
-        <v>91370</v>
+        <v>79029</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3820,21 +3820,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3844,10 +3844,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>443312</v>
+        <v>443411</v>
       </c>
       <c r="R33" t="n">
-        <v>6766713</v>
+        <v>6766676</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4008,32 +4008,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127722921</v>
+        <v>127723109</v>
       </c>
       <c r="B35" t="n">
-        <v>97345</v>
+        <v>79029</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4043,10 +4043,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>443330</v>
+        <v>443482</v>
       </c>
       <c r="R35" t="n">
-        <v>6766662</v>
+        <v>6766716</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4105,50 +4105,45 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127722944</v>
+        <v>127723115</v>
       </c>
       <c r="B36" t="n">
-        <v>8450</v>
+        <v>79029</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>443488</v>
+        <v>443495</v>
       </c>
       <c r="R36" t="n">
-        <v>6766671</v>
+        <v>6766641</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4207,7 +4202,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127722928</v>
+        <v>127722944</v>
       </c>
       <c r="B37" t="n">
         <v>8450</v>
@@ -4238,7 +4233,7 @@
       <c r="I37" t="inlineStr"/>
       <c r="M37" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
@@ -4247,10 +4242,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>443559</v>
+        <v>443488</v>
       </c>
       <c r="R37" t="n">
-        <v>6766616</v>
+        <v>6766671</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4309,45 +4304,50 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127723107</v>
+        <v>127722928</v>
       </c>
       <c r="B38" t="n">
-        <v>79029</v>
+        <v>8450</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>443493</v>
+        <v>443559</v>
       </c>
       <c r="R38" t="n">
-        <v>6766717</v>
+        <v>6766616</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4406,7 +4406,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127723109</v>
+        <v>127723107</v>
       </c>
       <c r="B39" t="n">
         <v>79029</v>
@@ -4441,10 +4441,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>443482</v>
+        <v>443493</v>
       </c>
       <c r="R39" t="n">
-        <v>6766716</v>
+        <v>6766717</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4600,32 +4600,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127723115</v>
+        <v>127722921</v>
       </c>
       <c r="B41" t="n">
-        <v>79029</v>
+        <v>97345</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4635,10 +4635,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>443495</v>
+        <v>443330</v>
       </c>
       <c r="R41" t="n">
-        <v>6766641</v>
+        <v>6766662</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4697,32 +4697,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>127723121</v>
+        <v>127723064</v>
       </c>
       <c r="B42" t="n">
-        <v>79029</v>
+        <v>91511</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>1503</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4732,10 +4732,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>443558</v>
+        <v>443329</v>
       </c>
       <c r="R42" t="n">
-        <v>6766620</v>
+        <v>6766670</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4794,7 +4794,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127723189</v>
+        <v>127723159</v>
       </c>
       <c r="B43" t="n">
         <v>79029</v>
@@ -4829,10 +4829,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>443446</v>
+        <v>443314</v>
       </c>
       <c r="R43" t="n">
-        <v>6766727</v>
+        <v>6766811</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4865,11 +4865,6 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-08-21</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Med grov gran i bäckmiljö</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -4896,10 +4891,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>127722876</v>
+        <v>127723121</v>
       </c>
       <c r="B44" t="n">
-        <v>91370</v>
+        <v>79029</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4907,21 +4902,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4931,10 +4926,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>443366</v>
+        <v>443558</v>
       </c>
       <c r="R44" t="n">
-        <v>6766661</v>
+        <v>6766620</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4993,32 +4988,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>127723064</v>
+        <v>127723091</v>
       </c>
       <c r="B45" t="n">
-        <v>91511</v>
+        <v>79029</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1503</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5028,10 +5023,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>443329</v>
+        <v>443587</v>
       </c>
       <c r="R45" t="n">
-        <v>6766670</v>
+        <v>6766651</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5090,7 +5085,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>127723091</v>
+        <v>127723189</v>
       </c>
       <c r="B46" t="n">
         <v>79029</v>
@@ -5125,10 +5120,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>443587</v>
+        <v>443446</v>
       </c>
       <c r="R46" t="n">
-        <v>6766651</v>
+        <v>6766727</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5161,6 +5156,11 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Med grov gran i bäckmiljö</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5187,10 +5187,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>127723159</v>
+        <v>127722876</v>
       </c>
       <c r="B47" t="n">
-        <v>79029</v>
+        <v>91370</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5198,21 +5198,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5222,10 +5222,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>443314</v>
+        <v>443366</v>
       </c>
       <c r="R47" t="n">
-        <v>6766811</v>
+        <v>6766661</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5284,50 +5284,45 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>127722957</v>
+        <v>127723102</v>
       </c>
       <c r="B48" t="n">
-        <v>8450</v>
+        <v>79029</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>443457</v>
+        <v>443556</v>
       </c>
       <c r="R48" t="n">
-        <v>6766726</v>
+        <v>6766717</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5386,10 +5381,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>127722868</v>
+        <v>127723185</v>
       </c>
       <c r="B49" t="n">
-        <v>57832</v>
+        <v>79029</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5397,39 +5392,34 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>443305</v>
+        <v>443452</v>
       </c>
       <c r="R49" t="n">
-        <v>6766767</v>
+        <v>6766711</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5488,7 +5478,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>127723185</v>
+        <v>127723110</v>
       </c>
       <c r="B50" t="n">
         <v>79029</v>
@@ -5523,10 +5513,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>443452</v>
+        <v>443479</v>
       </c>
       <c r="R50" t="n">
-        <v>6766711</v>
+        <v>6766703</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5585,10 +5575,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>127723180</v>
+        <v>127722868</v>
       </c>
       <c r="B51" t="n">
-        <v>79029</v>
+        <v>57832</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5596,34 +5586,39 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>443425</v>
+        <v>443305</v>
       </c>
       <c r="R51" t="n">
-        <v>6766665</v>
+        <v>6766767</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5682,7 +5677,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>127723102</v>
+        <v>127723180</v>
       </c>
       <c r="B52" t="n">
         <v>79029</v>
@@ -5717,10 +5712,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>443556</v>
+        <v>443425</v>
       </c>
       <c r="R52" t="n">
-        <v>6766717</v>
+        <v>6766665</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5779,45 +5774,50 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>127723110</v>
+        <v>127722957</v>
       </c>
       <c r="B53" t="n">
-        <v>79029</v>
+        <v>8450</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>443479</v>
+        <v>443457</v>
       </c>
       <c r="R53" t="n">
-        <v>6766703</v>
+        <v>6766726</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5876,50 +5876,45 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>127722943</v>
+        <v>127723184</v>
       </c>
       <c r="B54" t="n">
-        <v>8450</v>
+        <v>79029</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P54" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>443527</v>
+        <v>443446</v>
       </c>
       <c r="R54" t="n">
-        <v>6766711</v>
+        <v>6766702</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5978,50 +5973,45 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>127722956</v>
+        <v>127723138</v>
       </c>
       <c r="B55" t="n">
-        <v>8450</v>
+        <v>79029</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>443454</v>
+        <v>443391</v>
       </c>
       <c r="R55" t="n">
-        <v>6766718</v>
+        <v>6766625</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6080,45 +6070,50 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>127723138</v>
+        <v>127722943</v>
       </c>
       <c r="B56" t="n">
-        <v>79029</v>
+        <v>8450</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P56" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>443391</v>
+        <v>443527</v>
       </c>
       <c r="R56" t="n">
-        <v>6766625</v>
+        <v>6766711</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6177,45 +6172,50 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>127723184</v>
+        <v>127722956</v>
       </c>
       <c r="B57" t="n">
-        <v>79029</v>
+        <v>8450</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P57" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>443446</v>
+        <v>443454</v>
       </c>
       <c r="R57" t="n">
-        <v>6766702</v>
+        <v>6766718</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6468,7 +6468,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>127723119</v>
+        <v>127723153</v>
       </c>
       <c r="B60" t="n">
         <v>79029</v>
@@ -6503,10 +6503,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>443535</v>
+        <v>443436</v>
       </c>
       <c r="R60" t="n">
-        <v>6766639</v>
+        <v>6766648</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6565,7 +6565,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>127723134</v>
+        <v>127723119</v>
       </c>
       <c r="B61" t="n">
         <v>79029</v>
@@ -6600,10 +6600,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>443465</v>
+        <v>443535</v>
       </c>
       <c r="R61" t="n">
-        <v>6766607</v>
+        <v>6766639</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6662,7 +6662,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>127723153</v>
+        <v>127723106</v>
       </c>
       <c r="B62" t="n">
         <v>79029</v>
@@ -6697,10 +6697,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>443436</v>
+        <v>443516</v>
       </c>
       <c r="R62" t="n">
-        <v>6766648</v>
+        <v>6766720</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6759,7 +6759,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>127723106</v>
+        <v>127723188</v>
       </c>
       <c r="B63" t="n">
         <v>79029</v>
@@ -6794,10 +6794,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>443516</v>
+        <v>443454</v>
       </c>
       <c r="R63" t="n">
-        <v>6766720</v>
+        <v>6766724</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6856,7 +6856,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>127723188</v>
+        <v>127723134</v>
       </c>
       <c r="B64" t="n">
         <v>79029</v>
@@ -6891,10 +6891,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>443454</v>
+        <v>443465</v>
       </c>
       <c r="R64" t="n">
-        <v>6766724</v>
+        <v>6766607</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7050,32 +7050,32 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>127723150</v>
+        <v>127723065</v>
       </c>
       <c r="B66" t="n">
-        <v>79029</v>
+        <v>91511</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6425</v>
+        <v>1503</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7085,10 +7085,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>443415</v>
+        <v>443425</v>
       </c>
       <c r="R66" t="n">
-        <v>6766603</v>
+        <v>6766668</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7244,7 +7244,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>127729137</v>
+        <v>127723177</v>
       </c>
       <c r="B68" t="n">
         <v>79029</v>
@@ -7275,14 +7275,14 @@
       <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Oxeråsen S. om, Dlr</t>
+          <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>443391</v>
+        <v>443397</v>
       </c>
       <c r="R68" t="n">
-        <v>6766598</v>
+        <v>6766673</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7312,47 +7312,36 @@
           <t>2025-08-21</t>
         </is>
       </c>
-      <c r="Z68" t="inlineStr">
-        <is>
-          <t>14:00</t>
-        </is>
-      </c>
       <c r="AA68" t="inlineStr">
         <is>
           <t>2025-08-21</t>
         </is>
       </c>
-      <c r="AB68" t="inlineStr">
-        <is>
-          <t>14:00</t>
-        </is>
-      </c>
       <c r="AD68" t="b">
         <v>0</v>
       </c>
       <c r="AE68" t="b">
         <v>0</v>
       </c>
-      <c r="AF68" t="inlineStr"/>
       <c r="AG68" t="b">
         <v>0</v>
       </c>
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>127723158</v>
+        <v>127729137</v>
       </c>
       <c r="B69" t="n">
         <v>79029</v>
@@ -7383,14 +7372,14 @@
       <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Oxeråsen, Dlr</t>
+          <t>Oxeråsen S. om, Dlr</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>443312</v>
+        <v>443391</v>
       </c>
       <c r="R69" t="n">
-        <v>6766818</v>
+        <v>6766598</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7420,36 +7409,47 @@
           <t>2025-08-21</t>
         </is>
       </c>
+      <c r="Z69" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
       <c r="AA69" t="inlineStr">
         <is>
           <t>2025-08-21</t>
         </is>
       </c>
+      <c r="AB69" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
       <c r="AD69" t="b">
         <v>0</v>
       </c>
       <c r="AE69" t="b">
         <v>0</v>
       </c>
+      <c r="AF69" t="inlineStr"/>
       <c r="AG69" t="b">
         <v>0</v>
       </c>
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>127723177</v>
+        <v>127723158</v>
       </c>
       <c r="B70" t="n">
         <v>79029</v>
@@ -7484,10 +7484,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>443397</v>
+        <v>443312</v>
       </c>
       <c r="R70" t="n">
-        <v>6766673</v>
+        <v>6766818</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7546,50 +7546,45 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>127722941</v>
+        <v>127723150</v>
       </c>
       <c r="B71" t="n">
-        <v>8450</v>
+        <v>79029</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
-      <c r="M71" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P71" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>443557</v>
+        <v>443415</v>
       </c>
       <c r="R71" t="n">
-        <v>6766635</v>
+        <v>6766603</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7648,45 +7643,50 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>127723065</v>
+        <v>127722941</v>
       </c>
       <c r="B72" t="n">
-        <v>91511</v>
+        <v>8450</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>1503</v>
+        <v>106545</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P72" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>443425</v>
+        <v>443557</v>
       </c>
       <c r="R72" t="n">
-        <v>6766668</v>
+        <v>6766635</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7745,10 +7745,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>127723133</v>
+        <v>127722839</v>
       </c>
       <c r="B73" t="n">
-        <v>79029</v>
+        <v>79061</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7756,21 +7756,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -7780,10 +7780,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>443504</v>
+        <v>443554</v>
       </c>
       <c r="R73" t="n">
-        <v>6766593</v>
+        <v>6766649</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7939,10 +7939,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>127729092</v>
+        <v>127723108</v>
       </c>
       <c r="B75" t="n">
-        <v>78787</v>
+        <v>79029</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7950,34 +7950,34 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Oxeråsen S. om, Dlr</t>
+          <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>443381</v>
+        <v>443483</v>
       </c>
       <c r="R75" t="n">
-        <v>6766668</v>
+        <v>6766725</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8007,50 +8007,39 @@
           <t>2025-08-21</t>
         </is>
       </c>
-      <c r="Z75" t="inlineStr">
-        <is>
-          <t>13:51</t>
-        </is>
-      </c>
       <c r="AA75" t="inlineStr">
         <is>
           <t>2025-08-21</t>
         </is>
       </c>
-      <c r="AB75" t="inlineStr">
-        <is>
-          <t>13:51</t>
-        </is>
-      </c>
       <c r="AD75" t="b">
         <v>0</v>
       </c>
       <c r="AE75" t="b">
         <v>0</v>
       </c>
-      <c r="AF75" t="inlineStr"/>
       <c r="AG75" t="b">
         <v>0</v>
       </c>
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>127723108</v>
+        <v>127729092</v>
       </c>
       <c r="B76" t="n">
-        <v>79029</v>
+        <v>78787</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8058,34 +8047,34 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Oxeråsen, Dlr</t>
+          <t>Oxeråsen S. om, Dlr</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>443483</v>
+        <v>443381</v>
       </c>
       <c r="R76" t="n">
-        <v>6766725</v>
+        <v>6766668</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8115,39 +8104,50 @@
           <t>2025-08-21</t>
         </is>
       </c>
+      <c r="Z76" t="inlineStr">
+        <is>
+          <t>13:51</t>
+        </is>
+      </c>
       <c r="AA76" t="inlineStr">
         <is>
           <t>2025-08-21</t>
         </is>
       </c>
+      <c r="AB76" t="inlineStr">
+        <is>
+          <t>13:51</t>
+        </is>
+      </c>
       <c r="AD76" t="b">
         <v>0</v>
       </c>
       <c r="AE76" t="b">
         <v>0</v>
       </c>
+      <c r="AF76" t="inlineStr"/>
       <c r="AG76" t="b">
         <v>0</v>
       </c>
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>127722839</v>
+        <v>127723090</v>
       </c>
       <c r="B77" t="n">
-        <v>79061</v>
+        <v>79029</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8155,21 +8155,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8179,10 +8179,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>443554</v>
+        <v>443593</v>
       </c>
       <c r="R77" t="n">
-        <v>6766649</v>
+        <v>6766653</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8241,7 +8241,7 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>127723090</v>
+        <v>127723133</v>
       </c>
       <c r="B78" t="n">
         <v>79029</v>
@@ -8276,10 +8276,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>443593</v>
+        <v>443504</v>
       </c>
       <c r="R78" t="n">
-        <v>6766653</v>
+        <v>6766593</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8726,10 +8726,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>127723116</v>
+        <v>127722888</v>
       </c>
       <c r="B83" t="n">
-        <v>79029</v>
+        <v>57669</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8737,34 +8737,39 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P83" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>443509</v>
+        <v>443481</v>
       </c>
       <c r="R83" t="n">
-        <v>6766633</v>
+        <v>6766676</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -8823,10 +8828,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>127723178</v>
+        <v>127723570</v>
       </c>
       <c r="B84" t="n">
-        <v>79029</v>
+        <v>78696</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -8834,21 +8839,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -8858,10 +8863,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>443402</v>
+        <v>443319</v>
       </c>
       <c r="R84" t="n">
-        <v>6766682</v>
+        <v>6766670</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -8920,7 +8925,7 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>127723092</v>
+        <v>127723116</v>
       </c>
       <c r="B85" t="n">
         <v>79029</v>
@@ -8955,10 +8960,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>443572</v>
+        <v>443509</v>
       </c>
       <c r="R85" t="n">
-        <v>6766650</v>
+        <v>6766633</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9017,7 +9022,7 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>127723171</v>
+        <v>127723092</v>
       </c>
       <c r="B86" t="n">
         <v>79029</v>
@@ -9052,7 +9057,7 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>443342</v>
+        <v>443572</v>
       </c>
       <c r="R86" t="n">
         <v>6766650</v>
@@ -9114,10 +9119,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>127722888</v>
+        <v>127723178</v>
       </c>
       <c r="B87" t="n">
-        <v>57669</v>
+        <v>79029</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9125,39 +9130,34 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
-      <c r="M87" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P87" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>443481</v>
+        <v>443402</v>
       </c>
       <c r="R87" t="n">
-        <v>6766676</v>
+        <v>6766682</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9216,10 +9216,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>127723541</v>
+        <v>127723171</v>
       </c>
       <c r="B88" t="n">
-        <v>57672</v>
+        <v>79029</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9227,39 +9227,34 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
-      <c r="M88" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P88" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>443317</v>
+        <v>443342</v>
       </c>
       <c r="R88" t="n">
-        <v>6766816</v>
+        <v>6766650</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9318,7 +9313,7 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>127722916</v>
+        <v>127723541</v>
       </c>
       <c r="B89" t="n">
         <v>57672</v>
@@ -9358,10 +9353,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>443342</v>
+        <v>443317</v>
       </c>
       <c r="R89" t="n">
-        <v>6766806</v>
+        <v>6766816</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9394,11 +9389,6 @@
       <c r="AA89" t="inlineStr">
         <is>
           <t>2025-08-21</t>
-        </is>
-      </c>
-      <c r="AC89" t="inlineStr">
-        <is>
-          <t>Färska ringhack (gran), 4-5 år gamla</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -9425,10 +9415,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>127723570</v>
+        <v>127722916</v>
       </c>
       <c r="B90" t="n">
-        <v>78696</v>
+        <v>57672</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9436,34 +9426,39 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>353</v>
+        <v>100109</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P90" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>443319</v>
+        <v>443342</v>
       </c>
       <c r="R90" t="n">
-        <v>6766670</v>
+        <v>6766806</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9496,6 +9491,11 @@
       <c r="AA90" t="inlineStr">
         <is>
           <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AC90" t="inlineStr">
+        <is>
+          <t>Färska ringhack (gran), 4-5 år gamla</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -9522,10 +9522,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>127723105</v>
+        <v>127723041</v>
       </c>
       <c r="B91" t="n">
-        <v>79029</v>
+        <v>78788</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9533,21 +9533,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -9557,10 +9557,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>443525</v>
+        <v>443450</v>
       </c>
       <c r="R91" t="n">
-        <v>6766717</v>
+        <v>6766735</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9619,10 +9619,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>127723103</v>
+        <v>127723569</v>
       </c>
       <c r="B92" t="n">
-        <v>79029</v>
+        <v>78696</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9630,21 +9630,21 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -9654,10 +9654,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>443541</v>
+        <v>443332</v>
       </c>
       <c r="R92" t="n">
-        <v>6766696</v>
+        <v>6766677</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9716,7 +9716,7 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>127723161</v>
+        <v>127723103</v>
       </c>
       <c r="B93" t="n">
         <v>79029</v>
@@ -9751,10 +9751,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>443305</v>
+        <v>443541</v>
       </c>
       <c r="R93" t="n">
-        <v>6766767</v>
+        <v>6766696</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -9813,7 +9813,7 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>127723186</v>
+        <v>127723105</v>
       </c>
       <c r="B94" t="n">
         <v>79029</v>
@@ -9848,10 +9848,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>443454</v>
+        <v>443525</v>
       </c>
       <c r="R94" t="n">
-        <v>6766738</v>
+        <v>6766717</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -9910,7 +9910,7 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>127723174</v>
+        <v>127723161</v>
       </c>
       <c r="B95" t="n">
         <v>79029</v>
@@ -9945,10 +9945,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>443378</v>
+        <v>443305</v>
       </c>
       <c r="R95" t="n">
-        <v>6766657</v>
+        <v>6766767</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10007,10 +10007,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>127723041</v>
+        <v>127723114</v>
       </c>
       <c r="B96" t="n">
-        <v>78788</v>
+        <v>79029</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10018,21 +10018,21 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10042,10 +10042,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>443450</v>
+        <v>443487</v>
       </c>
       <c r="R96" t="n">
-        <v>6766735</v>
+        <v>6766651</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10104,10 +10104,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>127723569</v>
+        <v>127723097</v>
       </c>
       <c r="B97" t="n">
-        <v>78696</v>
+        <v>79029</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10115,21 +10115,21 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -10139,10 +10139,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>443332</v>
+        <v>443561</v>
       </c>
       <c r="R97" t="n">
-        <v>6766677</v>
+        <v>6766678</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10201,7 +10201,7 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>127723114</v>
+        <v>127723174</v>
       </c>
       <c r="B98" t="n">
         <v>79029</v>
@@ -10236,10 +10236,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>443487</v>
+        <v>443378</v>
       </c>
       <c r="R98" t="n">
-        <v>6766651</v>
+        <v>6766657</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10298,7 +10298,7 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>127723097</v>
+        <v>127723186</v>
       </c>
       <c r="B99" t="n">
         <v>79029</v>
@@ -10333,10 +10333,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>443561</v>
+        <v>443454</v>
       </c>
       <c r="R99" t="n">
-        <v>6766678</v>
+        <v>6766738</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10395,7 +10395,7 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>127723183</v>
+        <v>127723157</v>
       </c>
       <c r="B100" t="n">
         <v>79029</v>
@@ -10430,10 +10430,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>443441</v>
+        <v>443306</v>
       </c>
       <c r="R100" t="n">
-        <v>6766686</v>
+        <v>6766830</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10589,10 +10589,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>127723157</v>
+        <v>127722842</v>
       </c>
       <c r="B102" t="n">
-        <v>79029</v>
+        <v>79061</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -10600,21 +10600,21 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -10624,10 +10624,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>443306</v>
+        <v>443504</v>
       </c>
       <c r="R102" t="n">
-        <v>6766830</v>
+        <v>6766708</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -10686,7 +10686,7 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>127723182</v>
+        <v>127723183</v>
       </c>
       <c r="B103" t="n">
         <v>79029</v>
@@ -10721,10 +10721,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>443444</v>
+        <v>443441</v>
       </c>
       <c r="R103" t="n">
-        <v>6766677</v>
+        <v>6766686</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -10783,7 +10783,7 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>127723170</v>
+        <v>127723182</v>
       </c>
       <c r="B104" t="n">
         <v>79029</v>
@@ -10818,10 +10818,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>443333</v>
+        <v>443444</v>
       </c>
       <c r="R104" t="n">
-        <v>6766676</v>
+        <v>6766677</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -10880,7 +10880,7 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>127723098</v>
+        <v>127723096</v>
       </c>
       <c r="B105" t="n">
         <v>79029</v>
@@ -10915,10 +10915,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>443562</v>
+        <v>443554</v>
       </c>
       <c r="R105" t="n">
-        <v>6766684</v>
+        <v>6766650</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -10977,10 +10977,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>127723038</v>
+        <v>127723170</v>
       </c>
       <c r="B106" t="n">
-        <v>78788</v>
+        <v>79029</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -10988,21 +10988,21 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -11012,10 +11012,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>443328</v>
+        <v>443333</v>
       </c>
       <c r="R106" t="n">
-        <v>6766721</v>
+        <v>6766676</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11074,7 +11074,7 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>127723096</v>
+        <v>127723098</v>
       </c>
       <c r="B107" t="n">
         <v>79029</v>
@@ -11109,10 +11109,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>443554</v>
+        <v>443562</v>
       </c>
       <c r="R107" t="n">
-        <v>6766650</v>
+        <v>6766684</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11375,10 +11375,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>127722842</v>
+        <v>127723038</v>
       </c>
       <c r="B110" t="n">
-        <v>79061</v>
+        <v>78788</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -11386,21 +11386,21 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>185</v>
+        <v>228912</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -11410,10 +11410,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>443504</v>
+        <v>443328</v>
       </c>
       <c r="R110" t="n">
-        <v>6766708</v>
+        <v>6766721</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11472,10 +11472,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>127729086</v>
+        <v>127723154</v>
       </c>
       <c r="B111" t="n">
-        <v>78788</v>
+        <v>79029</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -11483,34 +11483,34 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
       <c r="P111" t="inlineStr">
         <is>
-          <t>Oxeråsen S. om, Dlr</t>
+          <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>443359</v>
+        <v>443369</v>
       </c>
       <c r="R111" t="n">
-        <v>6766650</v>
+        <v>6766695</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -11540,47 +11540,36 @@
           <t>2025-08-21</t>
         </is>
       </c>
-      <c r="Z111" t="inlineStr">
-        <is>
-          <t>13:53</t>
-        </is>
-      </c>
       <c r="AA111" t="inlineStr">
         <is>
           <t>2025-08-21</t>
         </is>
       </c>
-      <c r="AB111" t="inlineStr">
-        <is>
-          <t>13:53</t>
-        </is>
-      </c>
       <c r="AD111" t="b">
         <v>0</v>
       </c>
       <c r="AE111" t="b">
         <v>0</v>
       </c>
-      <c r="AF111" t="inlineStr"/>
       <c r="AG111" t="b">
         <v>0</v>
       </c>
       <c r="AT111" t="inlineStr"/>
       <c r="AW111" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX111" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>127723137</v>
+        <v>127723172</v>
       </c>
       <c r="B112" t="n">
         <v>79029</v>
@@ -11615,10 +11604,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>443418</v>
+        <v>443356</v>
       </c>
       <c r="R112" t="n">
-        <v>6766627</v>
+        <v>6766650</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -11677,10 +11666,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>127723154</v>
+        <v>127729086</v>
       </c>
       <c r="B113" t="n">
-        <v>79029</v>
+        <v>78788</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -11688,34 +11677,34 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
       <c r="P113" t="inlineStr">
         <is>
-          <t>Oxeråsen, Dlr</t>
+          <t>Oxeråsen S. om, Dlr</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>443369</v>
+        <v>443359</v>
       </c>
       <c r="R113" t="n">
-        <v>6766695</v>
+        <v>6766650</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -11745,36 +11734,47 @@
           <t>2025-08-21</t>
         </is>
       </c>
+      <c r="Z113" t="inlineStr">
+        <is>
+          <t>13:53</t>
+        </is>
+      </c>
       <c r="AA113" t="inlineStr">
         <is>
           <t>2025-08-21</t>
         </is>
       </c>
+      <c r="AB113" t="inlineStr">
+        <is>
+          <t>13:53</t>
+        </is>
+      </c>
       <c r="AD113" t="b">
         <v>0</v>
       </c>
       <c r="AE113" t="b">
         <v>0</v>
       </c>
+      <c r="AF113" t="inlineStr"/>
       <c r="AG113" t="b">
         <v>0</v>
       </c>
       <c r="AT113" t="inlineStr"/>
       <c r="AW113" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX113" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>127723172</v>
+        <v>127723137</v>
       </c>
       <c r="B114" t="n">
         <v>79029</v>
@@ -11809,10 +11809,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>443356</v>
+        <v>443418</v>
       </c>
       <c r="R114" t="n">
-        <v>6766650</v>
+        <v>6766627</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12167,45 +12167,50 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>127723135</v>
+        <v>127722955</v>
       </c>
       <c r="B118" t="n">
-        <v>79029</v>
+        <v>8450</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
+      <c r="M118" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P118" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>443454</v>
+        <v>443397</v>
       </c>
       <c r="R118" t="n">
-        <v>6766614</v>
+        <v>6766653</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12264,45 +12269,50 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>127723163</v>
+        <v>127722948</v>
       </c>
       <c r="B119" t="n">
-        <v>79029</v>
+        <v>8450</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
+      <c r="M119" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P119" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>443332</v>
+        <v>443457</v>
       </c>
       <c r="R119" t="n">
-        <v>6766744</v>
+        <v>6766613</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -12361,7 +12371,7 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>127723176</v>
+        <v>127723163</v>
       </c>
       <c r="B120" t="n">
         <v>79029</v>
@@ -12396,10 +12406,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>443407</v>
+        <v>443332</v>
       </c>
       <c r="R120" t="n">
-        <v>6766653</v>
+        <v>6766744</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -12458,10 +12468,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>127722903</v>
+        <v>127723176</v>
       </c>
       <c r="B121" t="n">
-        <v>57672</v>
+        <v>79029</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -12469,21 +12479,21 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -12493,10 +12503,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>443382</v>
+        <v>443407</v>
       </c>
       <c r="R121" t="n">
-        <v>6766657</v>
+        <v>6766653</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -12529,11 +12539,6 @@
       <c r="AA121" t="inlineStr">
         <is>
           <t>2025-08-21</t>
-        </is>
-      </c>
-      <c r="AC121" t="inlineStr">
-        <is>
-          <t>Äldre ringhack (tall)</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -12560,50 +12565,45 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>127722955</v>
+        <v>127723135</v>
       </c>
       <c r="B122" t="n">
-        <v>8450</v>
+        <v>79029</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
-      <c r="M122" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P122" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>443397</v>
+        <v>443454</v>
       </c>
       <c r="R122" t="n">
-        <v>6766653</v>
+        <v>6766614</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -12662,50 +12662,45 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>127722948</v>
+        <v>127722903</v>
       </c>
       <c r="B123" t="n">
-        <v>8450</v>
+        <v>57672</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>106545</v>
+        <v>100109</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
-      <c r="M123" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P123" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>443457</v>
+        <v>443382</v>
       </c>
       <c r="R123" t="n">
-        <v>6766613</v>
+        <v>6766657</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -12738,6 +12733,11 @@
       <c r="AA123" t="inlineStr">
         <is>
           <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AC123" t="inlineStr">
+        <is>
+          <t>Äldre ringhack (tall)</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -12861,32 +12861,32 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>127723555</v>
+        <v>127723118</v>
       </c>
       <c r="B125" t="n">
-        <v>92640</v>
+        <v>79029</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -12896,10 +12896,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>443554</v>
+        <v>443519</v>
       </c>
       <c r="R125" t="n">
-        <v>6766667</v>
+        <v>6766624</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -12958,50 +12958,45 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>127722954</v>
+        <v>127723140</v>
       </c>
       <c r="B126" t="n">
-        <v>8450</v>
+        <v>79029</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
-      <c r="M126" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P126" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>443348</v>
+        <v>443370</v>
       </c>
       <c r="R126" t="n">
-        <v>6766646</v>
+        <v>6766624</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -13060,10 +13055,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>127723037</v>
+        <v>127723165</v>
       </c>
       <c r="B127" t="n">
-        <v>78788</v>
+        <v>79029</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -13071,21 +13066,21 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -13095,10 +13090,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>443509</v>
+        <v>443327</v>
       </c>
       <c r="R127" t="n">
-        <v>6766722</v>
+        <v>6766717</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -13254,10 +13249,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>127723165</v>
+        <v>127723037</v>
       </c>
       <c r="B129" t="n">
-        <v>79029</v>
+        <v>78788</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -13265,21 +13260,21 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
@@ -13289,10 +13284,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>443327</v>
+        <v>443509</v>
       </c>
       <c r="R129" t="n">
-        <v>6766717</v>
+        <v>6766722</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -13351,32 +13346,32 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>127723118</v>
+        <v>127723555</v>
       </c>
       <c r="B130" t="n">
-        <v>79029</v>
+        <v>92640</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
@@ -13386,10 +13381,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>443519</v>
+        <v>443554</v>
       </c>
       <c r="R130" t="n">
-        <v>6766624</v>
+        <v>6766667</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -13448,45 +13443,50 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>127723140</v>
+        <v>127722954</v>
       </c>
       <c r="B131" t="n">
-        <v>79029</v>
+        <v>8450</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
+      <c r="M131" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P131" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>443370</v>
+        <v>443348</v>
       </c>
       <c r="R131" t="n">
-        <v>6766624</v>
+        <v>6766646</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>

--- a/artfynd/A 35484-2025 artfynd.xlsx
+++ b/artfynd/A 35484-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127621346</v>
+        <v>127621301</v>
       </c>
       <c r="B2" t="n">
-        <v>78787</v>
+        <v>79029</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -713,10 +713,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>443330</v>
+        <v>443316</v>
       </c>
       <c r="R2" t="n">
-        <v>6766724</v>
+        <v>6766797</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -749,6 +749,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>På 4 tallstammar</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -776,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127621301</v>
+        <v>127621346</v>
       </c>
       <c r="B3" t="n">
-        <v>79029</v>
+        <v>78787</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -787,21 +792,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -814,10 +819,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>443316</v>
+        <v>443330</v>
       </c>
       <c r="R3" t="n">
-        <v>6766797</v>
+        <v>6766724</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -850,11 +855,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-08-14</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>På 4 tallstammar</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -1627,7 +1627,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127621416</v>
+        <v>127621322</v>
       </c>
       <c r="B11" t="n">
         <v>79029</v>
@@ -1665,10 +1665,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>443416</v>
+        <v>443330</v>
       </c>
       <c r="R11" t="n">
-        <v>6766663</v>
+        <v>6766763</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1705,7 +1705,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>På levande Björk</t>
+          <t>2 granar</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1733,7 +1733,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127621322</v>
+        <v>127621416</v>
       </c>
       <c r="B12" t="n">
         <v>79029</v>
@@ -1771,10 +1771,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>443330</v>
+        <v>443416</v>
       </c>
       <c r="R12" t="n">
-        <v>6766763</v>
+        <v>6766663</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1811,7 +1811,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>2 granar</t>
+          <t>På levande Björk</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2431,45 +2431,50 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127723093</v>
+        <v>127722947</v>
       </c>
       <c r="B19" t="n">
-        <v>79029</v>
+        <v>8450</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>443572</v>
+        <v>443486</v>
       </c>
       <c r="R19" t="n">
-        <v>6766645</v>
+        <v>6766604</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2528,45 +2533,50 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127723099</v>
+        <v>127722942</v>
       </c>
       <c r="B20" t="n">
-        <v>79029</v>
+        <v>8450</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>443567</v>
+        <v>443542</v>
       </c>
       <c r="R20" t="n">
-        <v>6766695</v>
+        <v>6766699</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2625,50 +2635,45 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127722947</v>
+        <v>127723093</v>
       </c>
       <c r="B21" t="n">
-        <v>8450</v>
+        <v>79029</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>443486</v>
+        <v>443572</v>
       </c>
       <c r="R21" t="n">
-        <v>6766604</v>
+        <v>6766645</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2727,50 +2732,45 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127722942</v>
+        <v>127723099</v>
       </c>
       <c r="B22" t="n">
-        <v>8450</v>
+        <v>79029</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>443542</v>
+        <v>443567</v>
       </c>
       <c r="R22" t="n">
-        <v>6766699</v>
+        <v>6766695</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3023,45 +3023,50 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127723181</v>
+        <v>127722950</v>
       </c>
       <c r="B25" t="n">
-        <v>79029</v>
+        <v>8450</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>443436</v>
+        <v>443438</v>
       </c>
       <c r="R25" t="n">
-        <v>6766667</v>
+        <v>6766650</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3123,7 +3128,7 @@
         <v>127722874</v>
       </c>
       <c r="B26" t="n">
-        <v>91370</v>
+        <v>91371</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3217,50 +3222,45 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127722950</v>
+        <v>127723181</v>
       </c>
       <c r="B27" t="n">
-        <v>8450</v>
+        <v>79029</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>443438</v>
+        <v>443436</v>
       </c>
       <c r="R27" t="n">
-        <v>6766650</v>
+        <v>6766667</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3715,7 +3715,7 @@
         <v>127722875</v>
       </c>
       <c r="B32" t="n">
-        <v>91370</v>
+        <v>91371</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3906,10 +3906,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>127722896</v>
+        <v>127723109</v>
       </c>
       <c r="B34" t="n">
-        <v>57669</v>
+        <v>79029</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3917,39 +3917,34 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>443537</v>
+        <v>443482</v>
       </c>
       <c r="R34" t="n">
-        <v>6766699</v>
+        <v>6766716</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4008,7 +4003,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127723109</v>
+        <v>127723169</v>
       </c>
       <c r="B35" t="n">
         <v>79029</v>
@@ -4043,10 +4038,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>443482</v>
+        <v>443321</v>
       </c>
       <c r="R35" t="n">
-        <v>6766716</v>
+        <v>6766706</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4202,50 +4197,45 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127722944</v>
+        <v>127723107</v>
       </c>
       <c r="B37" t="n">
-        <v>8450</v>
+        <v>79029</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>443488</v>
+        <v>443493</v>
       </c>
       <c r="R37" t="n">
-        <v>6766671</v>
+        <v>6766717</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4304,38 +4294,38 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127722928</v>
+        <v>127722896</v>
       </c>
       <c r="B38" t="n">
-        <v>8450</v>
+        <v>57669</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="M38" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
@@ -4344,10 +4334,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>443559</v>
+        <v>443537</v>
       </c>
       <c r="R38" t="n">
-        <v>6766616</v>
+        <v>6766699</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4406,45 +4396,50 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127723107</v>
+        <v>127722944</v>
       </c>
       <c r="B39" t="n">
-        <v>79029</v>
+        <v>8450</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>443493</v>
+        <v>443488</v>
       </c>
       <c r="R39" t="n">
-        <v>6766717</v>
+        <v>6766671</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4503,45 +4498,50 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127723169</v>
+        <v>127722928</v>
       </c>
       <c r="B40" t="n">
-        <v>79029</v>
+        <v>8450</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>443321</v>
+        <v>443559</v>
       </c>
       <c r="R40" t="n">
-        <v>6766706</v>
+        <v>6766616</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4603,7 +4603,7 @@
         <v>127722921</v>
       </c>
       <c r="B41" t="n">
-        <v>97345</v>
+        <v>97346</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4700,7 +4700,7 @@
         <v>127723064</v>
       </c>
       <c r="B42" t="n">
-        <v>91511</v>
+        <v>91512</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4794,7 +4794,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127723159</v>
+        <v>127723091</v>
       </c>
       <c r="B43" t="n">
         <v>79029</v>
@@ -4829,10 +4829,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>443314</v>
+        <v>443587</v>
       </c>
       <c r="R43" t="n">
-        <v>6766811</v>
+        <v>6766651</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4891,7 +4891,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>127723121</v>
+        <v>127723159</v>
       </c>
       <c r="B44" t="n">
         <v>79029</v>
@@ -4926,10 +4926,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>443558</v>
+        <v>443314</v>
       </c>
       <c r="R44" t="n">
-        <v>6766620</v>
+        <v>6766811</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4988,7 +4988,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>127723091</v>
+        <v>127723189</v>
       </c>
       <c r="B45" t="n">
         <v>79029</v>
@@ -5023,10 +5023,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>443587</v>
+        <v>443446</v>
       </c>
       <c r="R45" t="n">
-        <v>6766651</v>
+        <v>6766727</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5059,6 +5059,11 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Med grov gran i bäckmiljö</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5085,7 +5090,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>127723189</v>
+        <v>127723121</v>
       </c>
       <c r="B46" t="n">
         <v>79029</v>
@@ -5120,10 +5125,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>443446</v>
+        <v>443558</v>
       </c>
       <c r="R46" t="n">
-        <v>6766727</v>
+        <v>6766620</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5156,11 +5161,6 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-08-21</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Med grov gran i bäckmiljö</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5190,7 +5190,7 @@
         <v>127722876</v>
       </c>
       <c r="B47" t="n">
-        <v>91370</v>
+        <v>91371</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5381,10 +5381,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>127723185</v>
+        <v>127722868</v>
       </c>
       <c r="B49" t="n">
-        <v>79029</v>
+        <v>57832</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5392,34 +5392,39 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>443452</v>
+        <v>443305</v>
       </c>
       <c r="R49" t="n">
-        <v>6766711</v>
+        <v>6766767</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5478,7 +5483,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>127723110</v>
+        <v>127723180</v>
       </c>
       <c r="B50" t="n">
         <v>79029</v>
@@ -5513,10 +5518,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>443479</v>
+        <v>443425</v>
       </c>
       <c r="R50" t="n">
-        <v>6766703</v>
+        <v>6766665</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5575,10 +5580,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>127722868</v>
+        <v>127723185</v>
       </c>
       <c r="B51" t="n">
-        <v>57832</v>
+        <v>79029</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5586,39 +5591,34 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>443305</v>
+        <v>443452</v>
       </c>
       <c r="R51" t="n">
-        <v>6766767</v>
+        <v>6766711</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5677,7 +5677,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>127723180</v>
+        <v>127723110</v>
       </c>
       <c r="B52" t="n">
         <v>79029</v>
@@ -5712,10 +5712,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>443425</v>
+        <v>443479</v>
       </c>
       <c r="R52" t="n">
-        <v>6766665</v>
+        <v>6766703</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5876,7 +5876,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>127723184</v>
+        <v>127723138</v>
       </c>
       <c r="B54" t="n">
         <v>79029</v>
@@ -5911,10 +5911,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>443446</v>
+        <v>443391</v>
       </c>
       <c r="R54" t="n">
-        <v>6766702</v>
+        <v>6766625</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5973,45 +5973,50 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>127723138</v>
+        <v>127722943</v>
       </c>
       <c r="B55" t="n">
-        <v>79029</v>
+        <v>8450</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>443391</v>
+        <v>443527</v>
       </c>
       <c r="R55" t="n">
-        <v>6766625</v>
+        <v>6766711</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6070,7 +6075,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>127722943</v>
+        <v>127722956</v>
       </c>
       <c r="B56" t="n">
         <v>8450</v>
@@ -6110,10 +6115,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>443527</v>
+        <v>443454</v>
       </c>
       <c r="R56" t="n">
-        <v>6766711</v>
+        <v>6766718</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6172,50 +6177,45 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>127722956</v>
+        <v>127723184</v>
       </c>
       <c r="B57" t="n">
-        <v>8450</v>
+        <v>79029</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P57" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>443454</v>
+        <v>443446</v>
       </c>
       <c r="R57" t="n">
-        <v>6766718</v>
+        <v>6766702</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6371,7 +6371,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>127723167</v>
+        <v>127723153</v>
       </c>
       <c r="B59" t="n">
         <v>79029</v>
@@ -6406,10 +6406,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>443316</v>
+        <v>443436</v>
       </c>
       <c r="R59" t="n">
-        <v>6766701</v>
+        <v>6766648</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6468,7 +6468,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>127723153</v>
+        <v>127723119</v>
       </c>
       <c r="B60" t="n">
         <v>79029</v>
@@ -6503,10 +6503,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>443436</v>
+        <v>443535</v>
       </c>
       <c r="R60" t="n">
-        <v>6766648</v>
+        <v>6766639</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6565,7 +6565,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>127723119</v>
+        <v>127723106</v>
       </c>
       <c r="B61" t="n">
         <v>79029</v>
@@ -6600,10 +6600,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>443535</v>
+        <v>443516</v>
       </c>
       <c r="R61" t="n">
-        <v>6766639</v>
+        <v>6766720</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6662,7 +6662,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>127723106</v>
+        <v>127723188</v>
       </c>
       <c r="B62" t="n">
         <v>79029</v>
@@ -6697,10 +6697,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>443516</v>
+        <v>443454</v>
       </c>
       <c r="R62" t="n">
-        <v>6766720</v>
+        <v>6766724</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6759,7 +6759,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>127723188</v>
+        <v>127723175</v>
       </c>
       <c r="B63" t="n">
         <v>79029</v>
@@ -6794,10 +6794,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>443454</v>
+        <v>443387</v>
       </c>
       <c r="R63" t="n">
-        <v>6766724</v>
+        <v>6766658</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6953,7 +6953,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>127723175</v>
+        <v>127723167</v>
       </c>
       <c r="B65" t="n">
         <v>79029</v>
@@ -6988,10 +6988,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>443387</v>
+        <v>443316</v>
       </c>
       <c r="R65" t="n">
-        <v>6766658</v>
+        <v>6766701</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7050,32 +7050,32 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>127723065</v>
+        <v>127722847</v>
       </c>
       <c r="B66" t="n">
-        <v>91511</v>
+        <v>79061</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>1503</v>
+        <v>185</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7085,10 +7085,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>443425</v>
+        <v>443320</v>
       </c>
       <c r="R66" t="n">
-        <v>6766668</v>
+        <v>6766703</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7147,10 +7147,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>127722847</v>
+        <v>127729137</v>
       </c>
       <c r="B67" t="n">
-        <v>79061</v>
+        <v>79029</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7158,34 +7158,34 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Oxeråsen, Dlr</t>
+          <t>Oxeråsen S. om, Dlr</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>443320</v>
+        <v>443391</v>
       </c>
       <c r="R67" t="n">
-        <v>6766703</v>
+        <v>6766598</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7215,36 +7215,47 @@
           <t>2025-08-21</t>
         </is>
       </c>
+      <c r="Z67" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-08-21</t>
         </is>
       </c>
+      <c r="AB67" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
       <c r="AD67" t="b">
         <v>0</v>
       </c>
       <c r="AE67" t="b">
         <v>0</v>
       </c>
+      <c r="AF67" t="inlineStr"/>
       <c r="AG67" t="b">
         <v>0</v>
       </c>
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>127723177</v>
+        <v>127723158</v>
       </c>
       <c r="B68" t="n">
         <v>79029</v>
@@ -7279,10 +7290,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>443397</v>
+        <v>443312</v>
       </c>
       <c r="R68" t="n">
-        <v>6766673</v>
+        <v>6766818</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7341,7 +7352,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>127729137</v>
+        <v>127723177</v>
       </c>
       <c r="B69" t="n">
         <v>79029</v>
@@ -7372,14 +7383,14 @@
       <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Oxeråsen S. om, Dlr</t>
+          <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>443391</v>
+        <v>443397</v>
       </c>
       <c r="R69" t="n">
-        <v>6766598</v>
+        <v>6766673</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7409,47 +7420,36 @@
           <t>2025-08-21</t>
         </is>
       </c>
-      <c r="Z69" t="inlineStr">
-        <is>
-          <t>14:00</t>
-        </is>
-      </c>
       <c r="AA69" t="inlineStr">
         <is>
           <t>2025-08-21</t>
         </is>
       </c>
-      <c r="AB69" t="inlineStr">
-        <is>
-          <t>14:00</t>
-        </is>
-      </c>
       <c r="AD69" t="b">
         <v>0</v>
       </c>
       <c r="AE69" t="b">
         <v>0</v>
       </c>
-      <c r="AF69" t="inlineStr"/>
       <c r="AG69" t="b">
         <v>0</v>
       </c>
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>127723158</v>
+        <v>127723150</v>
       </c>
       <c r="B70" t="n">
         <v>79029</v>
@@ -7484,10 +7484,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>443312</v>
+        <v>443415</v>
       </c>
       <c r="R70" t="n">
-        <v>6766818</v>
+        <v>6766603</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7546,32 +7546,32 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>127723150</v>
+        <v>127723065</v>
       </c>
       <c r="B71" t="n">
-        <v>79029</v>
+        <v>91512</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6425</v>
+        <v>1503</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7581,10 +7581,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>443415</v>
+        <v>443425</v>
       </c>
       <c r="R71" t="n">
-        <v>6766603</v>
+        <v>6766668</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7842,7 +7842,7 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>127723173</v>
+        <v>127723133</v>
       </c>
       <c r="B74" t="n">
         <v>79029</v>
@@ -7877,10 +7877,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>443365</v>
+        <v>443504</v>
       </c>
       <c r="R74" t="n">
-        <v>6766656</v>
+        <v>6766593</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -7939,7 +7939,7 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>127723108</v>
+        <v>127723173</v>
       </c>
       <c r="B75" t="n">
         <v>79029</v>
@@ -7974,10 +7974,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>443483</v>
+        <v>443365</v>
       </c>
       <c r="R75" t="n">
-        <v>6766725</v>
+        <v>6766656</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8036,10 +8036,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>127729092</v>
+        <v>127723108</v>
       </c>
       <c r="B76" t="n">
-        <v>78787</v>
+        <v>79029</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8047,34 +8047,34 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Oxeråsen S. om, Dlr</t>
+          <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>443381</v>
+        <v>443483</v>
       </c>
       <c r="R76" t="n">
-        <v>6766668</v>
+        <v>6766725</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8104,50 +8104,39 @@
           <t>2025-08-21</t>
         </is>
       </c>
-      <c r="Z76" t="inlineStr">
-        <is>
-          <t>13:51</t>
-        </is>
-      </c>
       <c r="AA76" t="inlineStr">
         <is>
           <t>2025-08-21</t>
         </is>
       </c>
-      <c r="AB76" t="inlineStr">
-        <is>
-          <t>13:51</t>
-        </is>
-      </c>
       <c r="AD76" t="b">
         <v>0</v>
       </c>
       <c r="AE76" t="b">
         <v>0</v>
       </c>
-      <c r="AF76" t="inlineStr"/>
       <c r="AG76" t="b">
         <v>0</v>
       </c>
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>127723090</v>
+        <v>127729092</v>
       </c>
       <c r="B77" t="n">
-        <v>79029</v>
+        <v>78787</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8155,34 +8144,34 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Oxeråsen, Dlr</t>
+          <t>Oxeråsen S. om, Dlr</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>443593</v>
+        <v>443381</v>
       </c>
       <c r="R77" t="n">
-        <v>6766653</v>
+        <v>6766668</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8212,36 +8201,47 @@
           <t>2025-08-21</t>
         </is>
       </c>
+      <c r="Z77" t="inlineStr">
+        <is>
+          <t>13:51</t>
+        </is>
+      </c>
       <c r="AA77" t="inlineStr">
         <is>
           <t>2025-08-21</t>
         </is>
       </c>
+      <c r="AB77" t="inlineStr">
+        <is>
+          <t>13:51</t>
+        </is>
+      </c>
       <c r="AD77" t="b">
         <v>0</v>
       </c>
       <c r="AE77" t="b">
         <v>0</v>
       </c>
+      <c r="AF77" t="inlineStr"/>
       <c r="AG77" t="b">
         <v>0</v>
       </c>
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>127723133</v>
+        <v>127723090</v>
       </c>
       <c r="B78" t="n">
         <v>79029</v>
@@ -8276,10 +8276,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>443504</v>
+        <v>443593</v>
       </c>
       <c r="R78" t="n">
-        <v>6766593</v>
+        <v>6766653</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8726,10 +8726,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>127722888</v>
+        <v>127723178</v>
       </c>
       <c r="B83" t="n">
-        <v>57669</v>
+        <v>79029</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8737,39 +8737,34 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
-      <c r="M83" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P83" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>443481</v>
+        <v>443402</v>
       </c>
       <c r="R83" t="n">
-        <v>6766676</v>
+        <v>6766682</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -8828,10 +8823,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>127723570</v>
+        <v>127722888</v>
       </c>
       <c r="B84" t="n">
-        <v>78696</v>
+        <v>57669</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -8839,34 +8834,39 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>353</v>
+        <v>100049</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P84" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>443319</v>
+        <v>443481</v>
       </c>
       <c r="R84" t="n">
-        <v>6766670</v>
+        <v>6766676</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -8925,10 +8925,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>127723116</v>
+        <v>127722916</v>
       </c>
       <c r="B85" t="n">
-        <v>79029</v>
+        <v>57672</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -8936,34 +8936,39 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P85" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>443509</v>
+        <v>443342</v>
       </c>
       <c r="R85" t="n">
-        <v>6766633</v>
+        <v>6766806</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -8996,6 +9001,11 @@
       <c r="AA85" t="inlineStr">
         <is>
           <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AC85" t="inlineStr">
+        <is>
+          <t>Färska ringhack (gran), 4-5 år gamla</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9022,10 +9032,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>127723092</v>
+        <v>127723570</v>
       </c>
       <c r="B86" t="n">
-        <v>79029</v>
+        <v>78696</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9033,21 +9043,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9057,10 +9067,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>443572</v>
+        <v>443319</v>
       </c>
       <c r="R86" t="n">
-        <v>6766650</v>
+        <v>6766670</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9119,10 +9129,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>127723178</v>
+        <v>127723541</v>
       </c>
       <c r="B87" t="n">
-        <v>79029</v>
+        <v>57672</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9130,34 +9140,39 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P87" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>443402</v>
+        <v>443317</v>
       </c>
       <c r="R87" t="n">
-        <v>6766682</v>
+        <v>6766816</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9216,7 +9231,7 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>127723171</v>
+        <v>127723116</v>
       </c>
       <c r="B88" t="n">
         <v>79029</v>
@@ -9251,10 +9266,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>443342</v>
+        <v>443509</v>
       </c>
       <c r="R88" t="n">
-        <v>6766650</v>
+        <v>6766633</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9313,10 +9328,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>127723541</v>
+        <v>127723092</v>
       </c>
       <c r="B89" t="n">
-        <v>57672</v>
+        <v>79029</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9324,39 +9339,34 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
-      <c r="M89" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P89" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>443317</v>
+        <v>443572</v>
       </c>
       <c r="R89" t="n">
-        <v>6766816</v>
+        <v>6766650</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9415,10 +9425,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>127722916</v>
+        <v>127723171</v>
       </c>
       <c r="B90" t="n">
-        <v>57672</v>
+        <v>79029</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9426,29 +9436,24 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
-      <c r="M90" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P90" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
@@ -9458,7 +9463,7 @@
         <v>443342</v>
       </c>
       <c r="R90" t="n">
-        <v>6766806</v>
+        <v>6766650</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9491,11 +9496,6 @@
       <c r="AA90" t="inlineStr">
         <is>
           <t>2025-08-21</t>
-        </is>
-      </c>
-      <c r="AC90" t="inlineStr">
-        <is>
-          <t>Färska ringhack (gran), 4-5 år gamla</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -9522,10 +9522,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>127723041</v>
+        <v>127723097</v>
       </c>
       <c r="B91" t="n">
-        <v>78788</v>
+        <v>79029</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9533,21 +9533,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -9557,10 +9557,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>443450</v>
+        <v>443561</v>
       </c>
       <c r="R91" t="n">
-        <v>6766735</v>
+        <v>6766678</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9619,10 +9619,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>127723569</v>
+        <v>127723114</v>
       </c>
       <c r="B92" t="n">
-        <v>78696</v>
+        <v>79029</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9630,21 +9630,21 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -9654,10 +9654,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>443332</v>
+        <v>443487</v>
       </c>
       <c r="R92" t="n">
-        <v>6766677</v>
+        <v>6766651</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9716,10 +9716,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>127723103</v>
+        <v>127723569</v>
       </c>
       <c r="B93" t="n">
-        <v>79029</v>
+        <v>78696</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9727,21 +9727,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -9751,10 +9751,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>443541</v>
+        <v>443332</v>
       </c>
       <c r="R93" t="n">
-        <v>6766696</v>
+        <v>6766677</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -9813,7 +9813,7 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>127723105</v>
+        <v>127723103</v>
       </c>
       <c r="B94" t="n">
         <v>79029</v>
@@ -9848,10 +9848,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>443525</v>
+        <v>443541</v>
       </c>
       <c r="R94" t="n">
-        <v>6766717</v>
+        <v>6766696</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -9910,7 +9910,7 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>127723161</v>
+        <v>127723105</v>
       </c>
       <c r="B95" t="n">
         <v>79029</v>
@@ -9945,10 +9945,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>443305</v>
+        <v>443525</v>
       </c>
       <c r="R95" t="n">
-        <v>6766767</v>
+        <v>6766717</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10007,7 +10007,7 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>127723114</v>
+        <v>127723161</v>
       </c>
       <c r="B96" t="n">
         <v>79029</v>
@@ -10042,10 +10042,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>443487</v>
+        <v>443305</v>
       </c>
       <c r="R96" t="n">
-        <v>6766651</v>
+        <v>6766767</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10104,7 +10104,7 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>127723097</v>
+        <v>127723174</v>
       </c>
       <c r="B97" t="n">
         <v>79029</v>
@@ -10139,10 +10139,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>443561</v>
+        <v>443378</v>
       </c>
       <c r="R97" t="n">
-        <v>6766678</v>
+        <v>6766657</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10201,7 +10201,7 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>127723174</v>
+        <v>127723186</v>
       </c>
       <c r="B98" t="n">
         <v>79029</v>
@@ -10236,10 +10236,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>443378</v>
+        <v>443454</v>
       </c>
       <c r="R98" t="n">
-        <v>6766657</v>
+        <v>6766738</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10298,10 +10298,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>127723186</v>
+        <v>127723041</v>
       </c>
       <c r="B99" t="n">
-        <v>79029</v>
+        <v>78788</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10309,21 +10309,21 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -10333,10 +10333,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>443454</v>
+        <v>443450</v>
       </c>
       <c r="R99" t="n">
-        <v>6766738</v>
+        <v>6766735</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10395,7 +10395,7 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>127723157</v>
+        <v>127723096</v>
       </c>
       <c r="B100" t="n">
         <v>79029</v>
@@ -10430,10 +10430,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>443306</v>
+        <v>443554</v>
       </c>
       <c r="R100" t="n">
-        <v>6766830</v>
+        <v>6766650</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10492,10 +10492,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>127723139</v>
+        <v>127723616</v>
       </c>
       <c r="B101" t="n">
-        <v>79029</v>
+        <v>57672</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -10503,34 +10503,39 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
+      <c r="M101" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
       <c r="P101" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>443381</v>
+        <v>443475</v>
       </c>
       <c r="R101" t="n">
-        <v>6766623</v>
+        <v>6766610</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10589,45 +10594,50 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>127722842</v>
+        <v>127722929</v>
       </c>
       <c r="B102" t="n">
-        <v>79061</v>
+        <v>8450</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>185</v>
+        <v>106545</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
+      <c r="M102" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P102" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>443504</v>
+        <v>443327</v>
       </c>
       <c r="R102" t="n">
-        <v>6766708</v>
+        <v>6766698</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -10686,10 +10696,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>127723183</v>
+        <v>127723038</v>
       </c>
       <c r="B103" t="n">
-        <v>79029</v>
+        <v>78788</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -10697,21 +10707,21 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -10721,10 +10731,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>443441</v>
+        <v>443328</v>
       </c>
       <c r="R103" t="n">
-        <v>6766686</v>
+        <v>6766721</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -10783,10 +10793,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>127723182</v>
+        <v>127722842</v>
       </c>
       <c r="B104" t="n">
-        <v>79029</v>
+        <v>79061</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -10794,21 +10804,21 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -10818,10 +10828,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>443444</v>
+        <v>443504</v>
       </c>
       <c r="R104" t="n">
-        <v>6766677</v>
+        <v>6766708</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -10880,7 +10890,7 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>127723096</v>
+        <v>127723183</v>
       </c>
       <c r="B105" t="n">
         <v>79029</v>
@@ -10915,10 +10925,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>443554</v>
+        <v>443441</v>
       </c>
       <c r="R105" t="n">
-        <v>6766650</v>
+        <v>6766686</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -10977,7 +10987,7 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>127723170</v>
+        <v>127723157</v>
       </c>
       <c r="B106" t="n">
         <v>79029</v>
@@ -11012,10 +11022,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>443333</v>
+        <v>443306</v>
       </c>
       <c r="R106" t="n">
-        <v>6766676</v>
+        <v>6766830</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11074,7 +11084,7 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>127723098</v>
+        <v>127723182</v>
       </c>
       <c r="B107" t="n">
         <v>79029</v>
@@ -11109,10 +11119,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>443562</v>
+        <v>443444</v>
       </c>
       <c r="R107" t="n">
-        <v>6766684</v>
+        <v>6766677</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11171,10 +11181,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>127723616</v>
+        <v>127723139</v>
       </c>
       <c r="B108" t="n">
-        <v>57672</v>
+        <v>79029</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11182,39 +11192,34 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
-      <c r="M108" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
       <c r="P108" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>443475</v>
+        <v>443381</v>
       </c>
       <c r="R108" t="n">
-        <v>6766610</v>
+        <v>6766623</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11273,50 +11278,45 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>127722929</v>
+        <v>127723170</v>
       </c>
       <c r="B109" t="n">
-        <v>8450</v>
+        <v>79029</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
-      <c r="M109" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P109" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>443327</v>
+        <v>443333</v>
       </c>
       <c r="R109" t="n">
-        <v>6766698</v>
+        <v>6766676</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11375,10 +11375,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>127723038</v>
+        <v>127723098</v>
       </c>
       <c r="B110" t="n">
-        <v>78788</v>
+        <v>79029</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -11386,21 +11386,21 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -11410,10 +11410,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>443328</v>
+        <v>443562</v>
       </c>
       <c r="R110" t="n">
-        <v>6766721</v>
+        <v>6766684</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11472,7 +11472,7 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>127723154</v>
+        <v>127723137</v>
       </c>
       <c r="B111" t="n">
         <v>79029</v>
@@ -11507,10 +11507,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>443369</v>
+        <v>443418</v>
       </c>
       <c r="R111" t="n">
-        <v>6766695</v>
+        <v>6766627</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -11569,7 +11569,7 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>127723172</v>
+        <v>127723154</v>
       </c>
       <c r="B112" t="n">
         <v>79029</v>
@@ -11604,10 +11604,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>443356</v>
+        <v>443369</v>
       </c>
       <c r="R112" t="n">
-        <v>6766650</v>
+        <v>6766695</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -11666,10 +11666,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>127729086</v>
+        <v>127723136</v>
       </c>
       <c r="B113" t="n">
-        <v>78788</v>
+        <v>79029</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -11677,34 +11677,34 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
       <c r="P113" t="inlineStr">
         <is>
-          <t>Oxeråsen S. om, Dlr</t>
+          <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>443359</v>
+        <v>443438</v>
       </c>
       <c r="R113" t="n">
-        <v>6766650</v>
+        <v>6766628</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -11734,47 +11734,36 @@
           <t>2025-08-21</t>
         </is>
       </c>
-      <c r="Z113" t="inlineStr">
-        <is>
-          <t>13:53</t>
-        </is>
-      </c>
       <c r="AA113" t="inlineStr">
         <is>
           <t>2025-08-21</t>
         </is>
       </c>
-      <c r="AB113" t="inlineStr">
-        <is>
-          <t>13:53</t>
-        </is>
-      </c>
       <c r="AD113" t="b">
         <v>0</v>
       </c>
       <c r="AE113" t="b">
         <v>0</v>
       </c>
-      <c r="AF113" t="inlineStr"/>
       <c r="AG113" t="b">
         <v>0</v>
       </c>
       <c r="AT113" t="inlineStr"/>
       <c r="AW113" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX113" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>127723137</v>
+        <v>127723160</v>
       </c>
       <c r="B114" t="n">
         <v>79029</v>
@@ -11809,10 +11798,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>443418</v>
+        <v>443309</v>
       </c>
       <c r="R114" t="n">
-        <v>6766627</v>
+        <v>6766785</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -11871,10 +11860,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>127723136</v>
+        <v>127729086</v>
       </c>
       <c r="B115" t="n">
-        <v>79029</v>
+        <v>78788</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -11882,34 +11871,34 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
       <c r="P115" t="inlineStr">
         <is>
-          <t>Oxeråsen, Dlr</t>
+          <t>Oxeråsen S. om, Dlr</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>443438</v>
+        <v>443359</v>
       </c>
       <c r="R115" t="n">
-        <v>6766628</v>
+        <v>6766650</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -11939,36 +11928,47 @@
           <t>2025-08-21</t>
         </is>
       </c>
+      <c r="Z115" t="inlineStr">
+        <is>
+          <t>13:53</t>
+        </is>
+      </c>
       <c r="AA115" t="inlineStr">
         <is>
           <t>2025-08-21</t>
         </is>
       </c>
+      <c r="AB115" t="inlineStr">
+        <is>
+          <t>13:53</t>
+        </is>
+      </c>
       <c r="AD115" t="b">
         <v>0</v>
       </c>
       <c r="AE115" t="b">
         <v>0</v>
       </c>
+      <c r="AF115" t="inlineStr"/>
       <c r="AG115" t="b">
         <v>0</v>
       </c>
       <c r="AT115" t="inlineStr"/>
       <c r="AW115" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX115" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>127723160</v>
+        <v>127723172</v>
       </c>
       <c r="B116" t="n">
         <v>79029</v>
@@ -12003,10 +12003,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>443309</v>
+        <v>443356</v>
       </c>
       <c r="R116" t="n">
-        <v>6766785</v>
+        <v>6766650</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12167,47 +12167,42 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>127722955</v>
+        <v>127723176</v>
       </c>
       <c r="B118" t="n">
-        <v>8450</v>
+        <v>79029</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
-      <c r="M118" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P118" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>443397</v>
+        <v>443407</v>
       </c>
       <c r="R118" t="n">
         <v>6766653</v>
@@ -12269,50 +12264,45 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>127722948</v>
+        <v>127723135</v>
       </c>
       <c r="B119" t="n">
-        <v>8450</v>
+        <v>79029</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
-      <c r="M119" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P119" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>443457</v>
+        <v>443454</v>
       </c>
       <c r="R119" t="n">
-        <v>6766613</v>
+        <v>6766614</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -12371,7 +12361,7 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>127723163</v>
+        <v>127723113</v>
       </c>
       <c r="B120" t="n">
         <v>79029</v>
@@ -12406,10 +12396,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>443332</v>
+        <v>443487</v>
       </c>
       <c r="R120" t="n">
-        <v>6766744</v>
+        <v>6766675</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -12468,10 +12458,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>127723176</v>
+        <v>127722903</v>
       </c>
       <c r="B121" t="n">
-        <v>79029</v>
+        <v>57672</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -12479,21 +12469,21 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -12503,10 +12493,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>443407</v>
+        <v>443382</v>
       </c>
       <c r="R121" t="n">
-        <v>6766653</v>
+        <v>6766657</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -12539,6 +12529,11 @@
       <c r="AA121" t="inlineStr">
         <is>
           <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AC121" t="inlineStr">
+        <is>
+          <t>Äldre ringhack (tall)</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -12565,7 +12560,7 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>127723135</v>
+        <v>127723163</v>
       </c>
       <c r="B122" t="n">
         <v>79029</v>
@@ -12600,10 +12595,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>443454</v>
+        <v>443332</v>
       </c>
       <c r="R122" t="n">
-        <v>6766614</v>
+        <v>6766744</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -12662,45 +12657,50 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>127722903</v>
+        <v>127722955</v>
       </c>
       <c r="B123" t="n">
-        <v>57672</v>
+        <v>8450</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>100109</v>
+        <v>106545</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
+      <c r="M123" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P123" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>443382</v>
+        <v>443397</v>
       </c>
       <c r="R123" t="n">
-        <v>6766657</v>
+        <v>6766653</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -12733,11 +12733,6 @@
       <c r="AA123" t="inlineStr">
         <is>
           <t>2025-08-21</t>
-        </is>
-      </c>
-      <c r="AC123" t="inlineStr">
-        <is>
-          <t>Äldre ringhack (tall)</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -12764,45 +12759,50 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>127723113</v>
+        <v>127722948</v>
       </c>
       <c r="B124" t="n">
-        <v>79029</v>
+        <v>8450</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
+      <c r="M124" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P124" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>443487</v>
+        <v>443457</v>
       </c>
       <c r="R124" t="n">
-        <v>6766675</v>
+        <v>6766613</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13249,32 +13249,32 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>127723037</v>
+        <v>127723555</v>
       </c>
       <c r="B129" t="n">
-        <v>78788</v>
+        <v>92641</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
@@ -13284,10 +13284,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>443509</v>
+        <v>443554</v>
       </c>
       <c r="R129" t="n">
-        <v>6766722</v>
+        <v>6766667</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -13346,10 +13346,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>127723555</v>
+        <v>127722954</v>
       </c>
       <c r="B130" t="n">
-        <v>92640</v>
+        <v>8450</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -13357,34 +13357,39 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>4364</v>
+        <v>106545</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
+      <c r="M130" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P130" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>443554</v>
+        <v>443348</v>
       </c>
       <c r="R130" t="n">
-        <v>6766667</v>
+        <v>6766646</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -13443,7 +13448,7 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>127722954</v>
+        <v>127722951</v>
       </c>
       <c r="B131" t="n">
         <v>8450</v>
@@ -13483,10 +13488,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>443348</v>
+        <v>443377</v>
       </c>
       <c r="R131" t="n">
-        <v>6766646</v>
+        <v>6766686</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -13545,50 +13550,45 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>127722951</v>
+        <v>127723037</v>
       </c>
       <c r="B132" t="n">
-        <v>8450</v>
+        <v>78788</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>106545</v>
+        <v>228912</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
-      <c r="M132" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P132" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>443377</v>
+        <v>443509</v>
       </c>
       <c r="R132" t="n">
-        <v>6766686</v>
+        <v>6766722</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -13647,10 +13647,10 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>127723162</v>
+        <v>127722855</v>
       </c>
       <c r="B133" t="n">
-        <v>79029</v>
+        <v>79618</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -13658,21 +13658,21 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
@@ -13682,10 +13682,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>443312</v>
+        <v>443510</v>
       </c>
       <c r="R133" t="n">
-        <v>6766762</v>
+        <v>6766723</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -13744,7 +13744,7 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>127723111</v>
+        <v>127723162</v>
       </c>
       <c r="B134" t="n">
         <v>79029</v>
@@ -13779,10 +13779,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>443474</v>
+        <v>443312</v>
       </c>
       <c r="R134" t="n">
-        <v>6766692</v>
+        <v>6766762</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -13841,10 +13841,10 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>127722855</v>
+        <v>127723111</v>
       </c>
       <c r="B135" t="n">
-        <v>79618</v>
+        <v>79029</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -13852,21 +13852,21 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
@@ -13876,10 +13876,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>443510</v>
+        <v>443474</v>
       </c>
       <c r="R135" t="n">
-        <v>6766723</v>
+        <v>6766692</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -14048,7 +14048,7 @@
         <v>127736007</v>
       </c>
       <c r="B137" t="n">
-        <v>91370</v>
+        <v>91371</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -14803,7 +14803,7 @@
         <v>127785472</v>
       </c>
       <c r="B144" t="n">
-        <v>91370</v>
+        <v>91371</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>

--- a/artfynd/A 35484-2025 artfynd.xlsx
+++ b/artfynd/A 35484-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127621301</v>
+        <v>127621346</v>
       </c>
       <c r="B2" t="n">
-        <v>79029</v>
+        <v>78787</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -713,10 +713,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>443316</v>
+        <v>443330</v>
       </c>
       <c r="R2" t="n">
-        <v>6766797</v>
+        <v>6766724</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -749,11 +749,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-08-14</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>På 4 tallstammar</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -781,10 +776,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127621346</v>
+        <v>127621301</v>
       </c>
       <c r="B3" t="n">
-        <v>78787</v>
+        <v>79029</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -792,21 +787,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -819,10 +814,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>443330</v>
+        <v>443316</v>
       </c>
       <c r="R3" t="n">
-        <v>6766724</v>
+        <v>6766797</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -855,6 +850,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>På 4 tallstammar</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -1839,7 +1839,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127723164</v>
+        <v>127723151</v>
       </c>
       <c r="B13" t="n">
         <v>79029</v>
@@ -1874,10 +1874,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>443329</v>
+        <v>443430</v>
       </c>
       <c r="R13" t="n">
-        <v>6766739</v>
+        <v>6766608</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1936,7 +1936,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127723117</v>
+        <v>127723164</v>
       </c>
       <c r="B14" t="n">
         <v>79029</v>
@@ -1971,10 +1971,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>443514</v>
+        <v>443329</v>
       </c>
       <c r="R14" t="n">
-        <v>6766630</v>
+        <v>6766739</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2033,7 +2033,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127723151</v>
+        <v>127723117</v>
       </c>
       <c r="B15" t="n">
         <v>79029</v>
@@ -2068,10 +2068,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>443430</v>
+        <v>443514</v>
       </c>
       <c r="R15" t="n">
-        <v>6766608</v>
+        <v>6766630</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2829,10 +2829,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127723112</v>
+        <v>127723039</v>
       </c>
       <c r="B23" t="n">
-        <v>79029</v>
+        <v>78788</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2840,21 +2840,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2864,10 +2864,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>443476</v>
+        <v>443356</v>
       </c>
       <c r="R23" t="n">
-        <v>6766681</v>
+        <v>6766650</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2926,10 +2926,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127723166</v>
+        <v>127723040</v>
       </c>
       <c r="B24" t="n">
-        <v>79029</v>
+        <v>78788</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2937,21 +2937,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2961,10 +2961,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>443326</v>
+        <v>443377</v>
       </c>
       <c r="R24" t="n">
-        <v>6766711</v>
+        <v>6766659</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3023,50 +3023,45 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127722950</v>
+        <v>127723112</v>
       </c>
       <c r="B25" t="n">
-        <v>8450</v>
+        <v>79029</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>443438</v>
+        <v>443476</v>
       </c>
       <c r="R25" t="n">
-        <v>6766650</v>
+        <v>6766681</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3125,10 +3120,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127722874</v>
+        <v>127723166</v>
       </c>
       <c r="B26" t="n">
-        <v>91371</v>
+        <v>79029</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3136,21 +3131,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3160,10 +3155,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>443388</v>
+        <v>443326</v>
       </c>
       <c r="R26" t="n">
-        <v>6766675</v>
+        <v>6766711</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3319,10 +3314,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127723039</v>
+        <v>127722874</v>
       </c>
       <c r="B28" t="n">
-        <v>78788</v>
+        <v>91372</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3330,21 +3325,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>228912</v>
+        <v>5442</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3354,10 +3349,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>443356</v>
+        <v>443388</v>
       </c>
       <c r="R28" t="n">
-        <v>6766650</v>
+        <v>6766675</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3416,45 +3411,50 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127723040</v>
+        <v>127722950</v>
       </c>
       <c r="B29" t="n">
-        <v>78788</v>
+        <v>8450</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>228912</v>
+        <v>106545</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>443377</v>
+        <v>443438</v>
       </c>
       <c r="R29" t="n">
-        <v>6766659</v>
+        <v>6766650</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3610,50 +3610,45 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127722945</v>
+        <v>127722875</v>
       </c>
       <c r="B31" t="n">
-        <v>8450</v>
+        <v>91372</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>106545</v>
+        <v>5442</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>443568</v>
+        <v>443312</v>
       </c>
       <c r="R31" t="n">
-        <v>6766605</v>
+        <v>6766713</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3712,10 +3707,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127722875</v>
+        <v>127723179</v>
       </c>
       <c r="B32" t="n">
-        <v>91371</v>
+        <v>79029</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3723,21 +3718,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3747,10 +3742,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>443312</v>
+        <v>443411</v>
       </c>
       <c r="R32" t="n">
-        <v>6766713</v>
+        <v>6766676</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3809,45 +3804,50 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127723179</v>
+        <v>127722945</v>
       </c>
       <c r="B33" t="n">
-        <v>79029</v>
+        <v>8450</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>443411</v>
+        <v>443568</v>
       </c>
       <c r="R33" t="n">
-        <v>6766676</v>
+        <v>6766605</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3906,7 +3906,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>127723109</v>
+        <v>127723107</v>
       </c>
       <c r="B34" t="n">
         <v>79029</v>
@@ -3941,10 +3941,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>443482</v>
+        <v>443493</v>
       </c>
       <c r="R34" t="n">
-        <v>6766716</v>
+        <v>6766717</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4003,7 +4003,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127723169</v>
+        <v>127723109</v>
       </c>
       <c r="B35" t="n">
         <v>79029</v>
@@ -4038,10 +4038,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>443321</v>
+        <v>443482</v>
       </c>
       <c r="R35" t="n">
-        <v>6766706</v>
+        <v>6766716</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4100,7 +4100,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127723115</v>
+        <v>127723169</v>
       </c>
       <c r="B36" t="n">
         <v>79029</v>
@@ -4135,10 +4135,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>443495</v>
+        <v>443321</v>
       </c>
       <c r="R36" t="n">
-        <v>6766641</v>
+        <v>6766706</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4197,7 +4197,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127723107</v>
+        <v>127723115</v>
       </c>
       <c r="B37" t="n">
         <v>79029</v>
@@ -4232,10 +4232,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>443493</v>
+        <v>443495</v>
       </c>
       <c r="R37" t="n">
-        <v>6766717</v>
+        <v>6766641</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4603,7 +4603,7 @@
         <v>127722921</v>
       </c>
       <c r="B41" t="n">
-        <v>97346</v>
+        <v>97347</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4700,7 +4700,7 @@
         <v>127723064</v>
       </c>
       <c r="B42" t="n">
-        <v>91512</v>
+        <v>91513</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4988,10 +4988,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>127723189</v>
+        <v>127722876</v>
       </c>
       <c r="B45" t="n">
-        <v>79029</v>
+        <v>91372</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4999,21 +4999,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5023,10 +5023,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>443446</v>
+        <v>443366</v>
       </c>
       <c r="R45" t="n">
-        <v>6766727</v>
+        <v>6766661</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5059,11 +5059,6 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-08-21</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Med grov gran i bäckmiljö</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5090,7 +5085,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>127723121</v>
+        <v>127723189</v>
       </c>
       <c r="B46" t="n">
         <v>79029</v>
@@ -5125,10 +5120,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>443558</v>
+        <v>443446</v>
       </c>
       <c r="R46" t="n">
-        <v>6766620</v>
+        <v>6766727</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5161,6 +5156,11 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Med grov gran i bäckmiljö</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5187,10 +5187,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>127722876</v>
+        <v>127723121</v>
       </c>
       <c r="B47" t="n">
-        <v>91371</v>
+        <v>79029</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5198,21 +5198,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5222,10 +5222,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>443366</v>
+        <v>443558</v>
       </c>
       <c r="R47" t="n">
-        <v>6766661</v>
+        <v>6766620</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5284,7 +5284,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>127723102</v>
+        <v>127723180</v>
       </c>
       <c r="B48" t="n">
         <v>79029</v>
@@ -5319,10 +5319,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>443556</v>
+        <v>443425</v>
       </c>
       <c r="R48" t="n">
-        <v>6766717</v>
+        <v>6766665</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5381,10 +5381,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>127722868</v>
+        <v>127723102</v>
       </c>
       <c r="B49" t="n">
-        <v>57832</v>
+        <v>79029</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5392,39 +5392,34 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>443305</v>
+        <v>443556</v>
       </c>
       <c r="R49" t="n">
-        <v>6766767</v>
+        <v>6766717</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5483,7 +5478,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>127723180</v>
+        <v>127723185</v>
       </c>
       <c r="B50" t="n">
         <v>79029</v>
@@ -5518,10 +5513,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>443425</v>
+        <v>443452</v>
       </c>
       <c r="R50" t="n">
-        <v>6766665</v>
+        <v>6766711</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5580,7 +5575,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>127723185</v>
+        <v>127723110</v>
       </c>
       <c r="B51" t="n">
         <v>79029</v>
@@ -5615,10 +5610,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>443452</v>
+        <v>443479</v>
       </c>
       <c r="R51" t="n">
-        <v>6766711</v>
+        <v>6766703</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5677,10 +5672,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>127723110</v>
+        <v>127722868</v>
       </c>
       <c r="B52" t="n">
-        <v>79029</v>
+        <v>57832</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5688,34 +5683,39 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>443479</v>
+        <v>443305</v>
       </c>
       <c r="R52" t="n">
-        <v>6766703</v>
+        <v>6766767</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5973,50 +5973,45 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>127722943</v>
+        <v>127723184</v>
       </c>
       <c r="B55" t="n">
-        <v>8450</v>
+        <v>79029</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>443527</v>
+        <v>443446</v>
       </c>
       <c r="R55" t="n">
-        <v>6766711</v>
+        <v>6766702</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6075,7 +6070,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>127722956</v>
+        <v>127722943</v>
       </c>
       <c r="B56" t="n">
         <v>8450</v>
@@ -6115,10 +6110,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>443454</v>
+        <v>443527</v>
       </c>
       <c r="R56" t="n">
-        <v>6766718</v>
+        <v>6766711</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6177,45 +6172,50 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>127723184</v>
+        <v>127722956</v>
       </c>
       <c r="B57" t="n">
-        <v>79029</v>
+        <v>8450</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P57" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>443446</v>
+        <v>443454</v>
       </c>
       <c r="R57" t="n">
-        <v>6766702</v>
+        <v>6766718</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6371,7 +6371,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>127723153</v>
+        <v>127723167</v>
       </c>
       <c r="B59" t="n">
         <v>79029</v>
@@ -6406,10 +6406,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>443436</v>
+        <v>443316</v>
       </c>
       <c r="R59" t="n">
-        <v>6766648</v>
+        <v>6766701</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6468,7 +6468,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>127723119</v>
+        <v>127723153</v>
       </c>
       <c r="B60" t="n">
         <v>79029</v>
@@ -6503,10 +6503,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>443535</v>
+        <v>443436</v>
       </c>
       <c r="R60" t="n">
-        <v>6766639</v>
+        <v>6766648</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6565,7 +6565,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>127723106</v>
+        <v>127723119</v>
       </c>
       <c r="B61" t="n">
         <v>79029</v>
@@ -6600,10 +6600,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>443516</v>
+        <v>443535</v>
       </c>
       <c r="R61" t="n">
-        <v>6766720</v>
+        <v>6766639</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6662,7 +6662,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>127723188</v>
+        <v>127723106</v>
       </c>
       <c r="B62" t="n">
         <v>79029</v>
@@ -6697,10 +6697,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>443454</v>
+        <v>443516</v>
       </c>
       <c r="R62" t="n">
-        <v>6766724</v>
+        <v>6766720</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6759,7 +6759,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>127723175</v>
+        <v>127723188</v>
       </c>
       <c r="B63" t="n">
         <v>79029</v>
@@ -6794,10 +6794,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>443387</v>
+        <v>443454</v>
       </c>
       <c r="R63" t="n">
-        <v>6766658</v>
+        <v>6766724</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6856,7 +6856,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>127723134</v>
+        <v>127723175</v>
       </c>
       <c r="B64" t="n">
         <v>79029</v>
@@ -6891,10 +6891,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>443465</v>
+        <v>443387</v>
       </c>
       <c r="R64" t="n">
-        <v>6766607</v>
+        <v>6766658</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -6953,7 +6953,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>127723167</v>
+        <v>127723134</v>
       </c>
       <c r="B65" t="n">
         <v>79029</v>
@@ -6988,10 +6988,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>443316</v>
+        <v>443465</v>
       </c>
       <c r="R65" t="n">
-        <v>6766701</v>
+        <v>6766607</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7050,32 +7050,32 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>127722847</v>
+        <v>127723065</v>
       </c>
       <c r="B66" t="n">
-        <v>79061</v>
+        <v>91513</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>185</v>
+        <v>1503</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7085,10 +7085,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>443320</v>
+        <v>443425</v>
       </c>
       <c r="R66" t="n">
-        <v>6766703</v>
+        <v>6766668</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7147,10 +7147,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>127729137</v>
+        <v>127722847</v>
       </c>
       <c r="B67" t="n">
-        <v>79029</v>
+        <v>79061</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7158,34 +7158,34 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Oxeråsen S. om, Dlr</t>
+          <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>443391</v>
+        <v>443320</v>
       </c>
       <c r="R67" t="n">
-        <v>6766598</v>
+        <v>6766703</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7215,47 +7215,36 @@
           <t>2025-08-21</t>
         </is>
       </c>
-      <c r="Z67" t="inlineStr">
-        <is>
-          <t>14:00</t>
-        </is>
-      </c>
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-08-21</t>
         </is>
       </c>
-      <c r="AB67" t="inlineStr">
-        <is>
-          <t>14:00</t>
-        </is>
-      </c>
       <c r="AD67" t="b">
         <v>0</v>
       </c>
       <c r="AE67" t="b">
         <v>0</v>
       </c>
-      <c r="AF67" t="inlineStr"/>
       <c r="AG67" t="b">
         <v>0</v>
       </c>
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>127723158</v>
+        <v>127729137</v>
       </c>
       <c r="B68" t="n">
         <v>79029</v>
@@ -7286,14 +7275,14 @@
       <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Oxeråsen, Dlr</t>
+          <t>Oxeråsen S. om, Dlr</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>443312</v>
+        <v>443391</v>
       </c>
       <c r="R68" t="n">
-        <v>6766818</v>
+        <v>6766598</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7323,29 +7312,40 @@
           <t>2025-08-21</t>
         </is>
       </c>
+      <c r="Z68" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
       <c r="AA68" t="inlineStr">
         <is>
           <t>2025-08-21</t>
         </is>
       </c>
+      <c r="AB68" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
       <c r="AD68" t="b">
         <v>0</v>
       </c>
       <c r="AE68" t="b">
         <v>0</v>
       </c>
+      <c r="AF68" t="inlineStr"/>
       <c r="AG68" t="b">
         <v>0</v>
       </c>
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
@@ -7449,7 +7449,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>127723150</v>
+        <v>127723158</v>
       </c>
       <c r="B70" t="n">
         <v>79029</v>
@@ -7484,10 +7484,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>443415</v>
+        <v>443312</v>
       </c>
       <c r="R70" t="n">
-        <v>6766603</v>
+        <v>6766818</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7546,32 +7546,32 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>127723065</v>
+        <v>127723150</v>
       </c>
       <c r="B71" t="n">
-        <v>91512</v>
+        <v>79029</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>1503</v>
+        <v>6425</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7581,10 +7581,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>443425</v>
+        <v>443415</v>
       </c>
       <c r="R71" t="n">
-        <v>6766668</v>
+        <v>6766603</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8338,10 +8338,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>127723571</v>
+        <v>127723156</v>
       </c>
       <c r="B79" t="n">
-        <v>78696</v>
+        <v>79029</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8349,21 +8349,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8373,10 +8373,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>443426</v>
+        <v>443346</v>
       </c>
       <c r="R79" t="n">
-        <v>6766668</v>
+        <v>6766766</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8435,7 +8435,7 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>127723156</v>
+        <v>127723120</v>
       </c>
       <c r="B80" t="n">
         <v>79029</v>
@@ -8470,10 +8470,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>443346</v>
+        <v>443548</v>
       </c>
       <c r="R80" t="n">
-        <v>6766766</v>
+        <v>6766624</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8532,7 +8532,7 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>127723120</v>
+        <v>127723104</v>
       </c>
       <c r="B81" t="n">
         <v>79029</v>
@@ -8567,10 +8567,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>443548</v>
+        <v>443536</v>
       </c>
       <c r="R81" t="n">
-        <v>6766624</v>
+        <v>6766704</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8629,10 +8629,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>127723104</v>
+        <v>127723571</v>
       </c>
       <c r="B82" t="n">
-        <v>79029</v>
+        <v>78696</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8640,21 +8640,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8664,10 +8664,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>443536</v>
+        <v>443426</v>
       </c>
       <c r="R82" t="n">
-        <v>6766704</v>
+        <v>6766668</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8726,10 +8726,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>127723178</v>
+        <v>127723570</v>
       </c>
       <c r="B83" t="n">
-        <v>79029</v>
+        <v>78696</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8737,21 +8737,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -8761,10 +8761,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>443402</v>
+        <v>443319</v>
       </c>
       <c r="R83" t="n">
-        <v>6766682</v>
+        <v>6766670</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -8823,10 +8823,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>127722888</v>
+        <v>127723116</v>
       </c>
       <c r="B84" t="n">
-        <v>57669</v>
+        <v>79029</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -8834,39 +8834,34 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
-      <c r="M84" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P84" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>443481</v>
+        <v>443509</v>
       </c>
       <c r="R84" t="n">
-        <v>6766676</v>
+        <v>6766633</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -8925,10 +8920,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>127722916</v>
+        <v>127723092</v>
       </c>
       <c r="B85" t="n">
-        <v>57672</v>
+        <v>79029</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -8936,39 +8931,34 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
-      <c r="M85" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P85" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>443342</v>
+        <v>443572</v>
       </c>
       <c r="R85" t="n">
-        <v>6766806</v>
+        <v>6766650</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9001,11 +8991,6 @@
       <c r="AA85" t="inlineStr">
         <is>
           <t>2025-08-21</t>
-        </is>
-      </c>
-      <c r="AC85" t="inlineStr">
-        <is>
-          <t>Färska ringhack (gran), 4-5 år gamla</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9032,10 +9017,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>127723570</v>
+        <v>127723178</v>
       </c>
       <c r="B86" t="n">
-        <v>78696</v>
+        <v>79029</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9043,21 +9028,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9067,10 +9052,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>443319</v>
+        <v>443402</v>
       </c>
       <c r="R86" t="n">
-        <v>6766670</v>
+        <v>6766682</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9129,10 +9114,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>127723541</v>
+        <v>127723171</v>
       </c>
       <c r="B87" t="n">
-        <v>57672</v>
+        <v>79029</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9140,39 +9125,34 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
-      <c r="M87" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P87" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>443317</v>
+        <v>443342</v>
       </c>
       <c r="R87" t="n">
-        <v>6766816</v>
+        <v>6766650</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9231,10 +9211,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>127723116</v>
+        <v>127722888</v>
       </c>
       <c r="B88" t="n">
-        <v>79029</v>
+        <v>57669</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9242,34 +9222,39 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P88" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>443509</v>
+        <v>443481</v>
       </c>
       <c r="R88" t="n">
-        <v>6766633</v>
+        <v>6766676</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9328,10 +9313,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>127723092</v>
+        <v>127722916</v>
       </c>
       <c r="B89" t="n">
-        <v>79029</v>
+        <v>57672</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9339,34 +9324,39 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P89" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>443572</v>
+        <v>443342</v>
       </c>
       <c r="R89" t="n">
-        <v>6766650</v>
+        <v>6766806</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9399,6 +9389,11 @@
       <c r="AA89" t="inlineStr">
         <is>
           <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AC89" t="inlineStr">
+        <is>
+          <t>Färska ringhack (gran), 4-5 år gamla</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -9425,10 +9420,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>127723171</v>
+        <v>127723541</v>
       </c>
       <c r="B90" t="n">
-        <v>79029</v>
+        <v>57672</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9436,34 +9431,39 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P90" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>443342</v>
+        <v>443317</v>
       </c>
       <c r="R90" t="n">
-        <v>6766650</v>
+        <v>6766816</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9522,10 +9522,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>127723097</v>
+        <v>127723569</v>
       </c>
       <c r="B91" t="n">
-        <v>79029</v>
+        <v>78696</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9533,21 +9533,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -9557,10 +9557,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>443561</v>
+        <v>443332</v>
       </c>
       <c r="R91" t="n">
-        <v>6766678</v>
+        <v>6766677</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9619,7 +9619,7 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>127723114</v>
+        <v>127723103</v>
       </c>
       <c r="B92" t="n">
         <v>79029</v>
@@ -9654,10 +9654,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>443487</v>
+        <v>443541</v>
       </c>
       <c r="R92" t="n">
-        <v>6766651</v>
+        <v>6766696</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9716,10 +9716,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>127723569</v>
+        <v>127723105</v>
       </c>
       <c r="B93" t="n">
-        <v>78696</v>
+        <v>79029</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9727,21 +9727,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -9751,10 +9751,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>443332</v>
+        <v>443525</v>
       </c>
       <c r="R93" t="n">
-        <v>6766677</v>
+        <v>6766717</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -9813,7 +9813,7 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>127723103</v>
+        <v>127723161</v>
       </c>
       <c r="B94" t="n">
         <v>79029</v>
@@ -9848,10 +9848,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>443541</v>
+        <v>443305</v>
       </c>
       <c r="R94" t="n">
-        <v>6766696</v>
+        <v>6766767</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -9910,7 +9910,7 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>127723105</v>
+        <v>127723186</v>
       </c>
       <c r="B95" t="n">
         <v>79029</v>
@@ -9945,10 +9945,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>443525</v>
+        <v>443454</v>
       </c>
       <c r="R95" t="n">
-        <v>6766717</v>
+        <v>6766738</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10007,7 +10007,7 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>127723161</v>
+        <v>127723114</v>
       </c>
       <c r="B96" t="n">
         <v>79029</v>
@@ -10042,10 +10042,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>443305</v>
+        <v>443487</v>
       </c>
       <c r="R96" t="n">
-        <v>6766767</v>
+        <v>6766651</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10104,7 +10104,7 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>127723174</v>
+        <v>127723097</v>
       </c>
       <c r="B97" t="n">
         <v>79029</v>
@@ -10139,10 +10139,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>443378</v>
+        <v>443561</v>
       </c>
       <c r="R97" t="n">
-        <v>6766657</v>
+        <v>6766678</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10201,7 +10201,7 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>127723186</v>
+        <v>127723174</v>
       </c>
       <c r="B98" t="n">
         <v>79029</v>
@@ -10236,10 +10236,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>443454</v>
+        <v>443378</v>
       </c>
       <c r="R98" t="n">
-        <v>6766738</v>
+        <v>6766657</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10395,10 +10395,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>127723096</v>
+        <v>127722842</v>
       </c>
       <c r="B100" t="n">
-        <v>79029</v>
+        <v>79061</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10406,21 +10406,21 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -10430,10 +10430,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>443554</v>
+        <v>443504</v>
       </c>
       <c r="R100" t="n">
-        <v>6766650</v>
+        <v>6766708</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10492,10 +10492,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>127723616</v>
+        <v>127723183</v>
       </c>
       <c r="B101" t="n">
-        <v>57672</v>
+        <v>79029</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -10503,39 +10503,34 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
-      <c r="M101" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
       <c r="P101" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>443475</v>
+        <v>443441</v>
       </c>
       <c r="R101" t="n">
-        <v>6766610</v>
+        <v>6766686</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10594,50 +10589,45 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>127722929</v>
+        <v>127723157</v>
       </c>
       <c r="B102" t="n">
-        <v>8450</v>
+        <v>79029</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
-      <c r="M102" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P102" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>443327</v>
+        <v>443306</v>
       </c>
       <c r="R102" t="n">
-        <v>6766698</v>
+        <v>6766830</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -10696,10 +10686,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>127723038</v>
+        <v>127723182</v>
       </c>
       <c r="B103" t="n">
-        <v>78788</v>
+        <v>79029</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -10707,21 +10697,21 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -10731,10 +10721,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>443328</v>
+        <v>443444</v>
       </c>
       <c r="R103" t="n">
-        <v>6766721</v>
+        <v>6766677</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -10793,10 +10783,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>127722842</v>
+        <v>127723139</v>
       </c>
       <c r="B104" t="n">
-        <v>79061</v>
+        <v>79029</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -10804,21 +10794,21 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -10828,10 +10818,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>443504</v>
+        <v>443381</v>
       </c>
       <c r="R104" t="n">
-        <v>6766708</v>
+        <v>6766623</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -10890,7 +10880,7 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>127723183</v>
+        <v>127723170</v>
       </c>
       <c r="B105" t="n">
         <v>79029</v>
@@ -10925,10 +10915,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>443441</v>
+        <v>443333</v>
       </c>
       <c r="R105" t="n">
-        <v>6766686</v>
+        <v>6766676</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -10987,7 +10977,7 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>127723157</v>
+        <v>127723098</v>
       </c>
       <c r="B106" t="n">
         <v>79029</v>
@@ -11022,10 +11012,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>443306</v>
+        <v>443562</v>
       </c>
       <c r="R106" t="n">
-        <v>6766830</v>
+        <v>6766684</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11084,10 +11074,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>127723182</v>
+        <v>127723616</v>
       </c>
       <c r="B107" t="n">
-        <v>79029</v>
+        <v>57672</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11095,34 +11085,39 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
+      <c r="M107" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
       <c r="P107" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>443444</v>
+        <v>443475</v>
       </c>
       <c r="R107" t="n">
-        <v>6766677</v>
+        <v>6766610</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11181,10 +11176,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>127723139</v>
+        <v>127723038</v>
       </c>
       <c r="B108" t="n">
-        <v>79029</v>
+        <v>78788</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11192,21 +11187,21 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -11216,10 +11211,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>443381</v>
+        <v>443328</v>
       </c>
       <c r="R108" t="n">
-        <v>6766623</v>
+        <v>6766721</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11278,7 +11273,7 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>127723170</v>
+        <v>127723096</v>
       </c>
       <c r="B109" t="n">
         <v>79029</v>
@@ -11313,10 +11308,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>443333</v>
+        <v>443554</v>
       </c>
       <c r="R109" t="n">
-        <v>6766676</v>
+        <v>6766650</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11375,45 +11370,50 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>127723098</v>
+        <v>127722929</v>
       </c>
       <c r="B110" t="n">
-        <v>79029</v>
+        <v>8450</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
+      <c r="M110" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P110" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>443562</v>
+        <v>443327</v>
       </c>
       <c r="R110" t="n">
-        <v>6766684</v>
+        <v>6766698</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11666,7 +11666,7 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>127723136</v>
+        <v>127723172</v>
       </c>
       <c r="B113" t="n">
         <v>79029</v>
@@ -11701,10 +11701,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>443438</v>
+        <v>443356</v>
       </c>
       <c r="R113" t="n">
-        <v>6766628</v>
+        <v>6766650</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -11763,7 +11763,7 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>127723160</v>
+        <v>127723136</v>
       </c>
       <c r="B114" t="n">
         <v>79029</v>
@@ -11798,10 +11798,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>443309</v>
+        <v>443438</v>
       </c>
       <c r="R114" t="n">
-        <v>6766785</v>
+        <v>6766628</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -11860,10 +11860,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>127729086</v>
+        <v>127723160</v>
       </c>
       <c r="B115" t="n">
-        <v>78788</v>
+        <v>79029</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -11871,34 +11871,34 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
       <c r="P115" t="inlineStr">
         <is>
-          <t>Oxeråsen S. om, Dlr</t>
+          <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>443359</v>
+        <v>443309</v>
       </c>
       <c r="R115" t="n">
-        <v>6766650</v>
+        <v>6766785</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -11928,50 +11928,39 @@
           <t>2025-08-21</t>
         </is>
       </c>
-      <c r="Z115" t="inlineStr">
-        <is>
-          <t>13:53</t>
-        </is>
-      </c>
       <c r="AA115" t="inlineStr">
         <is>
           <t>2025-08-21</t>
         </is>
       </c>
-      <c r="AB115" t="inlineStr">
-        <is>
-          <t>13:53</t>
-        </is>
-      </c>
       <c r="AD115" t="b">
         <v>0</v>
       </c>
       <c r="AE115" t="b">
         <v>0</v>
       </c>
-      <c r="AF115" t="inlineStr"/>
       <c r="AG115" t="b">
         <v>0</v>
       </c>
       <c r="AT115" t="inlineStr"/>
       <c r="AW115" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX115" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>127723172</v>
+        <v>127722904</v>
       </c>
       <c r="B116" t="n">
-        <v>79029</v>
+        <v>57672</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -11979,21 +11968,21 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -12003,10 +11992,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>443356</v>
+        <v>443419</v>
       </c>
       <c r="R116" t="n">
-        <v>6766650</v>
+        <v>6766676</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12039,6 +12028,11 @@
       <c r="AA116" t="inlineStr">
         <is>
           <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AC116" t="inlineStr">
+        <is>
+          <t>Äldre ringhack (tall)</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -12065,10 +12059,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>127722904</v>
+        <v>127729086</v>
       </c>
       <c r="B117" t="n">
-        <v>57672</v>
+        <v>78788</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -12076,34 +12070,34 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>100109</v>
+        <v>228912</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
       <c r="P117" t="inlineStr">
         <is>
-          <t>Oxeråsen, Dlr</t>
+          <t>Oxeråsen S. om, Dlr</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>443419</v>
+        <v>443359</v>
       </c>
       <c r="R117" t="n">
-        <v>6766676</v>
+        <v>6766650</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12133,14 +12127,19 @@
           <t>2025-08-21</t>
         </is>
       </c>
+      <c r="Z117" t="inlineStr">
+        <is>
+          <t>13:53</t>
+        </is>
+      </c>
       <c r="AA117" t="inlineStr">
         <is>
           <t>2025-08-21</t>
         </is>
       </c>
-      <c r="AC117" t="inlineStr">
-        <is>
-          <t>Äldre ringhack (tall)</t>
+      <c r="AB117" t="inlineStr">
+        <is>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -12149,25 +12148,26 @@
       <c r="AE117" t="b">
         <v>0</v>
       </c>
+      <c r="AF117" t="inlineStr"/>
       <c r="AG117" t="b">
         <v>0</v>
       </c>
       <c r="AT117" t="inlineStr"/>
       <c r="AW117" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX117" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>127723176</v>
+        <v>127723163</v>
       </c>
       <c r="B118" t="n">
         <v>79029</v>
@@ -12202,10 +12202,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>443407</v>
+        <v>443332</v>
       </c>
       <c r="R118" t="n">
-        <v>6766653</v>
+        <v>6766744</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12264,7 +12264,7 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>127723135</v>
+        <v>127723176</v>
       </c>
       <c r="B119" t="n">
         <v>79029</v>
@@ -12299,10 +12299,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>443454</v>
+        <v>443407</v>
       </c>
       <c r="R119" t="n">
-        <v>6766614</v>
+        <v>6766653</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -12361,7 +12361,7 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>127723113</v>
+        <v>127723135</v>
       </c>
       <c r="B120" t="n">
         <v>79029</v>
@@ -12396,10 +12396,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>443487</v>
+        <v>443454</v>
       </c>
       <c r="R120" t="n">
-        <v>6766675</v>
+        <v>6766614</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -12458,10 +12458,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>127722903</v>
+        <v>127723113</v>
       </c>
       <c r="B121" t="n">
-        <v>57672</v>
+        <v>79029</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -12469,21 +12469,21 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -12493,10 +12493,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>443382</v>
+        <v>443487</v>
       </c>
       <c r="R121" t="n">
-        <v>6766657</v>
+        <v>6766675</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -12529,11 +12529,6 @@
       <c r="AA121" t="inlineStr">
         <is>
           <t>2025-08-21</t>
-        </is>
-      </c>
-      <c r="AC121" t="inlineStr">
-        <is>
-          <t>Äldre ringhack (tall)</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -12560,10 +12555,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>127723163</v>
+        <v>127722903</v>
       </c>
       <c r="B122" t="n">
-        <v>79029</v>
+        <v>57672</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -12571,21 +12566,21 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -12595,10 +12590,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>443332</v>
+        <v>443382</v>
       </c>
       <c r="R122" t="n">
-        <v>6766744</v>
+        <v>6766657</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -12631,6 +12626,11 @@
       <c r="AA122" t="inlineStr">
         <is>
           <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AC122" t="inlineStr">
+        <is>
+          <t>Äldre ringhack (tall)</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -13249,10 +13249,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>127723555</v>
+        <v>127722954</v>
       </c>
       <c r="B129" t="n">
-        <v>92641</v>
+        <v>8450</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -13260,34 +13260,39 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>4364</v>
+        <v>106545</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
+      <c r="M129" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P129" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>443554</v>
+        <v>443348</v>
       </c>
       <c r="R129" t="n">
-        <v>6766667</v>
+        <v>6766646</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -13346,7 +13351,7 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>127722954</v>
+        <v>127722951</v>
       </c>
       <c r="B130" t="n">
         <v>8450</v>
@@ -13386,10 +13391,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>443348</v>
+        <v>443377</v>
       </c>
       <c r="R130" t="n">
-        <v>6766646</v>
+        <v>6766686</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -13448,10 +13453,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>127722951</v>
+        <v>127723555</v>
       </c>
       <c r="B131" t="n">
-        <v>8450</v>
+        <v>92642</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -13459,39 +13464,34 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>106545</v>
+        <v>4364</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
-      <c r="M131" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P131" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>443377</v>
+        <v>443554</v>
       </c>
       <c r="R131" t="n">
-        <v>6766686</v>
+        <v>6766667</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -13647,10 +13647,10 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>127722855</v>
+        <v>127723162</v>
       </c>
       <c r="B133" t="n">
-        <v>79618</v>
+        <v>79029</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -13658,21 +13658,21 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
@@ -13682,10 +13682,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>443510</v>
+        <v>443312</v>
       </c>
       <c r="R133" t="n">
-        <v>6766723</v>
+        <v>6766762</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -13744,7 +13744,7 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>127723162</v>
+        <v>127723111</v>
       </c>
       <c r="B134" t="n">
         <v>79029</v>
@@ -13779,10 +13779,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>443312</v>
+        <v>443474</v>
       </c>
       <c r="R134" t="n">
-        <v>6766762</v>
+        <v>6766692</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -13841,10 +13841,10 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>127723111</v>
+        <v>127722855</v>
       </c>
       <c r="B135" t="n">
-        <v>79029</v>
+        <v>79618</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -13852,21 +13852,21 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
@@ -13876,10 +13876,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>443474</v>
+        <v>443510</v>
       </c>
       <c r="R135" t="n">
-        <v>6766692</v>
+        <v>6766723</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -14048,7 +14048,7 @@
         <v>127736007</v>
       </c>
       <c r="B137" t="n">
-        <v>91371</v>
+        <v>91372</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -14803,7 +14803,7 @@
         <v>127785472</v>
       </c>
       <c r="B144" t="n">
-        <v>91371</v>
+        <v>91372</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>

--- a/artfynd/A 35484-2025 artfynd.xlsx
+++ b/artfynd/A 35484-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127621346</v>
+        <v>127621301</v>
       </c>
       <c r="B2" t="n">
-        <v>78787</v>
+        <v>79029</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -713,10 +713,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>443330</v>
+        <v>443316</v>
       </c>
       <c r="R2" t="n">
-        <v>6766724</v>
+        <v>6766797</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -749,6 +749,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>På 4 tallstammar</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -776,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127621301</v>
+        <v>127621346</v>
       </c>
       <c r="B3" t="n">
-        <v>79029</v>
+        <v>78787</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -787,21 +792,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -814,10 +819,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>443316</v>
+        <v>443330</v>
       </c>
       <c r="R3" t="n">
-        <v>6766797</v>
+        <v>6766724</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -850,11 +855,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-08-14</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>På 4 tallstammar</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -1839,45 +1839,50 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127723151</v>
+        <v>127722932</v>
       </c>
       <c r="B13" t="n">
-        <v>79029</v>
+        <v>8450</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>443430</v>
+        <v>443590</v>
       </c>
       <c r="R13" t="n">
-        <v>6766608</v>
+        <v>6766651</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2033,7 +2038,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127723117</v>
+        <v>127723151</v>
       </c>
       <c r="B15" t="n">
         <v>79029</v>
@@ -2068,10 +2073,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>443514</v>
+        <v>443430</v>
       </c>
       <c r="R15" t="n">
-        <v>6766630</v>
+        <v>6766608</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2130,50 +2135,45 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127722932</v>
+        <v>127723117</v>
       </c>
       <c r="B16" t="n">
-        <v>8450</v>
+        <v>79029</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>443590</v>
+        <v>443514</v>
       </c>
       <c r="R16" t="n">
-        <v>6766651</v>
+        <v>6766630</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2431,50 +2431,45 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127722947</v>
+        <v>127723099</v>
       </c>
       <c r="B19" t="n">
-        <v>8450</v>
+        <v>79029</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>443486</v>
+        <v>443567</v>
       </c>
       <c r="R19" t="n">
-        <v>6766604</v>
+        <v>6766695</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2533,50 +2528,45 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127722942</v>
+        <v>127723093</v>
       </c>
       <c r="B20" t="n">
-        <v>8450</v>
+        <v>79029</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>443542</v>
+        <v>443572</v>
       </c>
       <c r="R20" t="n">
-        <v>6766699</v>
+        <v>6766645</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2635,45 +2625,50 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127723093</v>
+        <v>127722942</v>
       </c>
       <c r="B21" t="n">
-        <v>79029</v>
+        <v>8450</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>443572</v>
+        <v>443542</v>
       </c>
       <c r="R21" t="n">
-        <v>6766645</v>
+        <v>6766699</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2732,45 +2727,50 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127723099</v>
+        <v>127722947</v>
       </c>
       <c r="B22" t="n">
-        <v>79029</v>
+        <v>8450</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>443567</v>
+        <v>443486</v>
       </c>
       <c r="R22" t="n">
-        <v>6766695</v>
+        <v>6766604</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2829,42 +2829,47 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127723039</v>
+        <v>127722950</v>
       </c>
       <c r="B23" t="n">
-        <v>78788</v>
+        <v>8450</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>228912</v>
+        <v>106545</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>443356</v>
+        <v>443438</v>
       </c>
       <c r="R23" t="n">
         <v>6766650</v>
@@ -3023,10 +3028,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127723112</v>
+        <v>127723039</v>
       </c>
       <c r="B25" t="n">
-        <v>79029</v>
+        <v>78788</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3034,21 +3039,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3058,10 +3063,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>443476</v>
+        <v>443356</v>
       </c>
       <c r="R25" t="n">
-        <v>6766681</v>
+        <v>6766650</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3411,50 +3416,45 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127722950</v>
+        <v>127723112</v>
       </c>
       <c r="B29" t="n">
-        <v>8450</v>
+        <v>79029</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>443438</v>
+        <v>443476</v>
       </c>
       <c r="R29" t="n">
-        <v>6766650</v>
+        <v>6766681</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3513,10 +3513,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127723152</v>
+        <v>127722875</v>
       </c>
       <c r="B30" t="n">
-        <v>79029</v>
+        <v>91372</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3524,21 +3524,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3548,10 +3548,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>443424</v>
+        <v>443312</v>
       </c>
       <c r="R30" t="n">
-        <v>6766627</v>
+        <v>6766713</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3610,45 +3610,50 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127722875</v>
+        <v>127722945</v>
       </c>
       <c r="B31" t="n">
-        <v>91372</v>
+        <v>8450</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>5442</v>
+        <v>106545</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>443312</v>
+        <v>443568</v>
       </c>
       <c r="R31" t="n">
-        <v>6766713</v>
+        <v>6766605</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3707,7 +3712,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127723179</v>
+        <v>127723152</v>
       </c>
       <c r="B32" t="n">
         <v>79029</v>
@@ -3742,10 +3747,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>443411</v>
+        <v>443424</v>
       </c>
       <c r="R32" t="n">
-        <v>6766676</v>
+        <v>6766627</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3804,50 +3809,45 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127722945</v>
+        <v>127723179</v>
       </c>
       <c r="B33" t="n">
-        <v>8450</v>
+        <v>79029</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>443568</v>
+        <v>443411</v>
       </c>
       <c r="R33" t="n">
-        <v>6766605</v>
+        <v>6766676</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3906,45 +3906,50 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>127723107</v>
+        <v>127722944</v>
       </c>
       <c r="B34" t="n">
-        <v>79029</v>
+        <v>8450</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>443493</v>
+        <v>443488</v>
       </c>
       <c r="R34" t="n">
-        <v>6766717</v>
+        <v>6766671</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4003,45 +4008,50 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127723109</v>
+        <v>127722928</v>
       </c>
       <c r="B35" t="n">
-        <v>79029</v>
+        <v>8450</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>443482</v>
+        <v>443559</v>
       </c>
       <c r="R35" t="n">
-        <v>6766716</v>
+        <v>6766616</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4100,32 +4110,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127723169</v>
+        <v>127722921</v>
       </c>
       <c r="B36" t="n">
-        <v>79029</v>
+        <v>97347</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4135,10 +4145,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>443321</v>
+        <v>443330</v>
       </c>
       <c r="R36" t="n">
-        <v>6766706</v>
+        <v>6766662</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4294,10 +4304,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127722896</v>
+        <v>127723169</v>
       </c>
       <c r="B38" t="n">
-        <v>57669</v>
+        <v>79029</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4305,39 +4315,34 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>443537</v>
+        <v>443321</v>
       </c>
       <c r="R38" t="n">
-        <v>6766699</v>
+        <v>6766706</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4396,50 +4401,45 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127722944</v>
+        <v>127723107</v>
       </c>
       <c r="B39" t="n">
-        <v>8450</v>
+        <v>79029</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>443488</v>
+        <v>443493</v>
       </c>
       <c r="R39" t="n">
-        <v>6766671</v>
+        <v>6766717</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4498,50 +4498,45 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127722928</v>
+        <v>127723109</v>
       </c>
       <c r="B40" t="n">
-        <v>8450</v>
+        <v>79029</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>443559</v>
+        <v>443482</v>
       </c>
       <c r="R40" t="n">
-        <v>6766616</v>
+        <v>6766716</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4600,45 +4595,50 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127722921</v>
+        <v>127722896</v>
       </c>
       <c r="B41" t="n">
-        <v>97347</v>
+        <v>57669</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>221945</v>
+        <v>100049</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>443330</v>
+        <v>443537</v>
       </c>
       <c r="R41" t="n">
-        <v>6766662</v>
+        <v>6766699</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4697,32 +4697,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>127723064</v>
+        <v>127722876</v>
       </c>
       <c r="B42" t="n">
-        <v>91513</v>
+        <v>91372</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1503</v>
+        <v>5442</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4732,10 +4732,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>443329</v>
+        <v>443366</v>
       </c>
       <c r="R42" t="n">
-        <v>6766670</v>
+        <v>6766661</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4794,32 +4794,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127723091</v>
+        <v>127723064</v>
       </c>
       <c r="B43" t="n">
-        <v>79029</v>
+        <v>91513</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>1503</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4829,10 +4829,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>443587</v>
+        <v>443329</v>
       </c>
       <c r="R43" t="n">
-        <v>6766651</v>
+        <v>6766670</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4891,7 +4891,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>127723159</v>
+        <v>127723189</v>
       </c>
       <c r="B44" t="n">
         <v>79029</v>
@@ -4926,10 +4926,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>443314</v>
+        <v>443446</v>
       </c>
       <c r="R44" t="n">
-        <v>6766811</v>
+        <v>6766727</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4962,6 +4962,11 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Med grov gran i bäckmiljö</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -4988,10 +4993,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>127722876</v>
+        <v>127723121</v>
       </c>
       <c r="B45" t="n">
-        <v>91372</v>
+        <v>79029</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4999,21 +5004,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5023,10 +5028,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>443366</v>
+        <v>443558</v>
       </c>
       <c r="R45" t="n">
-        <v>6766661</v>
+        <v>6766620</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5085,7 +5090,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>127723189</v>
+        <v>127723091</v>
       </c>
       <c r="B46" t="n">
         <v>79029</v>
@@ -5120,10 +5125,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>443446</v>
+        <v>443587</v>
       </c>
       <c r="R46" t="n">
-        <v>6766727</v>
+        <v>6766651</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5156,11 +5161,6 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-08-21</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Med grov gran i bäckmiljö</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5187,7 +5187,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>127723121</v>
+        <v>127723159</v>
       </c>
       <c r="B47" t="n">
         <v>79029</v>
@@ -5222,10 +5222,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>443558</v>
+        <v>443314</v>
       </c>
       <c r="R47" t="n">
-        <v>6766620</v>
+        <v>6766811</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5284,7 +5284,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>127723180</v>
+        <v>127723110</v>
       </c>
       <c r="B48" t="n">
         <v>79029</v>
@@ -5319,10 +5319,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>443425</v>
+        <v>443479</v>
       </c>
       <c r="R48" t="n">
-        <v>6766665</v>
+        <v>6766703</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5381,7 +5381,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>127723102</v>
+        <v>127723180</v>
       </c>
       <c r="B49" t="n">
         <v>79029</v>
@@ -5416,10 +5416,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>443556</v>
+        <v>443425</v>
       </c>
       <c r="R49" t="n">
-        <v>6766717</v>
+        <v>6766665</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5478,7 +5478,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>127723185</v>
+        <v>127723102</v>
       </c>
       <c r="B50" t="n">
         <v>79029</v>
@@ -5513,10 +5513,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>443452</v>
+        <v>443556</v>
       </c>
       <c r="R50" t="n">
-        <v>6766711</v>
+        <v>6766717</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5575,7 +5575,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>127723110</v>
+        <v>127723185</v>
       </c>
       <c r="B51" t="n">
         <v>79029</v>
@@ -5610,10 +5610,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>443479</v>
+        <v>443452</v>
       </c>
       <c r="R51" t="n">
-        <v>6766703</v>
+        <v>6766711</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5672,38 +5672,38 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>127722868</v>
+        <v>127722957</v>
       </c>
       <c r="B52" t="n">
-        <v>57832</v>
+        <v>8450</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>103021</v>
+        <v>106545</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="M52" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P52" t="inlineStr">
@@ -5712,10 +5712,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>443305</v>
+        <v>443457</v>
       </c>
       <c r="R52" t="n">
-        <v>6766767</v>
+        <v>6766726</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5774,38 +5774,38 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>127722957</v>
+        <v>127722868</v>
       </c>
       <c r="B53" t="n">
-        <v>8450</v>
+        <v>57832</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>106545</v>
+        <v>103021</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="M53" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
@@ -5814,10 +5814,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>443457</v>
+        <v>443305</v>
       </c>
       <c r="R53" t="n">
-        <v>6766726</v>
+        <v>6766767</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5876,7 +5876,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>127723138</v>
+        <v>127723184</v>
       </c>
       <c r="B54" t="n">
         <v>79029</v>
@@ -5911,10 +5911,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>443391</v>
+        <v>443446</v>
       </c>
       <c r="R54" t="n">
-        <v>6766625</v>
+        <v>6766702</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5973,7 +5973,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>127723184</v>
+        <v>127723138</v>
       </c>
       <c r="B55" t="n">
         <v>79029</v>
@@ -6008,10 +6008,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>443446</v>
+        <v>443391</v>
       </c>
       <c r="R55" t="n">
-        <v>6766702</v>
+        <v>6766625</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6070,7 +6070,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>127722943</v>
+        <v>127722956</v>
       </c>
       <c r="B56" t="n">
         <v>8450</v>
@@ -6110,10 +6110,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>443527</v>
+        <v>443454</v>
       </c>
       <c r="R56" t="n">
-        <v>6766711</v>
+        <v>6766718</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6172,7 +6172,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>127722956</v>
+        <v>127722943</v>
       </c>
       <c r="B57" t="n">
         <v>8450</v>
@@ -6212,10 +6212,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>443454</v>
+        <v>443527</v>
       </c>
       <c r="R57" t="n">
-        <v>6766718</v>
+        <v>6766711</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6274,10 +6274,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>127722841</v>
+        <v>127723175</v>
       </c>
       <c r="B58" t="n">
-        <v>79061</v>
+        <v>79029</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6285,21 +6285,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6309,10 +6309,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>443568</v>
+        <v>443387</v>
       </c>
       <c r="R58" t="n">
-        <v>6766695</v>
+        <v>6766658</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6371,7 +6371,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>127723167</v>
+        <v>127723134</v>
       </c>
       <c r="B59" t="n">
         <v>79029</v>
@@ -6406,10 +6406,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>443316</v>
+        <v>443465</v>
       </c>
       <c r="R59" t="n">
-        <v>6766701</v>
+        <v>6766607</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6468,7 +6468,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>127723153</v>
+        <v>127723106</v>
       </c>
       <c r="B60" t="n">
         <v>79029</v>
@@ -6503,10 +6503,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>443436</v>
+        <v>443516</v>
       </c>
       <c r="R60" t="n">
-        <v>6766648</v>
+        <v>6766720</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6565,7 +6565,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>127723119</v>
+        <v>127723188</v>
       </c>
       <c r="B61" t="n">
         <v>79029</v>
@@ -6600,10 +6600,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>443535</v>
+        <v>443454</v>
       </c>
       <c r="R61" t="n">
-        <v>6766639</v>
+        <v>6766724</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6662,10 +6662,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>127723106</v>
+        <v>127722841</v>
       </c>
       <c r="B62" t="n">
-        <v>79029</v>
+        <v>79061</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6673,21 +6673,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6697,10 +6697,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>443516</v>
+        <v>443568</v>
       </c>
       <c r="R62" t="n">
-        <v>6766720</v>
+        <v>6766695</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6759,7 +6759,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>127723188</v>
+        <v>127723167</v>
       </c>
       <c r="B63" t="n">
         <v>79029</v>
@@ -6794,10 +6794,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>443454</v>
+        <v>443316</v>
       </c>
       <c r="R63" t="n">
-        <v>6766724</v>
+        <v>6766701</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6856,7 +6856,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>127723175</v>
+        <v>127723153</v>
       </c>
       <c r="B64" t="n">
         <v>79029</v>
@@ -6891,10 +6891,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>443387</v>
+        <v>443436</v>
       </c>
       <c r="R64" t="n">
-        <v>6766658</v>
+        <v>6766648</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -6953,7 +6953,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>127723134</v>
+        <v>127723119</v>
       </c>
       <c r="B65" t="n">
         <v>79029</v>
@@ -6988,10 +6988,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>443465</v>
+        <v>443535</v>
       </c>
       <c r="R65" t="n">
-        <v>6766607</v>
+        <v>6766639</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7050,32 +7050,32 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>127723065</v>
+        <v>127722847</v>
       </c>
       <c r="B66" t="n">
-        <v>91513</v>
+        <v>79061</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>1503</v>
+        <v>185</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7085,10 +7085,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>443425</v>
+        <v>443320</v>
       </c>
       <c r="R66" t="n">
-        <v>6766668</v>
+        <v>6766703</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7147,32 +7147,32 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>127722847</v>
+        <v>127723065</v>
       </c>
       <c r="B67" t="n">
-        <v>79061</v>
+        <v>91513</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>185</v>
+        <v>1503</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7182,10 +7182,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>443320</v>
+        <v>443425</v>
       </c>
       <c r="R67" t="n">
-        <v>6766703</v>
+        <v>6766668</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7244,45 +7244,50 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>127729137</v>
+        <v>127722941</v>
       </c>
       <c r="B68" t="n">
-        <v>79029</v>
+        <v>8450</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Oxeråsen S. om, Dlr</t>
+          <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>443391</v>
+        <v>443557</v>
       </c>
       <c r="R68" t="n">
-        <v>6766598</v>
+        <v>6766635</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7312,47 +7317,36 @@
           <t>2025-08-21</t>
         </is>
       </c>
-      <c r="Z68" t="inlineStr">
-        <is>
-          <t>14:00</t>
-        </is>
-      </c>
       <c r="AA68" t="inlineStr">
         <is>
           <t>2025-08-21</t>
         </is>
       </c>
-      <c r="AB68" t="inlineStr">
-        <is>
-          <t>14:00</t>
-        </is>
-      </c>
       <c r="AD68" t="b">
         <v>0</v>
       </c>
       <c r="AE68" t="b">
         <v>0</v>
       </c>
-      <c r="AF68" t="inlineStr"/>
       <c r="AG68" t="b">
         <v>0</v>
       </c>
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>127723177</v>
+        <v>127723158</v>
       </c>
       <c r="B69" t="n">
         <v>79029</v>
@@ -7387,10 +7381,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>443397</v>
+        <v>443312</v>
       </c>
       <c r="R69" t="n">
-        <v>6766673</v>
+        <v>6766818</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7449,7 +7443,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>127723158</v>
+        <v>127723150</v>
       </c>
       <c r="B70" t="n">
         <v>79029</v>
@@ -7484,10 +7478,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>443312</v>
+        <v>443415</v>
       </c>
       <c r="R70" t="n">
-        <v>6766818</v>
+        <v>6766603</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7546,7 +7540,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>127723150</v>
+        <v>127729137</v>
       </c>
       <c r="B71" t="n">
         <v>79029</v>
@@ -7577,14 +7571,14 @@
       <c r="I71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Oxeråsen, Dlr</t>
+          <t>Oxeråsen S. om, Dlr</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>443415</v>
+        <v>443391</v>
       </c>
       <c r="R71" t="n">
-        <v>6766603</v>
+        <v>6766598</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7614,79 +7608,85 @@
           <t>2025-08-21</t>
         </is>
       </c>
+      <c r="Z71" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
       <c r="AA71" t="inlineStr">
         <is>
           <t>2025-08-21</t>
         </is>
       </c>
+      <c r="AB71" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
       <c r="AD71" t="b">
         <v>0</v>
       </c>
       <c r="AE71" t="b">
         <v>0</v>
       </c>
+      <c r="AF71" t="inlineStr"/>
       <c r="AG71" t="b">
         <v>0</v>
       </c>
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>127722941</v>
+        <v>127723177</v>
       </c>
       <c r="B72" t="n">
-        <v>8450</v>
+        <v>79029</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
-      <c r="M72" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P72" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>443557</v>
+        <v>443397</v>
       </c>
       <c r="R72" t="n">
-        <v>6766635</v>
+        <v>6766673</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7842,7 +7842,7 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>127723133</v>
+        <v>127723090</v>
       </c>
       <c r="B74" t="n">
         <v>79029</v>
@@ -7877,10 +7877,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>443504</v>
+        <v>443593</v>
       </c>
       <c r="R74" t="n">
-        <v>6766593</v>
+        <v>6766653</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -7939,7 +7939,7 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>127723173</v>
+        <v>127723108</v>
       </c>
       <c r="B75" t="n">
         <v>79029</v>
@@ -7974,10 +7974,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>443365</v>
+        <v>443483</v>
       </c>
       <c r="R75" t="n">
-        <v>6766656</v>
+        <v>6766725</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8036,7 +8036,7 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>127723108</v>
+        <v>127723133</v>
       </c>
       <c r="B76" t="n">
         <v>79029</v>
@@ -8071,10 +8071,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>443483</v>
+        <v>443504</v>
       </c>
       <c r="R76" t="n">
-        <v>6766725</v>
+        <v>6766593</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8133,10 +8133,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>127729092</v>
+        <v>127723173</v>
       </c>
       <c r="B77" t="n">
-        <v>78787</v>
+        <v>79029</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8144,34 +8144,34 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Oxeråsen S. om, Dlr</t>
+          <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>443381</v>
+        <v>443365</v>
       </c>
       <c r="R77" t="n">
-        <v>6766668</v>
+        <v>6766656</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8201,50 +8201,39 @@
           <t>2025-08-21</t>
         </is>
       </c>
-      <c r="Z77" t="inlineStr">
-        <is>
-          <t>13:51</t>
-        </is>
-      </c>
       <c r="AA77" t="inlineStr">
         <is>
           <t>2025-08-21</t>
         </is>
       </c>
-      <c r="AB77" t="inlineStr">
-        <is>
-          <t>13:51</t>
-        </is>
-      </c>
       <c r="AD77" t="b">
         <v>0</v>
       </c>
       <c r="AE77" t="b">
         <v>0</v>
       </c>
-      <c r="AF77" t="inlineStr"/>
       <c r="AG77" t="b">
         <v>0</v>
       </c>
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>127723090</v>
+        <v>127729092</v>
       </c>
       <c r="B78" t="n">
-        <v>79029</v>
+        <v>78787</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8252,34 +8241,34 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Oxeråsen, Dlr</t>
+          <t>Oxeråsen S. om, Dlr</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>443593</v>
+        <v>443381</v>
       </c>
       <c r="R78" t="n">
-        <v>6766653</v>
+        <v>6766668</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8309,36 +8298,47 @@
           <t>2025-08-21</t>
         </is>
       </c>
+      <c r="Z78" t="inlineStr">
+        <is>
+          <t>13:51</t>
+        </is>
+      </c>
       <c r="AA78" t="inlineStr">
         <is>
           <t>2025-08-21</t>
         </is>
       </c>
+      <c r="AB78" t="inlineStr">
+        <is>
+          <t>13:51</t>
+        </is>
+      </c>
       <c r="AD78" t="b">
         <v>0</v>
       </c>
       <c r="AE78" t="b">
         <v>0</v>
       </c>
+      <c r="AF78" t="inlineStr"/>
       <c r="AG78" t="b">
         <v>0</v>
       </c>
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>127723156</v>
+        <v>127723104</v>
       </c>
       <c r="B79" t="n">
         <v>79029</v>
@@ -8373,10 +8373,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>443346</v>
+        <v>443536</v>
       </c>
       <c r="R79" t="n">
-        <v>6766766</v>
+        <v>6766704</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8532,10 +8532,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>127723104</v>
+        <v>127723571</v>
       </c>
       <c r="B81" t="n">
-        <v>79029</v>
+        <v>78696</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8543,21 +8543,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8567,10 +8567,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>443536</v>
+        <v>443426</v>
       </c>
       <c r="R81" t="n">
-        <v>6766704</v>
+        <v>6766668</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8629,10 +8629,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>127723571</v>
+        <v>127723156</v>
       </c>
       <c r="B82" t="n">
-        <v>78696</v>
+        <v>79029</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8640,21 +8640,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8664,10 +8664,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>443426</v>
+        <v>443346</v>
       </c>
       <c r="R82" t="n">
-        <v>6766668</v>
+        <v>6766766</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8823,7 +8823,7 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>127723116</v>
+        <v>127723178</v>
       </c>
       <c r="B84" t="n">
         <v>79029</v>
@@ -8858,10 +8858,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>443509</v>
+        <v>443402</v>
       </c>
       <c r="R84" t="n">
-        <v>6766633</v>
+        <v>6766682</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -8920,7 +8920,7 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>127723092</v>
+        <v>127723116</v>
       </c>
       <c r="B85" t="n">
         <v>79029</v>
@@ -8955,10 +8955,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>443572</v>
+        <v>443509</v>
       </c>
       <c r="R85" t="n">
-        <v>6766650</v>
+        <v>6766633</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9017,7 +9017,7 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>127723178</v>
+        <v>127723092</v>
       </c>
       <c r="B86" t="n">
         <v>79029</v>
@@ -9052,10 +9052,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>443402</v>
+        <v>443572</v>
       </c>
       <c r="R86" t="n">
-        <v>6766682</v>
+        <v>6766650</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9522,10 +9522,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>127723569</v>
+        <v>127723103</v>
       </c>
       <c r="B91" t="n">
-        <v>78696</v>
+        <v>79029</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9533,21 +9533,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -9557,10 +9557,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>443332</v>
+        <v>443541</v>
       </c>
       <c r="R91" t="n">
-        <v>6766677</v>
+        <v>6766696</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9619,7 +9619,7 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>127723103</v>
+        <v>127723174</v>
       </c>
       <c r="B92" t="n">
         <v>79029</v>
@@ -9654,10 +9654,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>443541</v>
+        <v>443378</v>
       </c>
       <c r="R92" t="n">
-        <v>6766696</v>
+        <v>6766657</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9716,10 +9716,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>127723105</v>
+        <v>127723041</v>
       </c>
       <c r="B93" t="n">
-        <v>79029</v>
+        <v>78788</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9727,21 +9727,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -9751,10 +9751,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>443525</v>
+        <v>443450</v>
       </c>
       <c r="R93" t="n">
-        <v>6766717</v>
+        <v>6766735</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -9813,10 +9813,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>127723161</v>
+        <v>127723569</v>
       </c>
       <c r="B94" t="n">
-        <v>79029</v>
+        <v>78696</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -9824,21 +9824,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -9848,10 +9848,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>443305</v>
+        <v>443332</v>
       </c>
       <c r="R94" t="n">
-        <v>6766767</v>
+        <v>6766677</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -9910,7 +9910,7 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>127723186</v>
+        <v>127723105</v>
       </c>
       <c r="B95" t="n">
         <v>79029</v>
@@ -9945,10 +9945,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>443454</v>
+        <v>443525</v>
       </c>
       <c r="R95" t="n">
-        <v>6766738</v>
+        <v>6766717</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10007,7 +10007,7 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>127723114</v>
+        <v>127723161</v>
       </c>
       <c r="B96" t="n">
         <v>79029</v>
@@ -10042,10 +10042,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>443487</v>
+        <v>443305</v>
       </c>
       <c r="R96" t="n">
-        <v>6766651</v>
+        <v>6766767</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10104,7 +10104,7 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>127723097</v>
+        <v>127723186</v>
       </c>
       <c r="B97" t="n">
         <v>79029</v>
@@ -10139,10 +10139,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>443561</v>
+        <v>443454</v>
       </c>
       <c r="R97" t="n">
-        <v>6766678</v>
+        <v>6766738</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10201,7 +10201,7 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>127723174</v>
+        <v>127723114</v>
       </c>
       <c r="B98" t="n">
         <v>79029</v>
@@ -10236,10 +10236,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>443378</v>
+        <v>443487</v>
       </c>
       <c r="R98" t="n">
-        <v>6766657</v>
+        <v>6766651</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10298,10 +10298,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>127723041</v>
+        <v>127723097</v>
       </c>
       <c r="B99" t="n">
-        <v>78788</v>
+        <v>79029</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10309,21 +10309,21 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -10333,10 +10333,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>443450</v>
+        <v>443561</v>
       </c>
       <c r="R99" t="n">
-        <v>6766735</v>
+        <v>6766678</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10492,7 +10492,7 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>127723183</v>
+        <v>127723170</v>
       </c>
       <c r="B101" t="n">
         <v>79029</v>
@@ -10527,10 +10527,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>443441</v>
+        <v>443333</v>
       </c>
       <c r="R101" t="n">
-        <v>6766686</v>
+        <v>6766676</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10686,7 +10686,7 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>127723182</v>
+        <v>127723139</v>
       </c>
       <c r="B103" t="n">
         <v>79029</v>
@@ -10721,10 +10721,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>443444</v>
+        <v>443381</v>
       </c>
       <c r="R103" t="n">
-        <v>6766677</v>
+        <v>6766623</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -10783,7 +10783,7 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>127723139</v>
+        <v>127723096</v>
       </c>
       <c r="B104" t="n">
         <v>79029</v>
@@ -10818,10 +10818,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>443381</v>
+        <v>443554</v>
       </c>
       <c r="R104" t="n">
-        <v>6766623</v>
+        <v>6766650</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -10880,7 +10880,7 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>127723170</v>
+        <v>127723183</v>
       </c>
       <c r="B105" t="n">
         <v>79029</v>
@@ -10915,10 +10915,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>443333</v>
+        <v>443441</v>
       </c>
       <c r="R105" t="n">
-        <v>6766676</v>
+        <v>6766686</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -10977,7 +10977,7 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>127723098</v>
+        <v>127723182</v>
       </c>
       <c r="B106" t="n">
         <v>79029</v>
@@ -11012,10 +11012,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>443562</v>
+        <v>443444</v>
       </c>
       <c r="R106" t="n">
-        <v>6766684</v>
+        <v>6766677</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11074,10 +11074,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>127723616</v>
+        <v>127723098</v>
       </c>
       <c r="B107" t="n">
-        <v>57672</v>
+        <v>79029</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11085,39 +11085,34 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
-      <c r="M107" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
       <c r="P107" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>443475</v>
+        <v>443562</v>
       </c>
       <c r="R107" t="n">
-        <v>6766610</v>
+        <v>6766684</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11176,45 +11171,50 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>127723038</v>
+        <v>127722929</v>
       </c>
       <c r="B108" t="n">
-        <v>78788</v>
+        <v>8450</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>228912</v>
+        <v>106545</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
+      <c r="M108" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P108" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>443328</v>
+        <v>443327</v>
       </c>
       <c r="R108" t="n">
-        <v>6766721</v>
+        <v>6766698</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11273,10 +11273,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>127723096</v>
+        <v>127723038</v>
       </c>
       <c r="B109" t="n">
-        <v>79029</v>
+        <v>78788</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11284,21 +11284,21 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -11308,10 +11308,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>443554</v>
+        <v>443328</v>
       </c>
       <c r="R109" t="n">
-        <v>6766650</v>
+        <v>6766721</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11370,38 +11370,38 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>127722929</v>
+        <v>127723616</v>
       </c>
       <c r="B110" t="n">
-        <v>8450</v>
+        <v>57672</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>106545</v>
+        <v>100109</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
       <c r="M110" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>gammalt bo</t>
         </is>
       </c>
       <c r="P110" t="inlineStr">
@@ -11410,10 +11410,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>443327</v>
+        <v>443475</v>
       </c>
       <c r="R110" t="n">
-        <v>6766698</v>
+        <v>6766610</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11666,10 +11666,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>127723172</v>
+        <v>127722904</v>
       </c>
       <c r="B113" t="n">
-        <v>79029</v>
+        <v>57672</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -11677,21 +11677,21 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -11701,10 +11701,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>443356</v>
+        <v>443419</v>
       </c>
       <c r="R113" t="n">
-        <v>6766650</v>
+        <v>6766676</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -11737,6 +11737,11 @@
       <c r="AA113" t="inlineStr">
         <is>
           <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AC113" t="inlineStr">
+        <is>
+          <t>Äldre ringhack (tall)</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -11763,7 +11768,7 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>127723136</v>
+        <v>127723172</v>
       </c>
       <c r="B114" t="n">
         <v>79029</v>
@@ -11798,10 +11803,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>443438</v>
+        <v>443356</v>
       </c>
       <c r="R114" t="n">
-        <v>6766628</v>
+        <v>6766650</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -11860,7 +11865,7 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>127723160</v>
+        <v>127723136</v>
       </c>
       <c r="B115" t="n">
         <v>79029</v>
@@ -11895,10 +11900,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>443309</v>
+        <v>443438</v>
       </c>
       <c r="R115" t="n">
-        <v>6766785</v>
+        <v>6766628</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -11957,10 +11962,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>127722904</v>
+        <v>127723160</v>
       </c>
       <c r="B116" t="n">
-        <v>57672</v>
+        <v>79029</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -11968,21 +11973,21 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -11992,10 +11997,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>443419</v>
+        <v>443309</v>
       </c>
       <c r="R116" t="n">
-        <v>6766676</v>
+        <v>6766785</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12028,11 +12033,6 @@
       <c r="AA116" t="inlineStr">
         <is>
           <t>2025-08-21</t>
-        </is>
-      </c>
-      <c r="AC116" t="inlineStr">
-        <is>
-          <t>Äldre ringhack (tall)</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -12167,7 +12167,7 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>127723163</v>
+        <v>127723176</v>
       </c>
       <c r="B118" t="n">
         <v>79029</v>
@@ -12202,10 +12202,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>443332</v>
+        <v>443407</v>
       </c>
       <c r="R118" t="n">
-        <v>6766744</v>
+        <v>6766653</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12264,7 +12264,7 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>127723176</v>
+        <v>127723135</v>
       </c>
       <c r="B119" t="n">
         <v>79029</v>
@@ -12299,10 +12299,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>443407</v>
+        <v>443454</v>
       </c>
       <c r="R119" t="n">
-        <v>6766653</v>
+        <v>6766614</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -12361,7 +12361,7 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>127723135</v>
+        <v>127723113</v>
       </c>
       <c r="B120" t="n">
         <v>79029</v>
@@ -12396,10 +12396,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>443454</v>
+        <v>443487</v>
       </c>
       <c r="R120" t="n">
-        <v>6766614</v>
+        <v>6766675</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -12458,10 +12458,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>127723113</v>
+        <v>127722903</v>
       </c>
       <c r="B121" t="n">
-        <v>79029</v>
+        <v>57672</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -12469,21 +12469,21 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -12493,10 +12493,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>443487</v>
+        <v>443382</v>
       </c>
       <c r="R121" t="n">
-        <v>6766675</v>
+        <v>6766657</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -12529,6 +12529,11 @@
       <c r="AA121" t="inlineStr">
         <is>
           <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AC121" t="inlineStr">
+        <is>
+          <t>Äldre ringhack (tall)</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -12555,45 +12560,50 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>127722903</v>
+        <v>127722948</v>
       </c>
       <c r="B122" t="n">
-        <v>57672</v>
+        <v>8450</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>100109</v>
+        <v>106545</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
+      <c r="M122" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P122" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>443382</v>
+        <v>443457</v>
       </c>
       <c r="R122" t="n">
-        <v>6766657</v>
+        <v>6766613</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -12626,11 +12636,6 @@
       <c r="AA122" t="inlineStr">
         <is>
           <t>2025-08-21</t>
-        </is>
-      </c>
-      <c r="AC122" t="inlineStr">
-        <is>
-          <t>Äldre ringhack (tall)</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -12759,50 +12764,45 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>127722948</v>
+        <v>127723163</v>
       </c>
       <c r="B124" t="n">
-        <v>8450</v>
+        <v>79029</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
-      <c r="M124" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P124" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>443457</v>
+        <v>443332</v>
       </c>
       <c r="R124" t="n">
-        <v>6766613</v>
+        <v>6766744</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -12861,10 +12861,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>127723118</v>
+        <v>127723037</v>
       </c>
       <c r="B125" t="n">
-        <v>79029</v>
+        <v>78788</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -12872,21 +12872,21 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -12896,10 +12896,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>443519</v>
+        <v>443509</v>
       </c>
       <c r="R125" t="n">
-        <v>6766624</v>
+        <v>6766722</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -12958,7 +12958,7 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>127723140</v>
+        <v>127723165</v>
       </c>
       <c r="B126" t="n">
         <v>79029</v>
@@ -12993,10 +12993,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>443370</v>
+        <v>443327</v>
       </c>
       <c r="R126" t="n">
-        <v>6766624</v>
+        <v>6766717</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -13055,7 +13055,7 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>127723165</v>
+        <v>127723094</v>
       </c>
       <c r="B127" t="n">
         <v>79029</v>
@@ -13090,10 +13090,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>443327</v>
+        <v>443557</v>
       </c>
       <c r="R127" t="n">
-        <v>6766717</v>
+        <v>6766635</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -13152,7 +13152,7 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>127723094</v>
+        <v>127723118</v>
       </c>
       <c r="B128" t="n">
         <v>79029</v>
@@ -13187,10 +13187,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>443557</v>
+        <v>443519</v>
       </c>
       <c r="R128" t="n">
-        <v>6766635</v>
+        <v>6766624</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -13249,50 +13249,45 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>127722954</v>
+        <v>127723140</v>
       </c>
       <c r="B129" t="n">
-        <v>8450</v>
+        <v>79029</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
-      <c r="M129" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P129" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>443348</v>
+        <v>443370</v>
       </c>
       <c r="R129" t="n">
-        <v>6766646</v>
+        <v>6766624</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -13351,10 +13346,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>127722951</v>
+        <v>127723555</v>
       </c>
       <c r="B130" t="n">
-        <v>8450</v>
+        <v>92642</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -13362,39 +13357,34 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>106545</v>
+        <v>4364</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
-      <c r="M130" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P130" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>443377</v>
+        <v>443554</v>
       </c>
       <c r="R130" t="n">
-        <v>6766686</v>
+        <v>6766667</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -13453,10 +13443,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>127723555</v>
+        <v>127722951</v>
       </c>
       <c r="B131" t="n">
-        <v>92642</v>
+        <v>8450</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -13464,34 +13454,39 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>4364</v>
+        <v>106545</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
+      <c r="M131" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P131" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>443554</v>
+        <v>443377</v>
       </c>
       <c r="R131" t="n">
-        <v>6766667</v>
+        <v>6766686</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -13550,45 +13545,50 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>127723037</v>
+        <v>127722954</v>
       </c>
       <c r="B132" t="n">
-        <v>78788</v>
+        <v>8450</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>228912</v>
+        <v>106545</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
+      <c r="M132" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P132" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>443509</v>
+        <v>443348</v>
       </c>
       <c r="R132" t="n">
-        <v>6766722</v>
+        <v>6766646</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>

--- a/artfynd/A 35484-2025 artfynd.xlsx
+++ b/artfynd/A 35484-2025 artfynd.xlsx
@@ -2829,50 +2829,45 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127722950</v>
+        <v>127723112</v>
       </c>
       <c r="B23" t="n">
-        <v>8450</v>
+        <v>79029</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>443438</v>
+        <v>443476</v>
       </c>
       <c r="R23" t="n">
-        <v>6766650</v>
+        <v>6766681</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2931,10 +2926,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127723040</v>
+        <v>127723166</v>
       </c>
       <c r="B24" t="n">
-        <v>78788</v>
+        <v>79029</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2942,21 +2937,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2966,10 +2961,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>443377</v>
+        <v>443326</v>
       </c>
       <c r="R24" t="n">
-        <v>6766659</v>
+        <v>6766711</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3028,10 +3023,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127723039</v>
+        <v>127723181</v>
       </c>
       <c r="B25" t="n">
-        <v>78788</v>
+        <v>79029</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3039,21 +3034,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3063,10 +3058,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>443356</v>
+        <v>443436</v>
       </c>
       <c r="R25" t="n">
-        <v>6766650</v>
+        <v>6766667</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3125,10 +3120,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127723166</v>
+        <v>127723040</v>
       </c>
       <c r="B26" t="n">
-        <v>79029</v>
+        <v>78788</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3136,21 +3131,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3160,10 +3155,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>443326</v>
+        <v>443377</v>
       </c>
       <c r="R26" t="n">
-        <v>6766711</v>
+        <v>6766659</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3222,10 +3217,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127723181</v>
+        <v>127723039</v>
       </c>
       <c r="B27" t="n">
-        <v>79029</v>
+        <v>78788</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3233,21 +3228,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3257,10 +3252,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>443436</v>
+        <v>443356</v>
       </c>
       <c r="R27" t="n">
-        <v>6766667</v>
+        <v>6766650</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3416,45 +3411,50 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127723112</v>
+        <v>127722950</v>
       </c>
       <c r="B29" t="n">
-        <v>79029</v>
+        <v>8450</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>443476</v>
+        <v>443438</v>
       </c>
       <c r="R29" t="n">
-        <v>6766681</v>
+        <v>6766650</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -6274,10 +6274,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>127723175</v>
+        <v>127722841</v>
       </c>
       <c r="B58" t="n">
-        <v>79029</v>
+        <v>79061</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6285,21 +6285,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6309,10 +6309,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>443387</v>
+        <v>443568</v>
       </c>
       <c r="R58" t="n">
-        <v>6766658</v>
+        <v>6766695</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6371,7 +6371,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>127723134</v>
+        <v>127723175</v>
       </c>
       <c r="B59" t="n">
         <v>79029</v>
@@ -6406,10 +6406,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>443465</v>
+        <v>443387</v>
       </c>
       <c r="R59" t="n">
-        <v>6766607</v>
+        <v>6766658</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6468,7 +6468,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>127723106</v>
+        <v>127723134</v>
       </c>
       <c r="B60" t="n">
         <v>79029</v>
@@ -6503,10 +6503,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>443516</v>
+        <v>443465</v>
       </c>
       <c r="R60" t="n">
-        <v>6766720</v>
+        <v>6766607</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6565,7 +6565,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>127723188</v>
+        <v>127723106</v>
       </c>
       <c r="B61" t="n">
         <v>79029</v>
@@ -6600,10 +6600,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>443454</v>
+        <v>443516</v>
       </c>
       <c r="R61" t="n">
-        <v>6766724</v>
+        <v>6766720</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6662,10 +6662,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>127722841</v>
+        <v>127723188</v>
       </c>
       <c r="B62" t="n">
-        <v>79061</v>
+        <v>79029</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6673,21 +6673,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6697,10 +6697,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>443568</v>
+        <v>443454</v>
       </c>
       <c r="R62" t="n">
-        <v>6766695</v>
+        <v>6766724</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -9522,7 +9522,7 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>127723103</v>
+        <v>127723161</v>
       </c>
       <c r="B91" t="n">
         <v>79029</v>
@@ -9557,10 +9557,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>443541</v>
+        <v>443305</v>
       </c>
       <c r="R91" t="n">
-        <v>6766696</v>
+        <v>6766767</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9619,7 +9619,7 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>127723174</v>
+        <v>127723186</v>
       </c>
       <c r="B92" t="n">
         <v>79029</v>
@@ -9654,10 +9654,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>443378</v>
+        <v>443454</v>
       </c>
       <c r="R92" t="n">
-        <v>6766657</v>
+        <v>6766738</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9716,10 +9716,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>127723041</v>
+        <v>127723114</v>
       </c>
       <c r="B93" t="n">
-        <v>78788</v>
+        <v>79029</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9727,21 +9727,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -9751,10 +9751,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>443450</v>
+        <v>443487</v>
       </c>
       <c r="R93" t="n">
-        <v>6766735</v>
+        <v>6766651</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -9813,10 +9813,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>127723569</v>
+        <v>127723097</v>
       </c>
       <c r="B94" t="n">
-        <v>78696</v>
+        <v>79029</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -9824,21 +9824,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -9848,10 +9848,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>443332</v>
+        <v>443561</v>
       </c>
       <c r="R94" t="n">
-        <v>6766677</v>
+        <v>6766678</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -9910,10 +9910,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>127723105</v>
+        <v>127723041</v>
       </c>
       <c r="B95" t="n">
-        <v>79029</v>
+        <v>78788</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -9921,21 +9921,21 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -9945,10 +9945,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>443525</v>
+        <v>443450</v>
       </c>
       <c r="R95" t="n">
-        <v>6766717</v>
+        <v>6766735</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10007,10 +10007,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>127723161</v>
+        <v>127723569</v>
       </c>
       <c r="B96" t="n">
-        <v>79029</v>
+        <v>78696</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10018,21 +10018,21 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10042,10 +10042,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>443305</v>
+        <v>443332</v>
       </c>
       <c r="R96" t="n">
-        <v>6766767</v>
+        <v>6766677</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10104,7 +10104,7 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>127723186</v>
+        <v>127723103</v>
       </c>
       <c r="B97" t="n">
         <v>79029</v>
@@ -10139,10 +10139,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>443454</v>
+        <v>443541</v>
       </c>
       <c r="R97" t="n">
-        <v>6766738</v>
+        <v>6766696</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10201,7 +10201,7 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>127723114</v>
+        <v>127723174</v>
       </c>
       <c r="B98" t="n">
         <v>79029</v>
@@ -10236,10 +10236,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>443487</v>
+        <v>443378</v>
       </c>
       <c r="R98" t="n">
-        <v>6766651</v>
+        <v>6766657</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10298,7 +10298,7 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>127723097</v>
+        <v>127723105</v>
       </c>
       <c r="B99" t="n">
         <v>79029</v>
@@ -10333,10 +10333,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>443561</v>
+        <v>443525</v>
       </c>
       <c r="R99" t="n">
-        <v>6766678</v>
+        <v>6766717</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10395,10 +10395,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>127722842</v>
+        <v>127723183</v>
       </c>
       <c r="B100" t="n">
-        <v>79061</v>
+        <v>79029</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10406,21 +10406,21 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -10430,10 +10430,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>443504</v>
+        <v>443441</v>
       </c>
       <c r="R100" t="n">
-        <v>6766708</v>
+        <v>6766686</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10492,7 +10492,7 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>127723170</v>
+        <v>127723182</v>
       </c>
       <c r="B101" t="n">
         <v>79029</v>
@@ -10527,10 +10527,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>443333</v>
+        <v>443444</v>
       </c>
       <c r="R101" t="n">
-        <v>6766676</v>
+        <v>6766677</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10589,7 +10589,7 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>127723157</v>
+        <v>127723098</v>
       </c>
       <c r="B102" t="n">
         <v>79029</v>
@@ -10624,10 +10624,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>443306</v>
+        <v>443562</v>
       </c>
       <c r="R102" t="n">
-        <v>6766830</v>
+        <v>6766684</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -10686,45 +10686,50 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>127723139</v>
+        <v>127722929</v>
       </c>
       <c r="B103" t="n">
-        <v>79029</v>
+        <v>8450</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
+      <c r="M103" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P103" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>443381</v>
+        <v>443327</v>
       </c>
       <c r="R103" t="n">
-        <v>6766623</v>
+        <v>6766698</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -10783,10 +10788,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>127723096</v>
+        <v>127722842</v>
       </c>
       <c r="B104" t="n">
-        <v>79029</v>
+        <v>79061</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -10794,21 +10799,21 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -10818,10 +10823,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>443554</v>
+        <v>443504</v>
       </c>
       <c r="R104" t="n">
-        <v>6766650</v>
+        <v>6766708</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -10880,7 +10885,7 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>127723183</v>
+        <v>127723096</v>
       </c>
       <c r="B105" t="n">
         <v>79029</v>
@@ -10915,10 +10920,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>443441</v>
+        <v>443554</v>
       </c>
       <c r="R105" t="n">
-        <v>6766686</v>
+        <v>6766650</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -10977,7 +10982,7 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>127723182</v>
+        <v>127723157</v>
       </c>
       <c r="B106" t="n">
         <v>79029</v>
@@ -11012,10 +11017,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>443444</v>
+        <v>443306</v>
       </c>
       <c r="R106" t="n">
-        <v>6766677</v>
+        <v>6766830</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11074,7 +11079,7 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>127723098</v>
+        <v>127723139</v>
       </c>
       <c r="B107" t="n">
         <v>79029</v>
@@ -11109,10 +11114,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>443562</v>
+        <v>443381</v>
       </c>
       <c r="R107" t="n">
-        <v>6766684</v>
+        <v>6766623</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11171,50 +11176,45 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>127722929</v>
+        <v>127723170</v>
       </c>
       <c r="B108" t="n">
-        <v>8450</v>
+        <v>79029</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
-      <c r="M108" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P108" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>443327</v>
+        <v>443333</v>
       </c>
       <c r="R108" t="n">
-        <v>6766698</v>
+        <v>6766676</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11273,10 +11273,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>127723038</v>
+        <v>127723616</v>
       </c>
       <c r="B109" t="n">
-        <v>78788</v>
+        <v>57672</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11284,34 +11284,39 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
+      <c r="M109" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
       <c r="P109" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>443328</v>
+        <v>443475</v>
       </c>
       <c r="R109" t="n">
-        <v>6766721</v>
+        <v>6766610</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11370,10 +11375,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>127723616</v>
+        <v>127723038</v>
       </c>
       <c r="B110" t="n">
-        <v>57672</v>
+        <v>78788</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -11381,39 +11386,34 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>100109</v>
+        <v>228912</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
-      <c r="M110" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
       <c r="P110" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>443475</v>
+        <v>443328</v>
       </c>
       <c r="R110" t="n">
-        <v>6766610</v>
+        <v>6766721</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11666,10 +11666,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>127722904</v>
+        <v>127723172</v>
       </c>
       <c r="B113" t="n">
-        <v>57672</v>
+        <v>79029</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -11677,21 +11677,21 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -11701,10 +11701,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>443419</v>
+        <v>443356</v>
       </c>
       <c r="R113" t="n">
-        <v>6766676</v>
+        <v>6766650</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -11737,11 +11737,6 @@
       <c r="AA113" t="inlineStr">
         <is>
           <t>2025-08-21</t>
-        </is>
-      </c>
-      <c r="AC113" t="inlineStr">
-        <is>
-          <t>Äldre ringhack (tall)</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -11768,7 +11763,7 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>127723172</v>
+        <v>127723136</v>
       </c>
       <c r="B114" t="n">
         <v>79029</v>
@@ -11803,10 +11798,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>443356</v>
+        <v>443438</v>
       </c>
       <c r="R114" t="n">
-        <v>6766650</v>
+        <v>6766628</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -11865,7 +11860,7 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>127723136</v>
+        <v>127723160</v>
       </c>
       <c r="B115" t="n">
         <v>79029</v>
@@ -11900,10 +11895,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>443438</v>
+        <v>443309</v>
       </c>
       <c r="R115" t="n">
-        <v>6766628</v>
+        <v>6766785</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -11962,10 +11957,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>127723160</v>
+        <v>127722904</v>
       </c>
       <c r="B116" t="n">
-        <v>79029</v>
+        <v>57672</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -11973,21 +11968,21 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -11997,10 +11992,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>443309</v>
+        <v>443419</v>
       </c>
       <c r="R116" t="n">
-        <v>6766785</v>
+        <v>6766676</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12033,6 +12028,11 @@
       <c r="AA116" t="inlineStr">
         <is>
           <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AC116" t="inlineStr">
+        <is>
+          <t>Äldre ringhack (tall)</t>
         </is>
       </c>
       <c r="AD116" t="b">

--- a/artfynd/A 35484-2025 artfynd.xlsx
+++ b/artfynd/A 35484-2025 artfynd.xlsx
@@ -2829,45 +2829,50 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127723112</v>
+        <v>127722950</v>
       </c>
       <c r="B23" t="n">
-        <v>79029</v>
+        <v>8450</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>443476</v>
+        <v>443438</v>
       </c>
       <c r="R23" t="n">
-        <v>6766681</v>
+        <v>6766650</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2926,10 +2931,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127723166</v>
+        <v>127723040</v>
       </c>
       <c r="B24" t="n">
-        <v>79029</v>
+        <v>78788</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2937,21 +2942,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2961,10 +2966,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>443326</v>
+        <v>443377</v>
       </c>
       <c r="R24" t="n">
-        <v>6766711</v>
+        <v>6766659</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3023,10 +3028,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127723181</v>
+        <v>127723039</v>
       </c>
       <c r="B25" t="n">
-        <v>79029</v>
+        <v>78788</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3034,21 +3039,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3058,10 +3063,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>443436</v>
+        <v>443356</v>
       </c>
       <c r="R25" t="n">
-        <v>6766667</v>
+        <v>6766650</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3120,10 +3125,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127723040</v>
+        <v>127723166</v>
       </c>
       <c r="B26" t="n">
-        <v>78788</v>
+        <v>79029</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3131,21 +3136,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3155,10 +3160,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>443377</v>
+        <v>443326</v>
       </c>
       <c r="R26" t="n">
-        <v>6766659</v>
+        <v>6766711</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3217,10 +3222,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127723039</v>
+        <v>127723181</v>
       </c>
       <c r="B27" t="n">
-        <v>78788</v>
+        <v>79029</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3228,21 +3233,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3252,10 +3257,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>443356</v>
+        <v>443436</v>
       </c>
       <c r="R27" t="n">
-        <v>6766650</v>
+        <v>6766667</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3411,50 +3416,45 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127722950</v>
+        <v>127723112</v>
       </c>
       <c r="B29" t="n">
-        <v>8450</v>
+        <v>79029</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>443438</v>
+        <v>443476</v>
       </c>
       <c r="R29" t="n">
-        <v>6766650</v>
+        <v>6766681</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3513,10 +3513,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127722875</v>
+        <v>127723179</v>
       </c>
       <c r="B30" t="n">
-        <v>91372</v>
+        <v>79029</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3524,21 +3524,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3548,10 +3548,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>443312</v>
+        <v>443411</v>
       </c>
       <c r="R30" t="n">
-        <v>6766713</v>
+        <v>6766676</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3712,10 +3712,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127723152</v>
+        <v>127722875</v>
       </c>
       <c r="B32" t="n">
-        <v>79029</v>
+        <v>91372</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3723,21 +3723,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3747,10 +3747,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>443424</v>
+        <v>443312</v>
       </c>
       <c r="R32" t="n">
-        <v>6766627</v>
+        <v>6766713</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3809,7 +3809,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127723179</v>
+        <v>127723152</v>
       </c>
       <c r="B33" t="n">
         <v>79029</v>
@@ -3844,10 +3844,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>443411</v>
+        <v>443424</v>
       </c>
       <c r="R33" t="n">
-        <v>6766676</v>
+        <v>6766627</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4110,32 +4110,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127722921</v>
+        <v>127723115</v>
       </c>
       <c r="B36" t="n">
-        <v>97347</v>
+        <v>79029</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4145,10 +4145,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>443330</v>
+        <v>443495</v>
       </c>
       <c r="R36" t="n">
-        <v>6766662</v>
+        <v>6766641</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4207,7 +4207,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127723115</v>
+        <v>127723169</v>
       </c>
       <c r="B37" t="n">
         <v>79029</v>
@@ -4242,10 +4242,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>443495</v>
+        <v>443321</v>
       </c>
       <c r="R37" t="n">
-        <v>6766641</v>
+        <v>6766706</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4304,7 +4304,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127723169</v>
+        <v>127723107</v>
       </c>
       <c r="B38" t="n">
         <v>79029</v>
@@ -4339,10 +4339,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>443321</v>
+        <v>443493</v>
       </c>
       <c r="R38" t="n">
-        <v>6766706</v>
+        <v>6766717</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4401,7 +4401,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127723107</v>
+        <v>127723109</v>
       </c>
       <c r="B39" t="n">
         <v>79029</v>
@@ -4436,10 +4436,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>443493</v>
+        <v>443482</v>
       </c>
       <c r="R39" t="n">
-        <v>6766717</v>
+        <v>6766716</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4498,10 +4498,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127723109</v>
+        <v>127722896</v>
       </c>
       <c r="B40" t="n">
-        <v>79029</v>
+        <v>57669</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4509,34 +4509,39 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>443482</v>
+        <v>443537</v>
       </c>
       <c r="R40" t="n">
-        <v>6766716</v>
+        <v>6766699</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4595,50 +4600,45 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127722896</v>
+        <v>127722921</v>
       </c>
       <c r="B41" t="n">
-        <v>57669</v>
+        <v>97347</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100049</v>
+        <v>221945</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>443537</v>
+        <v>443330</v>
       </c>
       <c r="R41" t="n">
-        <v>6766699</v>
+        <v>6766662</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4697,32 +4697,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>127722876</v>
+        <v>127723064</v>
       </c>
       <c r="B42" t="n">
-        <v>91372</v>
+        <v>91513</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>5442</v>
+        <v>1503</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4732,10 +4732,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>443366</v>
+        <v>443329</v>
       </c>
       <c r="R42" t="n">
-        <v>6766661</v>
+        <v>6766670</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4794,32 +4794,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127723064</v>
+        <v>127723189</v>
       </c>
       <c r="B43" t="n">
-        <v>91513</v>
+        <v>79029</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1503</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4829,10 +4829,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>443329</v>
+        <v>443446</v>
       </c>
       <c r="R43" t="n">
-        <v>6766670</v>
+        <v>6766727</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4865,6 +4865,11 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Med grov gran i bäckmiljö</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -4891,7 +4896,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>127723189</v>
+        <v>127723121</v>
       </c>
       <c r="B44" t="n">
         <v>79029</v>
@@ -4926,10 +4931,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>443446</v>
+        <v>443558</v>
       </c>
       <c r="R44" t="n">
-        <v>6766727</v>
+        <v>6766620</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4962,11 +4967,6 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-08-21</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Med grov gran i bäckmiljö</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -4993,10 +4993,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>127723121</v>
+        <v>127722876</v>
       </c>
       <c r="B45" t="n">
-        <v>79029</v>
+        <v>91372</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5004,21 +5004,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5028,10 +5028,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>443558</v>
+        <v>443366</v>
       </c>
       <c r="R45" t="n">
-        <v>6766620</v>
+        <v>6766661</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5672,38 +5672,38 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>127722957</v>
+        <v>127722868</v>
       </c>
       <c r="B52" t="n">
-        <v>8450</v>
+        <v>57832</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>106545</v>
+        <v>103021</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="M52" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="P52" t="inlineStr">
@@ -5712,10 +5712,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>443457</v>
+        <v>443305</v>
       </c>
       <c r="R52" t="n">
-        <v>6766726</v>
+        <v>6766767</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5774,38 +5774,38 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>127722868</v>
+        <v>127722957</v>
       </c>
       <c r="B53" t="n">
-        <v>57832</v>
+        <v>8450</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>103021</v>
+        <v>106545</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="M53" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
@@ -5814,10 +5814,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>443305</v>
+        <v>443457</v>
       </c>
       <c r="R53" t="n">
-        <v>6766767</v>
+        <v>6766726</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -7050,45 +7050,50 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>127722847</v>
+        <v>127722941</v>
       </c>
       <c r="B66" t="n">
-        <v>79061</v>
+        <v>8450</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>185</v>
+        <v>106545</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P66" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>443320</v>
+        <v>443557</v>
       </c>
       <c r="R66" t="n">
-        <v>6766703</v>
+        <v>6766635</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7147,32 +7152,32 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>127723065</v>
+        <v>127722847</v>
       </c>
       <c r="B67" t="n">
-        <v>91513</v>
+        <v>79061</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>1503</v>
+        <v>185</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7182,10 +7187,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>443425</v>
+        <v>443320</v>
       </c>
       <c r="R67" t="n">
-        <v>6766668</v>
+        <v>6766703</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7244,50 +7249,45 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>127722941</v>
+        <v>127723065</v>
       </c>
       <c r="B68" t="n">
-        <v>8450</v>
+        <v>91513</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>106545</v>
+        <v>1503</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
-      <c r="M68" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P68" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>443557</v>
+        <v>443425</v>
       </c>
       <c r="R68" t="n">
-        <v>6766635</v>
+        <v>6766668</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -9522,7 +9522,7 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>127723161</v>
+        <v>127723103</v>
       </c>
       <c r="B91" t="n">
         <v>79029</v>
@@ -9557,10 +9557,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>443305</v>
+        <v>443541</v>
       </c>
       <c r="R91" t="n">
-        <v>6766767</v>
+        <v>6766696</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9619,7 +9619,7 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>127723186</v>
+        <v>127723174</v>
       </c>
       <c r="B92" t="n">
         <v>79029</v>
@@ -9654,10 +9654,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>443454</v>
+        <v>443378</v>
       </c>
       <c r="R92" t="n">
-        <v>6766738</v>
+        <v>6766657</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9716,10 +9716,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>127723114</v>
+        <v>127723041</v>
       </c>
       <c r="B93" t="n">
-        <v>79029</v>
+        <v>78788</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9727,21 +9727,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -9751,10 +9751,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>443487</v>
+        <v>443450</v>
       </c>
       <c r="R93" t="n">
-        <v>6766651</v>
+        <v>6766735</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -9813,10 +9813,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>127723097</v>
+        <v>127723569</v>
       </c>
       <c r="B94" t="n">
-        <v>79029</v>
+        <v>78696</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -9824,21 +9824,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -9848,10 +9848,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>443561</v>
+        <v>443332</v>
       </c>
       <c r="R94" t="n">
-        <v>6766678</v>
+        <v>6766677</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -9910,10 +9910,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>127723041</v>
+        <v>127723105</v>
       </c>
       <c r="B95" t="n">
-        <v>78788</v>
+        <v>79029</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -9921,21 +9921,21 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -9945,10 +9945,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>443450</v>
+        <v>443525</v>
       </c>
       <c r="R95" t="n">
-        <v>6766735</v>
+        <v>6766717</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10007,10 +10007,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>127723569</v>
+        <v>127723161</v>
       </c>
       <c r="B96" t="n">
-        <v>78696</v>
+        <v>79029</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10018,21 +10018,21 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10042,10 +10042,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>443332</v>
+        <v>443305</v>
       </c>
       <c r="R96" t="n">
-        <v>6766677</v>
+        <v>6766767</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10104,7 +10104,7 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>127723103</v>
+        <v>127723186</v>
       </c>
       <c r="B97" t="n">
         <v>79029</v>
@@ -10139,10 +10139,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>443541</v>
+        <v>443454</v>
       </c>
       <c r="R97" t="n">
-        <v>6766696</v>
+        <v>6766738</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10201,7 +10201,7 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>127723174</v>
+        <v>127723114</v>
       </c>
       <c r="B98" t="n">
         <v>79029</v>
@@ -10236,10 +10236,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>443378</v>
+        <v>443487</v>
       </c>
       <c r="R98" t="n">
-        <v>6766657</v>
+        <v>6766651</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10298,7 +10298,7 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>127723105</v>
+        <v>127723097</v>
       </c>
       <c r="B99" t="n">
         <v>79029</v>
@@ -10333,10 +10333,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>443525</v>
+        <v>443561</v>
       </c>
       <c r="R99" t="n">
-        <v>6766717</v>
+        <v>6766678</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -13647,7 +13647,7 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>127723162</v>
+        <v>127723111</v>
       </c>
       <c r="B133" t="n">
         <v>79029</v>
@@ -13682,10 +13682,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>443312</v>
+        <v>443474</v>
       </c>
       <c r="R133" t="n">
-        <v>6766762</v>
+        <v>6766692</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -13744,7 +13744,7 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>127723111</v>
+        <v>127723162</v>
       </c>
       <c r="B134" t="n">
         <v>79029</v>
@@ -13779,10 +13779,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>443474</v>
+        <v>443312</v>
       </c>
       <c r="R134" t="n">
-        <v>6766692</v>
+        <v>6766762</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>

--- a/artfynd/A 35484-2025 artfynd.xlsx
+++ b/artfynd/A 35484-2025 artfynd.xlsx
@@ -2829,50 +2829,45 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127722950</v>
+        <v>127723112</v>
       </c>
       <c r="B23" t="n">
-        <v>8450</v>
+        <v>79029</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>443438</v>
+        <v>443476</v>
       </c>
       <c r="R23" t="n">
-        <v>6766650</v>
+        <v>6766681</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2931,10 +2926,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127723040</v>
+        <v>127723166</v>
       </c>
       <c r="B24" t="n">
-        <v>78788</v>
+        <v>79029</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2942,21 +2937,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2966,10 +2961,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>443377</v>
+        <v>443326</v>
       </c>
       <c r="R24" t="n">
-        <v>6766659</v>
+        <v>6766711</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3028,10 +3023,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127723039</v>
+        <v>127723181</v>
       </c>
       <c r="B25" t="n">
-        <v>78788</v>
+        <v>79029</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3039,21 +3034,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3063,10 +3058,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>443356</v>
+        <v>443436</v>
       </c>
       <c r="R25" t="n">
-        <v>6766650</v>
+        <v>6766667</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3125,10 +3120,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127723166</v>
+        <v>127723040</v>
       </c>
       <c r="B26" t="n">
-        <v>79029</v>
+        <v>78788</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3136,21 +3131,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3160,10 +3155,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>443326</v>
+        <v>443377</v>
       </c>
       <c r="R26" t="n">
-        <v>6766711</v>
+        <v>6766659</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3222,10 +3217,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127723181</v>
+        <v>127723039</v>
       </c>
       <c r="B27" t="n">
-        <v>79029</v>
+        <v>78788</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3233,21 +3228,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3257,10 +3252,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>443436</v>
+        <v>443356</v>
       </c>
       <c r="R27" t="n">
-        <v>6766667</v>
+        <v>6766650</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3416,45 +3411,50 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127723112</v>
+        <v>127722950</v>
       </c>
       <c r="B29" t="n">
-        <v>79029</v>
+        <v>8450</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>443476</v>
+        <v>443438</v>
       </c>
       <c r="R29" t="n">
-        <v>6766681</v>
+        <v>6766650</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3513,10 +3513,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127723179</v>
+        <v>127722875</v>
       </c>
       <c r="B30" t="n">
-        <v>79029</v>
+        <v>91372</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3524,21 +3524,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3548,10 +3548,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>443411</v>
+        <v>443312</v>
       </c>
       <c r="R30" t="n">
-        <v>6766676</v>
+        <v>6766713</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3712,10 +3712,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127722875</v>
+        <v>127723152</v>
       </c>
       <c r="B32" t="n">
-        <v>91372</v>
+        <v>79029</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3723,21 +3723,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3747,10 +3747,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>443312</v>
+        <v>443424</v>
       </c>
       <c r="R32" t="n">
-        <v>6766713</v>
+        <v>6766627</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3809,7 +3809,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127723152</v>
+        <v>127723179</v>
       </c>
       <c r="B33" t="n">
         <v>79029</v>
@@ -3844,10 +3844,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>443424</v>
+        <v>443411</v>
       </c>
       <c r="R33" t="n">
-        <v>6766627</v>
+        <v>6766676</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4697,32 +4697,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>127723064</v>
+        <v>127722876</v>
       </c>
       <c r="B42" t="n">
-        <v>91513</v>
+        <v>91372</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1503</v>
+        <v>5442</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4732,10 +4732,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>443329</v>
+        <v>443366</v>
       </c>
       <c r="R42" t="n">
-        <v>6766670</v>
+        <v>6766661</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4794,32 +4794,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127723189</v>
+        <v>127723064</v>
       </c>
       <c r="B43" t="n">
-        <v>79029</v>
+        <v>91513</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>1503</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4829,10 +4829,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>443446</v>
+        <v>443329</v>
       </c>
       <c r="R43" t="n">
-        <v>6766727</v>
+        <v>6766670</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4865,11 +4865,6 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-08-21</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Med grov gran i bäckmiljö</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -4896,7 +4891,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>127723121</v>
+        <v>127723189</v>
       </c>
       <c r="B44" t="n">
         <v>79029</v>
@@ -4931,10 +4926,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>443558</v>
+        <v>443446</v>
       </c>
       <c r="R44" t="n">
-        <v>6766620</v>
+        <v>6766727</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4967,6 +4962,11 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Med grov gran i bäckmiljö</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -4993,10 +4993,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>127722876</v>
+        <v>127723121</v>
       </c>
       <c r="B45" t="n">
-        <v>91372</v>
+        <v>79029</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5004,21 +5004,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5028,10 +5028,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>443366</v>
+        <v>443558</v>
       </c>
       <c r="R45" t="n">
-        <v>6766661</v>
+        <v>6766620</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -6274,10 +6274,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>127722841</v>
+        <v>127723175</v>
       </c>
       <c r="B58" t="n">
-        <v>79061</v>
+        <v>79029</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6285,21 +6285,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6309,10 +6309,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>443568</v>
+        <v>443387</v>
       </c>
       <c r="R58" t="n">
-        <v>6766695</v>
+        <v>6766658</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6371,7 +6371,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>127723175</v>
+        <v>127723134</v>
       </c>
       <c r="B59" t="n">
         <v>79029</v>
@@ -6406,10 +6406,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>443387</v>
+        <v>443465</v>
       </c>
       <c r="R59" t="n">
-        <v>6766658</v>
+        <v>6766607</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6468,7 +6468,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>127723134</v>
+        <v>127723106</v>
       </c>
       <c r="B60" t="n">
         <v>79029</v>
@@ -6503,10 +6503,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>443465</v>
+        <v>443516</v>
       </c>
       <c r="R60" t="n">
-        <v>6766607</v>
+        <v>6766720</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6565,7 +6565,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>127723106</v>
+        <v>127723188</v>
       </c>
       <c r="B61" t="n">
         <v>79029</v>
@@ -6600,10 +6600,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>443516</v>
+        <v>443454</v>
       </c>
       <c r="R61" t="n">
-        <v>6766720</v>
+        <v>6766724</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6662,10 +6662,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>127723188</v>
+        <v>127722841</v>
       </c>
       <c r="B62" t="n">
-        <v>79029</v>
+        <v>79061</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6673,21 +6673,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6697,10 +6697,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>443454</v>
+        <v>443568</v>
       </c>
       <c r="R62" t="n">
-        <v>6766724</v>
+        <v>6766695</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -8726,10 +8726,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>127723570</v>
+        <v>127722888</v>
       </c>
       <c r="B83" t="n">
-        <v>78696</v>
+        <v>57669</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8737,34 +8737,39 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>353</v>
+        <v>100049</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P83" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>443319</v>
+        <v>443481</v>
       </c>
       <c r="R83" t="n">
-        <v>6766670</v>
+        <v>6766676</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -8823,10 +8828,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>127723178</v>
+        <v>127722916</v>
       </c>
       <c r="B84" t="n">
-        <v>79029</v>
+        <v>57672</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -8834,34 +8839,39 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P84" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>443402</v>
+        <v>443342</v>
       </c>
       <c r="R84" t="n">
-        <v>6766682</v>
+        <v>6766806</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -8894,6 +8904,11 @@
       <c r="AA84" t="inlineStr">
         <is>
           <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AC84" t="inlineStr">
+        <is>
+          <t>Färska ringhack (gran), 4-5 år gamla</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -8920,10 +8935,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>127723116</v>
+        <v>127723541</v>
       </c>
       <c r="B85" t="n">
-        <v>79029</v>
+        <v>57672</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -8931,34 +8946,39 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P85" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>443509</v>
+        <v>443317</v>
       </c>
       <c r="R85" t="n">
-        <v>6766633</v>
+        <v>6766816</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9017,10 +9037,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>127723092</v>
+        <v>127723570</v>
       </c>
       <c r="B86" t="n">
-        <v>79029</v>
+        <v>78696</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9028,21 +9048,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9052,10 +9072,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>443572</v>
+        <v>443319</v>
       </c>
       <c r="R86" t="n">
-        <v>6766650</v>
+        <v>6766670</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9114,7 +9134,7 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>127723171</v>
+        <v>127723178</v>
       </c>
       <c r="B87" t="n">
         <v>79029</v>
@@ -9149,10 +9169,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>443342</v>
+        <v>443402</v>
       </c>
       <c r="R87" t="n">
-        <v>6766650</v>
+        <v>6766682</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9211,10 +9231,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>127722888</v>
+        <v>127723116</v>
       </c>
       <c r="B88" t="n">
-        <v>57669</v>
+        <v>79029</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9222,39 +9242,34 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
-      <c r="M88" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P88" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>443481</v>
+        <v>443509</v>
       </c>
       <c r="R88" t="n">
-        <v>6766676</v>
+        <v>6766633</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9313,10 +9328,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>127722916</v>
+        <v>127723092</v>
       </c>
       <c r="B89" t="n">
-        <v>57672</v>
+        <v>79029</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9324,39 +9339,34 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
-      <c r="M89" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P89" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>443342</v>
+        <v>443572</v>
       </c>
       <c r="R89" t="n">
-        <v>6766806</v>
+        <v>6766650</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9389,11 +9399,6 @@
       <c r="AA89" t="inlineStr">
         <is>
           <t>2025-08-21</t>
-        </is>
-      </c>
-      <c r="AC89" t="inlineStr">
-        <is>
-          <t>Färska ringhack (gran), 4-5 år gamla</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -9420,10 +9425,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>127723541</v>
+        <v>127723171</v>
       </c>
       <c r="B90" t="n">
-        <v>57672</v>
+        <v>79029</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9431,39 +9436,34 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
-      <c r="M90" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P90" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>443317</v>
+        <v>443342</v>
       </c>
       <c r="R90" t="n">
-        <v>6766816</v>
+        <v>6766650</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10395,10 +10395,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>127723183</v>
+        <v>127722842</v>
       </c>
       <c r="B100" t="n">
-        <v>79029</v>
+        <v>79061</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10406,21 +10406,21 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -10430,10 +10430,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>443441</v>
+        <v>443504</v>
       </c>
       <c r="R100" t="n">
-        <v>6766686</v>
+        <v>6766708</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10492,7 +10492,7 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>127723182</v>
+        <v>127723170</v>
       </c>
       <c r="B101" t="n">
         <v>79029</v>
@@ -10527,10 +10527,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>443444</v>
+        <v>443333</v>
       </c>
       <c r="R101" t="n">
-        <v>6766677</v>
+        <v>6766676</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10589,7 +10589,7 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>127723098</v>
+        <v>127723157</v>
       </c>
       <c r="B102" t="n">
         <v>79029</v>
@@ -10624,10 +10624,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>443562</v>
+        <v>443306</v>
       </c>
       <c r="R102" t="n">
-        <v>6766684</v>
+        <v>6766830</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -10686,50 +10686,45 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>127722929</v>
+        <v>127723139</v>
       </c>
       <c r="B103" t="n">
-        <v>8450</v>
+        <v>79029</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
-      <c r="M103" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P103" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>443327</v>
+        <v>443381</v>
       </c>
       <c r="R103" t="n">
-        <v>6766698</v>
+        <v>6766623</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -10788,10 +10783,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>127722842</v>
+        <v>127723096</v>
       </c>
       <c r="B104" t="n">
-        <v>79061</v>
+        <v>79029</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -10799,21 +10794,21 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -10823,10 +10818,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>443504</v>
+        <v>443554</v>
       </c>
       <c r="R104" t="n">
-        <v>6766708</v>
+        <v>6766650</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -10885,7 +10880,7 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>127723096</v>
+        <v>127723183</v>
       </c>
       <c r="B105" t="n">
         <v>79029</v>
@@ -10920,10 +10915,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>443554</v>
+        <v>443441</v>
       </c>
       <c r="R105" t="n">
-        <v>6766650</v>
+        <v>6766686</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -10982,7 +10977,7 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>127723157</v>
+        <v>127723182</v>
       </c>
       <c r="B106" t="n">
         <v>79029</v>
@@ -11017,10 +11012,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>443306</v>
+        <v>443444</v>
       </c>
       <c r="R106" t="n">
-        <v>6766830</v>
+        <v>6766677</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11079,7 +11074,7 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>127723139</v>
+        <v>127723098</v>
       </c>
       <c r="B107" t="n">
         <v>79029</v>
@@ -11114,10 +11109,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>443381</v>
+        <v>443562</v>
       </c>
       <c r="R107" t="n">
-        <v>6766623</v>
+        <v>6766684</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11176,45 +11171,50 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>127723170</v>
+        <v>127722929</v>
       </c>
       <c r="B108" t="n">
-        <v>79029</v>
+        <v>8450</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
+      <c r="M108" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P108" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>443333</v>
+        <v>443327</v>
       </c>
       <c r="R108" t="n">
-        <v>6766676</v>
+        <v>6766698</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11273,10 +11273,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>127723616</v>
+        <v>127723038</v>
       </c>
       <c r="B109" t="n">
-        <v>57672</v>
+        <v>78788</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11284,39 +11284,34 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>100109</v>
+        <v>228912</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
-      <c r="M109" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
       <c r="P109" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>443475</v>
+        <v>443328</v>
       </c>
       <c r="R109" t="n">
-        <v>6766610</v>
+        <v>6766721</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11375,10 +11370,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>127723038</v>
+        <v>127723616</v>
       </c>
       <c r="B110" t="n">
-        <v>78788</v>
+        <v>57672</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -11386,34 +11381,39 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
+      <c r="M110" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
       <c r="P110" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>443328</v>
+        <v>443475</v>
       </c>
       <c r="R110" t="n">
-        <v>6766721</v>
+        <v>6766610</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11666,10 +11666,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>127723172</v>
+        <v>127722904</v>
       </c>
       <c r="B113" t="n">
-        <v>79029</v>
+        <v>57672</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -11677,21 +11677,21 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -11701,10 +11701,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>443356</v>
+        <v>443419</v>
       </c>
       <c r="R113" t="n">
-        <v>6766650</v>
+        <v>6766676</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -11737,6 +11737,11 @@
       <c r="AA113" t="inlineStr">
         <is>
           <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AC113" t="inlineStr">
+        <is>
+          <t>Äldre ringhack (tall)</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -11763,7 +11768,7 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>127723136</v>
+        <v>127723172</v>
       </c>
       <c r="B114" t="n">
         <v>79029</v>
@@ -11798,10 +11803,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>443438</v>
+        <v>443356</v>
       </c>
       <c r="R114" t="n">
-        <v>6766628</v>
+        <v>6766650</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -11860,7 +11865,7 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>127723160</v>
+        <v>127723136</v>
       </c>
       <c r="B115" t="n">
         <v>79029</v>
@@ -11895,10 +11900,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>443309</v>
+        <v>443438</v>
       </c>
       <c r="R115" t="n">
-        <v>6766785</v>
+        <v>6766628</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -11957,10 +11962,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>127722904</v>
+        <v>127723160</v>
       </c>
       <c r="B116" t="n">
-        <v>57672</v>
+        <v>79029</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -11968,21 +11973,21 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -11992,10 +11997,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>443419</v>
+        <v>443309</v>
       </c>
       <c r="R116" t="n">
-        <v>6766676</v>
+        <v>6766785</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12028,11 +12033,6 @@
       <c r="AA116" t="inlineStr">
         <is>
           <t>2025-08-21</t>
-        </is>
-      </c>
-      <c r="AC116" t="inlineStr">
-        <is>
-          <t>Äldre ringhack (tall)</t>
         </is>
       </c>
       <c r="AD116" t="b">

--- a/artfynd/A 35484-2025 artfynd.xlsx
+++ b/artfynd/A 35484-2025 artfynd.xlsx
@@ -2829,45 +2829,50 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127723112</v>
+        <v>127722950</v>
       </c>
       <c r="B23" t="n">
-        <v>79029</v>
+        <v>8450</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>443476</v>
+        <v>443438</v>
       </c>
       <c r="R23" t="n">
-        <v>6766681</v>
+        <v>6766650</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2926,10 +2931,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127723166</v>
+        <v>127723040</v>
       </c>
       <c r="B24" t="n">
-        <v>79029</v>
+        <v>78788</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2937,21 +2942,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2961,10 +2966,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>443326</v>
+        <v>443377</v>
       </c>
       <c r="R24" t="n">
-        <v>6766711</v>
+        <v>6766659</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3023,10 +3028,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127723181</v>
+        <v>127723039</v>
       </c>
       <c r="B25" t="n">
-        <v>79029</v>
+        <v>78788</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3034,21 +3039,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3058,10 +3063,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>443436</v>
+        <v>443356</v>
       </c>
       <c r="R25" t="n">
-        <v>6766667</v>
+        <v>6766650</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3120,10 +3125,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127723040</v>
+        <v>127723166</v>
       </c>
       <c r="B26" t="n">
-        <v>78788</v>
+        <v>79029</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3131,21 +3136,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3155,10 +3160,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>443377</v>
+        <v>443326</v>
       </c>
       <c r="R26" t="n">
-        <v>6766659</v>
+        <v>6766711</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3217,10 +3222,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127723039</v>
+        <v>127723181</v>
       </c>
       <c r="B27" t="n">
-        <v>78788</v>
+        <v>79029</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3228,21 +3233,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3252,10 +3257,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>443356</v>
+        <v>443436</v>
       </c>
       <c r="R27" t="n">
-        <v>6766650</v>
+        <v>6766667</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3411,50 +3416,45 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127722950</v>
+        <v>127723112</v>
       </c>
       <c r="B29" t="n">
-        <v>8450</v>
+        <v>79029</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>443438</v>
+        <v>443476</v>
       </c>
       <c r="R29" t="n">
-        <v>6766650</v>
+        <v>6766681</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3513,10 +3513,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127722875</v>
+        <v>127723179</v>
       </c>
       <c r="B30" t="n">
-        <v>91372</v>
+        <v>79029</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3524,21 +3524,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3548,10 +3548,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>443312</v>
+        <v>443411</v>
       </c>
       <c r="R30" t="n">
-        <v>6766713</v>
+        <v>6766676</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3712,10 +3712,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127723152</v>
+        <v>127722875</v>
       </c>
       <c r="B32" t="n">
-        <v>79029</v>
+        <v>91372</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3723,21 +3723,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3747,10 +3747,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>443424</v>
+        <v>443312</v>
       </c>
       <c r="R32" t="n">
-        <v>6766627</v>
+        <v>6766713</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3809,7 +3809,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127723179</v>
+        <v>127723152</v>
       </c>
       <c r="B33" t="n">
         <v>79029</v>
@@ -3844,10 +3844,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>443411</v>
+        <v>443424</v>
       </c>
       <c r="R33" t="n">
-        <v>6766676</v>
+        <v>6766627</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4697,32 +4697,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>127722876</v>
+        <v>127723064</v>
       </c>
       <c r="B42" t="n">
-        <v>91372</v>
+        <v>91513</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>5442</v>
+        <v>1503</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4732,10 +4732,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>443366</v>
+        <v>443329</v>
       </c>
       <c r="R42" t="n">
-        <v>6766661</v>
+        <v>6766670</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4794,32 +4794,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127723064</v>
+        <v>127723189</v>
       </c>
       <c r="B43" t="n">
-        <v>91513</v>
+        <v>79029</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1503</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4829,10 +4829,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>443329</v>
+        <v>443446</v>
       </c>
       <c r="R43" t="n">
-        <v>6766670</v>
+        <v>6766727</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4865,6 +4865,11 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Med grov gran i bäckmiljö</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -4891,7 +4896,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>127723189</v>
+        <v>127723121</v>
       </c>
       <c r="B44" t="n">
         <v>79029</v>
@@ -4926,10 +4931,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>443446</v>
+        <v>443558</v>
       </c>
       <c r="R44" t="n">
-        <v>6766727</v>
+        <v>6766620</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4962,11 +4967,6 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-08-21</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Med grov gran i bäckmiljö</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -4993,10 +4993,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>127723121</v>
+        <v>127722876</v>
       </c>
       <c r="B45" t="n">
-        <v>79029</v>
+        <v>91372</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5004,21 +5004,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5028,10 +5028,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>443558</v>
+        <v>443366</v>
       </c>
       <c r="R45" t="n">
-        <v>6766620</v>
+        <v>6766661</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -6274,10 +6274,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>127723175</v>
+        <v>127722841</v>
       </c>
       <c r="B58" t="n">
-        <v>79029</v>
+        <v>79061</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6285,21 +6285,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6309,10 +6309,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>443387</v>
+        <v>443568</v>
       </c>
       <c r="R58" t="n">
-        <v>6766658</v>
+        <v>6766695</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6371,7 +6371,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>127723134</v>
+        <v>127723175</v>
       </c>
       <c r="B59" t="n">
         <v>79029</v>
@@ -6406,10 +6406,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>443465</v>
+        <v>443387</v>
       </c>
       <c r="R59" t="n">
-        <v>6766607</v>
+        <v>6766658</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6468,7 +6468,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>127723106</v>
+        <v>127723134</v>
       </c>
       <c r="B60" t="n">
         <v>79029</v>
@@ -6503,10 +6503,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>443516</v>
+        <v>443465</v>
       </c>
       <c r="R60" t="n">
-        <v>6766720</v>
+        <v>6766607</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6565,7 +6565,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>127723188</v>
+        <v>127723106</v>
       </c>
       <c r="B61" t="n">
         <v>79029</v>
@@ -6600,10 +6600,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>443454</v>
+        <v>443516</v>
       </c>
       <c r="R61" t="n">
-        <v>6766724</v>
+        <v>6766720</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6662,10 +6662,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>127722841</v>
+        <v>127723188</v>
       </c>
       <c r="B62" t="n">
-        <v>79061</v>
+        <v>79029</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6673,21 +6673,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6697,10 +6697,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>443568</v>
+        <v>443454</v>
       </c>
       <c r="R62" t="n">
-        <v>6766695</v>
+        <v>6766724</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -8338,10 +8338,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>127723104</v>
+        <v>127723571</v>
       </c>
       <c r="B79" t="n">
-        <v>79029</v>
+        <v>78696</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8349,21 +8349,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8373,10 +8373,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>443536</v>
+        <v>443426</v>
       </c>
       <c r="R79" t="n">
-        <v>6766704</v>
+        <v>6766668</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8435,7 +8435,7 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>127723120</v>
+        <v>127723104</v>
       </c>
       <c r="B80" t="n">
         <v>79029</v>
@@ -8470,10 +8470,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>443548</v>
+        <v>443536</v>
       </c>
       <c r="R80" t="n">
-        <v>6766624</v>
+        <v>6766704</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8532,10 +8532,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>127723571</v>
+        <v>127723120</v>
       </c>
       <c r="B81" t="n">
-        <v>78696</v>
+        <v>79029</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8543,21 +8543,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8567,10 +8567,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>443426</v>
+        <v>443548</v>
       </c>
       <c r="R81" t="n">
-        <v>6766668</v>
+        <v>6766624</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9522,7 +9522,7 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>127723103</v>
+        <v>127723161</v>
       </c>
       <c r="B91" t="n">
         <v>79029</v>
@@ -9557,10 +9557,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>443541</v>
+        <v>443305</v>
       </c>
       <c r="R91" t="n">
-        <v>6766696</v>
+        <v>6766767</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9619,7 +9619,7 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>127723174</v>
+        <v>127723186</v>
       </c>
       <c r="B92" t="n">
         <v>79029</v>
@@ -9654,10 +9654,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>443378</v>
+        <v>443454</v>
       </c>
       <c r="R92" t="n">
-        <v>6766657</v>
+        <v>6766738</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9716,10 +9716,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>127723041</v>
+        <v>127723114</v>
       </c>
       <c r="B93" t="n">
-        <v>78788</v>
+        <v>79029</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9727,21 +9727,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -9751,10 +9751,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>443450</v>
+        <v>443487</v>
       </c>
       <c r="R93" t="n">
-        <v>6766735</v>
+        <v>6766651</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -9813,10 +9813,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>127723569</v>
+        <v>127723097</v>
       </c>
       <c r="B94" t="n">
-        <v>78696</v>
+        <v>79029</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -9824,21 +9824,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -9848,10 +9848,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>443332</v>
+        <v>443561</v>
       </c>
       <c r="R94" t="n">
-        <v>6766677</v>
+        <v>6766678</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -9910,10 +9910,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>127723105</v>
+        <v>127723041</v>
       </c>
       <c r="B95" t="n">
-        <v>79029</v>
+        <v>78788</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -9921,21 +9921,21 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -9945,10 +9945,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>443525</v>
+        <v>443450</v>
       </c>
       <c r="R95" t="n">
-        <v>6766717</v>
+        <v>6766735</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10007,10 +10007,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>127723161</v>
+        <v>127723569</v>
       </c>
       <c r="B96" t="n">
-        <v>79029</v>
+        <v>78696</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10018,21 +10018,21 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10042,10 +10042,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>443305</v>
+        <v>443332</v>
       </c>
       <c r="R96" t="n">
-        <v>6766767</v>
+        <v>6766677</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10104,7 +10104,7 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>127723186</v>
+        <v>127723103</v>
       </c>
       <c r="B97" t="n">
         <v>79029</v>
@@ -10139,10 +10139,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>443454</v>
+        <v>443541</v>
       </c>
       <c r="R97" t="n">
-        <v>6766738</v>
+        <v>6766696</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10201,7 +10201,7 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>127723114</v>
+        <v>127723174</v>
       </c>
       <c r="B98" t="n">
         <v>79029</v>
@@ -10236,10 +10236,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>443487</v>
+        <v>443378</v>
       </c>
       <c r="R98" t="n">
-        <v>6766651</v>
+        <v>6766657</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10298,7 +10298,7 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>127723097</v>
+        <v>127723105</v>
       </c>
       <c r="B99" t="n">
         <v>79029</v>
@@ -10333,10 +10333,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>443561</v>
+        <v>443525</v>
       </c>
       <c r="R99" t="n">
-        <v>6766678</v>
+        <v>6766717</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10395,10 +10395,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>127722842</v>
+        <v>127723183</v>
       </c>
       <c r="B100" t="n">
-        <v>79061</v>
+        <v>79029</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10406,21 +10406,21 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -10430,10 +10430,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>443504</v>
+        <v>443441</v>
       </c>
       <c r="R100" t="n">
-        <v>6766708</v>
+        <v>6766686</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10492,7 +10492,7 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>127723170</v>
+        <v>127723182</v>
       </c>
       <c r="B101" t="n">
         <v>79029</v>
@@ -10527,10 +10527,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>443333</v>
+        <v>443444</v>
       </c>
       <c r="R101" t="n">
-        <v>6766676</v>
+        <v>6766677</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10589,7 +10589,7 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>127723157</v>
+        <v>127723098</v>
       </c>
       <c r="B102" t="n">
         <v>79029</v>
@@ -10624,10 +10624,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>443306</v>
+        <v>443562</v>
       </c>
       <c r="R102" t="n">
-        <v>6766830</v>
+        <v>6766684</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -10686,45 +10686,50 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>127723139</v>
+        <v>127722929</v>
       </c>
       <c r="B103" t="n">
-        <v>79029</v>
+        <v>8450</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
+      <c r="M103" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P103" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>443381</v>
+        <v>443327</v>
       </c>
       <c r="R103" t="n">
-        <v>6766623</v>
+        <v>6766698</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -10783,10 +10788,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>127723096</v>
+        <v>127722842</v>
       </c>
       <c r="B104" t="n">
-        <v>79029</v>
+        <v>79061</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -10794,21 +10799,21 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -10818,10 +10823,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>443554</v>
+        <v>443504</v>
       </c>
       <c r="R104" t="n">
-        <v>6766650</v>
+        <v>6766708</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -10880,7 +10885,7 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>127723183</v>
+        <v>127723096</v>
       </c>
       <c r="B105" t="n">
         <v>79029</v>
@@ -10915,10 +10920,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>443441</v>
+        <v>443554</v>
       </c>
       <c r="R105" t="n">
-        <v>6766686</v>
+        <v>6766650</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -10977,7 +10982,7 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>127723182</v>
+        <v>127723157</v>
       </c>
       <c r="B106" t="n">
         <v>79029</v>
@@ -11012,10 +11017,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>443444</v>
+        <v>443306</v>
       </c>
       <c r="R106" t="n">
-        <v>6766677</v>
+        <v>6766830</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11074,7 +11079,7 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>127723098</v>
+        <v>127723139</v>
       </c>
       <c r="B107" t="n">
         <v>79029</v>
@@ -11109,10 +11114,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>443562</v>
+        <v>443381</v>
       </c>
       <c r="R107" t="n">
-        <v>6766684</v>
+        <v>6766623</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11171,50 +11176,45 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>127722929</v>
+        <v>127723170</v>
       </c>
       <c r="B108" t="n">
-        <v>8450</v>
+        <v>79029</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
-      <c r="M108" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P108" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>443327</v>
+        <v>443333</v>
       </c>
       <c r="R108" t="n">
-        <v>6766698</v>
+        <v>6766676</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11273,10 +11273,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>127723038</v>
+        <v>127723616</v>
       </c>
       <c r="B109" t="n">
-        <v>78788</v>
+        <v>57672</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11284,34 +11284,39 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
+      <c r="M109" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
       <c r="P109" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>443328</v>
+        <v>443475</v>
       </c>
       <c r="R109" t="n">
-        <v>6766721</v>
+        <v>6766610</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11370,10 +11375,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>127723616</v>
+        <v>127723038</v>
       </c>
       <c r="B110" t="n">
-        <v>57672</v>
+        <v>78788</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -11381,39 +11386,34 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>100109</v>
+        <v>228912</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
-      <c r="M110" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
       <c r="P110" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>443475</v>
+        <v>443328</v>
       </c>
       <c r="R110" t="n">
-        <v>6766610</v>
+        <v>6766721</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11666,10 +11666,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>127722904</v>
+        <v>127723172</v>
       </c>
       <c r="B113" t="n">
-        <v>57672</v>
+        <v>79029</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -11677,21 +11677,21 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -11701,10 +11701,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>443419</v>
+        <v>443356</v>
       </c>
       <c r="R113" t="n">
-        <v>6766676</v>
+        <v>6766650</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -11737,11 +11737,6 @@
       <c r="AA113" t="inlineStr">
         <is>
           <t>2025-08-21</t>
-        </is>
-      </c>
-      <c r="AC113" t="inlineStr">
-        <is>
-          <t>Äldre ringhack (tall)</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -11768,7 +11763,7 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>127723172</v>
+        <v>127723136</v>
       </c>
       <c r="B114" t="n">
         <v>79029</v>
@@ -11803,10 +11798,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>443356</v>
+        <v>443438</v>
       </c>
       <c r="R114" t="n">
-        <v>6766650</v>
+        <v>6766628</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -11865,7 +11860,7 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>127723136</v>
+        <v>127723160</v>
       </c>
       <c r="B115" t="n">
         <v>79029</v>
@@ -11900,10 +11895,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>443438</v>
+        <v>443309</v>
       </c>
       <c r="R115" t="n">
-        <v>6766628</v>
+        <v>6766785</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -11962,10 +11957,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>127723160</v>
+        <v>127722904</v>
       </c>
       <c r="B116" t="n">
-        <v>79029</v>
+        <v>57672</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -11973,21 +11968,21 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -11997,10 +11992,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>443309</v>
+        <v>443419</v>
       </c>
       <c r="R116" t="n">
-        <v>6766785</v>
+        <v>6766676</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12033,6 +12028,11 @@
       <c r="AA116" t="inlineStr">
         <is>
           <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AC116" t="inlineStr">
+        <is>
+          <t>Äldre ringhack (tall)</t>
         </is>
       </c>
       <c r="AD116" t="b">

--- a/artfynd/A 35484-2025 artfynd.xlsx
+++ b/artfynd/A 35484-2025 artfynd.xlsx
@@ -4697,32 +4697,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>127723064</v>
+        <v>127722876</v>
       </c>
       <c r="B42" t="n">
-        <v>91513</v>
+        <v>91372</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1503</v>
+        <v>5442</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4732,10 +4732,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>443329</v>
+        <v>443366</v>
       </c>
       <c r="R42" t="n">
-        <v>6766670</v>
+        <v>6766661</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4794,32 +4794,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127723189</v>
+        <v>127723064</v>
       </c>
       <c r="B43" t="n">
-        <v>79029</v>
+        <v>91513</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>1503</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4829,10 +4829,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>443446</v>
+        <v>443329</v>
       </c>
       <c r="R43" t="n">
-        <v>6766727</v>
+        <v>6766670</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4865,11 +4865,6 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-08-21</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Med grov gran i bäckmiljö</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -4896,7 +4891,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>127723121</v>
+        <v>127723189</v>
       </c>
       <c r="B44" t="n">
         <v>79029</v>
@@ -4931,10 +4926,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>443558</v>
+        <v>443446</v>
       </c>
       <c r="R44" t="n">
-        <v>6766620</v>
+        <v>6766727</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4967,6 +4962,11 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Med grov gran i bäckmiljö</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -4993,10 +4993,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>127722876</v>
+        <v>127723121</v>
       </c>
       <c r="B45" t="n">
-        <v>91372</v>
+        <v>79029</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5004,21 +5004,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5028,10 +5028,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>443366</v>
+        <v>443558</v>
       </c>
       <c r="R45" t="n">
-        <v>6766661</v>
+        <v>6766620</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -8338,10 +8338,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>127723571</v>
+        <v>127723104</v>
       </c>
       <c r="B79" t="n">
-        <v>78696</v>
+        <v>79029</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8349,21 +8349,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8373,10 +8373,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>443426</v>
+        <v>443536</v>
       </c>
       <c r="R79" t="n">
-        <v>6766668</v>
+        <v>6766704</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8435,7 +8435,7 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>127723104</v>
+        <v>127723120</v>
       </c>
       <c r="B80" t="n">
         <v>79029</v>
@@ -8470,10 +8470,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>443536</v>
+        <v>443548</v>
       </c>
       <c r="R80" t="n">
-        <v>6766704</v>
+        <v>6766624</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8532,10 +8532,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>127723120</v>
+        <v>127723571</v>
       </c>
       <c r="B81" t="n">
-        <v>79029</v>
+        <v>78696</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8543,21 +8543,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8567,10 +8567,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>443548</v>
+        <v>443426</v>
       </c>
       <c r="R81" t="n">
-        <v>6766624</v>
+        <v>6766668</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8726,10 +8726,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>127722888</v>
+        <v>127723570</v>
       </c>
       <c r="B83" t="n">
-        <v>57669</v>
+        <v>78696</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8737,39 +8737,34 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>100049</v>
+        <v>353</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
-      <c r="M83" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P83" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>443481</v>
+        <v>443319</v>
       </c>
       <c r="R83" t="n">
-        <v>6766676</v>
+        <v>6766670</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -8828,10 +8823,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>127722916</v>
+        <v>127723178</v>
       </c>
       <c r="B84" t="n">
-        <v>57672</v>
+        <v>79029</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -8839,39 +8834,34 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
-      <c r="M84" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P84" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>443342</v>
+        <v>443402</v>
       </c>
       <c r="R84" t="n">
-        <v>6766806</v>
+        <v>6766682</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -8904,11 +8894,6 @@
       <c r="AA84" t="inlineStr">
         <is>
           <t>2025-08-21</t>
-        </is>
-      </c>
-      <c r="AC84" t="inlineStr">
-        <is>
-          <t>Färska ringhack (gran), 4-5 år gamla</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -8935,10 +8920,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>127723541</v>
+        <v>127723116</v>
       </c>
       <c r="B85" t="n">
-        <v>57672</v>
+        <v>79029</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -8946,39 +8931,34 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
-      <c r="M85" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P85" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>443317</v>
+        <v>443509</v>
       </c>
       <c r="R85" t="n">
-        <v>6766816</v>
+        <v>6766633</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9037,10 +9017,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>127723570</v>
+        <v>127723092</v>
       </c>
       <c r="B86" t="n">
-        <v>78696</v>
+        <v>79029</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9048,21 +9028,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9072,10 +9052,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>443319</v>
+        <v>443572</v>
       </c>
       <c r="R86" t="n">
-        <v>6766670</v>
+        <v>6766650</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9134,7 +9114,7 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>127723178</v>
+        <v>127723171</v>
       </c>
       <c r="B87" t="n">
         <v>79029</v>
@@ -9169,10 +9149,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>443402</v>
+        <v>443342</v>
       </c>
       <c r="R87" t="n">
-        <v>6766682</v>
+        <v>6766650</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9231,10 +9211,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>127723116</v>
+        <v>127722888</v>
       </c>
       <c r="B88" t="n">
-        <v>79029</v>
+        <v>57669</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9242,34 +9222,39 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P88" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>443509</v>
+        <v>443481</v>
       </c>
       <c r="R88" t="n">
-        <v>6766633</v>
+        <v>6766676</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9328,10 +9313,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>127723092</v>
+        <v>127722916</v>
       </c>
       <c r="B89" t="n">
-        <v>79029</v>
+        <v>57672</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9339,34 +9324,39 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P89" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>443572</v>
+        <v>443342</v>
       </c>
       <c r="R89" t="n">
-        <v>6766650</v>
+        <v>6766806</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9399,6 +9389,11 @@
       <c r="AA89" t="inlineStr">
         <is>
           <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AC89" t="inlineStr">
+        <is>
+          <t>Färska ringhack (gran), 4-5 år gamla</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -9425,10 +9420,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>127723171</v>
+        <v>127723541</v>
       </c>
       <c r="B90" t="n">
-        <v>79029</v>
+        <v>57672</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9436,34 +9431,39 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P90" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>443342</v>
+        <v>443317</v>
       </c>
       <c r="R90" t="n">
-        <v>6766650</v>
+        <v>6766816</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -11666,10 +11666,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>127723172</v>
+        <v>127722904</v>
       </c>
       <c r="B113" t="n">
-        <v>79029</v>
+        <v>57672</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -11677,21 +11677,21 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -11701,10 +11701,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>443356</v>
+        <v>443419</v>
       </c>
       <c r="R113" t="n">
-        <v>6766650</v>
+        <v>6766676</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -11737,6 +11737,11 @@
       <c r="AA113" t="inlineStr">
         <is>
           <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AC113" t="inlineStr">
+        <is>
+          <t>Äldre ringhack (tall)</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -11763,7 +11768,7 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>127723136</v>
+        <v>127723172</v>
       </c>
       <c r="B114" t="n">
         <v>79029</v>
@@ -11798,10 +11803,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>443438</v>
+        <v>443356</v>
       </c>
       <c r="R114" t="n">
-        <v>6766628</v>
+        <v>6766650</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -11860,7 +11865,7 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>127723160</v>
+        <v>127723136</v>
       </c>
       <c r="B115" t="n">
         <v>79029</v>
@@ -11895,10 +11900,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>443309</v>
+        <v>443438</v>
       </c>
       <c r="R115" t="n">
-        <v>6766785</v>
+        <v>6766628</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -11957,10 +11962,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>127722904</v>
+        <v>127723160</v>
       </c>
       <c r="B116" t="n">
-        <v>57672</v>
+        <v>79029</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -11968,21 +11973,21 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -11992,10 +11997,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>443419</v>
+        <v>443309</v>
       </c>
       <c r="R116" t="n">
-        <v>6766676</v>
+        <v>6766785</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12028,11 +12033,6 @@
       <c r="AA116" t="inlineStr">
         <is>
           <t>2025-08-21</t>
-        </is>
-      </c>
-      <c r="AC116" t="inlineStr">
-        <is>
-          <t>Äldre ringhack (tall)</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -12958,32 +12958,32 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>127723165</v>
+        <v>127723555</v>
       </c>
       <c r="B126" t="n">
-        <v>79029</v>
+        <v>92642</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -12993,10 +12993,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>443327</v>
+        <v>443554</v>
       </c>
       <c r="R126" t="n">
-        <v>6766717</v>
+        <v>6766667</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -13055,7 +13055,7 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>127723094</v>
+        <v>127723165</v>
       </c>
       <c r="B127" t="n">
         <v>79029</v>
@@ -13090,10 +13090,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>443557</v>
+        <v>443327</v>
       </c>
       <c r="R127" t="n">
-        <v>6766635</v>
+        <v>6766717</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -13152,7 +13152,7 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>127723118</v>
+        <v>127723094</v>
       </c>
       <c r="B128" t="n">
         <v>79029</v>
@@ -13187,10 +13187,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>443519</v>
+        <v>443557</v>
       </c>
       <c r="R128" t="n">
-        <v>6766624</v>
+        <v>6766635</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -13249,7 +13249,7 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>127723140</v>
+        <v>127723118</v>
       </c>
       <c r="B129" t="n">
         <v>79029</v>
@@ -13284,7 +13284,7 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>443370</v>
+        <v>443519</v>
       </c>
       <c r="R129" t="n">
         <v>6766624</v>
@@ -13346,32 +13346,32 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>127723555</v>
+        <v>127723140</v>
       </c>
       <c r="B130" t="n">
-        <v>92642</v>
+        <v>79029</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
@@ -13381,10 +13381,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>443554</v>
+        <v>443370</v>
       </c>
       <c r="R130" t="n">
-        <v>6766667</v>
+        <v>6766624</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -13647,7 +13647,7 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>127723111</v>
+        <v>127723162</v>
       </c>
       <c r="B133" t="n">
         <v>79029</v>
@@ -13682,10 +13682,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>443474</v>
+        <v>443312</v>
       </c>
       <c r="R133" t="n">
-        <v>6766692</v>
+        <v>6766762</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -13744,7 +13744,7 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>127723162</v>
+        <v>127723111</v>
       </c>
       <c r="B134" t="n">
         <v>79029</v>
@@ -13779,10 +13779,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>443312</v>
+        <v>443474</v>
       </c>
       <c r="R134" t="n">
-        <v>6766762</v>
+        <v>6766692</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>

--- a/artfynd/A 35484-2025 artfynd.xlsx
+++ b/artfynd/A 35484-2025 artfynd.xlsx
@@ -2829,50 +2829,45 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127722950</v>
+        <v>127723112</v>
       </c>
       <c r="B23" t="n">
-        <v>8450</v>
+        <v>79029</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>443438</v>
+        <v>443476</v>
       </c>
       <c r="R23" t="n">
-        <v>6766650</v>
+        <v>6766681</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2931,10 +2926,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127723040</v>
+        <v>127723166</v>
       </c>
       <c r="B24" t="n">
-        <v>78788</v>
+        <v>79029</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2942,21 +2937,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2966,10 +2961,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>443377</v>
+        <v>443326</v>
       </c>
       <c r="R24" t="n">
-        <v>6766659</v>
+        <v>6766711</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3028,10 +3023,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127723039</v>
+        <v>127723181</v>
       </c>
       <c r="B25" t="n">
-        <v>78788</v>
+        <v>79029</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3039,21 +3034,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3063,10 +3058,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>443356</v>
+        <v>443436</v>
       </c>
       <c r="R25" t="n">
-        <v>6766650</v>
+        <v>6766667</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3125,10 +3120,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127723166</v>
+        <v>127723040</v>
       </c>
       <c r="B26" t="n">
-        <v>79029</v>
+        <v>78788</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3136,21 +3131,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3160,10 +3155,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>443326</v>
+        <v>443377</v>
       </c>
       <c r="R26" t="n">
-        <v>6766711</v>
+        <v>6766659</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3222,10 +3217,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127723181</v>
+        <v>127723039</v>
       </c>
       <c r="B27" t="n">
-        <v>79029</v>
+        <v>78788</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3233,21 +3228,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3257,10 +3252,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>443436</v>
+        <v>443356</v>
       </c>
       <c r="R27" t="n">
-        <v>6766667</v>
+        <v>6766650</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3416,45 +3411,50 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127723112</v>
+        <v>127722950</v>
       </c>
       <c r="B29" t="n">
-        <v>79029</v>
+        <v>8450</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>443476</v>
+        <v>443438</v>
       </c>
       <c r="R29" t="n">
-        <v>6766681</v>
+        <v>6766650</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3513,10 +3513,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127723179</v>
+        <v>127722875</v>
       </c>
       <c r="B30" t="n">
-        <v>79029</v>
+        <v>91372</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3524,21 +3524,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3548,10 +3548,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>443411</v>
+        <v>443312</v>
       </c>
       <c r="R30" t="n">
-        <v>6766676</v>
+        <v>6766713</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3712,10 +3712,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127722875</v>
+        <v>127723152</v>
       </c>
       <c r="B32" t="n">
-        <v>91372</v>
+        <v>79029</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3723,21 +3723,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3747,10 +3747,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>443312</v>
+        <v>443424</v>
       </c>
       <c r="R32" t="n">
-        <v>6766713</v>
+        <v>6766627</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3809,7 +3809,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127723152</v>
+        <v>127723179</v>
       </c>
       <c r="B33" t="n">
         <v>79029</v>
@@ -3844,10 +3844,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>443424</v>
+        <v>443411</v>
       </c>
       <c r="R33" t="n">
-        <v>6766627</v>
+        <v>6766676</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -8338,10 +8338,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>127723104</v>
+        <v>127723571</v>
       </c>
       <c r="B79" t="n">
-        <v>79029</v>
+        <v>78696</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8349,21 +8349,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8373,10 +8373,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>443536</v>
+        <v>443426</v>
       </c>
       <c r="R79" t="n">
-        <v>6766704</v>
+        <v>6766668</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8435,7 +8435,7 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>127723120</v>
+        <v>127723104</v>
       </c>
       <c r="B80" t="n">
         <v>79029</v>
@@ -8470,10 +8470,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>443548</v>
+        <v>443536</v>
       </c>
       <c r="R80" t="n">
-        <v>6766624</v>
+        <v>6766704</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8532,10 +8532,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>127723571</v>
+        <v>127723120</v>
       </c>
       <c r="B81" t="n">
-        <v>78696</v>
+        <v>79029</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8543,21 +8543,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8567,10 +8567,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>443426</v>
+        <v>443548</v>
       </c>
       <c r="R81" t="n">
-        <v>6766668</v>
+        <v>6766624</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8726,10 +8726,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>127723570</v>
+        <v>127722888</v>
       </c>
       <c r="B83" t="n">
-        <v>78696</v>
+        <v>57669</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8737,34 +8737,39 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>353</v>
+        <v>100049</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P83" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>443319</v>
+        <v>443481</v>
       </c>
       <c r="R83" t="n">
-        <v>6766670</v>
+        <v>6766676</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -8823,10 +8828,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>127723178</v>
+        <v>127722916</v>
       </c>
       <c r="B84" t="n">
-        <v>79029</v>
+        <v>57672</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -8834,34 +8839,39 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P84" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>443402</v>
+        <v>443342</v>
       </c>
       <c r="R84" t="n">
-        <v>6766682</v>
+        <v>6766806</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -8894,6 +8904,11 @@
       <c r="AA84" t="inlineStr">
         <is>
           <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AC84" t="inlineStr">
+        <is>
+          <t>Färska ringhack (gran), 4-5 år gamla</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -8920,10 +8935,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>127723116</v>
+        <v>127723541</v>
       </c>
       <c r="B85" t="n">
-        <v>79029</v>
+        <v>57672</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -8931,34 +8946,39 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P85" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>443509</v>
+        <v>443317</v>
       </c>
       <c r="R85" t="n">
-        <v>6766633</v>
+        <v>6766816</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9017,10 +9037,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>127723092</v>
+        <v>127723570</v>
       </c>
       <c r="B86" t="n">
-        <v>79029</v>
+        <v>78696</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9028,21 +9048,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9052,10 +9072,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>443572</v>
+        <v>443319</v>
       </c>
       <c r="R86" t="n">
-        <v>6766650</v>
+        <v>6766670</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9114,7 +9134,7 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>127723171</v>
+        <v>127723178</v>
       </c>
       <c r="B87" t="n">
         <v>79029</v>
@@ -9149,10 +9169,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>443342</v>
+        <v>443402</v>
       </c>
       <c r="R87" t="n">
-        <v>6766650</v>
+        <v>6766682</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9211,10 +9231,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>127722888</v>
+        <v>127723116</v>
       </c>
       <c r="B88" t="n">
-        <v>57669</v>
+        <v>79029</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9222,39 +9242,34 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
-      <c r="M88" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P88" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>443481</v>
+        <v>443509</v>
       </c>
       <c r="R88" t="n">
-        <v>6766676</v>
+        <v>6766633</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9313,10 +9328,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>127722916</v>
+        <v>127723092</v>
       </c>
       <c r="B89" t="n">
-        <v>57672</v>
+        <v>79029</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9324,39 +9339,34 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
-      <c r="M89" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P89" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>443342</v>
+        <v>443572</v>
       </c>
       <c r="R89" t="n">
-        <v>6766806</v>
+        <v>6766650</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9389,11 +9399,6 @@
       <c r="AA89" t="inlineStr">
         <is>
           <t>2025-08-21</t>
-        </is>
-      </c>
-      <c r="AC89" t="inlineStr">
-        <is>
-          <t>Färska ringhack (gran), 4-5 år gamla</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -9420,10 +9425,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>127723541</v>
+        <v>127723171</v>
       </c>
       <c r="B90" t="n">
-        <v>57672</v>
+        <v>79029</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9431,39 +9436,34 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
-      <c r="M90" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P90" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>443317</v>
+        <v>443342</v>
       </c>
       <c r="R90" t="n">
-        <v>6766816</v>
+        <v>6766650</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9522,7 +9522,7 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>127723161</v>
+        <v>127723103</v>
       </c>
       <c r="B91" t="n">
         <v>79029</v>
@@ -9557,10 +9557,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>443305</v>
+        <v>443541</v>
       </c>
       <c r="R91" t="n">
-        <v>6766767</v>
+        <v>6766696</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9619,7 +9619,7 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>127723186</v>
+        <v>127723174</v>
       </c>
       <c r="B92" t="n">
         <v>79029</v>
@@ -9654,10 +9654,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>443454</v>
+        <v>443378</v>
       </c>
       <c r="R92" t="n">
-        <v>6766738</v>
+        <v>6766657</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9716,10 +9716,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>127723114</v>
+        <v>127723041</v>
       </c>
       <c r="B93" t="n">
-        <v>79029</v>
+        <v>78788</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9727,21 +9727,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -9751,10 +9751,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>443487</v>
+        <v>443450</v>
       </c>
       <c r="R93" t="n">
-        <v>6766651</v>
+        <v>6766735</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -9813,10 +9813,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>127723097</v>
+        <v>127723569</v>
       </c>
       <c r="B94" t="n">
-        <v>79029</v>
+        <v>78696</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -9824,21 +9824,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -9848,10 +9848,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>443561</v>
+        <v>443332</v>
       </c>
       <c r="R94" t="n">
-        <v>6766678</v>
+        <v>6766677</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -9910,10 +9910,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>127723041</v>
+        <v>127723105</v>
       </c>
       <c r="B95" t="n">
-        <v>78788</v>
+        <v>79029</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -9921,21 +9921,21 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -9945,10 +9945,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>443450</v>
+        <v>443525</v>
       </c>
       <c r="R95" t="n">
-        <v>6766735</v>
+        <v>6766717</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10007,10 +10007,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>127723569</v>
+        <v>127723161</v>
       </c>
       <c r="B96" t="n">
-        <v>78696</v>
+        <v>79029</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10018,21 +10018,21 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10042,10 +10042,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>443332</v>
+        <v>443305</v>
       </c>
       <c r="R96" t="n">
-        <v>6766677</v>
+        <v>6766767</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10104,7 +10104,7 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>127723103</v>
+        <v>127723186</v>
       </c>
       <c r="B97" t="n">
         <v>79029</v>
@@ -10139,10 +10139,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>443541</v>
+        <v>443454</v>
       </c>
       <c r="R97" t="n">
-        <v>6766696</v>
+        <v>6766738</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10201,7 +10201,7 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>127723174</v>
+        <v>127723114</v>
       </c>
       <c r="B98" t="n">
         <v>79029</v>
@@ -10236,10 +10236,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>443378</v>
+        <v>443487</v>
       </c>
       <c r="R98" t="n">
-        <v>6766657</v>
+        <v>6766651</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10298,7 +10298,7 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>127723105</v>
+        <v>127723097</v>
       </c>
       <c r="B99" t="n">
         <v>79029</v>
@@ -10333,10 +10333,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>443525</v>
+        <v>443561</v>
       </c>
       <c r="R99" t="n">
-        <v>6766717</v>
+        <v>6766678</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10395,10 +10395,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>127723183</v>
+        <v>127722842</v>
       </c>
       <c r="B100" t="n">
-        <v>79029</v>
+        <v>79061</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10406,21 +10406,21 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -10430,10 +10430,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>443441</v>
+        <v>443504</v>
       </c>
       <c r="R100" t="n">
-        <v>6766686</v>
+        <v>6766708</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10492,7 +10492,7 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>127723182</v>
+        <v>127723170</v>
       </c>
       <c r="B101" t="n">
         <v>79029</v>
@@ -10527,10 +10527,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>443444</v>
+        <v>443333</v>
       </c>
       <c r="R101" t="n">
-        <v>6766677</v>
+        <v>6766676</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10589,7 +10589,7 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>127723098</v>
+        <v>127723157</v>
       </c>
       <c r="B102" t="n">
         <v>79029</v>
@@ -10624,10 +10624,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>443562</v>
+        <v>443306</v>
       </c>
       <c r="R102" t="n">
-        <v>6766684</v>
+        <v>6766830</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -10686,50 +10686,45 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>127722929</v>
+        <v>127723139</v>
       </c>
       <c r="B103" t="n">
-        <v>8450</v>
+        <v>79029</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
-      <c r="M103" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P103" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>443327</v>
+        <v>443381</v>
       </c>
       <c r="R103" t="n">
-        <v>6766698</v>
+        <v>6766623</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -10788,10 +10783,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>127722842</v>
+        <v>127723096</v>
       </c>
       <c r="B104" t="n">
-        <v>79061</v>
+        <v>79029</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -10799,21 +10794,21 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -10823,10 +10818,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>443504</v>
+        <v>443554</v>
       </c>
       <c r="R104" t="n">
-        <v>6766708</v>
+        <v>6766650</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -10885,7 +10880,7 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>127723096</v>
+        <v>127723183</v>
       </c>
       <c r="B105" t="n">
         <v>79029</v>
@@ -10920,10 +10915,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>443554</v>
+        <v>443441</v>
       </c>
       <c r="R105" t="n">
-        <v>6766650</v>
+        <v>6766686</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -10982,7 +10977,7 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>127723157</v>
+        <v>127723182</v>
       </c>
       <c r="B106" t="n">
         <v>79029</v>
@@ -11017,10 +11012,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>443306</v>
+        <v>443444</v>
       </c>
       <c r="R106" t="n">
-        <v>6766830</v>
+        <v>6766677</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11079,7 +11074,7 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>127723139</v>
+        <v>127723098</v>
       </c>
       <c r="B107" t="n">
         <v>79029</v>
@@ -11114,10 +11109,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>443381</v>
+        <v>443562</v>
       </c>
       <c r="R107" t="n">
-        <v>6766623</v>
+        <v>6766684</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11176,45 +11171,50 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>127723170</v>
+        <v>127722929</v>
       </c>
       <c r="B108" t="n">
-        <v>79029</v>
+        <v>8450</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
+      <c r="M108" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P108" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>443333</v>
+        <v>443327</v>
       </c>
       <c r="R108" t="n">
-        <v>6766676</v>
+        <v>6766698</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11273,10 +11273,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>127723616</v>
+        <v>127723038</v>
       </c>
       <c r="B109" t="n">
-        <v>57672</v>
+        <v>78788</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11284,39 +11284,34 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>100109</v>
+        <v>228912</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
-      <c r="M109" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
       <c r="P109" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>443475</v>
+        <v>443328</v>
       </c>
       <c r="R109" t="n">
-        <v>6766610</v>
+        <v>6766721</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11375,10 +11370,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>127723038</v>
+        <v>127723616</v>
       </c>
       <c r="B110" t="n">
-        <v>78788</v>
+        <v>57672</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -11386,34 +11381,39 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
+      <c r="M110" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
       <c r="P110" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>443328</v>
+        <v>443475</v>
       </c>
       <c r="R110" t="n">
-        <v>6766721</v>
+        <v>6766610</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11666,10 +11666,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>127722904</v>
+        <v>127723172</v>
       </c>
       <c r="B113" t="n">
-        <v>57672</v>
+        <v>79029</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -11677,21 +11677,21 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -11701,10 +11701,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>443419</v>
+        <v>443356</v>
       </c>
       <c r="R113" t="n">
-        <v>6766676</v>
+        <v>6766650</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -11737,11 +11737,6 @@
       <c r="AA113" t="inlineStr">
         <is>
           <t>2025-08-21</t>
-        </is>
-      </c>
-      <c r="AC113" t="inlineStr">
-        <is>
-          <t>Äldre ringhack (tall)</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -11768,7 +11763,7 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>127723172</v>
+        <v>127723136</v>
       </c>
       <c r="B114" t="n">
         <v>79029</v>
@@ -11803,10 +11798,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>443356</v>
+        <v>443438</v>
       </c>
       <c r="R114" t="n">
-        <v>6766650</v>
+        <v>6766628</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -11865,7 +11860,7 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>127723136</v>
+        <v>127723160</v>
       </c>
       <c r="B115" t="n">
         <v>79029</v>
@@ -11900,10 +11895,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>443438</v>
+        <v>443309</v>
       </c>
       <c r="R115" t="n">
-        <v>6766628</v>
+        <v>6766785</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -11962,10 +11957,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>127723160</v>
+        <v>127722904</v>
       </c>
       <c r="B116" t="n">
-        <v>79029</v>
+        <v>57672</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -11973,21 +11968,21 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -11997,10 +11992,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>443309</v>
+        <v>443419</v>
       </c>
       <c r="R116" t="n">
-        <v>6766785</v>
+        <v>6766676</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12033,6 +12028,11 @@
       <c r="AA116" t="inlineStr">
         <is>
           <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AC116" t="inlineStr">
+        <is>
+          <t>Äldre ringhack (tall)</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -13647,7 +13647,7 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>127723162</v>
+        <v>127723111</v>
       </c>
       <c r="B133" t="n">
         <v>79029</v>
@@ -13682,10 +13682,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>443312</v>
+        <v>443474</v>
       </c>
       <c r="R133" t="n">
-        <v>6766762</v>
+        <v>6766692</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -13744,7 +13744,7 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>127723111</v>
+        <v>127723162</v>
       </c>
       <c r="B134" t="n">
         <v>79029</v>
@@ -13779,10 +13779,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>443474</v>
+        <v>443312</v>
       </c>
       <c r="R134" t="n">
-        <v>6766692</v>
+        <v>6766762</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>

--- a/artfynd/A 35484-2025 artfynd.xlsx
+++ b/artfynd/A 35484-2025 artfynd.xlsx
@@ -1944,7 +1944,7 @@
         <v>127723164</v>
       </c>
       <c r="B14" t="n">
-        <v>79029</v>
+        <v>79032</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2038,10 +2038,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127723151</v>
+        <v>127723117</v>
       </c>
       <c r="B15" t="n">
-        <v>79029</v>
+        <v>79032</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2073,10 +2073,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>443430</v>
+        <v>443514</v>
       </c>
       <c r="R15" t="n">
-        <v>6766608</v>
+        <v>6766630</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2135,10 +2135,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127723117</v>
+        <v>127723151</v>
       </c>
       <c r="B16" t="n">
-        <v>79029</v>
+        <v>79032</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2170,10 +2170,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>443514</v>
+        <v>443430</v>
       </c>
       <c r="R16" t="n">
-        <v>6766630</v>
+        <v>6766608</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2235,7 +2235,7 @@
         <v>127723187</v>
       </c>
       <c r="B17" t="n">
-        <v>79029</v>
+        <v>79032</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2332,7 +2332,7 @@
         <v>127722870</v>
       </c>
       <c r="B18" t="n">
-        <v>57832</v>
+        <v>57833</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2431,10 +2431,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127723099</v>
+        <v>127723093</v>
       </c>
       <c r="B19" t="n">
-        <v>79029</v>
+        <v>79032</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2466,10 +2466,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>443567</v>
+        <v>443572</v>
       </c>
       <c r="R19" t="n">
-        <v>6766695</v>
+        <v>6766645</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2528,10 +2528,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127723093</v>
+        <v>127723099</v>
       </c>
       <c r="B20" t="n">
-        <v>79029</v>
+        <v>79032</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2563,10 +2563,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>443572</v>
+        <v>443567</v>
       </c>
       <c r="R20" t="n">
-        <v>6766645</v>
+        <v>6766695</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2625,7 +2625,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127722942</v>
+        <v>127722947</v>
       </c>
       <c r="B21" t="n">
         <v>8450</v>
@@ -2665,10 +2665,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>443542</v>
+        <v>443486</v>
       </c>
       <c r="R21" t="n">
-        <v>6766699</v>
+        <v>6766604</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2727,7 +2727,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127722947</v>
+        <v>127722942</v>
       </c>
       <c r="B22" t="n">
         <v>8450</v>
@@ -2767,10 +2767,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>443486</v>
+        <v>443542</v>
       </c>
       <c r="R22" t="n">
-        <v>6766604</v>
+        <v>6766699</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2829,10 +2829,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127723112</v>
+        <v>127723166</v>
       </c>
       <c r="B23" t="n">
-        <v>79029</v>
+        <v>79032</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2864,10 +2864,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>443476</v>
+        <v>443326</v>
       </c>
       <c r="R23" t="n">
-        <v>6766681</v>
+        <v>6766711</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2926,10 +2926,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127723166</v>
+        <v>127723040</v>
       </c>
       <c r="B24" t="n">
-        <v>79029</v>
+        <v>78791</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2937,21 +2937,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2961,10 +2961,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>443326</v>
+        <v>443377</v>
       </c>
       <c r="R24" t="n">
-        <v>6766711</v>
+        <v>6766659</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3023,10 +3023,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127723181</v>
+        <v>127723039</v>
       </c>
       <c r="B25" t="n">
-        <v>79029</v>
+        <v>78791</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3034,21 +3034,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3058,10 +3058,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>443436</v>
+        <v>443356</v>
       </c>
       <c r="R25" t="n">
-        <v>6766667</v>
+        <v>6766650</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3120,45 +3120,50 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127723040</v>
+        <v>127722950</v>
       </c>
       <c r="B26" t="n">
-        <v>78788</v>
+        <v>8450</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>228912</v>
+        <v>106545</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>443377</v>
+        <v>443438</v>
       </c>
       <c r="R26" t="n">
-        <v>6766659</v>
+        <v>6766650</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3217,10 +3222,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127723039</v>
+        <v>127722874</v>
       </c>
       <c r="B27" t="n">
-        <v>78788</v>
+        <v>91380</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3228,21 +3233,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>228912</v>
+        <v>5442</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3252,10 +3257,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>443356</v>
+        <v>443388</v>
       </c>
       <c r="R27" t="n">
-        <v>6766650</v>
+        <v>6766675</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3314,10 +3319,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127722874</v>
+        <v>127723112</v>
       </c>
       <c r="B28" t="n">
-        <v>91372</v>
+        <v>79032</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3325,21 +3330,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3349,10 +3354,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>443388</v>
+        <v>443476</v>
       </c>
       <c r="R28" t="n">
-        <v>6766675</v>
+        <v>6766681</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3411,50 +3416,45 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127722950</v>
+        <v>127723181</v>
       </c>
       <c r="B29" t="n">
-        <v>8450</v>
+        <v>79032</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>443438</v>
+        <v>443436</v>
       </c>
       <c r="R29" t="n">
-        <v>6766650</v>
+        <v>6766667</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3513,45 +3513,50 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127722875</v>
+        <v>127722945</v>
       </c>
       <c r="B30" t="n">
-        <v>91372</v>
+        <v>8450</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>5442</v>
+        <v>106545</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>443312</v>
+        <v>443568</v>
       </c>
       <c r="R30" t="n">
-        <v>6766713</v>
+        <v>6766605</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3610,50 +3615,45 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127722945</v>
+        <v>127722875</v>
       </c>
       <c r="B31" t="n">
-        <v>8450</v>
+        <v>91380</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>106545</v>
+        <v>5442</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>443568</v>
+        <v>443312</v>
       </c>
       <c r="R31" t="n">
-        <v>6766605</v>
+        <v>6766713</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3715,7 +3715,7 @@
         <v>127723152</v>
       </c>
       <c r="B32" t="n">
-        <v>79029</v>
+        <v>79032</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3812,7 +3812,7 @@
         <v>127723179</v>
       </c>
       <c r="B33" t="n">
-        <v>79029</v>
+        <v>79032</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3906,10 +3906,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>127722944</v>
+        <v>127722921</v>
       </c>
       <c r="B34" t="n">
-        <v>8450</v>
+        <v>97355</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3917,39 +3917,34 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>106545</v>
+        <v>221945</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>443488</v>
+        <v>443330</v>
       </c>
       <c r="R34" t="n">
-        <v>6766671</v>
+        <v>6766662</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4008,50 +4003,45 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127722928</v>
+        <v>127723107</v>
       </c>
       <c r="B35" t="n">
-        <v>8450</v>
+        <v>79032</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>443559</v>
+        <v>443493</v>
       </c>
       <c r="R35" t="n">
-        <v>6766616</v>
+        <v>6766717</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4110,10 +4100,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127723115</v>
+        <v>127723109</v>
       </c>
       <c r="B36" t="n">
-        <v>79029</v>
+        <v>79032</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4145,10 +4135,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>443495</v>
+        <v>443482</v>
       </c>
       <c r="R36" t="n">
-        <v>6766641</v>
+        <v>6766716</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4210,7 +4200,7 @@
         <v>127723169</v>
       </c>
       <c r="B37" t="n">
-        <v>79029</v>
+        <v>79032</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4304,10 +4294,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127723107</v>
+        <v>127723115</v>
       </c>
       <c r="B38" t="n">
-        <v>79029</v>
+        <v>79032</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4339,10 +4329,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>443493</v>
+        <v>443495</v>
       </c>
       <c r="R38" t="n">
-        <v>6766717</v>
+        <v>6766641</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4401,10 +4391,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127723109</v>
+        <v>127722896</v>
       </c>
       <c r="B39" t="n">
-        <v>79029</v>
+        <v>57670</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4412,34 +4402,39 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>443482</v>
+        <v>443537</v>
       </c>
       <c r="R39" t="n">
-        <v>6766716</v>
+        <v>6766699</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4498,38 +4493,38 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127722896</v>
+        <v>127722944</v>
       </c>
       <c r="B40" t="n">
-        <v>57669</v>
+        <v>8450</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="M40" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
@@ -4538,10 +4533,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>443537</v>
+        <v>443488</v>
       </c>
       <c r="R40" t="n">
-        <v>6766699</v>
+        <v>6766671</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4600,10 +4595,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127722921</v>
+        <v>127722928</v>
       </c>
       <c r="B41" t="n">
-        <v>97347</v>
+        <v>8450</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4611,34 +4606,39 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>221945</v>
+        <v>106545</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>443330</v>
+        <v>443559</v>
       </c>
       <c r="R41" t="n">
-        <v>6766662</v>
+        <v>6766616</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4697,10 +4697,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>127722876</v>
+        <v>127723159</v>
       </c>
       <c r="B42" t="n">
-        <v>91372</v>
+        <v>79032</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4708,21 +4708,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4732,10 +4732,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>443366</v>
+        <v>443314</v>
       </c>
       <c r="R42" t="n">
-        <v>6766661</v>
+        <v>6766811</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4794,32 +4794,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127723064</v>
+        <v>127723189</v>
       </c>
       <c r="B43" t="n">
-        <v>91513</v>
+        <v>79032</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1503</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4829,10 +4829,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>443329</v>
+        <v>443446</v>
       </c>
       <c r="R43" t="n">
-        <v>6766670</v>
+        <v>6766727</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4865,6 +4865,11 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Med grov gran i bäckmiljö</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -4891,10 +4896,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>127723189</v>
+        <v>127722876</v>
       </c>
       <c r="B44" t="n">
-        <v>79029</v>
+        <v>91380</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4902,21 +4907,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4926,10 +4931,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>443446</v>
+        <v>443366</v>
       </c>
       <c r="R44" t="n">
-        <v>6766727</v>
+        <v>6766661</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4962,11 +4967,6 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-08-21</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Med grov gran i bäckmiljö</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -4993,32 +4993,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>127723121</v>
+        <v>127723064</v>
       </c>
       <c r="B45" t="n">
-        <v>79029</v>
+        <v>91521</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>1503</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5028,10 +5028,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>443558</v>
+        <v>443329</v>
       </c>
       <c r="R45" t="n">
-        <v>6766620</v>
+        <v>6766670</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5093,7 +5093,7 @@
         <v>127723091</v>
       </c>
       <c r="B46" t="n">
-        <v>79029</v>
+        <v>79032</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5187,10 +5187,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>127723159</v>
+        <v>127723121</v>
       </c>
       <c r="B47" t="n">
-        <v>79029</v>
+        <v>79032</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5222,10 +5222,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>443314</v>
+        <v>443558</v>
       </c>
       <c r="R47" t="n">
-        <v>6766811</v>
+        <v>6766620</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5284,10 +5284,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>127723110</v>
+        <v>127722868</v>
       </c>
       <c r="B48" t="n">
-        <v>79029</v>
+        <v>57833</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5295,34 +5295,39 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>443479</v>
+        <v>443305</v>
       </c>
       <c r="R48" t="n">
-        <v>6766703</v>
+        <v>6766767</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5381,45 +5386,50 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>127723180</v>
+        <v>127722957</v>
       </c>
       <c r="B49" t="n">
-        <v>79029</v>
+        <v>8450</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>443425</v>
+        <v>443457</v>
       </c>
       <c r="R49" t="n">
-        <v>6766665</v>
+        <v>6766726</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5478,10 +5488,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>127723102</v>
+        <v>127723180</v>
       </c>
       <c r="B50" t="n">
-        <v>79029</v>
+        <v>79032</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5513,10 +5523,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>443556</v>
+        <v>443425</v>
       </c>
       <c r="R50" t="n">
-        <v>6766717</v>
+        <v>6766665</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5575,10 +5585,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>127723185</v>
+        <v>127723110</v>
       </c>
       <c r="B51" t="n">
-        <v>79029</v>
+        <v>79032</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5610,10 +5620,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>443452</v>
+        <v>443479</v>
       </c>
       <c r="R51" t="n">
-        <v>6766711</v>
+        <v>6766703</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5672,10 +5682,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>127722868</v>
+        <v>127723102</v>
       </c>
       <c r="B52" t="n">
-        <v>57832</v>
+        <v>79032</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5683,39 +5693,34 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>443305</v>
+        <v>443556</v>
       </c>
       <c r="R52" t="n">
-        <v>6766767</v>
+        <v>6766717</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5774,50 +5779,45 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>127722957</v>
+        <v>127723185</v>
       </c>
       <c r="B53" t="n">
-        <v>8450</v>
+        <v>79032</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>443457</v>
+        <v>443452</v>
       </c>
       <c r="R53" t="n">
-        <v>6766726</v>
+        <v>6766711</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5876,45 +5876,50 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>127723184</v>
+        <v>127722943</v>
       </c>
       <c r="B54" t="n">
-        <v>79029</v>
+        <v>8450</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P54" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>443446</v>
+        <v>443527</v>
       </c>
       <c r="R54" t="n">
-        <v>6766702</v>
+        <v>6766711</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5973,45 +5978,50 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>127723138</v>
+        <v>127722956</v>
       </c>
       <c r="B55" t="n">
-        <v>79029</v>
+        <v>8450</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>443391</v>
+        <v>443454</v>
       </c>
       <c r="R55" t="n">
-        <v>6766625</v>
+        <v>6766718</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6070,50 +6080,45 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>127722956</v>
+        <v>127723184</v>
       </c>
       <c r="B56" t="n">
-        <v>8450</v>
+        <v>79032</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
-      <c r="M56" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P56" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>443454</v>
+        <v>443446</v>
       </c>
       <c r="R56" t="n">
-        <v>6766718</v>
+        <v>6766702</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6172,50 +6177,45 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>127722943</v>
+        <v>127723138</v>
       </c>
       <c r="B57" t="n">
-        <v>8450</v>
+        <v>79032</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P57" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>443527</v>
+        <v>443391</v>
       </c>
       <c r="R57" t="n">
-        <v>6766711</v>
+        <v>6766625</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6277,7 +6277,7 @@
         <v>127722841</v>
       </c>
       <c r="B58" t="n">
-        <v>79061</v>
+        <v>79064</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6371,10 +6371,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>127723175</v>
+        <v>127723153</v>
       </c>
       <c r="B59" t="n">
-        <v>79029</v>
+        <v>79032</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6406,10 +6406,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>443387</v>
+        <v>443436</v>
       </c>
       <c r="R59" t="n">
-        <v>6766658</v>
+        <v>6766648</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6468,10 +6468,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>127723134</v>
+        <v>127723188</v>
       </c>
       <c r="B60" t="n">
-        <v>79029</v>
+        <v>79032</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6503,10 +6503,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>443465</v>
+        <v>443454</v>
       </c>
       <c r="R60" t="n">
-        <v>6766607</v>
+        <v>6766724</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6565,10 +6565,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>127723106</v>
+        <v>127723134</v>
       </c>
       <c r="B61" t="n">
-        <v>79029</v>
+        <v>79032</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6600,10 +6600,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>443516</v>
+        <v>443465</v>
       </c>
       <c r="R61" t="n">
-        <v>6766720</v>
+        <v>6766607</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6662,10 +6662,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>127723188</v>
+        <v>127723167</v>
       </c>
       <c r="B62" t="n">
-        <v>79029</v>
+        <v>79032</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6697,10 +6697,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>443454</v>
+        <v>443316</v>
       </c>
       <c r="R62" t="n">
-        <v>6766724</v>
+        <v>6766701</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6759,10 +6759,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>127723167</v>
+        <v>127723119</v>
       </c>
       <c r="B63" t="n">
-        <v>79029</v>
+        <v>79032</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6794,10 +6794,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>443316</v>
+        <v>443535</v>
       </c>
       <c r="R63" t="n">
-        <v>6766701</v>
+        <v>6766639</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6856,10 +6856,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>127723153</v>
+        <v>127723106</v>
       </c>
       <c r="B64" t="n">
-        <v>79029</v>
+        <v>79032</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6891,10 +6891,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>443436</v>
+        <v>443516</v>
       </c>
       <c r="R64" t="n">
-        <v>6766648</v>
+        <v>6766720</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -6953,10 +6953,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>127723119</v>
+        <v>127723175</v>
       </c>
       <c r="B65" t="n">
-        <v>79029</v>
+        <v>79032</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6988,10 +6988,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>443535</v>
+        <v>443387</v>
       </c>
       <c r="R65" t="n">
-        <v>6766639</v>
+        <v>6766658</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7050,50 +7050,45 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>127722941</v>
+        <v>127723065</v>
       </c>
       <c r="B66" t="n">
-        <v>8450</v>
+        <v>91521</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>106545</v>
+        <v>1503</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
-      <c r="M66" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P66" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>443557</v>
+        <v>443425</v>
       </c>
       <c r="R66" t="n">
-        <v>6766635</v>
+        <v>6766668</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7152,10 +7147,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>127722847</v>
+        <v>127723158</v>
       </c>
       <c r="B67" t="n">
-        <v>79061</v>
+        <v>79032</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7163,21 +7158,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7187,10 +7182,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>443320</v>
+        <v>443312</v>
       </c>
       <c r="R67" t="n">
-        <v>6766703</v>
+        <v>6766818</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7249,32 +7244,32 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>127723065</v>
+        <v>127723150</v>
       </c>
       <c r="B68" t="n">
-        <v>91513</v>
+        <v>79032</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>1503</v>
+        <v>6425</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7284,10 +7279,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>443425</v>
+        <v>443415</v>
       </c>
       <c r="R68" t="n">
-        <v>6766668</v>
+        <v>6766603</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7346,45 +7341,50 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>127723158</v>
+        <v>127722941</v>
       </c>
       <c r="B69" t="n">
-        <v>79029</v>
+        <v>8450</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P69" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>443312</v>
+        <v>443557</v>
       </c>
       <c r="R69" t="n">
-        <v>6766818</v>
+        <v>6766635</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7443,10 +7443,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>127723150</v>
+        <v>127722847</v>
       </c>
       <c r="B70" t="n">
-        <v>79029</v>
+        <v>79064</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7454,21 +7454,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7478,10 +7478,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>443415</v>
+        <v>443320</v>
       </c>
       <c r="R70" t="n">
-        <v>6766603</v>
+        <v>6766703</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7543,7 +7543,7 @@
         <v>127729137</v>
       </c>
       <c r="B71" t="n">
-        <v>79029</v>
+        <v>79032</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7651,7 +7651,7 @@
         <v>127723177</v>
       </c>
       <c r="B72" t="n">
-        <v>79029</v>
+        <v>79032</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7748,7 +7748,7 @@
         <v>127722839</v>
       </c>
       <c r="B73" t="n">
-        <v>79061</v>
+        <v>79064</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7842,10 +7842,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>127723090</v>
+        <v>127723133</v>
       </c>
       <c r="B74" t="n">
-        <v>79029</v>
+        <v>79032</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7877,10 +7877,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>443593</v>
+        <v>443504</v>
       </c>
       <c r="R74" t="n">
-        <v>6766653</v>
+        <v>6766593</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -7939,10 +7939,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>127723108</v>
+        <v>127723173</v>
       </c>
       <c r="B75" t="n">
-        <v>79029</v>
+        <v>79032</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7974,10 +7974,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>443483</v>
+        <v>443365</v>
       </c>
       <c r="R75" t="n">
-        <v>6766725</v>
+        <v>6766656</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8036,10 +8036,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>127723133</v>
+        <v>127723108</v>
       </c>
       <c r="B76" t="n">
-        <v>79029</v>
+        <v>79032</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8071,10 +8071,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>443504</v>
+        <v>443483</v>
       </c>
       <c r="R76" t="n">
-        <v>6766593</v>
+        <v>6766725</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8133,10 +8133,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>127723173</v>
+        <v>127729092</v>
       </c>
       <c r="B77" t="n">
-        <v>79029</v>
+        <v>78790</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8144,34 +8144,34 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Oxeråsen, Dlr</t>
+          <t>Oxeråsen S. om, Dlr</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>443365</v>
+        <v>443381</v>
       </c>
       <c r="R77" t="n">
-        <v>6766656</v>
+        <v>6766668</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8201,39 +8201,50 @@
           <t>2025-08-21</t>
         </is>
       </c>
+      <c r="Z77" t="inlineStr">
+        <is>
+          <t>13:51</t>
+        </is>
+      </c>
       <c r="AA77" t="inlineStr">
         <is>
           <t>2025-08-21</t>
         </is>
       </c>
+      <c r="AB77" t="inlineStr">
+        <is>
+          <t>13:51</t>
+        </is>
+      </c>
       <c r="AD77" t="b">
         <v>0</v>
       </c>
       <c r="AE77" t="b">
         <v>0</v>
       </c>
+      <c r="AF77" t="inlineStr"/>
       <c r="AG77" t="b">
         <v>0</v>
       </c>
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>127729092</v>
+        <v>127723090</v>
       </c>
       <c r="B78" t="n">
-        <v>78787</v>
+        <v>79032</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8241,34 +8252,34 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Oxeråsen S. om, Dlr</t>
+          <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>443381</v>
+        <v>443593</v>
       </c>
       <c r="R78" t="n">
-        <v>6766668</v>
+        <v>6766653</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8298,50 +8309,39 @@
           <t>2025-08-21</t>
         </is>
       </c>
-      <c r="Z78" t="inlineStr">
-        <is>
-          <t>13:51</t>
-        </is>
-      </c>
       <c r="AA78" t="inlineStr">
         <is>
           <t>2025-08-21</t>
         </is>
       </c>
-      <c r="AB78" t="inlineStr">
-        <is>
-          <t>13:51</t>
-        </is>
-      </c>
       <c r="AD78" t="b">
         <v>0</v>
       </c>
       <c r="AE78" t="b">
         <v>0</v>
       </c>
-      <c r="AF78" t="inlineStr"/>
       <c r="AG78" t="b">
         <v>0</v>
       </c>
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>127723571</v>
+        <v>127723156</v>
       </c>
       <c r="B79" t="n">
-        <v>78696</v>
+        <v>79032</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8349,21 +8349,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8373,10 +8373,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>443426</v>
+        <v>443346</v>
       </c>
       <c r="R79" t="n">
-        <v>6766668</v>
+        <v>6766766</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8435,10 +8435,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>127723104</v>
+        <v>127723571</v>
       </c>
       <c r="B80" t="n">
-        <v>79029</v>
+        <v>78699</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8446,21 +8446,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8470,10 +8470,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>443536</v>
+        <v>443426</v>
       </c>
       <c r="R80" t="n">
-        <v>6766704</v>
+        <v>6766668</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8535,7 +8535,7 @@
         <v>127723120</v>
       </c>
       <c r="B81" t="n">
-        <v>79029</v>
+        <v>79032</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8629,10 +8629,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>127723156</v>
+        <v>127723104</v>
       </c>
       <c r="B82" t="n">
-        <v>79029</v>
+        <v>79032</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8664,10 +8664,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>443346</v>
+        <v>443536</v>
       </c>
       <c r="R82" t="n">
-        <v>6766766</v>
+        <v>6766704</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8726,10 +8726,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>127722888</v>
+        <v>127723570</v>
       </c>
       <c r="B83" t="n">
-        <v>57669</v>
+        <v>78699</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8737,39 +8737,34 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>100049</v>
+        <v>353</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
-      <c r="M83" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P83" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>443481</v>
+        <v>443319</v>
       </c>
       <c r="R83" t="n">
-        <v>6766676</v>
+        <v>6766670</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -8828,10 +8823,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>127722916</v>
+        <v>127723171</v>
       </c>
       <c r="B84" t="n">
-        <v>57672</v>
+        <v>79032</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -8839,29 +8834,24 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
-      <c r="M84" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P84" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
@@ -8871,7 +8861,7 @@
         <v>443342</v>
       </c>
       <c r="R84" t="n">
-        <v>6766806</v>
+        <v>6766650</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -8904,11 +8894,6 @@
       <c r="AA84" t="inlineStr">
         <is>
           <t>2025-08-21</t>
-        </is>
-      </c>
-      <c r="AC84" t="inlineStr">
-        <is>
-          <t>Färska ringhack (gran), 4-5 år gamla</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -8935,10 +8920,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>127723541</v>
+        <v>127723092</v>
       </c>
       <c r="B85" t="n">
-        <v>57672</v>
+        <v>79032</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -8946,39 +8931,34 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
-      <c r="M85" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P85" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>443317</v>
+        <v>443572</v>
       </c>
       <c r="R85" t="n">
-        <v>6766816</v>
+        <v>6766650</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9037,10 +9017,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>127723570</v>
+        <v>127723178</v>
       </c>
       <c r="B86" t="n">
-        <v>78696</v>
+        <v>79032</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9048,21 +9028,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9072,10 +9052,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>443319</v>
+        <v>443402</v>
       </c>
       <c r="R86" t="n">
-        <v>6766670</v>
+        <v>6766682</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9134,10 +9114,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>127723178</v>
+        <v>127722888</v>
       </c>
       <c r="B87" t="n">
-        <v>79029</v>
+        <v>57670</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9145,34 +9125,39 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P87" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>443402</v>
+        <v>443481</v>
       </c>
       <c r="R87" t="n">
-        <v>6766682</v>
+        <v>6766676</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9234,7 +9219,7 @@
         <v>127723116</v>
       </c>
       <c r="B88" t="n">
-        <v>79029</v>
+        <v>79032</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9328,10 +9313,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>127723092</v>
+        <v>127722916</v>
       </c>
       <c r="B89" t="n">
-        <v>79029</v>
+        <v>57673</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9339,34 +9324,39 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P89" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>443572</v>
+        <v>443342</v>
       </c>
       <c r="R89" t="n">
-        <v>6766650</v>
+        <v>6766806</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9399,6 +9389,11 @@
       <c r="AA89" t="inlineStr">
         <is>
           <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AC89" t="inlineStr">
+        <is>
+          <t>Färska ringhack (gran), 4-5 år gamla</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -9425,10 +9420,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>127723171</v>
+        <v>127723541</v>
       </c>
       <c r="B90" t="n">
-        <v>79029</v>
+        <v>57673</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9436,34 +9431,39 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P90" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>443342</v>
+        <v>443317</v>
       </c>
       <c r="R90" t="n">
-        <v>6766650</v>
+        <v>6766816</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9522,10 +9522,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>127723103</v>
+        <v>127723569</v>
       </c>
       <c r="B91" t="n">
-        <v>79029</v>
+        <v>78699</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9533,21 +9533,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -9557,10 +9557,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>443541</v>
+        <v>443332</v>
       </c>
       <c r="R91" t="n">
-        <v>6766696</v>
+        <v>6766677</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9619,10 +9619,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>127723174</v>
+        <v>127723161</v>
       </c>
       <c r="B92" t="n">
-        <v>79029</v>
+        <v>79032</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9654,10 +9654,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>443378</v>
+        <v>443305</v>
       </c>
       <c r="R92" t="n">
-        <v>6766657</v>
+        <v>6766767</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9716,10 +9716,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>127723041</v>
+        <v>127723186</v>
       </c>
       <c r="B93" t="n">
-        <v>78788</v>
+        <v>79032</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9727,21 +9727,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -9751,10 +9751,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>443450</v>
+        <v>443454</v>
       </c>
       <c r="R93" t="n">
-        <v>6766735</v>
+        <v>6766738</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -9813,10 +9813,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>127723569</v>
+        <v>127723114</v>
       </c>
       <c r="B94" t="n">
-        <v>78696</v>
+        <v>79032</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -9824,21 +9824,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -9848,10 +9848,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>443332</v>
+        <v>443487</v>
       </c>
       <c r="R94" t="n">
-        <v>6766677</v>
+        <v>6766651</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -9910,10 +9910,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>127723105</v>
+        <v>127723174</v>
       </c>
       <c r="B95" t="n">
-        <v>79029</v>
+        <v>79032</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -9945,10 +9945,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>443525</v>
+        <v>443378</v>
       </c>
       <c r="R95" t="n">
-        <v>6766717</v>
+        <v>6766657</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10007,10 +10007,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>127723161</v>
+        <v>127723041</v>
       </c>
       <c r="B96" t="n">
-        <v>79029</v>
+        <v>78791</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10018,21 +10018,21 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10042,10 +10042,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>443305</v>
+        <v>443450</v>
       </c>
       <c r="R96" t="n">
-        <v>6766767</v>
+        <v>6766735</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10104,10 +10104,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>127723186</v>
+        <v>127723103</v>
       </c>
       <c r="B97" t="n">
-        <v>79029</v>
+        <v>79032</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10139,10 +10139,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>443454</v>
+        <v>443541</v>
       </c>
       <c r="R97" t="n">
-        <v>6766738</v>
+        <v>6766696</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10201,10 +10201,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>127723114</v>
+        <v>127723105</v>
       </c>
       <c r="B98" t="n">
-        <v>79029</v>
+        <v>79032</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10236,10 +10236,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>443487</v>
+        <v>443525</v>
       </c>
       <c r="R98" t="n">
-        <v>6766651</v>
+        <v>6766717</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10301,7 +10301,7 @@
         <v>127723097</v>
       </c>
       <c r="B99" t="n">
-        <v>79029</v>
+        <v>79032</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10395,10 +10395,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>127722842</v>
+        <v>127723157</v>
       </c>
       <c r="B100" t="n">
-        <v>79061</v>
+        <v>79032</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10406,21 +10406,21 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -10430,10 +10430,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>443504</v>
+        <v>443306</v>
       </c>
       <c r="R100" t="n">
-        <v>6766708</v>
+        <v>6766830</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10492,10 +10492,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>127723170</v>
+        <v>127723139</v>
       </c>
       <c r="B101" t="n">
-        <v>79029</v>
+        <v>79032</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -10527,10 +10527,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>443333</v>
+        <v>443381</v>
       </c>
       <c r="R101" t="n">
-        <v>6766676</v>
+        <v>6766623</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10589,10 +10589,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>127723157</v>
+        <v>127723170</v>
       </c>
       <c r="B102" t="n">
-        <v>79029</v>
+        <v>79032</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -10624,10 +10624,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>443306</v>
+        <v>443333</v>
       </c>
       <c r="R102" t="n">
-        <v>6766830</v>
+        <v>6766676</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -10686,45 +10686,50 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>127723139</v>
+        <v>127722929</v>
       </c>
       <c r="B103" t="n">
-        <v>79029</v>
+        <v>8450</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
+      <c r="M103" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P103" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>443381</v>
+        <v>443327</v>
       </c>
       <c r="R103" t="n">
-        <v>6766623</v>
+        <v>6766698</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -10783,10 +10788,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>127723096</v>
+        <v>127723616</v>
       </c>
       <c r="B104" t="n">
-        <v>79029</v>
+        <v>57673</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -10794,34 +10799,39 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
+      <c r="M104" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
       <c r="P104" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>443554</v>
+        <v>443475</v>
       </c>
       <c r="R104" t="n">
-        <v>6766650</v>
+        <v>6766610</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -10880,10 +10890,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>127723183</v>
+        <v>127723038</v>
       </c>
       <c r="B105" t="n">
-        <v>79029</v>
+        <v>78791</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -10891,21 +10901,21 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -10915,10 +10925,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>443441</v>
+        <v>443328</v>
       </c>
       <c r="R105" t="n">
-        <v>6766686</v>
+        <v>6766721</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -10977,10 +10987,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>127723182</v>
+        <v>127722842</v>
       </c>
       <c r="B106" t="n">
-        <v>79029</v>
+        <v>79064</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -10988,21 +10998,21 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -11012,10 +11022,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>443444</v>
+        <v>443504</v>
       </c>
       <c r="R106" t="n">
-        <v>6766677</v>
+        <v>6766708</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11074,10 +11084,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>127723098</v>
+        <v>127723183</v>
       </c>
       <c r="B107" t="n">
-        <v>79029</v>
+        <v>79032</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11109,10 +11119,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>443562</v>
+        <v>443441</v>
       </c>
       <c r="R107" t="n">
-        <v>6766684</v>
+        <v>6766686</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11171,50 +11181,45 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>127722929</v>
+        <v>127723182</v>
       </c>
       <c r="B108" t="n">
-        <v>8450</v>
+        <v>79032</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
-      <c r="M108" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P108" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>443327</v>
+        <v>443444</v>
       </c>
       <c r="R108" t="n">
-        <v>6766698</v>
+        <v>6766677</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11273,10 +11278,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>127723038</v>
+        <v>127723096</v>
       </c>
       <c r="B109" t="n">
-        <v>78788</v>
+        <v>79032</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11284,21 +11289,21 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -11308,10 +11313,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>443328</v>
+        <v>443554</v>
       </c>
       <c r="R109" t="n">
-        <v>6766721</v>
+        <v>6766650</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11370,10 +11375,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>127723616</v>
+        <v>127723098</v>
       </c>
       <c r="B110" t="n">
-        <v>57672</v>
+        <v>79032</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -11381,39 +11386,34 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
-      <c r="M110" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
       <c r="P110" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>443475</v>
+        <v>443562</v>
       </c>
       <c r="R110" t="n">
-        <v>6766610</v>
+        <v>6766684</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11475,7 +11475,7 @@
         <v>127723137</v>
       </c>
       <c r="B111" t="n">
-        <v>79029</v>
+        <v>79032</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -11572,7 +11572,7 @@
         <v>127723154</v>
       </c>
       <c r="B112" t="n">
-        <v>79029</v>
+        <v>79032</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -11669,7 +11669,7 @@
         <v>127723172</v>
       </c>
       <c r="B113" t="n">
-        <v>79029</v>
+        <v>79032</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -11766,7 +11766,7 @@
         <v>127723136</v>
       </c>
       <c r="B114" t="n">
-        <v>79029</v>
+        <v>79032</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -11863,7 +11863,7 @@
         <v>127723160</v>
       </c>
       <c r="B115" t="n">
-        <v>79029</v>
+        <v>79032</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -11960,7 +11960,7 @@
         <v>127722904</v>
       </c>
       <c r="B116" t="n">
-        <v>57672</v>
+        <v>57673</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -12062,7 +12062,7 @@
         <v>127729086</v>
       </c>
       <c r="B117" t="n">
-        <v>78788</v>
+        <v>78791</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -12167,10 +12167,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>127723176</v>
+        <v>127722903</v>
       </c>
       <c r="B118" t="n">
-        <v>79029</v>
+        <v>57673</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12178,21 +12178,21 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -12202,10 +12202,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>443407</v>
+        <v>443382</v>
       </c>
       <c r="R118" t="n">
-        <v>6766653</v>
+        <v>6766657</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12238,6 +12238,11 @@
       <c r="AA118" t="inlineStr">
         <is>
           <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AC118" t="inlineStr">
+        <is>
+          <t>Äldre ringhack (tall)</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -12264,10 +12269,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>127723135</v>
+        <v>127723163</v>
       </c>
       <c r="B119" t="n">
-        <v>79029</v>
+        <v>79032</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -12299,10 +12304,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>443454</v>
+        <v>443332</v>
       </c>
       <c r="R119" t="n">
-        <v>6766614</v>
+        <v>6766744</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -12364,7 +12369,7 @@
         <v>127723113</v>
       </c>
       <c r="B120" t="n">
-        <v>79029</v>
+        <v>79032</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -12458,10 +12463,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>127722903</v>
+        <v>127723176</v>
       </c>
       <c r="B121" t="n">
-        <v>57672</v>
+        <v>79032</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -12469,21 +12474,21 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -12493,10 +12498,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>443382</v>
+        <v>443407</v>
       </c>
       <c r="R121" t="n">
-        <v>6766657</v>
+        <v>6766653</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -12529,11 +12534,6 @@
       <c r="AA121" t="inlineStr">
         <is>
           <t>2025-08-21</t>
-        </is>
-      </c>
-      <c r="AC121" t="inlineStr">
-        <is>
-          <t>Äldre ringhack (tall)</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -12560,50 +12560,45 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>127722948</v>
+        <v>127723135</v>
       </c>
       <c r="B122" t="n">
-        <v>8450</v>
+        <v>79032</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
-      <c r="M122" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P122" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>443457</v>
+        <v>443454</v>
       </c>
       <c r="R122" t="n">
-        <v>6766613</v>
+        <v>6766614</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -12764,45 +12759,50 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>127723163</v>
+        <v>127722948</v>
       </c>
       <c r="B124" t="n">
-        <v>79029</v>
+        <v>8450</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
+      <c r="M124" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P124" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>443332</v>
+        <v>443457</v>
       </c>
       <c r="R124" t="n">
-        <v>6766744</v>
+        <v>6766613</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -12864,7 +12864,7 @@
         <v>127723037</v>
       </c>
       <c r="B125" t="n">
-        <v>78788</v>
+        <v>78791</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -12958,32 +12958,32 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>127723555</v>
+        <v>127723118</v>
       </c>
       <c r="B126" t="n">
-        <v>92642</v>
+        <v>79032</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -12993,10 +12993,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>443554</v>
+        <v>443519</v>
       </c>
       <c r="R126" t="n">
-        <v>6766667</v>
+        <v>6766624</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -13055,10 +13055,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>127723165</v>
+        <v>127723140</v>
       </c>
       <c r="B127" t="n">
-        <v>79029</v>
+        <v>79032</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -13090,10 +13090,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>443327</v>
+        <v>443370</v>
       </c>
       <c r="R127" t="n">
-        <v>6766717</v>
+        <v>6766624</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -13155,7 +13155,7 @@
         <v>127723094</v>
       </c>
       <c r="B128" t="n">
-        <v>79029</v>
+        <v>79032</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -13249,32 +13249,32 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>127723118</v>
+        <v>127723555</v>
       </c>
       <c r="B129" t="n">
-        <v>79029</v>
+        <v>92650</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
@@ -13284,10 +13284,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>443519</v>
+        <v>443554</v>
       </c>
       <c r="R129" t="n">
-        <v>6766624</v>
+        <v>6766667</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -13346,10 +13346,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>127723140</v>
+        <v>127723165</v>
       </c>
       <c r="B130" t="n">
-        <v>79029</v>
+        <v>79032</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -13381,10 +13381,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>443370</v>
+        <v>443327</v>
       </c>
       <c r="R130" t="n">
-        <v>6766624</v>
+        <v>6766717</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -13443,7 +13443,7 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>127722951</v>
+        <v>127722954</v>
       </c>
       <c r="B131" t="n">
         <v>8450</v>
@@ -13483,10 +13483,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>443377</v>
+        <v>443348</v>
       </c>
       <c r="R131" t="n">
-        <v>6766686</v>
+        <v>6766646</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -13545,7 +13545,7 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>127722954</v>
+        <v>127722951</v>
       </c>
       <c r="B132" t="n">
         <v>8450</v>
@@ -13585,10 +13585,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>443348</v>
+        <v>443377</v>
       </c>
       <c r="R132" t="n">
-        <v>6766646</v>
+        <v>6766686</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -13647,10 +13647,10 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>127723111</v>
+        <v>127723162</v>
       </c>
       <c r="B133" t="n">
-        <v>79029</v>
+        <v>79032</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -13682,10 +13682,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>443474</v>
+        <v>443312</v>
       </c>
       <c r="R133" t="n">
-        <v>6766692</v>
+        <v>6766762</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -13744,10 +13744,10 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>127723162</v>
+        <v>127723111</v>
       </c>
       <c r="B134" t="n">
-        <v>79029</v>
+        <v>79032</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -13779,10 +13779,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>443312</v>
+        <v>443474</v>
       </c>
       <c r="R134" t="n">
-        <v>6766762</v>
+        <v>6766692</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -13844,7 +13844,7 @@
         <v>127722855</v>
       </c>
       <c r="B135" t="n">
-        <v>79618</v>
+        <v>79621</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -13941,7 +13941,7 @@
         <v>127723619</v>
       </c>
       <c r="B136" t="n">
-        <v>57672</v>
+        <v>57673</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -14048,7 +14048,7 @@
         <v>127736007</v>
       </c>
       <c r="B137" t="n">
-        <v>91372</v>
+        <v>91380</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -14155,7 +14155,7 @@
         <v>127736019</v>
       </c>
       <c r="B138" t="n">
-        <v>79029</v>
+        <v>79032</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -14262,7 +14262,7 @@
         <v>127785482</v>
       </c>
       <c r="B139" t="n">
-        <v>79029</v>
+        <v>79032</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -14369,7 +14369,7 @@
         <v>127785478</v>
       </c>
       <c r="B140" t="n">
-        <v>79029</v>
+        <v>79032</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -14482,7 +14482,7 @@
         <v>127785484</v>
       </c>
       <c r="B141" t="n">
-        <v>79029</v>
+        <v>79032</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -14589,7 +14589,7 @@
         <v>127785481</v>
       </c>
       <c r="B142" t="n">
-        <v>79029</v>
+        <v>79032</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -14696,7 +14696,7 @@
         <v>127785483</v>
       </c>
       <c r="B143" t="n">
-        <v>79029</v>
+        <v>79032</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -14803,7 +14803,7 @@
         <v>127785472</v>
       </c>
       <c r="B144" t="n">
-        <v>91372</v>
+        <v>91380</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -15017,7 +15017,7 @@
         <v>127795299</v>
       </c>
       <c r="B146" t="n">
-        <v>78787</v>
+        <v>78790</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -15118,7 +15118,7 @@
         <v>127795339</v>
       </c>
       <c r="B147" t="n">
-        <v>79029</v>
+        <v>79032</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>

--- a/artfynd/A 35484-2025 artfynd.xlsx
+++ b/artfynd/A 35484-2025 artfynd.xlsx
@@ -2431,45 +2431,50 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127723093</v>
+        <v>127722947</v>
       </c>
       <c r="B19" t="n">
-        <v>79032</v>
+        <v>8450</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>443572</v>
+        <v>443486</v>
       </c>
       <c r="R19" t="n">
-        <v>6766645</v>
+        <v>6766604</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2528,45 +2533,50 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127723099</v>
+        <v>127722942</v>
       </c>
       <c r="B20" t="n">
-        <v>79032</v>
+        <v>8450</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>443567</v>
+        <v>443542</v>
       </c>
       <c r="R20" t="n">
-        <v>6766695</v>
+        <v>6766699</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2625,50 +2635,45 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127722947</v>
+        <v>127723093</v>
       </c>
       <c r="B21" t="n">
-        <v>8450</v>
+        <v>79032</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>443486</v>
+        <v>443572</v>
       </c>
       <c r="R21" t="n">
-        <v>6766604</v>
+        <v>6766645</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2727,50 +2732,45 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127722942</v>
+        <v>127723099</v>
       </c>
       <c r="B22" t="n">
-        <v>8450</v>
+        <v>79032</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>443542</v>
+        <v>443567</v>
       </c>
       <c r="R22" t="n">
-        <v>6766699</v>
+        <v>6766695</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2829,10 +2829,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127723166</v>
+        <v>127723040</v>
       </c>
       <c r="B23" t="n">
-        <v>79032</v>
+        <v>78791</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2840,21 +2840,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2864,10 +2864,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>443326</v>
+        <v>443377</v>
       </c>
       <c r="R23" t="n">
-        <v>6766711</v>
+        <v>6766659</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2926,7 +2926,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127723040</v>
+        <v>127723039</v>
       </c>
       <c r="B24" t="n">
         <v>78791</v>
@@ -2961,10 +2961,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>443377</v>
+        <v>443356</v>
       </c>
       <c r="R24" t="n">
-        <v>6766659</v>
+        <v>6766650</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3023,42 +3023,47 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127723039</v>
+        <v>127722950</v>
       </c>
       <c r="B25" t="n">
-        <v>78791</v>
+        <v>8450</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>228912</v>
+        <v>106545</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>443356</v>
+        <v>443438</v>
       </c>
       <c r="R25" t="n">
         <v>6766650</v>
@@ -3120,50 +3125,45 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127722950</v>
+        <v>127722874</v>
       </c>
       <c r="B26" t="n">
-        <v>8450</v>
+        <v>91380</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>106545</v>
+        <v>5442</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>443438</v>
+        <v>443388</v>
       </c>
       <c r="R26" t="n">
-        <v>6766650</v>
+        <v>6766675</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3222,10 +3222,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127722874</v>
+        <v>127723112</v>
       </c>
       <c r="B27" t="n">
-        <v>91380</v>
+        <v>79032</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3233,21 +3233,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3257,10 +3257,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>443388</v>
+        <v>443476</v>
       </c>
       <c r="R27" t="n">
-        <v>6766675</v>
+        <v>6766681</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3319,7 +3319,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127723112</v>
+        <v>127723181</v>
       </c>
       <c r="B28" t="n">
         <v>79032</v>
@@ -3354,10 +3354,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>443476</v>
+        <v>443436</v>
       </c>
       <c r="R28" t="n">
-        <v>6766681</v>
+        <v>6766667</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3416,7 +3416,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127723181</v>
+        <v>127723166</v>
       </c>
       <c r="B29" t="n">
         <v>79032</v>
@@ -3451,10 +3451,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>443436</v>
+        <v>443326</v>
       </c>
       <c r="R29" t="n">
-        <v>6766667</v>
+        <v>6766711</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -5284,10 +5284,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>127722868</v>
+        <v>127723180</v>
       </c>
       <c r="B48" t="n">
-        <v>57833</v>
+        <v>79032</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5295,39 +5295,34 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>443305</v>
+        <v>443425</v>
       </c>
       <c r="R48" t="n">
-        <v>6766767</v>
+        <v>6766665</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5386,50 +5381,45 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>127722957</v>
+        <v>127723110</v>
       </c>
       <c r="B49" t="n">
-        <v>8450</v>
+        <v>79032</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>443457</v>
+        <v>443479</v>
       </c>
       <c r="R49" t="n">
-        <v>6766726</v>
+        <v>6766703</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5488,7 +5478,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>127723180</v>
+        <v>127723102</v>
       </c>
       <c r="B50" t="n">
         <v>79032</v>
@@ -5523,10 +5513,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>443425</v>
+        <v>443556</v>
       </c>
       <c r="R50" t="n">
-        <v>6766665</v>
+        <v>6766717</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5585,7 +5575,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>127723110</v>
+        <v>127723185</v>
       </c>
       <c r="B51" t="n">
         <v>79032</v>
@@ -5620,10 +5610,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>443479</v>
+        <v>443452</v>
       </c>
       <c r="R51" t="n">
-        <v>6766703</v>
+        <v>6766711</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5682,10 +5672,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>127723102</v>
+        <v>127722868</v>
       </c>
       <c r="B52" t="n">
-        <v>79032</v>
+        <v>57833</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5693,34 +5683,39 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>443556</v>
+        <v>443305</v>
       </c>
       <c r="R52" t="n">
-        <v>6766717</v>
+        <v>6766767</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5779,45 +5774,50 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>127723185</v>
+        <v>127722957</v>
       </c>
       <c r="B53" t="n">
-        <v>79032</v>
+        <v>8450</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>443452</v>
+        <v>443457</v>
       </c>
       <c r="R53" t="n">
-        <v>6766711</v>
+        <v>6766726</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6371,7 +6371,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>127723153</v>
+        <v>127723167</v>
       </c>
       <c r="B59" t="n">
         <v>79032</v>
@@ -6406,10 +6406,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>443436</v>
+        <v>443316</v>
       </c>
       <c r="R59" t="n">
-        <v>6766648</v>
+        <v>6766701</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6468,7 +6468,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>127723188</v>
+        <v>127723119</v>
       </c>
       <c r="B60" t="n">
         <v>79032</v>
@@ -6503,10 +6503,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>443454</v>
+        <v>443535</v>
       </c>
       <c r="R60" t="n">
-        <v>6766724</v>
+        <v>6766639</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6565,7 +6565,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>127723134</v>
+        <v>127723106</v>
       </c>
       <c r="B61" t="n">
         <v>79032</v>
@@ -6600,10 +6600,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>443465</v>
+        <v>443516</v>
       </c>
       <c r="R61" t="n">
-        <v>6766607</v>
+        <v>6766720</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6662,7 +6662,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>127723167</v>
+        <v>127723175</v>
       </c>
       <c r="B62" t="n">
         <v>79032</v>
@@ -6697,10 +6697,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>443316</v>
+        <v>443387</v>
       </c>
       <c r="R62" t="n">
-        <v>6766701</v>
+        <v>6766658</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6759,7 +6759,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>127723119</v>
+        <v>127723153</v>
       </c>
       <c r="B63" t="n">
         <v>79032</v>
@@ -6794,10 +6794,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>443535</v>
+        <v>443436</v>
       </c>
       <c r="R63" t="n">
-        <v>6766639</v>
+        <v>6766648</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6856,7 +6856,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>127723106</v>
+        <v>127723188</v>
       </c>
       <c r="B64" t="n">
         <v>79032</v>
@@ -6891,10 +6891,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>443516</v>
+        <v>443454</v>
       </c>
       <c r="R64" t="n">
-        <v>6766720</v>
+        <v>6766724</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -6953,7 +6953,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>127723175</v>
+        <v>127723134</v>
       </c>
       <c r="B65" t="n">
         <v>79032</v>
@@ -6988,10 +6988,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>443387</v>
+        <v>443465</v>
       </c>
       <c r="R65" t="n">
-        <v>6766658</v>
+        <v>6766607</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7050,32 +7050,32 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>127723065</v>
+        <v>127722847</v>
       </c>
       <c r="B66" t="n">
-        <v>91521</v>
+        <v>79064</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>1503</v>
+        <v>185</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7085,10 +7085,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>443425</v>
+        <v>443320</v>
       </c>
       <c r="R66" t="n">
-        <v>6766668</v>
+        <v>6766703</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7147,7 +7147,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>127723158</v>
+        <v>127729137</v>
       </c>
       <c r="B67" t="n">
         <v>79032</v>
@@ -7178,14 +7178,14 @@
       <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Oxeråsen, Dlr</t>
+          <t>Oxeråsen S. om, Dlr</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>443312</v>
+        <v>443391</v>
       </c>
       <c r="R67" t="n">
-        <v>6766818</v>
+        <v>6766598</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7215,61 +7215,72 @@
           <t>2025-08-21</t>
         </is>
       </c>
+      <c r="Z67" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-08-21</t>
         </is>
       </c>
+      <c r="AB67" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
       <c r="AD67" t="b">
         <v>0</v>
       </c>
       <c r="AE67" t="b">
         <v>0</v>
       </c>
+      <c r="AF67" t="inlineStr"/>
       <c r="AG67" t="b">
         <v>0</v>
       </c>
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>127723150</v>
+        <v>127723065</v>
       </c>
       <c r="B68" t="n">
-        <v>79032</v>
+        <v>91521</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6425</v>
+        <v>1503</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7279,10 +7290,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>443415</v>
+        <v>443425</v>
       </c>
       <c r="R68" t="n">
-        <v>6766603</v>
+        <v>6766668</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7341,50 +7352,45 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>127722941</v>
+        <v>127723177</v>
       </c>
       <c r="B69" t="n">
-        <v>8450</v>
+        <v>79032</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
-      <c r="M69" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P69" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>443557</v>
+        <v>443397</v>
       </c>
       <c r="R69" t="n">
-        <v>6766635</v>
+        <v>6766673</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7443,10 +7449,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>127722847</v>
+        <v>127723158</v>
       </c>
       <c r="B70" t="n">
-        <v>79064</v>
+        <v>79032</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7454,21 +7460,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7478,10 +7484,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>443320</v>
+        <v>443312</v>
       </c>
       <c r="R70" t="n">
-        <v>6766703</v>
+        <v>6766818</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7540,7 +7546,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>127729137</v>
+        <v>127723150</v>
       </c>
       <c r="B71" t="n">
         <v>79032</v>
@@ -7571,14 +7577,14 @@
       <c r="I71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Oxeråsen S. om, Dlr</t>
+          <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>443391</v>
+        <v>443415</v>
       </c>
       <c r="R71" t="n">
-        <v>6766598</v>
+        <v>6766603</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7608,85 +7614,79 @@
           <t>2025-08-21</t>
         </is>
       </c>
-      <c r="Z71" t="inlineStr">
-        <is>
-          <t>14:00</t>
-        </is>
-      </c>
       <c r="AA71" t="inlineStr">
         <is>
           <t>2025-08-21</t>
         </is>
       </c>
-      <c r="AB71" t="inlineStr">
-        <is>
-          <t>14:00</t>
-        </is>
-      </c>
       <c r="AD71" t="b">
         <v>0</v>
       </c>
       <c r="AE71" t="b">
         <v>0</v>
       </c>
-      <c r="AF71" t="inlineStr"/>
       <c r="AG71" t="b">
         <v>0</v>
       </c>
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>127723177</v>
+        <v>127722941</v>
       </c>
       <c r="B72" t="n">
-        <v>79032</v>
+        <v>8450</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P72" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>443397</v>
+        <v>443557</v>
       </c>
       <c r="R72" t="n">
-        <v>6766673</v>
+        <v>6766635</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8726,10 +8726,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>127723570</v>
+        <v>127723171</v>
       </c>
       <c r="B83" t="n">
-        <v>78699</v>
+        <v>79032</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8737,21 +8737,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -8761,10 +8761,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>443319</v>
+        <v>443342</v>
       </c>
       <c r="R83" t="n">
-        <v>6766670</v>
+        <v>6766650</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -8823,7 +8823,7 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>127723171</v>
+        <v>127723116</v>
       </c>
       <c r="B84" t="n">
         <v>79032</v>
@@ -8858,10 +8858,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>443342</v>
+        <v>443509</v>
       </c>
       <c r="R84" t="n">
-        <v>6766650</v>
+        <v>6766633</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9114,10 +9114,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>127722888</v>
+        <v>127722916</v>
       </c>
       <c r="B87" t="n">
-        <v>57670</v>
+        <v>57673</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9125,16 +9125,16 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
@@ -9145,7 +9145,7 @@
       <c r="I87" t="inlineStr"/>
       <c r="M87" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P87" t="inlineStr">
@@ -9154,10 +9154,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>443481</v>
+        <v>443342</v>
       </c>
       <c r="R87" t="n">
-        <v>6766676</v>
+        <v>6766806</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9190,6 +9190,11 @@
       <c r="AA87" t="inlineStr">
         <is>
           <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AC87" t="inlineStr">
+        <is>
+          <t>Färska ringhack (gran), 4-5 år gamla</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9216,10 +9221,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>127723116</v>
+        <v>127723541</v>
       </c>
       <c r="B88" t="n">
-        <v>79032</v>
+        <v>57673</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9227,34 +9232,39 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P88" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>443509</v>
+        <v>443317</v>
       </c>
       <c r="R88" t="n">
-        <v>6766633</v>
+        <v>6766816</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9313,10 +9323,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>127722916</v>
+        <v>127723570</v>
       </c>
       <c r="B89" t="n">
-        <v>57673</v>
+        <v>78699</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9324,39 +9334,34 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>100109</v>
+        <v>353</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
-      <c r="M89" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P89" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>443342</v>
+        <v>443319</v>
       </c>
       <c r="R89" t="n">
-        <v>6766806</v>
+        <v>6766670</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9389,11 +9394,6 @@
       <c r="AA89" t="inlineStr">
         <is>
           <t>2025-08-21</t>
-        </is>
-      </c>
-      <c r="AC89" t="inlineStr">
-        <is>
-          <t>Färska ringhack (gran), 4-5 år gamla</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -9420,10 +9420,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>127723541</v>
+        <v>127722888</v>
       </c>
       <c r="B90" t="n">
-        <v>57673</v>
+        <v>57670</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9431,16 +9431,16 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
@@ -9451,7 +9451,7 @@
       <c r="I90" t="inlineStr"/>
       <c r="M90" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P90" t="inlineStr">
@@ -9460,10 +9460,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>443317</v>
+        <v>443481</v>
       </c>
       <c r="R90" t="n">
-        <v>6766816</v>
+        <v>6766676</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10395,45 +10395,50 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>127723157</v>
+        <v>127722929</v>
       </c>
       <c r="B100" t="n">
-        <v>79032</v>
+        <v>8450</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
+      <c r="M100" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P100" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>443306</v>
+        <v>443327</v>
       </c>
       <c r="R100" t="n">
-        <v>6766830</v>
+        <v>6766698</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10492,7 +10497,7 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>127723139</v>
+        <v>127723157</v>
       </c>
       <c r="B101" t="n">
         <v>79032</v>
@@ -10527,10 +10532,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>443381</v>
+        <v>443306</v>
       </c>
       <c r="R101" t="n">
-        <v>6766623</v>
+        <v>6766830</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10589,7 +10594,7 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>127723170</v>
+        <v>127723139</v>
       </c>
       <c r="B102" t="n">
         <v>79032</v>
@@ -10624,10 +10629,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>443333</v>
+        <v>443381</v>
       </c>
       <c r="R102" t="n">
-        <v>6766676</v>
+        <v>6766623</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -10686,50 +10691,45 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>127722929</v>
+        <v>127723170</v>
       </c>
       <c r="B103" t="n">
-        <v>8450</v>
+        <v>79032</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
-      <c r="M103" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P103" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>443327</v>
+        <v>443333</v>
       </c>
       <c r="R103" t="n">
-        <v>6766698</v>
+        <v>6766676</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -12167,10 +12167,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>127722903</v>
+        <v>127723176</v>
       </c>
       <c r="B118" t="n">
-        <v>57673</v>
+        <v>79032</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12178,21 +12178,21 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -12202,10 +12202,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>443382</v>
+        <v>443407</v>
       </c>
       <c r="R118" t="n">
-        <v>6766657</v>
+        <v>6766653</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12238,11 +12238,6 @@
       <c r="AA118" t="inlineStr">
         <is>
           <t>2025-08-21</t>
-        </is>
-      </c>
-      <c r="AC118" t="inlineStr">
-        <is>
-          <t>Äldre ringhack (tall)</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -12269,7 +12264,7 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>127723163</v>
+        <v>127723135</v>
       </c>
       <c r="B119" t="n">
         <v>79032</v>
@@ -12304,10 +12299,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>443332</v>
+        <v>443454</v>
       </c>
       <c r="R119" t="n">
-        <v>6766744</v>
+        <v>6766614</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -12366,10 +12361,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>127723113</v>
+        <v>127722903</v>
       </c>
       <c r="B120" t="n">
-        <v>79032</v>
+        <v>57673</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -12377,21 +12372,21 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -12401,10 +12396,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>443487</v>
+        <v>443382</v>
       </c>
       <c r="R120" t="n">
-        <v>6766675</v>
+        <v>6766657</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -12437,6 +12432,11 @@
       <c r="AA120" t="inlineStr">
         <is>
           <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AC120" t="inlineStr">
+        <is>
+          <t>Äldre ringhack (tall)</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -12463,42 +12463,47 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>127723176</v>
+        <v>127722955</v>
       </c>
       <c r="B121" t="n">
-        <v>79032</v>
+        <v>8450</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
+      <c r="M121" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P121" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>443407</v>
+        <v>443397</v>
       </c>
       <c r="R121" t="n">
         <v>6766653</v>
@@ -12560,45 +12565,50 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>127723135</v>
+        <v>127722948</v>
       </c>
       <c r="B122" t="n">
-        <v>79032</v>
+        <v>8450</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
+      <c r="M122" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P122" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>443454</v>
+        <v>443457</v>
       </c>
       <c r="R122" t="n">
-        <v>6766614</v>
+        <v>6766613</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -12657,50 +12667,45 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>127722955</v>
+        <v>127723163</v>
       </c>
       <c r="B123" t="n">
-        <v>8450</v>
+        <v>79032</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
-      <c r="M123" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P123" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>443397</v>
+        <v>443332</v>
       </c>
       <c r="R123" t="n">
-        <v>6766653</v>
+        <v>6766744</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -12759,50 +12764,45 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>127722948</v>
+        <v>127723113</v>
       </c>
       <c r="B124" t="n">
-        <v>8450</v>
+        <v>79032</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
-      <c r="M124" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P124" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>443457</v>
+        <v>443487</v>
       </c>
       <c r="R124" t="n">
-        <v>6766613</v>
+        <v>6766675</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>

--- a/artfynd/A 35484-2025 artfynd.xlsx
+++ b/artfynd/A 35484-2025 artfynd.xlsx
@@ -1839,50 +1839,45 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127722932</v>
+        <v>127723164</v>
       </c>
       <c r="B13" t="n">
-        <v>8450</v>
+        <v>79043</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>443590</v>
+        <v>443329</v>
       </c>
       <c r="R13" t="n">
-        <v>6766651</v>
+        <v>6766739</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1941,10 +1936,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127723164</v>
+        <v>127723117</v>
       </c>
       <c r="B14" t="n">
-        <v>79032</v>
+        <v>79043</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1976,10 +1971,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>443329</v>
+        <v>443514</v>
       </c>
       <c r="R14" t="n">
-        <v>6766739</v>
+        <v>6766630</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2038,10 +2033,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127723117</v>
+        <v>127723151</v>
       </c>
       <c r="B15" t="n">
-        <v>79032</v>
+        <v>79043</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2073,10 +2068,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>443514</v>
+        <v>443430</v>
       </c>
       <c r="R15" t="n">
-        <v>6766630</v>
+        <v>6766608</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2135,45 +2130,50 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127723151</v>
+        <v>127722932</v>
       </c>
       <c r="B16" t="n">
-        <v>79032</v>
+        <v>8450</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>443430</v>
+        <v>443590</v>
       </c>
       <c r="R16" t="n">
-        <v>6766608</v>
+        <v>6766651</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2235,7 +2235,7 @@
         <v>127723187</v>
       </c>
       <c r="B17" t="n">
-        <v>79032</v>
+        <v>79043</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2332,7 +2332,7 @@
         <v>127722870</v>
       </c>
       <c r="B18" t="n">
-        <v>57833</v>
+        <v>57844</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2431,50 +2431,45 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127722947</v>
+        <v>127723093</v>
       </c>
       <c r="B19" t="n">
-        <v>8450</v>
+        <v>79043</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>443486</v>
+        <v>443572</v>
       </c>
       <c r="R19" t="n">
-        <v>6766604</v>
+        <v>6766645</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2533,50 +2528,45 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127722942</v>
+        <v>127723099</v>
       </c>
       <c r="B20" t="n">
-        <v>8450</v>
+        <v>79043</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>443542</v>
+        <v>443567</v>
       </c>
       <c r="R20" t="n">
-        <v>6766699</v>
+        <v>6766695</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2635,45 +2625,50 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127723093</v>
+        <v>127722947</v>
       </c>
       <c r="B21" t="n">
-        <v>79032</v>
+        <v>8450</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>443572</v>
+        <v>443486</v>
       </c>
       <c r="R21" t="n">
-        <v>6766645</v>
+        <v>6766604</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2732,45 +2727,50 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127723099</v>
+        <v>127722942</v>
       </c>
       <c r="B22" t="n">
-        <v>79032</v>
+        <v>8450</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>443567</v>
+        <v>443542</v>
       </c>
       <c r="R22" t="n">
-        <v>6766695</v>
+        <v>6766699</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2829,10 +2829,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127723040</v>
+        <v>127722874</v>
       </c>
       <c r="B23" t="n">
-        <v>78791</v>
+        <v>91391</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2840,21 +2840,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>228912</v>
+        <v>5442</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2864,10 +2864,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>443377</v>
+        <v>443388</v>
       </c>
       <c r="R23" t="n">
-        <v>6766659</v>
+        <v>6766675</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2926,10 +2926,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127723039</v>
+        <v>127723112</v>
       </c>
       <c r="B24" t="n">
-        <v>78791</v>
+        <v>79043</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2937,21 +2937,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2961,10 +2961,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>443356</v>
+        <v>443476</v>
       </c>
       <c r="R24" t="n">
-        <v>6766650</v>
+        <v>6766681</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3023,50 +3023,45 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127722950</v>
+        <v>127723166</v>
       </c>
       <c r="B25" t="n">
-        <v>8450</v>
+        <v>79043</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>443438</v>
+        <v>443326</v>
       </c>
       <c r="R25" t="n">
-        <v>6766650</v>
+        <v>6766711</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3125,45 +3120,50 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127722874</v>
+        <v>127722950</v>
       </c>
       <c r="B26" t="n">
-        <v>91380</v>
+        <v>8450</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>5442</v>
+        <v>106545</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>443388</v>
+        <v>443438</v>
       </c>
       <c r="R26" t="n">
-        <v>6766675</v>
+        <v>6766650</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3222,10 +3222,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127723112</v>
+        <v>127723181</v>
       </c>
       <c r="B27" t="n">
-        <v>79032</v>
+        <v>79043</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3257,10 +3257,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>443476</v>
+        <v>443436</v>
       </c>
       <c r="R27" t="n">
-        <v>6766681</v>
+        <v>6766667</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3319,10 +3319,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127723181</v>
+        <v>127723040</v>
       </c>
       <c r="B28" t="n">
-        <v>79032</v>
+        <v>78802</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3330,21 +3330,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3354,10 +3354,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>443436</v>
+        <v>443377</v>
       </c>
       <c r="R28" t="n">
-        <v>6766667</v>
+        <v>6766659</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3416,10 +3416,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127723166</v>
+        <v>127723039</v>
       </c>
       <c r="B29" t="n">
-        <v>79032</v>
+        <v>78802</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3427,21 +3427,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3451,10 +3451,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>443326</v>
+        <v>443356</v>
       </c>
       <c r="R29" t="n">
-        <v>6766711</v>
+        <v>6766650</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3513,50 +3513,45 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127722945</v>
+        <v>127722875</v>
       </c>
       <c r="B30" t="n">
-        <v>8450</v>
+        <v>91391</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>106545</v>
+        <v>5442</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>443568</v>
+        <v>443312</v>
       </c>
       <c r="R30" t="n">
-        <v>6766605</v>
+        <v>6766713</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3615,10 +3610,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127722875</v>
+        <v>127723179</v>
       </c>
       <c r="B31" t="n">
-        <v>91380</v>
+        <v>79043</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3626,21 +3621,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3650,10 +3645,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>443312</v>
+        <v>443411</v>
       </c>
       <c r="R31" t="n">
-        <v>6766713</v>
+        <v>6766676</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3715,7 +3710,7 @@
         <v>127723152</v>
       </c>
       <c r="B32" t="n">
-        <v>79032</v>
+        <v>79043</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3809,45 +3804,50 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127723179</v>
+        <v>127722945</v>
       </c>
       <c r="B33" t="n">
-        <v>79032</v>
+        <v>8450</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>443411</v>
+        <v>443568</v>
       </c>
       <c r="R33" t="n">
-        <v>6766676</v>
+        <v>6766605</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3906,32 +3906,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>127722921</v>
+        <v>127723107</v>
       </c>
       <c r="B34" t="n">
-        <v>97355</v>
+        <v>79043</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3941,10 +3941,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>443330</v>
+        <v>443493</v>
       </c>
       <c r="R34" t="n">
-        <v>6766662</v>
+        <v>6766717</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4003,10 +4003,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127723107</v>
+        <v>127723109</v>
       </c>
       <c r="B35" t="n">
-        <v>79032</v>
+        <v>79043</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4038,10 +4038,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>443493</v>
+        <v>443482</v>
       </c>
       <c r="R35" t="n">
-        <v>6766717</v>
+        <v>6766716</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4100,10 +4100,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127723109</v>
+        <v>127723115</v>
       </c>
       <c r="B36" t="n">
-        <v>79032</v>
+        <v>79043</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4135,10 +4135,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>443482</v>
+        <v>443495</v>
       </c>
       <c r="R36" t="n">
-        <v>6766716</v>
+        <v>6766641</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4200,7 +4200,7 @@
         <v>127723169</v>
       </c>
       <c r="B37" t="n">
-        <v>79032</v>
+        <v>79043</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4294,10 +4294,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127723115</v>
+        <v>127722896</v>
       </c>
       <c r="B38" t="n">
-        <v>79032</v>
+        <v>57681</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4305,34 +4305,39 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>443495</v>
+        <v>443537</v>
       </c>
       <c r="R38" t="n">
-        <v>6766641</v>
+        <v>6766699</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4391,38 +4396,38 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127722896</v>
+        <v>127722944</v>
       </c>
       <c r="B39" t="n">
-        <v>57670</v>
+        <v>8450</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="M39" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
@@ -4431,10 +4436,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>443537</v>
+        <v>443488</v>
       </c>
       <c r="R39" t="n">
-        <v>6766699</v>
+        <v>6766671</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4493,7 +4498,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127722944</v>
+        <v>127722928</v>
       </c>
       <c r="B40" t="n">
         <v>8450</v>
@@ -4524,7 +4529,7 @@
       <c r="I40" t="inlineStr"/>
       <c r="M40" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
@@ -4533,10 +4538,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>443488</v>
+        <v>443559</v>
       </c>
       <c r="R40" t="n">
-        <v>6766671</v>
+        <v>6766616</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4595,10 +4600,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127722928</v>
+        <v>127722921</v>
       </c>
       <c r="B41" t="n">
-        <v>8450</v>
+        <v>97367</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4606,39 +4611,34 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>106545</v>
+        <v>221945</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>443559</v>
+        <v>443330</v>
       </c>
       <c r="R41" t="n">
-        <v>6766616</v>
+        <v>6766662</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4697,10 +4697,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>127723159</v>
+        <v>127723189</v>
       </c>
       <c r="B42" t="n">
-        <v>79032</v>
+        <v>79043</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4732,10 +4732,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>443314</v>
+        <v>443446</v>
       </c>
       <c r="R42" t="n">
-        <v>6766811</v>
+        <v>6766727</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4768,6 +4768,11 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Med grov gran i bäckmiljö</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4794,10 +4799,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127723189</v>
+        <v>127723121</v>
       </c>
       <c r="B43" t="n">
-        <v>79032</v>
+        <v>79043</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4829,10 +4834,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>443446</v>
+        <v>443558</v>
       </c>
       <c r="R43" t="n">
-        <v>6766727</v>
+        <v>6766620</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4865,11 +4870,6 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-08-21</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Med grov gran i bäckmiljö</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -4899,7 +4899,7 @@
         <v>127722876</v>
       </c>
       <c r="B44" t="n">
-        <v>91380</v>
+        <v>91391</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4996,7 +4996,7 @@
         <v>127723064</v>
       </c>
       <c r="B45" t="n">
-        <v>91521</v>
+        <v>91532</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5093,7 +5093,7 @@
         <v>127723091</v>
       </c>
       <c r="B46" t="n">
-        <v>79032</v>
+        <v>79043</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5187,10 +5187,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>127723121</v>
+        <v>127723159</v>
       </c>
       <c r="B47" t="n">
-        <v>79032</v>
+        <v>79043</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5222,10 +5222,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>443558</v>
+        <v>443314</v>
       </c>
       <c r="R47" t="n">
-        <v>6766620</v>
+        <v>6766811</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5287,7 +5287,7 @@
         <v>127723180</v>
       </c>
       <c r="B48" t="n">
-        <v>79032</v>
+        <v>79043</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5381,10 +5381,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>127723110</v>
+        <v>127723185</v>
       </c>
       <c r="B49" t="n">
-        <v>79032</v>
+        <v>79043</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5416,10 +5416,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>443479</v>
+        <v>443452</v>
       </c>
       <c r="R49" t="n">
-        <v>6766703</v>
+        <v>6766711</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5478,10 +5478,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>127723102</v>
+        <v>127723110</v>
       </c>
       <c r="B50" t="n">
-        <v>79032</v>
+        <v>79043</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5513,10 +5513,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>443556</v>
+        <v>443479</v>
       </c>
       <c r="R50" t="n">
-        <v>6766717</v>
+        <v>6766703</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5575,10 +5575,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>127723185</v>
+        <v>127723102</v>
       </c>
       <c r="B51" t="n">
-        <v>79032</v>
+        <v>79043</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5610,10 +5610,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>443452</v>
+        <v>443556</v>
       </c>
       <c r="R51" t="n">
-        <v>6766711</v>
+        <v>6766717</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5675,7 +5675,7 @@
         <v>127722868</v>
       </c>
       <c r="B52" t="n">
-        <v>57833</v>
+        <v>57844</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6083,7 +6083,7 @@
         <v>127723184</v>
       </c>
       <c r="B56" t="n">
-        <v>79032</v>
+        <v>79043</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6180,7 +6180,7 @@
         <v>127723138</v>
       </c>
       <c r="B57" t="n">
-        <v>79032</v>
+        <v>79043</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6274,10 +6274,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>127722841</v>
+        <v>127723167</v>
       </c>
       <c r="B58" t="n">
-        <v>79064</v>
+        <v>79043</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6285,21 +6285,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6309,10 +6309,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>443568</v>
+        <v>443316</v>
       </c>
       <c r="R58" t="n">
-        <v>6766695</v>
+        <v>6766701</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6371,10 +6371,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>127723167</v>
+        <v>127723153</v>
       </c>
       <c r="B59" t="n">
-        <v>79032</v>
+        <v>79043</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6406,10 +6406,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>443316</v>
+        <v>443436</v>
       </c>
       <c r="R59" t="n">
-        <v>6766701</v>
+        <v>6766648</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6471,7 +6471,7 @@
         <v>127723119</v>
       </c>
       <c r="B60" t="n">
-        <v>79032</v>
+        <v>79043</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6565,10 +6565,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>127723106</v>
+        <v>127723188</v>
       </c>
       <c r="B61" t="n">
-        <v>79032</v>
+        <v>79043</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6600,10 +6600,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>443516</v>
+        <v>443454</v>
       </c>
       <c r="R61" t="n">
-        <v>6766720</v>
+        <v>6766724</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6665,7 +6665,7 @@
         <v>127723175</v>
       </c>
       <c r="B62" t="n">
-        <v>79032</v>
+        <v>79043</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6759,10 +6759,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>127723153</v>
+        <v>127723134</v>
       </c>
       <c r="B63" t="n">
-        <v>79032</v>
+        <v>79043</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6794,10 +6794,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>443436</v>
+        <v>443465</v>
       </c>
       <c r="R63" t="n">
-        <v>6766648</v>
+        <v>6766607</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6856,10 +6856,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>127723188</v>
+        <v>127722841</v>
       </c>
       <c r="B64" t="n">
-        <v>79032</v>
+        <v>79075</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6867,21 +6867,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -6891,10 +6891,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>443454</v>
+        <v>443568</v>
       </c>
       <c r="R64" t="n">
-        <v>6766724</v>
+        <v>6766695</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -6953,10 +6953,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>127723134</v>
+        <v>127723106</v>
       </c>
       <c r="B65" t="n">
-        <v>79032</v>
+        <v>79043</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6988,10 +6988,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>443465</v>
+        <v>443516</v>
       </c>
       <c r="R65" t="n">
-        <v>6766607</v>
+        <v>6766720</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7050,10 +7050,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>127722847</v>
+        <v>127723177</v>
       </c>
       <c r="B66" t="n">
-        <v>79064</v>
+        <v>79043</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7061,21 +7061,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7085,10 +7085,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>443320</v>
+        <v>443397</v>
       </c>
       <c r="R66" t="n">
-        <v>6766703</v>
+        <v>6766673</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7150,7 +7150,7 @@
         <v>127729137</v>
       </c>
       <c r="B67" t="n">
-        <v>79032</v>
+        <v>79043</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7255,32 +7255,32 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>127723065</v>
+        <v>127723158</v>
       </c>
       <c r="B68" t="n">
-        <v>91521</v>
+        <v>79043</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>1503</v>
+        <v>6425</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7290,10 +7290,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>443425</v>
+        <v>443312</v>
       </c>
       <c r="R68" t="n">
-        <v>6766668</v>
+        <v>6766818</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7352,32 +7352,32 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>127723177</v>
+        <v>127723065</v>
       </c>
       <c r="B69" t="n">
-        <v>79032</v>
+        <v>91532</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6425</v>
+        <v>1503</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7387,10 +7387,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>443397</v>
+        <v>443425</v>
       </c>
       <c r="R69" t="n">
-        <v>6766673</v>
+        <v>6766668</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7449,10 +7449,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>127723158</v>
+        <v>127722847</v>
       </c>
       <c r="B70" t="n">
-        <v>79032</v>
+        <v>79075</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7460,21 +7460,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7484,10 +7484,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>443312</v>
+        <v>443320</v>
       </c>
       <c r="R70" t="n">
-        <v>6766818</v>
+        <v>6766703</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7549,7 +7549,7 @@
         <v>127723150</v>
       </c>
       <c r="B71" t="n">
-        <v>79032</v>
+        <v>79043</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7748,7 +7748,7 @@
         <v>127722839</v>
       </c>
       <c r="B73" t="n">
-        <v>79064</v>
+        <v>79075</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7842,10 +7842,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>127723133</v>
+        <v>127723173</v>
       </c>
       <c r="B74" t="n">
-        <v>79032</v>
+        <v>79043</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7877,10 +7877,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>443504</v>
+        <v>443365</v>
       </c>
       <c r="R74" t="n">
-        <v>6766593</v>
+        <v>6766656</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -7939,10 +7939,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>127723173</v>
+        <v>127723108</v>
       </c>
       <c r="B75" t="n">
-        <v>79032</v>
+        <v>79043</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7974,10 +7974,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>443365</v>
+        <v>443483</v>
       </c>
       <c r="R75" t="n">
-        <v>6766656</v>
+        <v>6766725</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8036,10 +8036,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>127723108</v>
+        <v>127723090</v>
       </c>
       <c r="B76" t="n">
-        <v>79032</v>
+        <v>79043</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8071,10 +8071,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>443483</v>
+        <v>443593</v>
       </c>
       <c r="R76" t="n">
-        <v>6766725</v>
+        <v>6766653</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8133,10 +8133,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>127729092</v>
+        <v>127723133</v>
       </c>
       <c r="B77" t="n">
-        <v>78790</v>
+        <v>79043</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8144,34 +8144,34 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Oxeråsen S. om, Dlr</t>
+          <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>443381</v>
+        <v>443504</v>
       </c>
       <c r="R77" t="n">
-        <v>6766668</v>
+        <v>6766593</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8201,50 +8201,39 @@
           <t>2025-08-21</t>
         </is>
       </c>
-      <c r="Z77" t="inlineStr">
-        <is>
-          <t>13:51</t>
-        </is>
-      </c>
       <c r="AA77" t="inlineStr">
         <is>
           <t>2025-08-21</t>
         </is>
       </c>
-      <c r="AB77" t="inlineStr">
-        <is>
-          <t>13:51</t>
-        </is>
-      </c>
       <c r="AD77" t="b">
         <v>0</v>
       </c>
       <c r="AE77" t="b">
         <v>0</v>
       </c>
-      <c r="AF77" t="inlineStr"/>
       <c r="AG77" t="b">
         <v>0</v>
       </c>
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>127723090</v>
+        <v>127729092</v>
       </c>
       <c r="B78" t="n">
-        <v>79032</v>
+        <v>78801</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8252,34 +8241,34 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Oxeråsen, Dlr</t>
+          <t>Oxeråsen S. om, Dlr</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>443593</v>
+        <v>443381</v>
       </c>
       <c r="R78" t="n">
-        <v>6766653</v>
+        <v>6766668</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8309,39 +8298,50 @@
           <t>2025-08-21</t>
         </is>
       </c>
+      <c r="Z78" t="inlineStr">
+        <is>
+          <t>13:51</t>
+        </is>
+      </c>
       <c r="AA78" t="inlineStr">
         <is>
           <t>2025-08-21</t>
         </is>
       </c>
+      <c r="AB78" t="inlineStr">
+        <is>
+          <t>13:51</t>
+        </is>
+      </c>
       <c r="AD78" t="b">
         <v>0</v>
       </c>
       <c r="AE78" t="b">
         <v>0</v>
       </c>
+      <c r="AF78" t="inlineStr"/>
       <c r="AG78" t="b">
         <v>0</v>
       </c>
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>127723156</v>
+        <v>127723571</v>
       </c>
       <c r="B79" t="n">
-        <v>79032</v>
+        <v>78710</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8349,21 +8349,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8373,10 +8373,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>443346</v>
+        <v>443426</v>
       </c>
       <c r="R79" t="n">
-        <v>6766766</v>
+        <v>6766668</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8435,10 +8435,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>127723571</v>
+        <v>127723156</v>
       </c>
       <c r="B80" t="n">
-        <v>78699</v>
+        <v>79043</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8446,21 +8446,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8470,10 +8470,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>443426</v>
+        <v>443346</v>
       </c>
       <c r="R80" t="n">
-        <v>6766668</v>
+        <v>6766766</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8535,7 +8535,7 @@
         <v>127723120</v>
       </c>
       <c r="B81" t="n">
-        <v>79032</v>
+        <v>79043</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8632,7 +8632,7 @@
         <v>127723104</v>
       </c>
       <c r="B82" t="n">
-        <v>79032</v>
+        <v>79043</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8726,10 +8726,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>127723171</v>
+        <v>127723570</v>
       </c>
       <c r="B83" t="n">
-        <v>79032</v>
+        <v>78710</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8737,21 +8737,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -8761,10 +8761,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>443342</v>
+        <v>443319</v>
       </c>
       <c r="R83" t="n">
-        <v>6766650</v>
+        <v>6766670</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -8826,7 +8826,7 @@
         <v>127723116</v>
       </c>
       <c r="B84" t="n">
-        <v>79032</v>
+        <v>79043</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -8920,10 +8920,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>127723092</v>
+        <v>127723178</v>
       </c>
       <c r="B85" t="n">
-        <v>79032</v>
+        <v>79043</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -8955,10 +8955,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>443572</v>
+        <v>443402</v>
       </c>
       <c r="R85" t="n">
-        <v>6766650</v>
+        <v>6766682</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9017,10 +9017,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>127723178</v>
+        <v>127723171</v>
       </c>
       <c r="B86" t="n">
-        <v>79032</v>
+        <v>79043</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9052,10 +9052,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>443402</v>
+        <v>443342</v>
       </c>
       <c r="R86" t="n">
-        <v>6766682</v>
+        <v>6766650</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9114,10 +9114,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>127722916</v>
+        <v>127723092</v>
       </c>
       <c r="B87" t="n">
-        <v>57673</v>
+        <v>79043</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9125,39 +9125,34 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
-      <c r="M87" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P87" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>443342</v>
+        <v>443572</v>
       </c>
       <c r="R87" t="n">
-        <v>6766806</v>
+        <v>6766650</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9190,11 +9185,6 @@
       <c r="AA87" t="inlineStr">
         <is>
           <t>2025-08-21</t>
-        </is>
-      </c>
-      <c r="AC87" t="inlineStr">
-        <is>
-          <t>Färska ringhack (gran), 4-5 år gamla</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9224,7 +9214,7 @@
         <v>127723541</v>
       </c>
       <c r="B88" t="n">
-        <v>57673</v>
+        <v>57684</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9323,10 +9313,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>127723570</v>
+        <v>127722916</v>
       </c>
       <c r="B89" t="n">
-        <v>78699</v>
+        <v>57684</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9334,34 +9324,39 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>353</v>
+        <v>100109</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P89" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>443319</v>
+        <v>443342</v>
       </c>
       <c r="R89" t="n">
-        <v>6766670</v>
+        <v>6766806</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9394,6 +9389,11 @@
       <c r="AA89" t="inlineStr">
         <is>
           <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AC89" t="inlineStr">
+        <is>
+          <t>Färska ringhack (gran), 4-5 år gamla</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -9423,7 +9423,7 @@
         <v>127722888</v>
       </c>
       <c r="B90" t="n">
-        <v>57670</v>
+        <v>57681</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9525,7 +9525,7 @@
         <v>127723569</v>
       </c>
       <c r="B91" t="n">
-        <v>78699</v>
+        <v>78710</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9619,10 +9619,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>127723161</v>
+        <v>127723103</v>
       </c>
       <c r="B92" t="n">
-        <v>79032</v>
+        <v>79043</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9654,10 +9654,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>443305</v>
+        <v>443541</v>
       </c>
       <c r="R92" t="n">
-        <v>6766767</v>
+        <v>6766696</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9716,10 +9716,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>127723186</v>
+        <v>127723105</v>
       </c>
       <c r="B93" t="n">
-        <v>79032</v>
+        <v>79043</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9751,10 +9751,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>443454</v>
+        <v>443525</v>
       </c>
       <c r="R93" t="n">
-        <v>6766738</v>
+        <v>6766717</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -9813,10 +9813,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>127723114</v>
+        <v>127723161</v>
       </c>
       <c r="B94" t="n">
-        <v>79032</v>
+        <v>79043</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -9848,10 +9848,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>443487</v>
+        <v>443305</v>
       </c>
       <c r="R94" t="n">
-        <v>6766651</v>
+        <v>6766767</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -9910,10 +9910,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>127723174</v>
+        <v>127723114</v>
       </c>
       <c r="B95" t="n">
-        <v>79032</v>
+        <v>79043</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -9945,10 +9945,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>443378</v>
+        <v>443487</v>
       </c>
       <c r="R95" t="n">
-        <v>6766657</v>
+        <v>6766651</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10010,7 +10010,7 @@
         <v>127723041</v>
       </c>
       <c r="B96" t="n">
-        <v>78791</v>
+        <v>78802</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10104,10 +10104,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>127723103</v>
+        <v>127723186</v>
       </c>
       <c r="B97" t="n">
-        <v>79032</v>
+        <v>79043</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10139,10 +10139,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>443541</v>
+        <v>443454</v>
       </c>
       <c r="R97" t="n">
-        <v>6766696</v>
+        <v>6766738</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10201,10 +10201,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>127723105</v>
+        <v>127723097</v>
       </c>
       <c r="B98" t="n">
-        <v>79032</v>
+        <v>79043</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10236,10 +10236,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>443525</v>
+        <v>443561</v>
       </c>
       <c r="R98" t="n">
-        <v>6766717</v>
+        <v>6766678</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10298,10 +10298,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>127723097</v>
+        <v>127723174</v>
       </c>
       <c r="B99" t="n">
-        <v>79032</v>
+        <v>79043</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10333,10 +10333,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>443561</v>
+        <v>443378</v>
       </c>
       <c r="R99" t="n">
-        <v>6766678</v>
+        <v>6766657</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10395,50 +10395,45 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>127722929</v>
+        <v>127722842</v>
       </c>
       <c r="B100" t="n">
-        <v>8450</v>
+        <v>79075</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>106545</v>
+        <v>185</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
-      <c r="M100" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P100" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>443327</v>
+        <v>443504</v>
       </c>
       <c r="R100" t="n">
-        <v>6766698</v>
+        <v>6766708</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10497,10 +10492,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>127723157</v>
+        <v>127723616</v>
       </c>
       <c r="B101" t="n">
-        <v>79032</v>
+        <v>57684</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -10508,34 +10503,39 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
+      <c r="M101" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
       <c r="P101" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>443306</v>
+        <v>443475</v>
       </c>
       <c r="R101" t="n">
-        <v>6766830</v>
+        <v>6766610</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10594,10 +10594,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>127723139</v>
+        <v>127723038</v>
       </c>
       <c r="B102" t="n">
-        <v>79032</v>
+        <v>78802</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -10605,21 +10605,21 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -10629,10 +10629,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>443381</v>
+        <v>443328</v>
       </c>
       <c r="R102" t="n">
-        <v>6766623</v>
+        <v>6766721</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -10691,10 +10691,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>127723170</v>
+        <v>127723157</v>
       </c>
       <c r="B103" t="n">
-        <v>79032</v>
+        <v>79043</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -10726,10 +10726,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>443333</v>
+        <v>443306</v>
       </c>
       <c r="R103" t="n">
-        <v>6766676</v>
+        <v>6766830</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -10788,10 +10788,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>127723616</v>
+        <v>127723182</v>
       </c>
       <c r="B104" t="n">
-        <v>57673</v>
+        <v>79043</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -10799,39 +10799,34 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
-      <c r="M104" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
       <c r="P104" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>443475</v>
+        <v>443444</v>
       </c>
       <c r="R104" t="n">
-        <v>6766610</v>
+        <v>6766677</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -10890,10 +10885,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>127723038</v>
+        <v>127723183</v>
       </c>
       <c r="B105" t="n">
-        <v>78791</v>
+        <v>79043</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -10901,21 +10896,21 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -10925,10 +10920,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>443328</v>
+        <v>443441</v>
       </c>
       <c r="R105" t="n">
-        <v>6766721</v>
+        <v>6766686</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -10987,10 +10982,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>127722842</v>
+        <v>127723096</v>
       </c>
       <c r="B106" t="n">
-        <v>79064</v>
+        <v>79043</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -10998,21 +10993,21 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -11022,10 +11017,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>443504</v>
+        <v>443554</v>
       </c>
       <c r="R106" t="n">
-        <v>6766708</v>
+        <v>6766650</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11084,10 +11079,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>127723183</v>
+        <v>127723139</v>
       </c>
       <c r="B107" t="n">
-        <v>79032</v>
+        <v>79043</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11119,10 +11114,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>443441</v>
+        <v>443381</v>
       </c>
       <c r="R107" t="n">
-        <v>6766686</v>
+        <v>6766623</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11181,10 +11176,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>127723182</v>
+        <v>127723170</v>
       </c>
       <c r="B108" t="n">
-        <v>79032</v>
+        <v>79043</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11216,10 +11211,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>443444</v>
+        <v>443333</v>
       </c>
       <c r="R108" t="n">
-        <v>6766677</v>
+        <v>6766676</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11278,10 +11273,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>127723096</v>
+        <v>127723098</v>
       </c>
       <c r="B109" t="n">
-        <v>79032</v>
+        <v>79043</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11313,10 +11308,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>443554</v>
+        <v>443562</v>
       </c>
       <c r="R109" t="n">
-        <v>6766650</v>
+        <v>6766684</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11375,45 +11370,50 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>127723098</v>
+        <v>127722929</v>
       </c>
       <c r="B110" t="n">
-        <v>79032</v>
+        <v>8450</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
+      <c r="M110" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P110" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>443562</v>
+        <v>443327</v>
       </c>
       <c r="R110" t="n">
-        <v>6766684</v>
+        <v>6766698</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11475,7 +11475,7 @@
         <v>127723137</v>
       </c>
       <c r="B111" t="n">
-        <v>79032</v>
+        <v>79043</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -11569,10 +11569,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>127723154</v>
+        <v>127723172</v>
       </c>
       <c r="B112" t="n">
-        <v>79032</v>
+        <v>79043</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -11604,10 +11604,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>443369</v>
+        <v>443356</v>
       </c>
       <c r="R112" t="n">
-        <v>6766695</v>
+        <v>6766650</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -11666,10 +11666,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>127723172</v>
+        <v>127723136</v>
       </c>
       <c r="B113" t="n">
-        <v>79032</v>
+        <v>79043</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -11701,10 +11701,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>443356</v>
+        <v>443438</v>
       </c>
       <c r="R113" t="n">
-        <v>6766650</v>
+        <v>6766628</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -11763,10 +11763,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>127723136</v>
+        <v>127723160</v>
       </c>
       <c r="B114" t="n">
-        <v>79032</v>
+        <v>79043</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -11798,10 +11798,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>443438</v>
+        <v>443309</v>
       </c>
       <c r="R114" t="n">
-        <v>6766628</v>
+        <v>6766785</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -11860,10 +11860,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>127723160</v>
+        <v>127722904</v>
       </c>
       <c r="B115" t="n">
-        <v>79032</v>
+        <v>57684</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -11871,21 +11871,21 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -11895,10 +11895,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>443309</v>
+        <v>443419</v>
       </c>
       <c r="R115" t="n">
-        <v>6766785</v>
+        <v>6766676</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -11931,6 +11931,11 @@
       <c r="AA115" t="inlineStr">
         <is>
           <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AC115" t="inlineStr">
+        <is>
+          <t>Äldre ringhack (tall)</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -11957,10 +11962,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>127722904</v>
+        <v>127729086</v>
       </c>
       <c r="B116" t="n">
-        <v>57673</v>
+        <v>78802</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -11968,34 +11973,34 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>100109</v>
+        <v>228912</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
       <c r="P116" t="inlineStr">
         <is>
-          <t>Oxeråsen, Dlr</t>
+          <t>Oxeråsen S. om, Dlr</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>443419</v>
+        <v>443359</v>
       </c>
       <c r="R116" t="n">
-        <v>6766676</v>
+        <v>6766650</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12025,14 +12030,19 @@
           <t>2025-08-21</t>
         </is>
       </c>
+      <c r="Z116" t="inlineStr">
+        <is>
+          <t>13:53</t>
+        </is>
+      </c>
       <c r="AA116" t="inlineStr">
         <is>
           <t>2025-08-21</t>
         </is>
       </c>
-      <c r="AC116" t="inlineStr">
-        <is>
-          <t>Äldre ringhack (tall)</t>
+      <c r="AB116" t="inlineStr">
+        <is>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -12041,28 +12051,29 @@
       <c r="AE116" t="b">
         <v>0</v>
       </c>
+      <c r="AF116" t="inlineStr"/>
       <c r="AG116" t="b">
         <v>0</v>
       </c>
       <c r="AT116" t="inlineStr"/>
       <c r="AW116" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX116" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>127729086</v>
+        <v>127723154</v>
       </c>
       <c r="B117" t="n">
-        <v>78791</v>
+        <v>79043</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -12070,34 +12081,34 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
       <c r="P117" t="inlineStr">
         <is>
-          <t>Oxeråsen S. om, Dlr</t>
+          <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>443359</v>
+        <v>443369</v>
       </c>
       <c r="R117" t="n">
-        <v>6766650</v>
+        <v>6766695</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12127,50 +12138,39 @@
           <t>2025-08-21</t>
         </is>
       </c>
-      <c r="Z117" t="inlineStr">
-        <is>
-          <t>13:53</t>
-        </is>
-      </c>
       <c r="AA117" t="inlineStr">
         <is>
           <t>2025-08-21</t>
         </is>
       </c>
-      <c r="AB117" t="inlineStr">
-        <is>
-          <t>13:53</t>
-        </is>
-      </c>
       <c r="AD117" t="b">
         <v>0</v>
       </c>
       <c r="AE117" t="b">
         <v>0</v>
       </c>
-      <c r="AF117" t="inlineStr"/>
       <c r="AG117" t="b">
         <v>0</v>
       </c>
       <c r="AT117" t="inlineStr"/>
       <c r="AW117" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX117" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>127723176</v>
+        <v>127723163</v>
       </c>
       <c r="B118" t="n">
-        <v>79032</v>
+        <v>79043</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12202,10 +12202,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>443407</v>
+        <v>443332</v>
       </c>
       <c r="R118" t="n">
-        <v>6766653</v>
+        <v>6766744</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12264,10 +12264,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>127723135</v>
+        <v>127723176</v>
       </c>
       <c r="B119" t="n">
-        <v>79032</v>
+        <v>79043</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -12299,10 +12299,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>443454</v>
+        <v>443407</v>
       </c>
       <c r="R119" t="n">
-        <v>6766614</v>
+        <v>6766653</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -12361,10 +12361,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>127722903</v>
+        <v>127723135</v>
       </c>
       <c r="B120" t="n">
-        <v>57673</v>
+        <v>79043</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -12372,21 +12372,21 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -12396,10 +12396,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>443382</v>
+        <v>443454</v>
       </c>
       <c r="R120" t="n">
-        <v>6766657</v>
+        <v>6766614</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -12432,11 +12432,6 @@
       <c r="AA120" t="inlineStr">
         <is>
           <t>2025-08-21</t>
-        </is>
-      </c>
-      <c r="AC120" t="inlineStr">
-        <is>
-          <t>Äldre ringhack (tall)</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -12463,50 +12458,45 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>127722955</v>
+        <v>127723113</v>
       </c>
       <c r="B121" t="n">
-        <v>8450</v>
+        <v>79043</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
-      <c r="M121" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P121" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>443397</v>
+        <v>443487</v>
       </c>
       <c r="R121" t="n">
-        <v>6766653</v>
+        <v>6766675</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -12565,50 +12555,45 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>127722948</v>
+        <v>127722903</v>
       </c>
       <c r="B122" t="n">
-        <v>8450</v>
+        <v>57684</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>106545</v>
+        <v>100109</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
-      <c r="M122" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P122" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>443457</v>
+        <v>443382</v>
       </c>
       <c r="R122" t="n">
-        <v>6766613</v>
+        <v>6766657</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -12641,6 +12626,11 @@
       <c r="AA122" t="inlineStr">
         <is>
           <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AC122" t="inlineStr">
+        <is>
+          <t>Äldre ringhack (tall)</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -12667,45 +12657,50 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>127723163</v>
+        <v>127722955</v>
       </c>
       <c r="B123" t="n">
-        <v>79032</v>
+        <v>8450</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
+      <c r="M123" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P123" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>443332</v>
+        <v>443397</v>
       </c>
       <c r="R123" t="n">
-        <v>6766744</v>
+        <v>6766653</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -12764,45 +12759,50 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>127723113</v>
+        <v>127722948</v>
       </c>
       <c r="B124" t="n">
-        <v>79032</v>
+        <v>8450</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
+      <c r="M124" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P124" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>443487</v>
+        <v>443457</v>
       </c>
       <c r="R124" t="n">
-        <v>6766675</v>
+        <v>6766613</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -12864,7 +12864,7 @@
         <v>127723037</v>
       </c>
       <c r="B125" t="n">
-        <v>78791</v>
+        <v>78802</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -12961,7 +12961,7 @@
         <v>127723118</v>
       </c>
       <c r="B126" t="n">
-        <v>79032</v>
+        <v>79043</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -13058,7 +13058,7 @@
         <v>127723140</v>
       </c>
       <c r="B127" t="n">
-        <v>79032</v>
+        <v>79043</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -13152,32 +13152,32 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>127723094</v>
+        <v>127723555</v>
       </c>
       <c r="B128" t="n">
-        <v>79032</v>
+        <v>92661</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
@@ -13187,10 +13187,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>443557</v>
+        <v>443554</v>
       </c>
       <c r="R128" t="n">
-        <v>6766635</v>
+        <v>6766667</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -13249,32 +13249,32 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>127723555</v>
+        <v>127723165</v>
       </c>
       <c r="B129" t="n">
-        <v>92650</v>
+        <v>79043</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
@@ -13284,10 +13284,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>443554</v>
+        <v>443327</v>
       </c>
       <c r="R129" t="n">
-        <v>6766667</v>
+        <v>6766717</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -13346,10 +13346,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>127723165</v>
+        <v>127723094</v>
       </c>
       <c r="B130" t="n">
-        <v>79032</v>
+        <v>79043</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -13381,10 +13381,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>443327</v>
+        <v>443557</v>
       </c>
       <c r="R130" t="n">
-        <v>6766717</v>
+        <v>6766635</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -13650,7 +13650,7 @@
         <v>127723162</v>
       </c>
       <c r="B133" t="n">
-        <v>79032</v>
+        <v>79043</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -13747,7 +13747,7 @@
         <v>127723111</v>
       </c>
       <c r="B134" t="n">
-        <v>79032</v>
+        <v>79043</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -13844,7 +13844,7 @@
         <v>127722855</v>
       </c>
       <c r="B135" t="n">
-        <v>79621</v>
+        <v>79632</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -13941,7 +13941,7 @@
         <v>127723619</v>
       </c>
       <c r="B136" t="n">
-        <v>57673</v>
+        <v>57685</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -14048,7 +14048,7 @@
         <v>127736007</v>
       </c>
       <c r="B137" t="n">
-        <v>91380</v>
+        <v>91472</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -14155,7 +14155,7 @@
         <v>127736019</v>
       </c>
       <c r="B138" t="n">
-        <v>79032</v>
+        <v>79083</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -14262,7 +14262,7 @@
         <v>127785482</v>
       </c>
       <c r="B139" t="n">
-        <v>79032</v>
+        <v>79083</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -14369,7 +14369,7 @@
         <v>127785478</v>
       </c>
       <c r="B140" t="n">
-        <v>79032</v>
+        <v>79083</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -14482,7 +14482,7 @@
         <v>127785484</v>
       </c>
       <c r="B141" t="n">
-        <v>79032</v>
+        <v>79083</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -14589,7 +14589,7 @@
         <v>127785481</v>
       </c>
       <c r="B142" t="n">
-        <v>79032</v>
+        <v>79083</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -14696,7 +14696,7 @@
         <v>127785483</v>
       </c>
       <c r="B143" t="n">
-        <v>79032</v>
+        <v>79083</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -14803,7 +14803,7 @@
         <v>127785472</v>
       </c>
       <c r="B144" t="n">
-        <v>91380</v>
+        <v>91472</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -15017,7 +15017,7 @@
         <v>127795299</v>
       </c>
       <c r="B146" t="n">
-        <v>78790</v>
+        <v>78840</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -15118,7 +15118,7 @@
         <v>127795339</v>
       </c>
       <c r="B147" t="n">
-        <v>79032</v>
+        <v>79083</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>

--- a/artfynd/A 35484-2025 artfynd.xlsx
+++ b/artfynd/A 35484-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY181"/>
+  <dimension ref="A1:AZ181"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127722851</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127722839</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127722841</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127722842</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127722843</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1254,6 +1284,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127722846</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1351,6 +1386,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127722847</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1448,6 +1488,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723569</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1545,6 +1590,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723570</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1642,6 +1692,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723571</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1739,6 +1794,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723563</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1836,6 +1896,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723064</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1933,6 +1998,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723065</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2030,6 +2100,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127722927</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2127,6 +2202,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723555</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2224,6 +2304,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127722874</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2321,6 +2406,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127722875</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2418,6 +2508,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127722876</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2525,6 +2620,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127736007</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2632,6 +2732,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127785472</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2738,6 +2843,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127621301</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2844,6 +2954,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127621322</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2950,6 +3065,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127621344</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3051,6 +3171,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127621380</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3157,6 +3282,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127621416</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3263,6 +3393,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127621440</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3369,6 +3504,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127621456</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3466,6 +3606,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723078</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3563,6 +3708,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723089</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3660,6 +3810,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723090</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3757,6 +3912,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723091</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3854,6 +4014,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723092</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -3951,6 +4116,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723093</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4048,6 +4218,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723094</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4145,6 +4320,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723096</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4242,6 +4422,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723097</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4339,6 +4524,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723098</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4436,6 +4626,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723099</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4533,6 +4728,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723100</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4630,6 +4830,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723101</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4727,6 +4932,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723102</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -4824,6 +5034,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723103</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -4921,6 +5136,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723104</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5018,6 +5238,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723105</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5115,6 +5340,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723106</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5212,6 +5442,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723107</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5309,6 +5544,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723108</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5406,6 +5646,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723109</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5503,6 +5748,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723110</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5600,6 +5850,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723111</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -5697,6 +5952,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723112</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -5794,6 +6054,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723113</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -5891,6 +6156,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723114</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -5988,6 +6258,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723115</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6085,6 +6360,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723116</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6182,6 +6462,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723117</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6279,6 +6564,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723118</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6376,6 +6666,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723119</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -6473,6 +6768,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723120</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -6570,6 +6870,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723121</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -6667,6 +6972,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723122</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -6764,6 +7074,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723123</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -6861,6 +7176,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723124</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -6958,6 +7278,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723125</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7055,6 +7380,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723126</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -7152,6 +7482,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723127</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -7249,6 +7584,11 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723128</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -7346,6 +7686,11 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723129</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -7443,6 +7788,11 @@
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723130</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -7540,6 +7890,11 @@
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723131</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -7637,6 +7992,11 @@
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723132</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -7734,6 +8094,11 @@
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723133</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -7831,6 +8196,11 @@
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723134</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -7928,6 +8298,11 @@
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723135</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -8025,6 +8400,11 @@
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723136</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -8122,6 +8502,11 @@
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723137</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -8219,6 +8604,11 @@
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723138</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -8316,6 +8706,11 @@
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723139</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -8413,6 +8808,11 @@
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723140</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -8510,6 +8910,11 @@
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723146</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -8607,6 +9012,11 @@
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723147</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -8704,6 +9114,11 @@
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723148</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -8801,6 +9216,11 @@
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723149</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -8898,6 +9318,11 @@
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723150</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -8995,6 +9420,11 @@
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723151</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -9092,6 +9522,11 @@
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723152</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -9189,6 +9624,11 @@
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
+      <c r="AZ88" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723153</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -9286,6 +9726,11 @@
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
+      <c r="AZ89" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723154</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -9383,6 +9828,11 @@
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
+      <c r="AZ90" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723155</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -9480,6 +9930,11 @@
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
+      <c r="AZ91" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723156</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -9577,6 +10032,11 @@
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
+      <c r="AZ92" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723157</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -9674,6 +10134,11 @@
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
+      <c r="AZ93" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723158</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -9771,6 +10236,11 @@
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
+      <c r="AZ94" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723159</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -9868,6 +10338,11 @@
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
+      <c r="AZ95" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723160</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -9965,6 +10440,11 @@
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
+      <c r="AZ96" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723161</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -10062,6 +10542,11 @@
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
+      <c r="AZ97" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723162</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -10159,6 +10644,11 @@
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
+      <c r="AZ98" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723163</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -10256,6 +10746,11 @@
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
+      <c r="AZ99" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723164</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -10353,6 +10848,11 @@
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
+      <c r="AZ100" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723165</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -10450,6 +10950,11 @@
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
+      <c r="AZ101" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723166</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -10547,6 +11052,11 @@
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
+      <c r="AZ102" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723167</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -10644,6 +11154,11 @@
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
+      <c r="AZ103" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723169</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -10741,6 +11256,11 @@
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
+      <c r="AZ104" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723170</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -10838,6 +11358,11 @@
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
+      <c r="AZ105" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723171</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -10935,6 +11460,11 @@
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
+      <c r="AZ106" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723172</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -11032,6 +11562,11 @@
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
+      <c r="AZ107" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723173</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
@@ -11129,6 +11664,11 @@
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
+      <c r="AZ108" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723174</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
@@ -11226,6 +11766,11 @@
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
+      <c r="AZ109" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723175</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
@@ -11323,6 +11868,11 @@
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
+      <c r="AZ110" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723176</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
@@ -11420,6 +11970,11 @@
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
+      <c r="AZ111" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723177</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
@@ -11517,6 +12072,11 @@
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
+      <c r="AZ112" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723178</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
@@ -11614,6 +12174,11 @@
         </is>
       </c>
       <c r="AY113" t="inlineStr"/>
+      <c r="AZ113" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723179</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
@@ -11711,6 +12276,11 @@
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
+      <c r="AZ114" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723180</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
@@ -11808,6 +12378,11 @@
         </is>
       </c>
       <c r="AY115" t="inlineStr"/>
+      <c r="AZ115" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723181</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
@@ -11905,6 +12480,11 @@
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>
+      <c r="AZ116" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723182</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
@@ -12002,6 +12582,11 @@
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
+      <c r="AZ117" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723183</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
@@ -12099,6 +12684,11 @@
         </is>
       </c>
       <c r="AY118" t="inlineStr"/>
+      <c r="AZ118" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723184</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
@@ -12196,6 +12786,11 @@
         </is>
       </c>
       <c r="AY119" t="inlineStr"/>
+      <c r="AZ119" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723185</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
@@ -12293,6 +12888,11 @@
         </is>
       </c>
       <c r="AY120" t="inlineStr"/>
+      <c r="AZ120" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723186</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
@@ -12390,6 +12990,11 @@
         </is>
       </c>
       <c r="AY121" t="inlineStr"/>
+      <c r="AZ121" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723187</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
@@ -12487,6 +13092,11 @@
         </is>
       </c>
       <c r="AY122" t="inlineStr"/>
+      <c r="AZ122" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723188</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
@@ -12589,6 +13199,11 @@
         </is>
       </c>
       <c r="AY123" t="inlineStr"/>
+      <c r="AZ123" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723189</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
@@ -12697,6 +13312,11 @@
         </is>
       </c>
       <c r="AY124" t="inlineStr"/>
+      <c r="AZ124" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127729137</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
@@ -12805,6 +13425,11 @@
         </is>
       </c>
       <c r="AY125" t="inlineStr"/>
+      <c r="AZ125" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127729138</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
@@ -12912,6 +13537,11 @@
         </is>
       </c>
       <c r="AY126" t="inlineStr"/>
+      <c r="AZ126" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127736019</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
@@ -13025,6 +13655,11 @@
         </is>
       </c>
       <c r="AY127" t="inlineStr"/>
+      <c r="AZ127" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127785478</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
@@ -13145,6 +13780,11 @@
         </is>
       </c>
       <c r="AY128" t="inlineStr"/>
+      <c r="AZ128" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127785480</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
@@ -13252,6 +13892,11 @@
         </is>
       </c>
       <c r="AY129" t="inlineStr"/>
+      <c r="AZ129" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127785481</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
@@ -13359,6 +14004,11 @@
         </is>
       </c>
       <c r="AY130" t="inlineStr"/>
+      <c r="AZ130" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127785482</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
@@ -13466,6 +14116,11 @@
         </is>
       </c>
       <c r="AY131" t="inlineStr"/>
+      <c r="AZ131" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127785483</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
@@ -13573,6 +14228,11 @@
         </is>
       </c>
       <c r="AY132" t="inlineStr"/>
+      <c r="AZ132" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127785484</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
@@ -13674,6 +14334,11 @@
         </is>
       </c>
       <c r="AY133" t="inlineStr"/>
+      <c r="AZ133" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127795339</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
@@ -13775,6 +14440,11 @@
         </is>
       </c>
       <c r="AY134" t="inlineStr"/>
+      <c r="AZ134" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127621346</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
@@ -13883,6 +14553,11 @@
         </is>
       </c>
       <c r="AY135" t="inlineStr"/>
+      <c r="AZ135" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127729092</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
@@ -13984,6 +14659,11 @@
         </is>
       </c>
       <c r="AY136" t="inlineStr"/>
+      <c r="AZ136" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127795299</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
@@ -14081,6 +14761,11 @@
         </is>
       </c>
       <c r="AY137" t="inlineStr"/>
+      <c r="AZ137" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127722926</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="n">
@@ -14183,6 +14868,11 @@
         </is>
       </c>
       <c r="AY138" t="inlineStr"/>
+      <c r="AZ138" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127722888</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
@@ -14285,6 +14975,11 @@
         </is>
       </c>
       <c r="AY139" t="inlineStr"/>
+      <c r="AZ139" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127722896</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
@@ -14387,6 +15082,11 @@
         </is>
       </c>
       <c r="AY140" t="inlineStr"/>
+      <c r="AZ140" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127722897</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
@@ -14489,6 +15189,11 @@
         </is>
       </c>
       <c r="AY141" t="inlineStr"/>
+      <c r="AZ141" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127722903</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="n">
@@ -14591,6 +15296,11 @@
         </is>
       </c>
       <c r="AY142" t="inlineStr"/>
+      <c r="AZ142" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127722904</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="n">
@@ -14698,6 +15408,11 @@
         </is>
       </c>
       <c r="AY143" t="inlineStr"/>
+      <c r="AZ143" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127722916</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="n">
@@ -14800,6 +15515,11 @@
         </is>
       </c>
       <c r="AY144" t="inlineStr"/>
+      <c r="AZ144" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723540</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="n">
@@ -14902,6 +15622,11 @@
         </is>
       </c>
       <c r="AY145" t="inlineStr"/>
+      <c r="AZ145" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723541</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="n">
@@ -15004,6 +15729,11 @@
         </is>
       </c>
       <c r="AY146" t="inlineStr"/>
+      <c r="AZ146" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723616</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="n">
@@ -15111,6 +15841,11 @@
         </is>
       </c>
       <c r="AY147" t="inlineStr"/>
+      <c r="AZ147" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723619</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="n">
@@ -15213,6 +15948,11 @@
         </is>
       </c>
       <c r="AY148" t="inlineStr"/>
+      <c r="AZ148" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127722868</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="n">
@@ -15315,6 +16055,11 @@
         </is>
       </c>
       <c r="AY149" t="inlineStr"/>
+      <c r="AZ149" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127722870</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="n">
@@ -15427,6 +16172,11 @@
         </is>
       </c>
       <c r="AY150" t="inlineStr"/>
+      <c r="AZ150" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127621376</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="n">
@@ -15534,6 +16284,11 @@
         </is>
       </c>
       <c r="AY151" t="inlineStr"/>
+      <c r="AZ151" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127621404</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="n">
@@ -15636,6 +16391,11 @@
         </is>
       </c>
       <c r="AY152" t="inlineStr"/>
+      <c r="AZ152" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127722928</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="n">
@@ -15738,6 +16498,11 @@
         </is>
       </c>
       <c r="AY153" t="inlineStr"/>
+      <c r="AZ153" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127722929</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="n">
@@ -15840,6 +16605,11 @@
         </is>
       </c>
       <c r="AY154" t="inlineStr"/>
+      <c r="AZ154" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127722932</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="n">
@@ -15942,6 +16712,11 @@
         </is>
       </c>
       <c r="AY155" t="inlineStr"/>
+      <c r="AZ155" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127722941</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="n">
@@ -16044,6 +16819,11 @@
         </is>
       </c>
       <c r="AY156" t="inlineStr"/>
+      <c r="AZ156" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127722942</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="n">
@@ -16146,6 +16926,11 @@
         </is>
       </c>
       <c r="AY157" t="inlineStr"/>
+      <c r="AZ157" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127722943</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="n">
@@ -16248,6 +17033,11 @@
         </is>
       </c>
       <c r="AY158" t="inlineStr"/>
+      <c r="AZ158" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127722944</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="n">
@@ -16350,6 +17140,11 @@
         </is>
       </c>
       <c r="AY159" t="inlineStr"/>
+      <c r="AZ159" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127722945</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="n">
@@ -16452,6 +17247,11 @@
         </is>
       </c>
       <c r="AY160" t="inlineStr"/>
+      <c r="AZ160" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127722946</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="n">
@@ -16554,6 +17354,11 @@
         </is>
       </c>
       <c r="AY161" t="inlineStr"/>
+      <c r="AZ161" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127722947</t>
+        </is>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="n">
@@ -16656,6 +17461,11 @@
         </is>
       </c>
       <c r="AY162" t="inlineStr"/>
+      <c r="AZ162" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127722948</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="n">
@@ -16758,6 +17568,11 @@
         </is>
       </c>
       <c r="AY163" t="inlineStr"/>
+      <c r="AZ163" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127722950</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="n">
@@ -16860,6 +17675,11 @@
         </is>
       </c>
       <c r="AY164" t="inlineStr"/>
+      <c r="AZ164" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127722951</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="n">
@@ -16962,6 +17782,11 @@
         </is>
       </c>
       <c r="AY165" t="inlineStr"/>
+      <c r="AZ165" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127722952</t>
+        </is>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="n">
@@ -17064,6 +17889,11 @@
         </is>
       </c>
       <c r="AY166" t="inlineStr"/>
+      <c r="AZ166" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127722953</t>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="n">
@@ -17166,6 +17996,11 @@
         </is>
       </c>
       <c r="AY167" t="inlineStr"/>
+      <c r="AZ167" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127722954</t>
+        </is>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="n">
@@ -17268,6 +18103,11 @@
         </is>
       </c>
       <c r="AY168" t="inlineStr"/>
+      <c r="AZ168" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127722955</t>
+        </is>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="n">
@@ -17370,6 +18210,11 @@
         </is>
       </c>
       <c r="AY169" t="inlineStr"/>
+      <c r="AZ169" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127722956</t>
+        </is>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="n">
@@ -17472,6 +18317,11 @@
         </is>
       </c>
       <c r="AY170" t="inlineStr"/>
+      <c r="AZ170" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127722957</t>
+        </is>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="n">
@@ -17579,6 +18429,11 @@
         </is>
       </c>
       <c r="AY171" t="inlineStr"/>
+      <c r="AZ171" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127795289</t>
+        </is>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="n">
@@ -17686,6 +18541,11 @@
         </is>
       </c>
       <c r="AY172" t="inlineStr"/>
+      <c r="AZ172" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127795321</t>
+        </is>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="n">
@@ -17793,6 +18653,11 @@
         </is>
       </c>
       <c r="AY173" t="inlineStr"/>
+      <c r="AZ173" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127621350</t>
+        </is>
+      </c>
     </row>
     <row r="174">
       <c r="A174" t="n">
@@ -17890,6 +18755,11 @@
         </is>
       </c>
       <c r="AY174" t="inlineStr"/>
+      <c r="AZ174" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127722921</t>
+        </is>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="n">
@@ -17987,6 +18857,11 @@
         </is>
       </c>
       <c r="AY175" t="inlineStr"/>
+      <c r="AZ175" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723037</t>
+        </is>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="n">
@@ -18084,6 +18959,11 @@
         </is>
       </c>
       <c r="AY176" t="inlineStr"/>
+      <c r="AZ176" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723038</t>
+        </is>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="n">
@@ -18181,6 +19061,11 @@
         </is>
       </c>
       <c r="AY177" t="inlineStr"/>
+      <c r="AZ177" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723039</t>
+        </is>
+      </c>
     </row>
     <row r="178">
       <c r="A178" t="n">
@@ -18278,6 +19163,11 @@
         </is>
       </c>
       <c r="AY178" t="inlineStr"/>
+      <c r="AZ178" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723040</t>
+        </is>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="n">
@@ -18375,6 +19265,11 @@
         </is>
       </c>
       <c r="AY179" t="inlineStr"/>
+      <c r="AZ179" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723041</t>
+        </is>
+      </c>
     </row>
     <row r="180">
       <c r="A180" t="n">
@@ -18483,6 +19378,11 @@
         </is>
       </c>
       <c r="AY180" t="inlineStr"/>
+      <c r="AZ180" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127729086</t>
+        </is>
+      </c>
     </row>
     <row r="181">
       <c r="A181" t="n">
@@ -18580,8 +19480,195 @@
         </is>
       </c>
       <c r="AY181" t="inlineStr"/>
+      <c r="AZ181" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127722855</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ93" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ94" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ95" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ96" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ97" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ98" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ99" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ100" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ101" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ102" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ103" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ104" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ105" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ106" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ107" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ108" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ109" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ110" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ111" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ112" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ113" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ114" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ115" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ116" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ117" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ118" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ119" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ120" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ121" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ122" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ123" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ124" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ125" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ126" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ127" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ128" r:id="rId127"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ129" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ130" r:id="rId129"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ131" r:id="rId130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ132" r:id="rId131"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ133" r:id="rId132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ134" r:id="rId133"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ135" r:id="rId134"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ136" r:id="rId135"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ137" r:id="rId136"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ138" r:id="rId137"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ139" r:id="rId138"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ140" r:id="rId139"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ141" r:id="rId140"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ142" r:id="rId141"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ143" r:id="rId142"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ144" r:id="rId143"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ145" r:id="rId144"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ146" r:id="rId145"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ147" r:id="rId146"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ148" r:id="rId147"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ149" r:id="rId148"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ150" r:id="rId149"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ151" r:id="rId150"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ152" r:id="rId151"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ153" r:id="rId152"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ154" r:id="rId153"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ155" r:id="rId154"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ156" r:id="rId155"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ157" r:id="rId156"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ158" r:id="rId157"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ159" r:id="rId158"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ160" r:id="rId159"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ161" r:id="rId160"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ162" r:id="rId161"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ163" r:id="rId162"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ164" r:id="rId163"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ165" r:id="rId164"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ166" r:id="rId165"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ167" r:id="rId166"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ168" r:id="rId167"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ169" r:id="rId168"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ170" r:id="rId169"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ171" r:id="rId170"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ172" r:id="rId171"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ173" r:id="rId172"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ174" r:id="rId173"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ175" r:id="rId174"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ176" r:id="rId175"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ177" r:id="rId176"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ178" r:id="rId177"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ179" r:id="rId178"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ180" r:id="rId179"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ181" r:id="rId180"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>